--- a/data/grants.xlsx
+++ b/data/grants.xlsx
@@ -508,7 +508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:T119"/>
+  <dimension ref="A1:T144"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="6" customWidth="1" style="10" min="1" max="1"/>
@@ -542,7 +542,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="33.75" customHeight="1" s="11">
       <c r="A4" s="14" t="inlineStr">
         <is>
@@ -629,17 +628,17 @@
           <t>Notes</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="R4" s="10" t="inlineStr">
         <is>
           <t>Startup Stage</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S4" s="10" t="inlineStr">
         <is>
           <t>Company Status</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="T4" s="10" t="inlineStr">
         <is>
           <t>Funding Type</t>
         </is>
@@ -1079,17 +1078,17 @@
           <t>Only open to existing ERC grantees.</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="R9" s="10" t="inlineStr">
         <is>
           <t>Pre-seed</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S9" s="10" t="inlineStr">
         <is>
           <t>Not yet founded (research result)</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="T9" s="10" t="inlineStr">
         <is>
           <t>Grant</t>
         </is>
@@ -9533,17 +9532,17 @@
           <t>For scientists exploring the startup path without leaving research.</t>
         </is>
       </c>
-      <c r="R106" t="inlineStr">
+      <c r="R106" s="10" t="inlineStr">
         <is>
           <t>Pre-seed</t>
         </is>
       </c>
-      <c r="S106" t="inlineStr">
+      <c r="S106" s="10" t="inlineStr">
         <is>
           <t>Not yet founded</t>
         </is>
       </c>
-      <c r="T106" t="inlineStr">
+      <c r="T106" s="10" t="inlineStr">
         <is>
           <t>Grant (salary)</t>
         </is>
@@ -9722,17 +9721,17 @@
           <t>Classic first money for academic founders in Austria.</t>
         </is>
       </c>
-      <c r="R108" t="inlineStr">
+      <c r="R108" s="10" t="inlineStr">
         <is>
           <t>Pre-seed</t>
         </is>
       </c>
-      <c r="S108" t="inlineStr">
+      <c r="S108" s="10" t="inlineStr">
         <is>
           <t>Not yet founded / just founded</t>
         </is>
       </c>
-      <c r="T108" t="inlineStr">
+      <c r="T108" s="10" t="inlineStr">
         <is>
           <t>Grant</t>
         </is>
@@ -9824,17 +9823,17 @@
           <t>Natural successor to aws Preseed.</t>
         </is>
       </c>
-      <c r="R109" t="inlineStr">
+      <c r="R109" s="10" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="S109" t="inlineStr">
+      <c r="S109" s="10" t="inlineStr">
         <is>
           <t>Founded (&lt;6 years)</t>
         </is>
       </c>
-      <c r="T109" t="inlineStr">
+      <c r="T109" s="10" t="inlineStr">
         <is>
           <t>Conditionally repayable grant</t>
         </is>
@@ -9883,7 +9882,7 @@
       </c>
       <c r="I110" s="10" t="inlineStr">
         <is>
-          <t>Grant up to €2.5M + equity up to €10M+</t>
+          <t>Grant up to €2.5M + equity €1–10M (blended finance)</t>
         </is>
       </c>
       <c r="J110" s="10" t="inlineStr">
@@ -9898,7 +9897,7 @@
       </c>
       <c r="L110" s="10" t="inlineStr">
         <is>
-          <t>Several cut-offs/yr (check EIC work programme)</t>
+          <t>Full-proposal deadline 2 Sep 2026 (next batch 4 Nov 2026); short proposal any time</t>
         </is>
       </c>
       <c r="M110" s="10" t="inlineStr">
@@ -9913,7 +9912,7 @@
       </c>
       <c r="O110" s="10" t="inlineStr">
         <is>
-          <t>~5% overall</t>
+          <t>~5%</t>
         </is>
       </c>
       <c r="P110" s="10" t="inlineStr">
@@ -9923,20 +9922,20 @@
       </c>
       <c r="Q110" s="10" t="inlineStr">
         <is>
-          <t>Very competitive; strong for science-based ventures.</t>
-        </is>
-      </c>
-      <c r="R110" t="inlineStr">
+          <t>2026 budget: €414M Open + €220M Challenges. Short proposals anytime (batched first Tuesday monthly), full proposals to fixed batch dates, then EIC Jury interview. One live application at a time. Verified 23 Jul 2026.</t>
+        </is>
+      </c>
+      <c r="R110" s="10" t="inlineStr">
         <is>
           <t>Growth</t>
         </is>
       </c>
-      <c r="S110" t="inlineStr">
+      <c r="S110" s="10" t="inlineStr">
         <is>
           <t>Founded (SME)</t>
         </is>
       </c>
-      <c r="T110" t="inlineStr">
+      <c r="T110" s="10" t="inlineStr">
         <is>
           <t>Grant + equity</t>
         </is>
@@ -10028,17 +10027,17 @@
           <t>The bridge from academic results to a fundable company.</t>
         </is>
       </c>
-      <c r="R111" t="inlineStr">
+      <c r="R111" s="10" t="inlineStr">
         <is>
           <t>Pre-seed;Seed</t>
         </is>
       </c>
-      <c r="S111" t="inlineStr">
+      <c r="S111" s="10" t="inlineStr">
         <is>
           <t>Not yet founded / just founded</t>
         </is>
       </c>
-      <c r="T111" t="inlineStr">
+      <c r="T111" s="10" t="inlineStr">
         <is>
           <t>Grant</t>
         </is>
@@ -10130,17 +10129,17 @@
           <t>Good odds compared to EIC; requires an international partner.</t>
         </is>
       </c>
-      <c r="R112" t="inlineStr">
+      <c r="R112" s="10" t="inlineStr">
         <is>
           <t>Seed;Growth</t>
         </is>
       </c>
-      <c r="S112" t="inlineStr">
+      <c r="S112" s="10" t="inlineStr">
         <is>
           <t>Founded (SME)</t>
         </is>
       </c>
-      <c r="T112" t="inlineStr">
+      <c r="T112" s="10" t="inlineStr">
         <is>
           <t>Grant (via national agency)</t>
         </is>
@@ -10232,17 +10231,17 @@
           <t>Pick the community matching your field (EIT Health for life-science founders etc.).</t>
         </is>
       </c>
-      <c r="R113" t="inlineStr">
+      <c r="R113" s="10" t="inlineStr">
         <is>
           <t>Seed;Growth</t>
         </is>
       </c>
-      <c r="S113" t="inlineStr">
+      <c r="S113" s="10" t="inlineStr">
         <is>
           <t>Founded</t>
         </is>
       </c>
-      <c r="T113" t="inlineStr">
+      <c r="T113" s="10" t="inlineStr">
         <is>
           <t>Grant + services</t>
         </is>
@@ -10334,17 +10333,17 @@
           <t>Science Park Graz runs the Graz location.</t>
         </is>
       </c>
-      <c r="R114" t="inlineStr">
+      <c r="R114" s="10" t="inlineStr">
         <is>
           <t>Pre-seed;Seed</t>
         </is>
       </c>
-      <c r="S114" t="inlineStr">
+      <c r="S114" s="10" t="inlineStr">
         <is>
           <t>Founded (&lt;5 years)</t>
         </is>
       </c>
-      <c r="T114" t="inlineStr">
+      <c r="T114" s="10" t="inlineStr">
         <is>
           <t>Grant + incubation</t>
         </is>
@@ -10436,17 +10435,17 @@
           <t>In Graz: Science Park Graz; in Vienna: INiTS.</t>
         </is>
       </c>
-      <c r="R115" t="inlineStr">
+      <c r="R115" s="10" t="inlineStr">
         <is>
           <t>Pre-seed</t>
         </is>
       </c>
-      <c r="S115" t="inlineStr">
+      <c r="S115" s="10" t="inlineStr">
         <is>
           <t>Not yet founded</t>
         </is>
       </c>
-      <c r="T115" t="inlineStr">
+      <c r="T115" s="10" t="inlineStr">
         <is>
           <t>Grant + incubation</t>
         </is>
@@ -10538,17 +10537,17 @@
           <t>Only for Vienna-based ventures — location matters.</t>
         </is>
       </c>
-      <c r="R116" t="inlineStr">
+      <c r="R116" s="10" t="inlineStr">
         <is>
           <t>Pre-seed;Seed;Growth</t>
         </is>
       </c>
-      <c r="S116" t="inlineStr">
+      <c r="S116" s="10" t="inlineStr">
         <is>
           <t>Founded (Vienna-based)</t>
         </is>
       </c>
-      <c r="T116" t="inlineStr">
+      <c r="T116" s="10" t="inlineStr">
         <is>
           <t>Grant</t>
         </is>
@@ -10640,17 +10639,17 @@
           <t>Relevant for Graz-based founders; programmes change, check current lineup.</t>
         </is>
       </c>
-      <c r="R117" t="inlineStr">
+      <c r="R117" s="10" t="inlineStr">
         <is>
           <t>Pre-seed;Seed</t>
         </is>
       </c>
-      <c r="S117" t="inlineStr">
+      <c r="S117" s="10" t="inlineStr">
         <is>
           <t>Founded (Styria-based)</t>
         </is>
       </c>
-      <c r="T117" t="inlineStr">
+      <c r="T117" s="10" t="inlineStr">
         <is>
           <t>Grant + consulting subsidy</t>
         </is>
@@ -10742,17 +10741,17 @@
           <t>Best first stop to map which Austrian funding fits your founding stage.</t>
         </is>
       </c>
-      <c r="R118" t="inlineStr">
+      <c r="R118" s="10" t="inlineStr">
         <is>
           <t>Pre-seed</t>
         </is>
       </c>
-      <c r="S118" t="inlineStr">
+      <c r="S118" s="10" t="inlineStr">
         <is>
           <t>Not yet founded</t>
         </is>
       </c>
-      <c r="T118" t="inlineStr">
+      <c r="T118" s="10" t="inlineStr">
         <is>
           <t>Free advisory service</t>
         </is>
@@ -10844,21 +10843,2415 @@
           <t>High acceptance rate; the workhorse of Austrian applied R&amp;D funding.</t>
         </is>
       </c>
-      <c r="R119" t="inlineStr">
+      <c r="R119" s="10" t="inlineStr">
         <is>
           <t>Seed;Growth</t>
         </is>
       </c>
-      <c r="S119" t="inlineStr">
+      <c r="S119" s="10" t="inlineStr">
         <is>
           <t>Founded</t>
         </is>
       </c>
-      <c r="T119" t="inlineStr">
+      <c r="T119" s="10" t="inlineStr">
         <is>
           <t>Grant + soft loan</t>
         </is>
       </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="10" t="inlineStr">
+        <is>
+          <t>G116</t>
+        </is>
+      </c>
+      <c r="B120" s="10" t="inlineStr">
+        <is>
+          <t>EIC Pre-Accelerator</t>
+        </is>
+      </c>
+      <c r="C120" s="10" t="inlineStr">
+        <is>
+          <t>European Innovation Council (EIC) &amp; WIDERA</t>
+        </is>
+      </c>
+      <c r="D120" s="10" t="inlineStr">
+        <is>
+          <t>EIC</t>
+        </is>
+      </c>
+      <c r="E120" s="10" t="inlineStr">
+        <is>
+          <t>EU (widening countries only)</t>
+        </is>
+      </c>
+      <c r="F120" s="10" t="inlineStr">
+        <is>
+          <t>Startup funding (deep tech)</t>
+        </is>
+      </c>
+      <c r="G120" s="10" t="inlineStr">
+        <is>
+          <t>Early-stage deep-tech startups</t>
+        </is>
+      </c>
+      <c r="H120" s="10" t="inlineStr">
+        <is>
+          <t>Raises the business, investor and technology readiness of early-stage deep-tech startups in widening countries (TRL 4-6), with a fast track into the EIC Accelerator.</t>
+        </is>
+      </c>
+      <c r="I120" s="10" t="inlineStr">
+        <is>
+          <t>€500k-1M lump sum in the 2027 call (€300-500k in 2025), covering 70% of costs</t>
+        </is>
+      </c>
+      <c r="J120" s="10" t="inlineStr">
+        <is>
+          <t>Max 2 years</t>
+        </is>
+      </c>
+      <c r="K120" s="10" t="inlineStr">
+        <is>
+          <t>Single SMEs registered in Horizon Europe widening countries ONLY - Austrian, German, French etc. companies are not eligible. TRL 4+, own IP, clear route to market</t>
+        </is>
+      </c>
+      <c r="L120" s="10" t="inlineStr">
+        <is>
+          <t>Call opens 5 May 2027; deadline 18 Nov 2027</t>
+        </is>
+      </c>
+      <c r="M120" s="10" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders Portal</t>
+        </is>
+      </c>
+      <c r="N120" s="10" t="inlineStr">
+        <is>
+          <t>No - written evaluation</t>
+        </is>
+      </c>
+      <c r="O120" s="10" t="inlineStr">
+        <is>
+          <t>70 companies funded in the 2025 round</t>
+        </is>
+      </c>
+      <c r="P120" s="10" t="inlineStr">
+        <is>
+          <t>https://eic.ec.europa.eu/eic-funding-opportunities/eic-pre-accelerator_en</t>
+        </is>
+      </c>
+      <c r="Q120" s="10" t="inlineStr">
+        <is>
+          <t>Eligible countries: BG, HR, CY, CZ, EE, GR, HU, LV, LT, MT, PL, PT, RO, SK, SI plus associated widening countries. Includes free Business Acceleration Services and a Seal of Excellence. Verified 23 Jul 2026.</t>
+        </is>
+      </c>
+      <c r="R120" s="10" t="inlineStr">
+        <is>
+          <t>Pre-seed;Seed</t>
+        </is>
+      </c>
+      <c r="S120" s="10" t="inlineStr">
+        <is>
+          <t>Founded (SME, widening country)</t>
+        </is>
+      </c>
+      <c r="T120" s="10" t="inlineStr">
+        <is>
+          <t>Grant + coaching</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="10" t="inlineStr">
+        <is>
+          <t>G117</t>
+        </is>
+      </c>
+      <c r="B121" s="10" t="inlineStr">
+        <is>
+          <t>EIC STEP Scale Up</t>
+        </is>
+      </c>
+      <c r="C121" s="10" t="inlineStr">
+        <is>
+          <t>European Innovation Council (EIC)</t>
+        </is>
+      </c>
+      <c r="D121" s="10" t="inlineStr">
+        <is>
+          <t>EIC</t>
+        </is>
+      </c>
+      <c r="E121" s="10" t="inlineStr">
+        <is>
+          <t>EU + Associated Countries</t>
+        </is>
+      </c>
+      <c r="F121" s="10" t="inlineStr">
+        <is>
+          <t>Startup funding (scale-up)</t>
+        </is>
+      </c>
+      <c r="G121" s="10" t="inlineStr">
+        <is>
+          <t>Scale-ups</t>
+        </is>
+      </c>
+      <c r="H121" s="10" t="inlineStr">
+        <is>
+          <t>Large-ticket investment for European deep-tech companies scaling critical technologies, well beyond the standard EIC Accelerator ceiling.</t>
+        </is>
+      </c>
+      <c r="I121" s="10" t="inlineStr">
+        <is>
+          <t>Equity investments above €10M</t>
+        </is>
+      </c>
+      <c r="J121" s="10" t="inlineStr">
+        <is>
+          <t>Investment (no fixed project term)</t>
+        </is>
+      </c>
+      <c r="K121" s="10" t="inlineStr">
+        <is>
+          <t>European scale-ups working on STEP priority technologies (deep tech, clean tech, biotech)</t>
+        </is>
+      </c>
+      <c r="L121" s="10" t="inlineStr">
+        <is>
+          <t>Rolling / periodic (check site)</t>
+        </is>
+      </c>
+      <c r="M121" s="10" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders Portal / EIC Fund</t>
+        </is>
+      </c>
+      <c r="N121" s="10" t="inlineStr">
+        <is>
+          <t>Yes - due diligence</t>
+        </is>
+      </c>
+      <c r="O121" s="10" t="inlineStr">
+        <is>
+          <t>Selective</t>
+        </is>
+      </c>
+      <c r="P121" s="10" t="inlineStr">
+        <is>
+          <t>https://eic.ec.europa.eu/eic-funding-opportunities/step-scale_en</t>
+        </is>
+      </c>
+      <c r="Q121" s="10" t="inlineStr">
+        <is>
+          <t>Since June 2026 the EIC also invests in defence and dual-use technologies through a separate STEP Scale Up Defence strand.</t>
+        </is>
+      </c>
+      <c r="R121" s="10" t="inlineStr">
+        <is>
+          <t>Growth</t>
+        </is>
+      </c>
+      <c r="S121" s="10" t="inlineStr">
+        <is>
+          <t>Founded (scale-up)</t>
+        </is>
+      </c>
+      <c r="T121" s="10" t="inlineStr">
+        <is>
+          <t>Equity investment</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="10" t="inlineStr">
+        <is>
+          <t>G118</t>
+        </is>
+      </c>
+      <c r="B122" s="10" t="inlineStr">
+        <is>
+          <t>European Prize for Women Innovators</t>
+        </is>
+      </c>
+      <c r="C122" s="10" t="inlineStr">
+        <is>
+          <t>European Innovation Council &amp; EIT</t>
+        </is>
+      </c>
+      <c r="D122" s="10" t="inlineStr">
+        <is>
+          <t>EIC</t>
+        </is>
+      </c>
+      <c r="E122" s="10" t="inlineStr">
+        <is>
+          <t>EU + Associated Countries</t>
+        </is>
+      </c>
+      <c r="F122" s="10" t="inlineStr">
+        <is>
+          <t>Innovation prize (women founders)</t>
+        </is>
+      </c>
+      <c r="G122" s="10" t="inlineStr">
+        <is>
+          <t>Women founders (any stage)</t>
+        </is>
+      </c>
+      <c r="H122" s="10" t="inlineStr">
+        <is>
+          <t>Annual EU prize recognising outstanding women entrepreneurs behind innovative companies, including a Rising Innovators category for younger founders.</t>
+        </is>
+      </c>
+      <c r="I122" s="10" t="inlineStr">
+        <is>
+          <t>Cash prizes (typically €50k-100k per winner)</t>
+        </is>
+      </c>
+      <c r="J122" s="10" t="inlineStr">
+        <is>
+          <t>One-off award</t>
+        </is>
+      </c>
+      <c r="K122" s="10" t="inlineStr">
+        <is>
+          <t>Women founders or co-founders of a company registered in the EU or an Associated Country</t>
+        </is>
+      </c>
+      <c r="L122" s="10" t="inlineStr">
+        <is>
+          <t>Annual call (check site)</t>
+        </is>
+      </c>
+      <c r="M122" s="10" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders Portal</t>
+        </is>
+      </c>
+      <c r="N122" s="10" t="inlineStr">
+        <is>
+          <t>Yes - final jury</t>
+        </is>
+      </c>
+      <c r="O122" s="10" t="inlineStr">
+        <is>
+          <t>Selective</t>
+        </is>
+      </c>
+      <c r="P122" s="10" t="inlineStr">
+        <is>
+          <t>https://eic.ec.europa.eu/eic-prizes/european-prize-women-innovators-powered-eic-eit_en</t>
+        </is>
+      </c>
+      <c r="Q122" s="10" t="inlineStr">
+        <is>
+          <t>Prize money rather than project funding, but strong visibility for later fundraising.</t>
+        </is>
+      </c>
+      <c r="R122" s="10" t="inlineStr">
+        <is>
+          <t>Pre-seed;Seed;Growth</t>
+        </is>
+      </c>
+      <c r="S122" s="10" t="inlineStr">
+        <is>
+          <t>Founded</t>
+        </is>
+      </c>
+      <c r="T122" s="10" t="inlineStr">
+        <is>
+          <t>Cash prize</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="10" t="inlineStr">
+        <is>
+          <t>G119</t>
+        </is>
+      </c>
+      <c r="B123" s="10" t="inlineStr">
+        <is>
+          <t>EIC Business Acceleration Services (BAS)</t>
+        </is>
+      </c>
+      <c r="C123" s="10" t="inlineStr">
+        <is>
+          <t>European Innovation Council (EIC)</t>
+        </is>
+      </c>
+      <c r="D123" s="10" t="inlineStr">
+        <is>
+          <t>EIC</t>
+        </is>
+      </c>
+      <c r="E123" s="10" t="inlineStr">
+        <is>
+          <t>EU + Associated Countries</t>
+        </is>
+      </c>
+      <c r="F123" s="10" t="inlineStr">
+        <is>
+          <t>Startup support (non-financial)</t>
+        </is>
+      </c>
+      <c r="G123" s="10" t="inlineStr">
+        <is>
+          <t>EIC-supported companies</t>
+        </is>
+      </c>
+      <c r="H123" s="10" t="inlineStr">
+        <is>
+          <t>Free coaching, mentoring, investor matchmaking and partnering for companies and projects already supported by the EIC.</t>
+        </is>
+      </c>
+      <c r="I123" s="10" t="inlineStr">
+        <is>
+          <t>Free services (no cash award)</t>
+        </is>
+      </c>
+      <c r="J123" s="10" t="inlineStr">
+        <is>
+          <t>Duration of the EIC project</t>
+        </is>
+      </c>
+      <c r="K123" s="10" t="inlineStr">
+        <is>
+          <t>Open to EIC-supported companies and projects (Pathfinder, Transition, Accelerator, Pre-Accelerator)</t>
+        </is>
+      </c>
+      <c r="L123" s="10" t="inlineStr">
+        <is>
+          <t>Continuous, alongside EIC funding</t>
+        </is>
+      </c>
+      <c r="M123" s="10" t="inlineStr">
+        <is>
+          <t>Automatic with EIC support</t>
+        </is>
+      </c>
+      <c r="N123" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O123" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P123" s="10" t="inlineStr">
+        <is>
+          <t>https://eic.ec.europa.eu/eic-funding-opportunities/bas_en</t>
+        </is>
+      </c>
+      <c r="Q123" s="10" t="inlineStr">
+        <is>
+          <t>Worth weighing when comparing EIC schemes against national funding.</t>
+        </is>
+      </c>
+      <c r="R123" s="10" t="inlineStr">
+        <is>
+          <t>Pre-seed;Seed;Growth</t>
+        </is>
+      </c>
+      <c r="S123" s="10" t="inlineStr">
+        <is>
+          <t>Founded (EIC-supported)</t>
+        </is>
+      </c>
+      <c r="T123" s="10" t="inlineStr">
+        <is>
+          <t>Free services</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="10" t="inlineStr">
+        <is>
+          <t>G120</t>
+        </is>
+      </c>
+      <c r="B124" s="10" t="inlineStr">
+        <is>
+          <t>EIT Digital Co-Creation Accelerator</t>
+        </is>
+      </c>
+      <c r="C124" s="10" t="inlineStr">
+        <is>
+          <t>EIT Digital / 28DIGITAL</t>
+        </is>
+      </c>
+      <c r="D124" s="10" t="inlineStr">
+        <is>
+          <t>EIT Digital</t>
+        </is>
+      </c>
+      <c r="E124" s="10" t="inlineStr">
+        <is>
+          <t>EU-wide</t>
+        </is>
+      </c>
+      <c r="F124" s="10" t="inlineStr">
+        <is>
+          <t>Startup funding (digital / deep tech)</t>
+        </is>
+      </c>
+      <c r="G124" s="10" t="inlineStr">
+        <is>
+          <t>Early-stage teams (TRL 4-5)</t>
+        </is>
+      </c>
+      <c r="H124" s="10" t="inlineStr">
+        <is>
+          <t>Four-month programme developing early-stage digital solutions together with industry partners, with funding attached.</t>
+        </is>
+      </c>
+      <c r="I124" s="10" t="inlineStr">
+        <is>
+          <t>Up to €250,000</t>
+        </is>
+      </c>
+      <c r="J124" s="10" t="inlineStr">
+        <is>
+          <t>4 months</t>
+        </is>
+      </c>
+      <c r="K124" s="10" t="inlineStr">
+        <is>
+          <t>Early-stage digital or deep-tech teams (TRL 4-5) in the EIT Digital ecosystem</t>
+        </is>
+      </c>
+      <c r="L124" s="10" t="inlineStr">
+        <is>
+          <t>Applications close 30 Sep 2026 (window opened July 2026)</t>
+        </is>
+      </c>
+      <c r="M124" s="10" t="inlineStr">
+        <is>
+          <t>28DIGITAL application</t>
+        </is>
+      </c>
+      <c r="N124" s="10" t="inlineStr">
+        <is>
+          <t>Yes - selection</t>
+        </is>
+      </c>
+      <c r="O124" s="10" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="P124" s="10" t="inlineStr">
+        <is>
+          <t>https://28digital.eu/co-creation-accelerator-2026-2027/</t>
+        </is>
+      </c>
+      <c r="Q124" s="10" t="inlineStr">
+        <is>
+          <t>Application window open right now, closing September 2026. Verified 23 Jul 2026.</t>
+        </is>
+      </c>
+      <c r="R124" s="10" t="inlineStr">
+        <is>
+          <t>Pre-seed;Seed</t>
+        </is>
+      </c>
+      <c r="S124" s="10" t="inlineStr">
+        <is>
+          <t>Founded or forming</t>
+        </is>
+      </c>
+      <c r="T124" s="10" t="inlineStr">
+        <is>
+          <t>Grant + acceleration</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="10" t="inlineStr">
+        <is>
+          <t>G121</t>
+        </is>
+      </c>
+      <c r="B125" s="10" t="inlineStr">
+        <is>
+          <t>EIT Digital Venture Incubation Programme</t>
+        </is>
+      </c>
+      <c r="C125" s="10" t="inlineStr">
+        <is>
+          <t>EIT Digital / 28DIGITAL</t>
+        </is>
+      </c>
+      <c r="D125" s="10" t="inlineStr">
+        <is>
+          <t>EIT Digital</t>
+        </is>
+      </c>
+      <c r="E125" s="10" t="inlineStr">
+        <is>
+          <t>EU-wide</t>
+        </is>
+      </c>
+      <c r="F125" s="10" t="inlineStr">
+        <is>
+          <t>Startup funding (idea to MVP)</t>
+        </is>
+      </c>
+      <c r="G125" s="10" t="inlineStr">
+        <is>
+          <t>Idea-stage founders</t>
+        </is>
+      </c>
+      <c r="H125" s="10" t="inlineStr">
+        <is>
+          <t>Takes entrepreneurs from concept to MVP, market validation and funding in under a year, with a small grant plus optional follow-on investment.</t>
+        </is>
+      </c>
+      <c r="I125" s="10" t="inlineStr">
+        <is>
+          <t>€5,000 grant + optional €15,000 investment</t>
+        </is>
+      </c>
+      <c r="J125" s="10" t="inlineStr">
+        <is>
+          <t>Up to 12 months</t>
+        </is>
+      </c>
+      <c r="K125" s="10" t="inlineStr">
+        <is>
+          <t>Founders with an early digital or deep-tech idea; EIT Digital ecosystem</t>
+        </is>
+      </c>
+      <c r="L125" s="10" t="inlineStr">
+        <is>
+          <t>Batch intakes (Q2 2026 round; check site)</t>
+        </is>
+      </c>
+      <c r="M125" s="10" t="inlineStr">
+        <is>
+          <t>28DIGITAL application</t>
+        </is>
+      </c>
+      <c r="N125" s="10" t="inlineStr">
+        <is>
+          <t>Yes - selection</t>
+        </is>
+      </c>
+      <c r="O125" s="10" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="P125" s="10" t="inlineStr">
+        <is>
+          <t>https://28digital.eu/venture-incubation-program/</t>
+        </is>
+      </c>
+      <c r="Q125" s="10" t="inlineStr">
+        <is>
+          <t>Small money but a structured path and network - a sensible very first step.</t>
+        </is>
+      </c>
+      <c r="R125" s="10" t="inlineStr">
+        <is>
+          <t>Pre-seed</t>
+        </is>
+      </c>
+      <c r="S125" s="10" t="inlineStr">
+        <is>
+          <t>Not yet founded</t>
+        </is>
+      </c>
+      <c r="T125" s="10" t="inlineStr">
+        <is>
+          <t>Grant + incubation</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="10" t="inlineStr">
+        <is>
+          <t>G122</t>
+        </is>
+      </c>
+      <c r="B126" s="10" t="inlineStr">
+        <is>
+          <t>EIT Digital SPIN (Explore &amp; Rise)</t>
+        </is>
+      </c>
+      <c r="C126" s="10" t="inlineStr">
+        <is>
+          <t>EIT Digital / 28DIGITAL</t>
+        </is>
+      </c>
+      <c r="D126" s="10" t="inlineStr">
+        <is>
+          <t>EIT Digital</t>
+        </is>
+      </c>
+      <c r="E126" s="10" t="inlineStr">
+        <is>
+          <t>EU-wide</t>
+        </is>
+      </c>
+      <c r="F126" s="10" t="inlineStr">
+        <is>
+          <t>Research-to-market training (free)</t>
+        </is>
+      </c>
+      <c r="G126" s="10" t="inlineStr">
+        <is>
+          <t>Researchers &amp; early-career academics</t>
+        </is>
+      </c>
+      <c r="H126" s="10" t="inlineStr">
+        <is>
+          <t>Free pre-incubation for deep-tech researchers: SPIN Explore is a 9-hour online course on innovation readiness and IP, SPIN Rise a 9-week hybrid programme with mentoring and business model development.</t>
+        </is>
+      </c>
+      <c r="I126" s="10" t="inlineStr">
+        <is>
+          <t>Free (no cash award)</t>
+        </is>
+      </c>
+      <c r="J126" s="10" t="inlineStr">
+        <is>
+          <t>Explore: 9 hours; Rise: 9 weeks</t>
+        </is>
+      </c>
+      <c r="K126" s="10" t="inlineStr">
+        <is>
+          <t>Deep-tech researchers and early-career academics in Europe</t>
+        </is>
+      </c>
+      <c r="L126" s="10" t="inlineStr">
+        <is>
+          <t>Explore: continuous; Rise: 2026 intake (check site)</t>
+        </is>
+      </c>
+      <c r="M126" s="10" t="inlineStr">
+        <is>
+          <t>28DIGITAL application</t>
+        </is>
+      </c>
+      <c r="N126" s="10" t="inlineStr">
+        <is>
+          <t>No (Explore) / selection (Rise)</t>
+        </is>
+      </c>
+      <c r="O126" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P126" s="10" t="inlineStr">
+        <is>
+          <t>https://28digital.eu/spin/</t>
+        </is>
+      </c>
+      <c r="Q126" s="10" t="inlineStr">
+        <is>
+          <t>An ideal bridge for scientists weighing commercialisation - costs nothing but time.</t>
+        </is>
+      </c>
+      <c r="R126" s="10" t="inlineStr">
+        <is>
+          <t>Pre-seed</t>
+        </is>
+      </c>
+      <c r="S126" s="10" t="inlineStr">
+        <is>
+          <t>Not yet founded</t>
+        </is>
+      </c>
+      <c r="T126" s="10" t="inlineStr">
+        <is>
+          <t>Free training</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="10" t="inlineStr">
+        <is>
+          <t>G123</t>
+        </is>
+      </c>
+      <c r="B127" s="10" t="inlineStr">
+        <is>
+          <t>SPEX Venture Health-Tech Fund</t>
+        </is>
+      </c>
+      <c r="C127" s="10" t="inlineStr">
+        <is>
+          <t>Spex Capital (EIT Digital-linked)</t>
+        </is>
+      </c>
+      <c r="D127" s="10" t="inlineStr">
+        <is>
+          <t>Private (Spex)</t>
+        </is>
+      </c>
+      <c r="E127" s="10" t="inlineStr">
+        <is>
+          <t>International (Europe-focused)</t>
+        </is>
+      </c>
+      <c r="F127" s="10" t="inlineStr">
+        <is>
+          <t>Venture investment (digital health)</t>
+        </is>
+      </c>
+      <c r="G127" s="10" t="inlineStr">
+        <is>
+          <t>Seed to Series A</t>
+        </is>
+      </c>
+      <c r="H127" s="10" t="inlineStr">
+        <is>
+          <t>A €100M fund investing in the next generation of digital healthcare and med-tech companies.</t>
+        </is>
+      </c>
+      <c r="I127" s="10" t="inlineStr">
+        <is>
+          <t>€500,000-5,000,000 (equity)</t>
+        </is>
+      </c>
+      <c r="J127" s="10" t="inlineStr">
+        <is>
+          <t>Investment</t>
+        </is>
+      </c>
+      <c r="K127" s="10" t="inlineStr">
+        <is>
+          <t>Seed to Series A digital health or med-tech startups</t>
+        </is>
+      </c>
+      <c r="L127" s="10" t="inlineStr">
+        <is>
+          <t>Continuous (investing since Q4 2025)</t>
+        </is>
+      </c>
+      <c r="M127" s="10" t="inlineStr">
+        <is>
+          <t>Direct approach to the fund</t>
+        </is>
+      </c>
+      <c r="N127" s="10" t="inlineStr">
+        <is>
+          <t>Yes - investment process</t>
+        </is>
+      </c>
+      <c r="O127" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P127" s="10" t="inlineStr">
+        <is>
+          <t>https://www.spexcapital.com/</t>
+        </is>
+      </c>
+      <c r="Q127" s="10" t="inlineStr">
+        <is>
+          <t>Equity investment rather than a grant: dilutive, but far larger tickets.</t>
+        </is>
+      </c>
+      <c r="R127" s="10" t="inlineStr">
+        <is>
+          <t>Seed;Growth</t>
+        </is>
+      </c>
+      <c r="S127" s="10" t="inlineStr">
+        <is>
+          <t>Founded</t>
+        </is>
+      </c>
+      <c r="T127" s="10" t="inlineStr">
+        <is>
+          <t>Equity investment</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="10" t="inlineStr">
+        <is>
+          <t>G124</t>
+        </is>
+      </c>
+      <c r="B128" s="10" t="inlineStr">
+        <is>
+          <t>EUDOROS Open Call (Cybersecurity)</t>
+        </is>
+      </c>
+      <c r="C128" s="10" t="inlineStr">
+        <is>
+          <t>EUDOROS (Horizon Europe project)</t>
+        </is>
+      </c>
+      <c r="D128" s="10" t="inlineStr">
+        <is>
+          <t>EU cascade funding</t>
+        </is>
+      </c>
+      <c r="E128" s="10" t="inlineStr">
+        <is>
+          <t>EU + Associated Countries</t>
+        </is>
+      </c>
+      <c r="F128" s="10" t="inlineStr">
+        <is>
+          <t>Startup funding (cybersecurity)</t>
+        </is>
+      </c>
+      <c r="G128" s="10" t="inlineStr">
+        <is>
+          <t>SMEs &amp; technology providers</t>
+        </is>
+      </c>
+      <c r="H128" s="10" t="inlineStr">
+        <is>
+          <t>Cascade-funding call for cybersecurity service providers and tool creators to deploy their solutions with new customers.</t>
+        </is>
+      </c>
+      <c r="I128" s="10" t="inlineStr">
+        <is>
+          <t>€20,000-200,000</t>
+        </is>
+      </c>
+      <c r="J128" s="10" t="inlineStr">
+        <is>
+          <t>Project-dependent</t>
+        </is>
+      </c>
+      <c r="K128" s="10" t="inlineStr">
+        <is>
+          <t>Cybersecurity SMEs and tool providers in eligible countries</t>
+        </is>
+      </c>
+      <c r="L128" s="10" t="inlineStr">
+        <is>
+          <t>7 August 2026</t>
+        </is>
+      </c>
+      <c r="M128" s="10" t="inlineStr">
+        <is>
+          <t>EUDOROS open call portal</t>
+        </is>
+      </c>
+      <c r="N128" s="10" t="inlineStr">
+        <is>
+          <t>No - written review</t>
+        </is>
+      </c>
+      <c r="O128" s="10" t="inlineStr">
+        <is>
+          <t>Good (cascade calls are less crowded)</t>
+        </is>
+      </c>
+      <c r="P128" s="10" t="inlineStr">
+        <is>
+          <t>https://eudoros.eu/open-call-2/</t>
+        </is>
+      </c>
+      <c r="Q128" s="10" t="inlineStr">
+        <is>
+          <t>Closing soon. Cascade funding (financial support to third parties) is much less competitive than the main EU calls. Verified 23 Jul 2026.</t>
+        </is>
+      </c>
+      <c r="R128" s="10" t="inlineStr">
+        <is>
+          <t>Seed;Growth</t>
+        </is>
+      </c>
+      <c r="S128" s="10" t="inlineStr">
+        <is>
+          <t>Founded (SME)</t>
+        </is>
+      </c>
+      <c r="T128" s="10" t="inlineStr">
+        <is>
+          <t>Grant (cascade funding)</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="10" t="inlineStr">
+        <is>
+          <t>G125</t>
+        </is>
+      </c>
+      <c r="B129" s="10" t="inlineStr">
+        <is>
+          <t>RIVCircular Open Call (Circular Economy)</t>
+        </is>
+      </c>
+      <c r="C129" s="10" t="inlineStr">
+        <is>
+          <t>RIVCircular (Horizon Europe project)</t>
+        </is>
+      </c>
+      <c r="D129" s="10" t="inlineStr">
+        <is>
+          <t>EU cascade funding</t>
+        </is>
+      </c>
+      <c r="E129" s="10" t="inlineStr">
+        <is>
+          <t>EU (5 innovation ecosystems)</t>
+        </is>
+      </c>
+      <c r="F129" s="10" t="inlineStr">
+        <is>
+          <t>Startup funding (circular economy)</t>
+        </is>
+      </c>
+      <c r="G129" s="10" t="inlineStr">
+        <is>
+          <t>SMEs &amp; research-industry teams</t>
+        </is>
+      </c>
+      <c r="H129" s="10" t="inlineStr">
+        <is>
+          <t>Cascade funding for circular-economy projects across construction, textiles, electric vehicles, waste-to-resource and digital technologies.</t>
+        </is>
+      </c>
+      <c r="I129" s="10" t="inlineStr">
+        <is>
+          <t>Up to €600,000</t>
+        </is>
+      </c>
+      <c r="J129" s="10" t="inlineStr">
+        <is>
+          <t>Project-dependent</t>
+        </is>
+      </c>
+      <c r="K129" s="10" t="inlineStr">
+        <is>
+          <t>Research and industry stakeholders in the participating European innovation ecosystems</t>
+        </is>
+      </c>
+      <c r="L129" s="10" t="inlineStr">
+        <is>
+          <t>17 September 2026</t>
+        </is>
+      </c>
+      <c r="M129" s="10" t="inlineStr">
+        <is>
+          <t>RIVCircular open call</t>
+        </is>
+      </c>
+      <c r="N129" s="10" t="inlineStr">
+        <is>
+          <t>No - written review</t>
+        </is>
+      </c>
+      <c r="O129" s="10" t="inlineStr">
+        <is>
+          <t>Good (cascade calls are less crowded)</t>
+        </is>
+      </c>
+      <c r="P129" s="10" t="inlineStr">
+        <is>
+          <t>https://www.rivcircular.eu</t>
+        </is>
+      </c>
+      <c r="Q129" s="10" t="inlineStr">
+        <is>
+          <t>Verified 23 Jul 2026.</t>
+        </is>
+      </c>
+      <c r="R129" s="10" t="inlineStr">
+        <is>
+          <t>Seed;Growth</t>
+        </is>
+      </c>
+      <c r="S129" s="10" t="inlineStr">
+        <is>
+          <t>Founded</t>
+        </is>
+      </c>
+      <c r="T129" s="10" t="inlineStr">
+        <is>
+          <t>Grant (cascade funding)</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="10" t="inlineStr">
+        <is>
+          <t>G126</t>
+        </is>
+      </c>
+      <c r="B130" s="10" t="inlineStr">
+        <is>
+          <t>UNITE Open Call (Digital Health)</t>
+        </is>
+      </c>
+      <c r="C130" s="10" t="inlineStr">
+        <is>
+          <t>UNITE (Horizon Europe project)</t>
+        </is>
+      </c>
+      <c r="D130" s="10" t="inlineStr">
+        <is>
+          <t>EU cascade funding</t>
+        </is>
+      </c>
+      <c r="E130" s="10" t="inlineStr">
+        <is>
+          <t>EU-wide</t>
+        </is>
+      </c>
+      <c r="F130" s="10" t="inlineStr">
+        <is>
+          <t>Startup funding (digital health)</t>
+        </is>
+      </c>
+      <c r="G130" s="10" t="inlineStr">
+        <is>
+          <t>Digital health startups</t>
+        </is>
+      </c>
+      <c r="H130" s="10" t="inlineStr">
+        <is>
+          <t>Fast-tracks digital health startups tackling ageing populations and demographic change, with funding plus market-entry support.</t>
+        </is>
+      </c>
+      <c r="I130" s="10" t="inlineStr">
+        <is>
+          <t>€200,000-1,000,000 (grant)</t>
+        </is>
+      </c>
+      <c r="J130" s="10" t="inlineStr">
+        <is>
+          <t>Programme-dependent</t>
+        </is>
+      </c>
+      <c r="K130" s="10" t="inlineStr">
+        <is>
+          <t>Digital health startups able to scale across European markets</t>
+        </is>
+      </c>
+      <c r="L130" s="10" t="inlineStr">
+        <is>
+          <t>Call opening soon (check site)</t>
+        </is>
+      </c>
+      <c r="M130" s="10" t="inlineStr">
+        <is>
+          <t>UNITE open call</t>
+        </is>
+      </c>
+      <c r="N130" s="10" t="inlineStr">
+        <is>
+          <t>Yes - selection</t>
+        </is>
+      </c>
+      <c r="O130" s="10" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="P130" s="10" t="inlineStr">
+        <is>
+          <t>https://unitedigihealth.eu/open-call</t>
+        </is>
+      </c>
+      <c r="Q130" s="10" t="inlineStr">
+        <is>
+          <t>One of the larger cascade-funding opportunities for health tech.</t>
+        </is>
+      </c>
+      <c r="R130" s="10" t="inlineStr">
+        <is>
+          <t>Seed;Growth</t>
+        </is>
+      </c>
+      <c r="S130" s="10" t="inlineStr">
+        <is>
+          <t>Founded</t>
+        </is>
+      </c>
+      <c r="T130" s="10" t="inlineStr">
+        <is>
+          <t>Grant (cascade funding)</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="10" t="inlineStr">
+        <is>
+          <t>G127</t>
+        </is>
+      </c>
+      <c r="B131" s="10" t="inlineStr">
+        <is>
+          <t>LLM-BRIDGE Open Call (Generative AI)</t>
+        </is>
+      </c>
+      <c r="C131" s="10" t="inlineStr">
+        <is>
+          <t>LLM-BRIDGE (Horizon Europe project)</t>
+        </is>
+      </c>
+      <c r="D131" s="10" t="inlineStr">
+        <is>
+          <t>EU cascade funding</t>
+        </is>
+      </c>
+      <c r="E131" s="10" t="inlineStr">
+        <is>
+          <t>EU-wide</t>
+        </is>
+      </c>
+      <c r="F131" s="10" t="inlineStr">
+        <is>
+          <t>Startup funding (generative AI)</t>
+        </is>
+      </c>
+      <c r="G131" s="10" t="inlineStr">
+        <is>
+          <t>Early-stage GenAI ventures</t>
+        </is>
+      </c>
+      <c r="H131" s="10" t="inlineStr">
+        <is>
+          <t>Pan-European programme creating and growing European generative-AI ventures, with incubation funding and free support services.</t>
+        </is>
+      </c>
+      <c r="I131" s="10" t="inlineStr">
+        <is>
+          <t>€25,000 (incubation) + free services</t>
+        </is>
+      </c>
+      <c r="J131" s="10" t="inlineStr">
+        <is>
+          <t>Programme-dependent</t>
+        </is>
+      </c>
+      <c r="K131" s="10" t="inlineStr">
+        <is>
+          <t>Early-stage European generative-AI ventures</t>
+        </is>
+      </c>
+      <c r="L131" s="10" t="inlineStr">
+        <is>
+          <t>Periodic calls (check site)</t>
+        </is>
+      </c>
+      <c r="M131" s="10" t="inlineStr">
+        <is>
+          <t>LLM-BRIDGE open call</t>
+        </is>
+      </c>
+      <c r="N131" s="10" t="inlineStr">
+        <is>
+          <t>Yes - selection</t>
+        </is>
+      </c>
+      <c r="O131" s="10" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="P131" s="10" t="inlineStr">
+        <is>
+          <t>https://28digital.eu/all-startup-opportunities/</t>
+        </is>
+      </c>
+      <c r="Q131" s="10" t="inlineStr">
+        <is>
+          <t>Part of the EIT Digital ecosystem; check the current round for exact dates.</t>
+        </is>
+      </c>
+      <c r="R131" s="10" t="inlineStr">
+        <is>
+          <t>Pre-seed;Seed</t>
+        </is>
+      </c>
+      <c r="S131" s="10" t="inlineStr">
+        <is>
+          <t>Founded or forming</t>
+        </is>
+      </c>
+      <c r="T131" s="10" t="inlineStr">
+        <is>
+          <t>Grant + incubation</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>G128</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>CEEPUS (Central European Exchange Programme for University Studies)</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>OeAD / CEEPUS national offices</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>OeAD / CEEPUS</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Austria + Central &amp; Eastern Europe</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Mobility / All disciplines</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Master, PhD &amp; postdocs</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Multilateral exchange programme funding study and research stays across 16 Central and Eastern European countries, either within university networks or as a 'freemover'.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Monthly scholarship set by the host country (Austria: ~€1,250/mo for PhD level) + often waived fees</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>1–10 months (short stays also possible)</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Students, doctoral candidates and academic staff at participating universities in CEEPUS member countries</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>Network applications ~15 Jun; freemover deadlines vary by country (check site)</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>CEEPUS online system (www.ceepus.info)</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>No — network or national selection</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>https://oead.at/en/study-research-teaching/overview-grants-and-scholarships</t>
+        </is>
+      </c>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>Underused route for short research stays in the region; freemover track needs no network membership.</t>
+        </is>
+      </c>
+      <c r="R132" t="inlineStr"/>
+      <c r="S132" t="inlineStr"/>
+      <c r="T132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>G129</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Aktion Austria–Czech Republic / Slovakia / Hungary</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>OeAD (bilateral 'Aktion' programmes)</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>OeAD</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Austria ↔ CZ / SK / HU</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Mobility / All disciplines</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Master, PhD &amp; postdocs</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Bilateral programmes funding research and study stays between Austria and Czechia, Slovakia or Hungary, in both directions, plus small cooperative projects.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Monthly scholarship (~€1,150–1,250) or project funding for travel/accommodation</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>1–5 months (stays); project funding varies</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Students, doctoral candidates and researchers at universities in Austria and the respective partner country</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>Annual/biannual deadlines per programme (check site)</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>OeAD grants platform</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>No — bilateral committee</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>https://oead.at/en/study-research-teaching/overview-grants-and-scholarships</t>
+        </is>
+      </c>
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t>Three parallel programmes with near-identical rules — check the one matching your partner country.</t>
+        </is>
+      </c>
+      <c r="R133" t="inlineStr"/>
+      <c r="S133" t="inlineStr"/>
+      <c r="T133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>G130</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Richard Plaschka Fellowship</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>OeAD on behalf of the BMFWF</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>OeAD</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Austria (incoming)</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Mobility / All disciplines</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>PhD candidates &amp; postdocs</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Research fellowships for foreign university teachers and researchers to carry out a research stay at an Austrian institution.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Monthly scholarship (~€1,250–1,500) + insurance</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>3–9 months</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Non-Austrian university teachers and researchers; host institution in Austria required</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>Annual call (check site)</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>OeAD grants platform</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>No — written review</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>https://oead.at/en/study-research-teaching/overview-grants-and-scholarships</t>
+        </is>
+      </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>Open worldwide; aimed at researchers already holding a university position.</t>
+        </is>
+      </c>
+      <c r="R134" t="inlineStr"/>
+      <c r="S134" t="inlineStr"/>
+      <c r="T134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>G131</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Ernst Mach Follow-up Grant</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>OeAD</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>OeAD</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Austria (incoming)</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Mobility / All disciplines</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Postdoctoral (former Ernst Mach holders)</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Return grant enabling former Ernst Mach scholarship holders from developing countries to come back to Austria for a further research stay.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Monthly scholarship (~€1,250) + travel</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>1–3 months</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Former Ernst Mach grantees from non-European developing countries</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>Annual call (check site)</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>OeAD grants platform</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>https://oead.at/en/study-research-teaching/overview-grants-and-scholarships</t>
+        </is>
+      </c>
+      <c r="Q135" t="inlineStr">
+        <is>
+          <t>Only open to alumni of the main Ernst Mach programme.</t>
+        </is>
+      </c>
+      <c r="R135" t="inlineStr"/>
+      <c r="S135" t="inlineStr"/>
+      <c r="T135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>G132</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Ernst Mach – ASEA-UNINET Short-term Research Grant</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>OeAD / ASEA-UNINET</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>OeAD</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Austria (incoming, Southeast Asia)</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Natural sciences, engineering &amp; medicine</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Postdoctoral</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Short research stays in Austria for researchers from ASEA-UNINET partner universities in Southeast Asia.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Monthly scholarship (~€1,250) + travel</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>1–3 months</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Researchers at ASEA-UNINET member universities (Indonesia, Malaysia, Philippines, Thailand, Vietnam)</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>Annual call (check site)</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>OeAD grants platform / home university</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>https://oead.at/en/study-research-teaching/overview-grants-and-scholarships</t>
+        </is>
+      </c>
+      <c r="Q136" t="inlineStr">
+        <is>
+          <t>Requires an Austrian host institute; nomination usually via the home university.</t>
+        </is>
+      </c>
+      <c r="R136" t="inlineStr"/>
+      <c r="S136" t="inlineStr"/>
+      <c r="T136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>G133</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Ernst Mach Grant – Ukraine</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>OeAD</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>OeAD</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Austria (incoming, Ukraine)</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Mobility / All disciplines</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>PhD candidates &amp; postdocs</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Dedicated Ernst Mach strand supporting Ukrainian students and researchers to study or carry out research in Austria.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Monthly scholarship (~€1,250–1,500) + insurance</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>Duration per call</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Ukrainian nationals; conditions per current call</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>Annual call (check site)</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>OeAD grants platform</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>https://oead.at/en/study-research-teaching/overview-grants-and-scholarships</t>
+        </is>
+      </c>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>Conditions have changed between rounds — check the current call text carefully.</t>
+        </is>
+      </c>
+      <c r="R137" t="inlineStr"/>
+      <c r="S137" t="inlineStr"/>
+      <c r="T137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>G134</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Indonesia–Austria Scholarship Programme (IASP)</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>OeAD / Indonesian Ministry of Education</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>OeAD</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Austria (incoming, Indonesia)</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Natural sciences, engineering &amp; all disciplines</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>PhD candidates</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Joint programme funding Indonesian doctoral candidates to complete a PhD at an Austrian university.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Monthly scholarship + fees (split funding Austria/Indonesia)</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>Up to 4 years (PhD)</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Indonesian nationals admitted to an Austrian doctoral programme</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>Annual call (check site)</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>OeAD grants platform</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>Possibly — selection panel</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>https://oead.at/en/study-research-teaching/overview-grants-and-scholarships</t>
+        </is>
+      </c>
+      <c r="Q138" t="inlineStr">
+        <is>
+          <t>Co-funded scheme; requires acceptance by the Austrian host university first.</t>
+        </is>
+      </c>
+      <c r="R138" t="inlineStr"/>
+      <c r="S138" t="inlineStr"/>
+      <c r="T138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>G135</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Franz Werfel Fellowship</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>OeAD on behalf of the BMFWF</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>OeAD</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Austria (incoming)</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Humanities (German language &amp; Austrian literature)</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Postdoctoral / young university teachers</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Fellowship for young university teachers of German language and Austrian literature to conduct research in Austria, with a long-term alumni network.</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Monthly scholarship (~€1,250) + insurance + follow-up support</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>Up to 12 months (renewable)</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Young university teachers of German/Austrian literature; typically under 35; non-Austrian</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>Annual deadline (check site)</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>OeAD grants platform</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>No — written review</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>https://oead.at/en/study-research-teaching/overview-grants-and-scholarships</t>
+        </is>
+      </c>
+      <c r="Q139" t="inlineStr">
+        <is>
+          <t>Includes alumni follow-up grants and conference invitations after the fellowship.</t>
+        </is>
+      </c>
+      <c r="R139" t="inlineStr"/>
+      <c r="S139" t="inlineStr"/>
+      <c r="T139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>G136</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Erhard Busek Grant (Danube Region)</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>OeAD on behalf of the BMFWF</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>OeAD</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Austria (incoming, Danube region)</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Mobility / All disciplines</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Master &amp; PhD candidates</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Scholarship for students and young researchers from Danube region countries to study or research in Austria.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Monthly scholarship (~€1,150–1,250)</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>Duration per call</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Nationals of eligible Danube region countries; admission to an Austrian institution</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>Annual call (check site)</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>OeAD grants platform</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>https://oead.at/en/study-research-teaching/overview-grants-and-scholarships</t>
+        </is>
+      </c>
+      <c r="Q140" t="inlineStr">
+        <is>
+          <t>Named after the former Austrian vice-chancellor; focused on regional academic ties.</t>
+        </is>
+      </c>
+      <c r="R140" t="inlineStr"/>
+      <c r="S140" t="inlineStr"/>
+      <c r="T140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>G137</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>ISTA Summer Fellowship (via OeAD)</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Institute of Science and Technology Austria (ISTA)</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>OeAD / ISTA</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Austria (Klosterneuburg)</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Natural sciences &amp; engineering</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Master students / pre-PhD</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Paid summer research placement in a research group at ISTA — biology, neuroscience, physics, chemistry, mathematics, computer science and data science.</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Stipend + accommodation support</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>~2–3 months (summer)</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Undergraduate and Master students with strong science background; international applicants welcome</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>Annual call (typically ~Jan/Feb; check site)</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>ISTA online application</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>Possibly — group selection</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>https://oead.at/en/study-research-teaching/overview-grants-and-scholarships</t>
+        </is>
+      </c>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>Excellent stepping stone into a PhD at ISTA or elsewhere.</t>
+        </is>
+      </c>
+      <c r="R141" t="inlineStr"/>
+      <c r="S141" t="inlineStr"/>
+      <c r="T141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>G138</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Doctoral Grant for the European University Institute (EUI)</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>OeAD on behalf of the BMFWF</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>OeAD</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Austria → Italy (Florence)</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Social sciences (economics, law, history, political &amp; social sciences)</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>PhD candidates</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Funds Austrian doctoral candidates to complete their PhD at the European University Institute in Florence.</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Monthly grant (EUI standard rate) + travel + insurance</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>Up to 4 years</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Austrian citizens (or equivalent) admitted to an EUI doctoral programme</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>Annual (EUI application ~Jan; grant follows admission)</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>EUI application + OeAD</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>Yes — EUI admission interview</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>https://oead.at/en/study-research-teaching/overview-grants-and-scholarships</t>
+        </is>
+      </c>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>You apply to the EUI first; the Austrian grant covers admitted national candidates.</t>
+        </is>
+      </c>
+      <c r="R142" t="inlineStr"/>
+      <c r="S142" t="inlineStr"/>
+      <c r="T142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>G139</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Scientific Stays at Taiwanese Universities</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>OeAD / Taiwanese Ministry of Education</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>OeAD</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Austria → Taiwan</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Natural sciences, engineering &amp; all disciplines</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>PhD candidates, lecturers &amp; researchers</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Funds research stays at Taiwanese universities for doctoral candidates, lecturers and researchers based in Austria.</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Monthly scholarship + travel allowance</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>1–12 months</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Doctoral candidates, lecturers and researchers at Austrian institutions; Taiwanese host required</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>Annual call (check site)</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>OeAD grants platform</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>https://oead.at/en/study-research-teaching/overview-grants-and-scholarships</t>
+        </is>
+      </c>
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t>Useful and under-applied route to Asian research collaborations.</t>
+        </is>
+      </c>
+      <c r="R143" t="inlineStr"/>
+      <c r="S143" t="inlineStr"/>
+      <c r="T143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>G140</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>OeAD Bilateral Project Funding (Scientific &amp; Technological Cooperation, WTZ)</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>OeAD on behalf of the BMFWF</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>OeAD</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Austria + partner countries</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Mobility / All disciplines (project cooperation)</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Any (project leaders at Austrian institutions)</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Funds cross-border scientific project cooperation under bilateral agreements and multilateral networks — primarily covering travel and accommodation for exchange visits.</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Travel and accommodation costs (typically €5k–20k per project)</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>2 years typical</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Researchers at Austrian institutions with a partner in the respective country</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>Country-specific calls (check site)</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>OeAD project platform</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>No — bilateral review</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>https://oead.at/en/study-research-teaching/overview-grants-and-scholarships</t>
+        </is>
+      </c>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>Small budgets but a low-friction way to seed international collaborations.</t>
+        </is>
+      </c>
+      <c r="R144" t="inlineStr"/>
+      <c r="S144" t="inlineStr"/>
+      <c r="T144" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:Q52"/>

--- a/data/grants.xlsx
+++ b/data/grants.xlsx
@@ -508,7 +508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:T292"/>
+  <dimension ref="A1:T342"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="6" customWidth="1" style="10" min="1" max="1"/>
@@ -23658,3676 +23658,8332 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" t="inlineStr">
+      <c r="A257" s="10" t="inlineStr">
         <is>
           <t>G253</t>
         </is>
       </c>
-      <c r="B257" t="inlineStr">
+      <c r="B257" s="10" t="inlineStr">
         <is>
           <t>Innosuisse Start-up Innovation Projects &amp; Coaching</t>
         </is>
       </c>
-      <c r="C257" t="inlineStr">
+      <c r="C257" s="10" t="inlineStr">
         <is>
           <t>Innosuisse — Swiss Innovation Agency</t>
         </is>
       </c>
-      <c r="D257" t="inlineStr">
+      <c r="D257" s="10" t="inlineStr">
         <is>
           <t>Switzerland (Innosuisse)</t>
         </is>
       </c>
-      <c r="E257" t="inlineStr">
+      <c r="E257" s="10" t="inlineStr">
         <is>
           <t>Switzerland</t>
         </is>
       </c>
-      <c r="F257" t="inlineStr">
+      <c r="F257" s="10" t="inlineStr">
         <is>
           <t>Startup funding (science-based innovation)</t>
         </is>
       </c>
-      <c r="G257" t="inlineStr">
+      <c r="G257" s="10" t="inlineStr">
         <is>
           <t>Researchers &amp; startups</t>
         </is>
       </c>
-      <c r="H257" t="inlineStr">
+      <c r="H257" s="10" t="inlineStr">
         <is>
           <t>Switzerland's federal innovation agency funds science-based innovation projects with research partners, plus structured start-up coaching and training.</t>
         </is>
       </c>
-      <c r="I257" t="inlineStr">
+      <c r="I257" s="10" t="inlineStr">
         <is>
           <t>Innovation projects: research partner costs covered (often CHF 100k-1M); coaching subsidised</t>
         </is>
       </c>
-      <c r="J257" t="inlineStr">
+      <c r="J257" s="10" t="inlineStr">
         <is>
           <t>1-3 years</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr">
+      <c r="K257" s="10" t="inlineStr">
         <is>
           <t>Swiss-based company with a Swiss research partner; coaching open to early founders</t>
         </is>
       </c>
-      <c r="L257" t="inlineStr">
+      <c r="L257" s="10" t="inlineStr">
         <is>
           <t>Rolling submission for innovation projects</t>
         </is>
       </c>
-      <c r="M257" t="inlineStr">
+      <c r="M257" s="10" t="inlineStr">
         <is>
           <t>Innosuisse online portal</t>
         </is>
       </c>
-      <c r="N257" t="inlineStr">
+      <c r="N257" s="10" t="inlineStr">
         <is>
           <t>Yes — for coaching admission</t>
         </is>
       </c>
-      <c r="O257" t="inlineStr">
+      <c r="O257" s="10" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="P257" t="inlineStr">
+      <c r="P257" s="10" t="inlineStr">
         <is>
           <t>https://www.innosuisse.admin.ch/en</t>
         </is>
       </c>
-      <c r="Q257" t="inlineStr">
+      <c r="Q257" s="10" t="inlineStr">
         <is>
           <t>Unusually, the money goes to your academic research partner — ideal for spin-offs still tied to a lab.</t>
         </is>
       </c>
-      <c r="R257" t="inlineStr">
+      <c r="R257" s="10" t="inlineStr">
         <is>
           <t>Pre-seed;Seed</t>
         </is>
       </c>
-      <c r="S257" t="inlineStr">
+      <c r="S257" s="10" t="inlineStr">
         <is>
           <t>Founded or forming</t>
         </is>
       </c>
-      <c r="T257" t="inlineStr">
+      <c r="T257" s="10" t="inlineStr">
         <is>
           <t>Grant (to research partner) + coaching</t>
         </is>
       </c>
     </row>
     <row r="258">
-      <c r="A258" t="inlineStr">
+      <c r="A258" s="10" t="inlineStr">
         <is>
           <t>G254</t>
         </is>
       </c>
-      <c r="B258" t="inlineStr">
+      <c r="B258" s="10" t="inlineStr">
         <is>
           <t>Venture Kick</t>
         </is>
       </c>
-      <c r="C258" t="inlineStr">
+      <c r="C258" s="10" t="inlineStr">
         <is>
           <t>Venture Kick (private consortium)</t>
         </is>
       </c>
-      <c r="D258" t="inlineStr">
+      <c r="D258" s="10" t="inlineStr">
         <is>
           <t>Private (Venture Kick)</t>
         </is>
       </c>
-      <c r="E258" t="inlineStr">
+      <c r="E258" s="10" t="inlineStr">
         <is>
           <t>Switzerland</t>
         </is>
       </c>
-      <c r="F258" t="inlineStr">
+      <c r="F258" s="10" t="inlineStr">
         <is>
           <t>Startup funding (university spin-offs)</t>
         </is>
       </c>
-      <c r="G258" t="inlineStr">
+      <c r="G258" s="10" t="inlineStr">
         <is>
           <t>Pre-seed founders</t>
         </is>
       </c>
-      <c r="H258" t="inlineStr">
+      <c r="H258" s="10" t="inlineStr">
         <is>
           <t>Staged pre-seed funding for Swiss university spin-offs, awarded through three pitch rounds with escalating amounts.</t>
         </is>
       </c>
-      <c r="I258" t="inlineStr">
+      <c r="I258" s="10" t="inlineStr">
         <is>
           <t>CHF 40k → 100k → 150k (up to CHF 290k total)</t>
         </is>
       </c>
-      <c r="J258" t="inlineStr">
+      <c r="J258" s="10" t="inlineStr">
         <is>
           <t>Staged over ~12 months</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr">
+      <c r="K258" s="10" t="inlineStr">
         <is>
           <t>Project based at a Swiss university or research institution; company may not yet exist</t>
         </is>
       </c>
-      <c r="L258" t="inlineStr">
+      <c r="L258" s="10" t="inlineStr">
         <is>
           <t>Rolling applications (check site)</t>
         </is>
       </c>
-      <c r="M258" t="inlineStr">
+      <c r="M258" s="10" t="inlineStr">
         <is>
           <t>Venture Kick online application</t>
         </is>
       </c>
-      <c r="N258" t="inlineStr">
+      <c r="N258" s="10" t="inlineStr">
         <is>
           <t>Yes — jury pitch at each stage</t>
         </is>
       </c>
-      <c r="O258" t="inlineStr">
+      <c r="O258" s="10" t="inlineStr">
         <is>
           <t>Competitive</t>
         </is>
       </c>
-      <c r="P258" t="inlineStr">
+      <c r="P258" s="10" t="inlineStr">
         <is>
           <t>https://www.venturekick.ch/</t>
         </is>
       </c>
-      <c r="Q258" t="inlineStr">
+      <c r="Q258" s="10" t="inlineStr">
         <is>
           <t>Staged design means a fast, low-risk first test of your idea. Very strong Swiss alumni record.</t>
         </is>
       </c>
-      <c r="R258" t="inlineStr">
+      <c r="R258" s="10" t="inlineStr">
         <is>
           <t>Pre-seed</t>
         </is>
       </c>
-      <c r="S258" t="inlineStr">
+      <c r="S258" s="10" t="inlineStr">
         <is>
           <t>Not yet founded / just founded</t>
         </is>
       </c>
-      <c r="T258" t="inlineStr">
+      <c r="T258" s="10" t="inlineStr">
         <is>
           <t>Grant (staged)</t>
         </is>
       </c>
     </row>
     <row r="259">
-      <c r="A259" t="inlineStr">
+      <c r="A259" s="10" t="inlineStr">
         <is>
           <t>G255</t>
         </is>
       </c>
-      <c r="B259" t="inlineStr">
+      <c r="B259" s="10" t="inlineStr">
         <is>
           <t>Innovate UK Smart Grants</t>
         </is>
       </c>
-      <c r="C259" t="inlineStr">
+      <c r="C259" s="10" t="inlineStr">
         <is>
           <t>Innovate UK (UKRI)</t>
         </is>
       </c>
-      <c r="D259" t="inlineStr">
+      <c r="D259" s="10" t="inlineStr">
         <is>
           <t>UKRI / Innovate UK</t>
         </is>
       </c>
-      <c r="E259" t="inlineStr">
+      <c r="E259" s="10" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="F259" t="inlineStr">
+      <c r="F259" s="10" t="inlineStr">
         <is>
           <t>Startup funding (all technology sectors)</t>
         </is>
       </c>
-      <c r="G259" t="inlineStr">
+      <c r="G259" s="10" t="inlineStr">
         <is>
           <t>Startups &amp; SMEs</t>
         </is>
       </c>
-      <c r="H259" t="inlineStr">
+      <c r="H259" s="10" t="inlineStr">
         <is>
           <t>The UK's main open innovation grant: funds game-changing, commercially viable R&amp;D from any sector, with no set topics.</t>
         </is>
       </c>
-      <c r="I259" t="inlineStr">
+      <c r="I259" s="10" t="inlineStr">
         <is>
           <t>£100,000-£2,000,000 (typically 70% of costs for SMEs)</t>
         </is>
       </c>
-      <c r="J259" t="inlineStr">
+      <c r="J259" s="10" t="inlineStr">
         <is>
           <t>6-36 months</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr">
+      <c r="K259" s="10" t="inlineStr">
         <is>
           <t>UK-registered business; can be single company or collaborative</t>
         </is>
       </c>
-      <c r="L259" t="inlineStr">
+      <c r="L259" s="10" t="inlineStr">
         <is>
           <t>Regular rounds (~2-3 per year; check site)</t>
         </is>
       </c>
-      <c r="M259" t="inlineStr">
+      <c r="M259" s="10" t="inlineStr">
         <is>
           <t>Innovation Funding Service</t>
         </is>
       </c>
-      <c r="N259" t="inlineStr">
+      <c r="N259" s="10" t="inlineStr">
         <is>
           <t>No — independent assessors</t>
         </is>
       </c>
-      <c r="O259" t="inlineStr">
+      <c r="O259" s="10" t="inlineStr">
         <is>
           <t>~10-15%</t>
         </is>
       </c>
-      <c r="P259" t="inlineStr">
+      <c r="P259" s="10" t="inlineStr">
         <is>
           <t>https://www.ukri.org/councils/innovate-uk/</t>
         </is>
       </c>
-      <c r="Q259" t="inlineStr">
+      <c r="Q259" s="10" t="inlineStr">
         <is>
           <t>'Smart' means open to any technology — the flagship non-thematic UK grant.</t>
         </is>
       </c>
-      <c r="R259" t="inlineStr">
+      <c r="R259" s="10" t="inlineStr">
         <is>
           <t>Pre-seed;Seed;Growth</t>
         </is>
       </c>
-      <c r="S259" t="inlineStr">
+      <c r="S259" s="10" t="inlineStr">
         <is>
           <t>Founded (UK-registered)</t>
         </is>
       </c>
-      <c r="T259" t="inlineStr">
+      <c r="T259" s="10" t="inlineStr">
         <is>
           <t>Grant</t>
         </is>
       </c>
     </row>
     <row r="260">
-      <c r="A260" t="inlineStr">
+      <c r="A260" s="10" t="inlineStr">
         <is>
           <t>G256</t>
         </is>
       </c>
-      <c r="B260" t="inlineStr">
+      <c r="B260" s="10" t="inlineStr">
         <is>
           <t>ICURe Programme (Innovation to Commercialisation of University Research)</t>
         </is>
       </c>
-      <c r="C260" t="inlineStr">
+      <c r="C260" s="10" t="inlineStr">
         <is>
           <t>Innovate UK / SETsquared</t>
         </is>
       </c>
-      <c r="D260" t="inlineStr">
+      <c r="D260" s="10" t="inlineStr">
         <is>
           <t>UKRI / Innovate UK</t>
         </is>
       </c>
-      <c r="E260" t="inlineStr">
+      <c r="E260" s="10" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="F260" t="inlineStr">
+      <c r="F260" s="10" t="inlineStr">
         <is>
           <t>Research commercialisation</t>
         </is>
       </c>
-      <c r="G260" t="inlineStr">
+      <c r="G260" s="10" t="inlineStr">
         <is>
           <t>Researchers pre-company</t>
         </is>
       </c>
-      <c r="H260" t="inlineStr">
+      <c r="H260" s="10" t="inlineStr">
         <is>
           <t>Pays university researchers to spend three months validating whether their research has a market, before committing to a spin-out.</t>
         </is>
       </c>
-      <c r="I260" t="inlineStr">
+      <c r="I260" s="10" t="inlineStr">
         <is>
           <t>~£35,000 for market validation + follow-on grants up to £300k</t>
         </is>
       </c>
-      <c r="J260" t="inlineStr">
+      <c r="J260" s="10" t="inlineStr">
         <is>
           <t>3 months (Explore/Exploit phases)</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr">
+      <c r="K260" s="10" t="inlineStr">
         <is>
           <t>Researchers at UK universities with commercialisable research; university must support</t>
         </is>
       </c>
-      <c r="L260" t="inlineStr">
+      <c r="L260" s="10" t="inlineStr">
         <is>
           <t>Periodic cohorts (check site)</t>
         </is>
       </c>
-      <c r="M260" t="inlineStr">
+      <c r="M260" s="10" t="inlineStr">
         <is>
           <t>Via university commercialisation office</t>
         </is>
       </c>
-      <c r="N260" t="inlineStr">
+      <c r="N260" s="10" t="inlineStr">
         <is>
           <t>Yes — selection panel</t>
         </is>
       </c>
-      <c r="O260" t="inlineStr">
+      <c r="O260" s="10" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="P260" t="inlineStr">
+      <c r="P260" s="10" t="inlineStr">
         <is>
           <t>https://icureprogramme.com/</t>
         </is>
       </c>
-      <c r="Q260" t="inlineStr">
+      <c r="Q260" s="10" t="inlineStr">
         <is>
           <t>The UK's answer to NSF I-Corps: paid customer discovery before you commit.</t>
         </is>
       </c>
-      <c r="R260" t="inlineStr">
+      <c r="R260" s="10" t="inlineStr">
         <is>
           <t>Pre-seed</t>
         </is>
       </c>
-      <c r="S260" t="inlineStr">
+      <c r="S260" s="10" t="inlineStr">
         <is>
           <t>Not yet founded</t>
         </is>
       </c>
-      <c r="T260" t="inlineStr">
+      <c r="T260" s="10" t="inlineStr">
         <is>
           <t>Grant + training</t>
         </is>
       </c>
     </row>
     <row r="261">
-      <c r="A261" t="inlineStr">
+      <c r="A261" s="10" t="inlineStr">
         <is>
           <t>G257</t>
         </is>
       </c>
-      <c r="B261" t="inlineStr">
+      <c r="B261" s="10" t="inlineStr">
         <is>
           <t>SEIS and EIS Investor Tax Relief</t>
         </is>
       </c>
-      <c r="C261" t="inlineStr">
+      <c r="C261" s="10" t="inlineStr">
         <is>
           <t>HM Revenue &amp; Customs (UK Government)</t>
         </is>
       </c>
-      <c r="D261" t="inlineStr">
+      <c r="D261" s="10" t="inlineStr">
         <is>
           <t>UK (HMRC)</t>
         </is>
       </c>
-      <c r="E261" t="inlineStr">
+      <c r="E261" s="10" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="F261" t="inlineStr">
+      <c r="F261" s="10" t="inlineStr">
         <is>
           <t>Investment incentive (all sectors)</t>
         </is>
       </c>
-      <c r="G261" t="inlineStr">
+      <c r="G261" s="10" t="inlineStr">
         <is>
           <t>Startups raising angel/seed money</t>
         </is>
       </c>
-      <c r="H261" t="inlineStr">
+      <c r="H261" s="10" t="inlineStr">
         <is>
           <t>UK tax schemes giving investors 50% (SEIS) or 30% (EIS) income tax relief, making it dramatically easier for early-stage companies to raise.</t>
         </is>
       </c>
-      <c r="I261" t="inlineStr">
+      <c r="I261" s="10" t="inlineStr">
         <is>
           <t>SEIS: up to £250k raised; EIS: up to £12M (£20M knowledge-intensive)</t>
         </is>
       </c>
-      <c r="J261" t="inlineStr">
+      <c r="J261" s="10" t="inlineStr">
         <is>
           <t>Per funding round</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr">
+      <c r="K261" s="10" t="inlineStr">
         <is>
           <t>UK company meeting age, size and trade conditions; advance assurance recommended</t>
         </is>
       </c>
-      <c r="L261" t="inlineStr">
+      <c r="L261" s="10" t="inlineStr">
         <is>
           <t>Rolling (apply for advance assurance before raising)</t>
         </is>
       </c>
-      <c r="M261" t="inlineStr">
+      <c r="M261" s="10" t="inlineStr">
         <is>
           <t>HMRC advance assurance application</t>
         </is>
       </c>
-      <c r="N261" t="inlineStr">
+      <c r="N261" s="10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="O261" t="inlineStr">
+      <c r="O261" s="10" t="inlineStr">
         <is>
           <t>High (if eligible)</t>
         </is>
       </c>
-      <c r="P261" t="inlineStr">
+      <c r="P261" s="10" t="inlineStr">
         <is>
           <t>https://www.gov.uk/guidance/venture-capital-schemes-apply-for-the-seed-enterprise-investment-scheme</t>
         </is>
       </c>
-      <c r="Q261" t="inlineStr">
+      <c r="Q261" s="10" t="inlineStr">
         <is>
           <t>Knowledge-intensive companies (most deep tech) get extended limits and longer eligibility windows.</t>
         </is>
       </c>
-      <c r="R261" t="inlineStr">
+      <c r="R261" s="10" t="inlineStr">
         <is>
           <t>Pre-seed;Seed</t>
         </is>
       </c>
-      <c r="S261" t="inlineStr">
+      <c r="S261" s="10" t="inlineStr">
         <is>
           <t>Founded (UK-registered)</t>
         </is>
       </c>
-      <c r="T261" t="inlineStr">
+      <c r="T261" s="10" t="inlineStr">
         <is>
           <t>Investor tax relief</t>
         </is>
       </c>
     </row>
     <row r="262">
-      <c r="A262" t="inlineStr">
+      <c r="A262" s="10" t="inlineStr">
         <is>
           <t>G258</t>
         </is>
       </c>
-      <c r="B262" t="inlineStr">
+      <c r="B262" s="10" t="inlineStr">
         <is>
           <t>Enterprise Ireland Pre-Seed Start Fund &amp; HPSU Funding</t>
         </is>
       </c>
-      <c r="C262" t="inlineStr">
+      <c r="C262" s="10" t="inlineStr">
         <is>
           <t>Enterprise Ireland</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr">
+      <c r="D262" s="10" t="inlineStr">
         <is>
           <t>Ireland (EI)</t>
         </is>
       </c>
-      <c r="E262" t="inlineStr">
+      <c r="E262" s="10" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="F262" t="inlineStr">
+      <c r="F262" s="10" t="inlineStr">
         <is>
           <t>Startup funding (all innovative sectors)</t>
         </is>
       </c>
-      <c r="G262" t="inlineStr">
+      <c r="G262" s="10" t="inlineStr">
         <is>
           <t>Pre-seed to growth</t>
         </is>
       </c>
-      <c r="H262" t="inlineStr">
+      <c r="H262" s="10" t="inlineStr">
         <is>
           <t>Ireland's state agency backs High Potential Start-Ups with equity and grants, plus a pre-seed fund for very early companies.</t>
         </is>
       </c>
-      <c r="I262" t="inlineStr">
+      <c r="I262" s="10" t="inlineStr">
         <is>
           <t>Pre-Seed Start Fund €50k-100k; HPSU investments €250k-1M+</t>
         </is>
       </c>
-      <c r="J262" t="inlineStr">
+      <c r="J262" s="10" t="inlineStr">
         <is>
           <t>Per funding round</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr">
+      <c r="K262" s="10" t="inlineStr">
         <is>
           <t>Irish-registered company with export potential; HPSU criteria apply</t>
         </is>
       </c>
-      <c r="L262" t="inlineStr">
+      <c r="L262" s="10" t="inlineStr">
         <is>
           <t>Rolling (via development adviser)</t>
         </is>
       </c>
-      <c r="M262" t="inlineStr">
+      <c r="M262" s="10" t="inlineStr">
         <is>
           <t>Enterprise Ireland application</t>
         </is>
       </c>
-      <c r="N262" t="inlineStr">
+      <c r="N262" s="10" t="inlineStr">
         <is>
           <t>Yes — investment committee</t>
         </is>
       </c>
-      <c r="O262" t="inlineStr">
+      <c r="O262" s="10" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="P262" t="inlineStr">
+      <c r="P262" s="10" t="inlineStr">
         <is>
           <t>https://www.enterprise-ireland.com/en/funding-supports/</t>
         </is>
       </c>
-      <c r="Q262" t="inlineStr">
+      <c r="Q262" s="10" t="inlineStr">
         <is>
           <t>Also runs Commercialisation Fund grants for researchers pre-company.</t>
         </is>
       </c>
-      <c r="R262" t="inlineStr">
+      <c r="R262" s="10" t="inlineStr">
         <is>
           <t>Pre-seed;Seed;Growth</t>
         </is>
       </c>
-      <c r="S262" t="inlineStr">
+      <c r="S262" s="10" t="inlineStr">
         <is>
           <t>Founded (Irish-registered)</t>
         </is>
       </c>
-      <c r="T262" t="inlineStr">
+      <c r="T262" s="10" t="inlineStr">
         <is>
           <t>Grant + equity</t>
         </is>
       </c>
     </row>
     <row r="263">
-      <c r="A263" t="inlineStr">
+      <c r="A263" s="10" t="inlineStr">
         <is>
           <t>G259</t>
         </is>
       </c>
-      <c r="B263" t="inlineStr">
+      <c r="B263" s="10" t="inlineStr">
         <is>
           <t>Enterprise Ireland Commercialisation Fund</t>
         </is>
       </c>
-      <c r="C263" t="inlineStr">
+      <c r="C263" s="10" t="inlineStr">
         <is>
           <t>Enterprise Ireland</t>
         </is>
       </c>
-      <c r="D263" t="inlineStr">
+      <c r="D263" s="10" t="inlineStr">
         <is>
           <t>Ireland (EI)</t>
         </is>
       </c>
-      <c r="E263" t="inlineStr">
+      <c r="E263" s="10" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="F263" t="inlineStr">
+      <c r="F263" s="10" t="inlineStr">
         <is>
           <t>Research commercialisation</t>
         </is>
       </c>
-      <c r="G263" t="inlineStr">
+      <c r="G263" s="10" t="inlineStr">
         <is>
           <t>Academic researchers pre-company</t>
         </is>
       </c>
-      <c r="H263" t="inlineStr">
+      <c r="H263" s="10" t="inlineStr">
         <is>
           <t>Funds researchers in Irish higher education and research institutes to develop innovations to the point of a licence or spin-out.</t>
         </is>
       </c>
-      <c r="I263" t="inlineStr">
+      <c r="I263" s="10" t="inlineStr">
         <is>
           <t>€80,000-€350,000 depending on phase</t>
         </is>
       </c>
-      <c r="J263" t="inlineStr">
+      <c r="J263" s="10" t="inlineStr">
         <is>
           <t>1-2 years</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr">
+      <c r="K263" s="10" t="inlineStr">
         <is>
           <t>Researchers at Irish HEIs and research performing organisations</t>
         </is>
       </c>
-      <c r="L263" t="inlineStr">
+      <c r="L263" s="10" t="inlineStr">
         <is>
           <t>Periodic calls (check site)</t>
         </is>
       </c>
-      <c r="M263" t="inlineStr">
+      <c r="M263" s="10" t="inlineStr">
         <is>
           <t>Via institution's technology transfer office</t>
         </is>
       </c>
-      <c r="N263" t="inlineStr">
+      <c r="N263" s="10" t="inlineStr">
         <is>
           <t>Yes — panel</t>
         </is>
       </c>
-      <c r="O263" t="inlineStr">
+      <c r="O263" s="10" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="P263" t="inlineStr">
+      <c r="P263" s="10" t="inlineStr">
         <is>
           <t>https://www.enterprise-ireland.com/en/research-innovation/</t>
         </is>
       </c>
-      <c r="Q263" t="inlineStr">
+      <c r="Q263" s="10" t="inlineStr">
         <is>
           <t>Ireland's equivalent of EXIST Research Transfer, run through the TTO.</t>
         </is>
       </c>
-      <c r="R263" t="inlineStr">
+      <c r="R263" s="10" t="inlineStr">
         <is>
           <t>Pre-seed</t>
         </is>
       </c>
-      <c r="S263" t="inlineStr">
+      <c r="S263" s="10" t="inlineStr">
         <is>
           <t>Not yet founded</t>
         </is>
       </c>
-      <c r="T263" t="inlineStr">
+      <c r="T263" s="10" t="inlineStr">
         <is>
           <t>Grant</t>
         </is>
       </c>
     </row>
     <row r="264">
-      <c r="A264" t="inlineStr">
+      <c r="A264" s="10" t="inlineStr">
         <is>
           <t>G260</t>
         </is>
       </c>
-      <c r="B264" t="inlineStr">
+      <c r="B264" s="10" t="inlineStr">
         <is>
           <t>Vinnova Innovation Grants</t>
         </is>
       </c>
-      <c r="C264" t="inlineStr">
+      <c r="C264" s="10" t="inlineStr">
         <is>
           <t>Vinnova — Sweden's Innovation Agency</t>
         </is>
       </c>
-      <c r="D264" t="inlineStr">
+      <c r="D264" s="10" t="inlineStr">
         <is>
           <t>Sweden (Vinnova)</t>
         </is>
       </c>
-      <c r="E264" t="inlineStr">
+      <c r="E264" s="10" t="inlineStr">
         <is>
           <t>Sweden</t>
         </is>
       </c>
-      <c r="F264" t="inlineStr">
+      <c r="F264" s="10" t="inlineStr">
         <is>
           <t>Startup funding (all innovation sectors)</t>
         </is>
       </c>
-      <c r="G264" t="inlineStr">
+      <c r="G264" s="10" t="inlineStr">
         <is>
           <t>Startups &amp; SMEs</t>
         </is>
       </c>
-      <c r="H264" t="inlineStr">
+      <c r="H264" s="10" t="inlineStr">
         <is>
           <t>Sweden's innovation agency runs a wide range of calls, from small early-stage grants to large collaborative innovation programmes.</t>
         </is>
       </c>
-      <c r="I264" t="inlineStr">
+      <c r="I264" s="10" t="inlineStr">
         <is>
           <t>SEK 300k-5M+ depending on call</t>
         </is>
       </c>
-      <c r="J264" t="inlineStr">
+      <c r="J264" s="10" t="inlineStr">
         <is>
           <t>6 months-3 years</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr">
+      <c r="K264" s="10" t="inlineStr">
         <is>
           <t>Swedish-registered organisations including startups; call-specific eligibility</t>
         </is>
       </c>
-      <c r="L264" t="inlineStr">
+      <c r="L264" s="10" t="inlineStr">
         <is>
           <t>Rolling programme of calls (check site)</t>
         </is>
       </c>
-      <c r="M264" t="inlineStr">
+      <c r="M264" s="10" t="inlineStr">
         <is>
           <t>Vinnova online portal (Intressentportalen)</t>
         </is>
       </c>
-      <c r="N264" t="inlineStr">
+      <c r="N264" s="10" t="inlineStr">
         <is>
           <t>No — assessor review</t>
         </is>
       </c>
-      <c r="O264" t="inlineStr">
+      <c r="O264" s="10" t="inlineStr">
         <is>
           <t>Varies by call</t>
         </is>
       </c>
-      <c r="P264" t="inlineStr">
+      <c r="P264" s="10" t="inlineStr">
         <is>
           <t>https://www.vinnova.se/en/</t>
         </is>
       </c>
-      <c r="Q264" t="inlineStr">
+      <c r="Q264" s="10" t="inlineStr">
         <is>
           <t>Many calls are thematic; the 'Innovative Startups' track is the standard early-stage entry.</t>
         </is>
       </c>
-      <c r="R264" t="inlineStr">
+      <c r="R264" s="10" t="inlineStr">
         <is>
           <t>Pre-seed;Seed</t>
         </is>
       </c>
-      <c r="S264" t="inlineStr">
+      <c r="S264" s="10" t="inlineStr">
         <is>
           <t>Founded (Swedish-registered)</t>
         </is>
       </c>
-      <c r="T264" t="inlineStr">
+      <c r="T264" s="10" t="inlineStr">
         <is>
           <t>Grant</t>
         </is>
       </c>
     </row>
     <row r="265">
-      <c r="A265" t="inlineStr">
+      <c r="A265" s="10" t="inlineStr">
         <is>
           <t>G261</t>
         </is>
       </c>
-      <c r="B265" t="inlineStr">
+      <c r="B265" s="10" t="inlineStr">
         <is>
           <t>Innovation Fund Denmark — Innobooster &amp; InnoExplorer</t>
         </is>
       </c>
-      <c r="C265" t="inlineStr">
+      <c r="C265" s="10" t="inlineStr">
         <is>
           <t>Innovation Fund Denmark (Innovationsfonden)</t>
         </is>
       </c>
-      <c r="D265" t="inlineStr">
+      <c r="D265" s="10" t="inlineStr">
         <is>
           <t>Denmark (IFD)</t>
         </is>
       </c>
-      <c r="E265" t="inlineStr">
+      <c r="E265" s="10" t="inlineStr">
         <is>
           <t>Denmark</t>
         </is>
       </c>
-      <c r="F265" t="inlineStr">
+      <c r="F265" s="10" t="inlineStr">
         <is>
           <t>Startup and research commercialisation funding</t>
         </is>
       </c>
-      <c r="G265" t="inlineStr">
+      <c r="G265" s="10" t="inlineStr">
         <is>
           <t>Researchers &amp; startups</t>
         </is>
       </c>
-      <c r="H265" t="inlineStr">
+      <c r="H265" s="10" t="inlineStr">
         <is>
           <t>Denmark's innovation fund supports both researchers commercialising results (InnoExplorer) and companies developing products (Innobooster).</t>
         </is>
       </c>
-      <c r="I265" t="inlineStr">
+      <c r="I265" s="10" t="inlineStr">
         <is>
           <t>InnoExplorer up to DKK 1.5M; Innobooster typically DKK 0.5-5M</t>
         </is>
       </c>
-      <c r="J265" t="inlineStr">
+      <c r="J265" s="10" t="inlineStr">
         <is>
           <t>1-2 years</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr">
+      <c r="K265" s="10" t="inlineStr">
         <is>
           <t>Danish companies, or researchers at Danish institutions for InnoExplorer</t>
         </is>
       </c>
-      <c r="L265" t="inlineStr">
+      <c r="L265" s="10" t="inlineStr">
         <is>
           <t>Periodic calls (check site)</t>
         </is>
       </c>
-      <c r="M265" t="inlineStr">
+      <c r="M265" s="10" t="inlineStr">
         <is>
           <t>Innovation Fund Denmark portal</t>
         </is>
       </c>
-      <c r="N265" t="inlineStr">
+      <c r="N265" s="10" t="inlineStr">
         <is>
           <t>Yes — for larger grants</t>
         </is>
       </c>
-      <c r="O265" t="inlineStr">
+      <c r="O265" s="10" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="P265" t="inlineStr">
+      <c r="P265" s="10" t="inlineStr">
         <is>
           <t>https://innovationsfonden.dk/en</t>
         </is>
       </c>
-      <c r="Q265" t="inlineStr">
+      <c r="Q265" s="10" t="inlineStr">
         <is>
           <t>InnoExplorer is the pre-company route; Innobooster is for companies that already exist.</t>
         </is>
       </c>
-      <c r="R265" t="inlineStr">
+      <c r="R265" s="10" t="inlineStr">
         <is>
           <t>Pre-seed;Seed</t>
         </is>
       </c>
-      <c r="S265" t="inlineStr">
+      <c r="S265" s="10" t="inlineStr">
         <is>
           <t>Not yet founded / founded</t>
         </is>
       </c>
-      <c r="T265" t="inlineStr">
+      <c r="T265" s="10" t="inlineStr">
         <is>
           <t>Grant</t>
         </is>
       </c>
     </row>
     <row r="266">
-      <c r="A266" t="inlineStr">
+      <c r="A266" s="10" t="inlineStr">
         <is>
           <t>G262</t>
         </is>
       </c>
-      <c r="B266" t="inlineStr">
+      <c r="B266" s="10" t="inlineStr">
         <is>
           <t>Business Finland — Tempo &amp; Research to Business (R2B)</t>
         </is>
       </c>
-      <c r="C266" t="inlineStr">
+      <c r="C266" s="10" t="inlineStr">
         <is>
           <t>Business Finland</t>
         </is>
       </c>
-      <c r="D266" t="inlineStr">
+      <c r="D266" s="10" t="inlineStr">
         <is>
           <t>Finland (BF)</t>
         </is>
       </c>
-      <c r="E266" t="inlineStr">
+      <c r="E266" s="10" t="inlineStr">
         <is>
           <t>Finland</t>
         </is>
       </c>
-      <c r="F266" t="inlineStr">
+      <c r="F266" s="10" t="inlineStr">
         <is>
           <t>Startup and research commercialisation funding</t>
         </is>
       </c>
-      <c r="G266" t="inlineStr">
+      <c r="G266" s="10" t="inlineStr">
         <is>
           <t>Researchers &amp; startups</t>
         </is>
       </c>
-      <c r="H266" t="inlineStr">
+      <c r="H266" s="10" t="inlineStr">
         <is>
           <t>Finland's funding agency supports early startups (Tempo) and research groups preparing to commercialise or spin out (Research to Business).</t>
         </is>
       </c>
-      <c r="I266" t="inlineStr">
+      <c r="I266" s="10" t="inlineStr">
         <is>
           <t>Tempo up to €50k-100k; R2B up to €500k+</t>
         </is>
       </c>
-      <c r="J266" t="inlineStr">
+      <c r="J266" s="10" t="inlineStr">
         <is>
           <t>6 months-2 years</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr">
+      <c r="K266" s="10" t="inlineStr">
         <is>
           <t>Finnish-registered startups (Tempo); Finnish research organisations (R2B)</t>
         </is>
       </c>
-      <c r="L266" t="inlineStr">
+      <c r="L266" s="10" t="inlineStr">
         <is>
           <t>Rolling submission</t>
         </is>
       </c>
-      <c r="M266" t="inlineStr">
+      <c r="M266" s="10" t="inlineStr">
         <is>
           <t>Business Finland online service</t>
         </is>
       </c>
-      <c r="N266" t="inlineStr">
+      <c r="N266" s="10" t="inlineStr">
         <is>
           <t>No — advisor review</t>
         </is>
       </c>
-      <c r="O266" t="inlineStr">
+      <c r="O266" s="10" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="P266" t="inlineStr">
+      <c r="P266" s="10" t="inlineStr">
         <is>
           <t>https://www.businessfinland.fi/en/</t>
         </is>
       </c>
-      <c r="Q266" t="inlineStr">
+      <c r="Q266" s="10" t="inlineStr">
         <is>
           <t>R2B funds the research group directly — one of the most generous pre-company instruments in Europe.</t>
         </is>
       </c>
-      <c r="R266" t="inlineStr">
+      <c r="R266" s="10" t="inlineStr">
         <is>
           <t>Pre-seed;Seed</t>
         </is>
       </c>
-      <c r="S266" t="inlineStr">
+      <c r="S266" s="10" t="inlineStr">
         <is>
           <t>Not yet founded / founded</t>
         </is>
       </c>
-      <c r="T266" t="inlineStr">
+      <c r="T266" s="10" t="inlineStr">
         <is>
           <t>Grant</t>
         </is>
       </c>
     </row>
     <row r="267">
-      <c r="A267" t="inlineStr">
+      <c r="A267" s="10" t="inlineStr">
         <is>
           <t>G263</t>
         </is>
       </c>
-      <c r="B267" t="inlineStr">
+      <c r="B267" s="10" t="inlineStr">
         <is>
           <t>Innovation Norway — Market Clarification &amp; Innovation Grants</t>
         </is>
       </c>
-      <c r="C267" t="inlineStr">
+      <c r="C267" s="10" t="inlineStr">
         <is>
           <t>Innovation Norway (Innovasjon Norge)</t>
         </is>
       </c>
-      <c r="D267" t="inlineStr">
+      <c r="D267" s="10" t="inlineStr">
         <is>
           <t>Norway (IN)</t>
         </is>
       </c>
-      <c r="E267" t="inlineStr">
+      <c r="E267" s="10" t="inlineStr">
         <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="F267" t="inlineStr">
+      <c r="F267" s="10" t="inlineStr">
         <is>
           <t>Startup funding (all sectors)</t>
         </is>
       </c>
-      <c r="G267" t="inlineStr">
+      <c r="G267" s="10" t="inlineStr">
         <is>
           <t>Pre-seed to growth</t>
         </is>
       </c>
-      <c r="H267" t="inlineStr">
+      <c r="H267" s="10" t="inlineStr">
         <is>
           <t>Norway's state agency funds startups through staged grants: market clarification, commercialisation, and scale-up support.</t>
         </is>
       </c>
-      <c r="I267" t="inlineStr">
+      <c r="I267" s="10" t="inlineStr">
         <is>
           <t>NOK 100k (market clarification) to NOK 1-5M (commercialisation)</t>
         </is>
       </c>
-      <c r="J267" t="inlineStr">
+      <c r="J267" s="10" t="inlineStr">
         <is>
           <t>Staged, project-dependent</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr">
+      <c r="K267" s="10" t="inlineStr">
         <is>
           <t>Norwegian-registered company with growth and international ambition</t>
         </is>
       </c>
-      <c r="L267" t="inlineStr">
+      <c r="L267" s="10" t="inlineStr">
         <is>
           <t>Rolling submission</t>
         </is>
       </c>
-      <c r="M267" t="inlineStr">
+      <c r="M267" s="10" t="inlineStr">
         <is>
           <t>Innovation Norway online portal</t>
         </is>
       </c>
-      <c r="N267" t="inlineStr">
+      <c r="N267" s="10" t="inlineStr">
         <is>
           <t>Yes — adviser meeting</t>
         </is>
       </c>
-      <c r="O267" t="inlineStr">
+      <c r="O267" s="10" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="P267" t="inlineStr">
+      <c r="P267" s="10" t="inlineStr">
         <is>
           <t>https://www.innovasjonnorge.no/en/</t>
         </is>
       </c>
-      <c r="Q267" t="inlineStr">
+      <c r="Q267" s="10" t="inlineStr">
         <is>
           <t>Staged structure means a small first grant is quite achievable and unlocks the larger ones.</t>
         </is>
       </c>
-      <c r="R267" t="inlineStr">
+      <c r="R267" s="10" t="inlineStr">
         <is>
           <t>Pre-seed;Seed;Growth</t>
         </is>
       </c>
-      <c r="S267" t="inlineStr">
+      <c r="S267" s="10" t="inlineStr">
         <is>
           <t>Founded (Norwegian-registered)</t>
         </is>
       </c>
-      <c r="T267" t="inlineStr">
+      <c r="T267" s="10" t="inlineStr">
         <is>
           <t>Grant</t>
         </is>
       </c>
     </row>
     <row r="268">
-      <c r="A268" t="inlineStr">
+      <c r="A268" s="10" t="inlineStr">
         <is>
           <t>G264</t>
         </is>
       </c>
-      <c r="B268" t="inlineStr">
+      <c r="B268" s="10" t="inlineStr">
         <is>
           <t>VLAIO Innovation Funding (Flanders)</t>
         </is>
       </c>
-      <c r="C268" t="inlineStr">
+      <c r="C268" s="10" t="inlineStr">
         <is>
           <t>Flanders Innovation &amp; Entrepreneurship (VLAIO)</t>
         </is>
       </c>
-      <c r="D268" t="inlineStr">
+      <c r="D268" s="10" t="inlineStr">
         <is>
           <t>Belgium (VLAIO)</t>
         </is>
       </c>
-      <c r="E268" t="inlineStr">
+      <c r="E268" s="10" t="inlineStr">
         <is>
           <t>Belgium (Flanders)</t>
         </is>
       </c>
-      <c r="F268" t="inlineStr">
+      <c r="F268" s="10" t="inlineStr">
         <is>
           <t>Startup and R&amp;D funding</t>
         </is>
       </c>
-      <c r="G268" t="inlineStr">
+      <c r="G268" s="10" t="inlineStr">
         <is>
           <t>Startups &amp; SMEs</t>
         </is>
       </c>
-      <c r="H268" t="inlineStr">
+      <c r="H268" s="10" t="inlineStr">
         <is>
           <t>Flanders' agency funds development and research projects for companies, with dedicated instruments for young innovative firms.</t>
         </is>
       </c>
-      <c r="I268" t="inlineStr">
+      <c r="I268" s="10" t="inlineStr">
         <is>
           <t>Development projects €25k-3M (25-60% of costs)</t>
         </is>
       </c>
-      <c r="J268" t="inlineStr">
+      <c r="J268" s="10" t="inlineStr">
         <is>
           <t>1-3 years</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr">
+      <c r="K268" s="10" t="inlineStr">
         <is>
           <t>Company with an operation in Flanders</t>
         </is>
       </c>
-      <c r="L268" t="inlineStr">
+      <c r="L268" s="10" t="inlineStr">
         <is>
           <t>Rolling submission</t>
         </is>
       </c>
-      <c r="M268" t="inlineStr">
+      <c r="M268" s="10" t="inlineStr">
         <is>
           <t>VLAIO online portal</t>
         </is>
       </c>
-      <c r="N268" t="inlineStr">
+      <c r="N268" s="10" t="inlineStr">
         <is>
           <t>Yes — for larger projects</t>
         </is>
       </c>
-      <c r="O268" t="inlineStr">
+      <c r="O268" s="10" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="P268" t="inlineStr">
+      <c r="P268" s="10" t="inlineStr">
         <is>
           <t>https://www.vlaio.be/en</t>
         </is>
       </c>
-      <c r="Q268" t="inlineStr">
+      <c r="Q268" s="10" t="inlineStr">
         <is>
           <t>Also runs innovation mandates that fund a researcher to prepare a spin-off.</t>
         </is>
       </c>
-      <c r="R268" t="inlineStr">
+      <c r="R268" s="10" t="inlineStr">
         <is>
           <t>Pre-seed;Seed;Growth</t>
         </is>
       </c>
-      <c r="S268" t="inlineStr">
+      <c r="S268" s="10" t="inlineStr">
         <is>
           <t>Founded (Flanders-based)</t>
         </is>
       </c>
-      <c r="T268" t="inlineStr">
+      <c r="T268" s="10" t="inlineStr">
         <is>
           <t>Grant</t>
         </is>
       </c>
     </row>
     <row r="269">
-      <c r="A269" t="inlineStr">
+      <c r="A269" s="10" t="inlineStr">
         <is>
           <t>G265</t>
         </is>
       </c>
-      <c r="B269" t="inlineStr">
+      <c r="B269" s="10" t="inlineStr">
         <is>
           <t>EIT Health Accelerator &amp; Innovation Projects</t>
         </is>
       </c>
-      <c r="C269" t="inlineStr">
+      <c r="C269" s="10" t="inlineStr">
         <is>
           <t>EIT Health</t>
         </is>
       </c>
-      <c r="D269" t="inlineStr">
+      <c r="D269" s="10" t="inlineStr">
         <is>
           <t>EIT</t>
         </is>
       </c>
-      <c r="E269" t="inlineStr">
+      <c r="E269" s="10" t="inlineStr">
         <is>
           <t>EU-wide</t>
         </is>
       </c>
-      <c r="F269" t="inlineStr">
+      <c r="F269" s="10" t="inlineStr">
         <is>
           <t>Healthcare &amp; life sciences innovation</t>
         </is>
       </c>
-      <c r="G269" t="inlineStr">
+      <c r="G269" s="10" t="inlineStr">
         <is>
           <t>Startups &amp; scale-ups</t>
         </is>
       </c>
-      <c r="H269" t="inlineStr">
+      <c r="H269" s="10" t="inlineStr">
         <is>
           <t>Europe's largest healthcare innovation network, running accelerator programmes, bootcamps and funded innovation projects for health startups.</t>
         </is>
       </c>
-      <c r="I269" t="inlineStr">
+      <c r="I269" s="10" t="inlineStr">
         <is>
           <t>Programme-dependent (€25k-2M+)</t>
         </is>
       </c>
-      <c r="J269" t="inlineStr">
+      <c r="J269" s="10" t="inlineStr">
         <is>
           <t>Months to 2 years</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr">
+      <c r="K269" s="10" t="inlineStr">
         <is>
           <t>Health/life-science startups and consortia in EU and associated countries</t>
         </is>
       </c>
-      <c r="L269" t="inlineStr">
+      <c r="L269" s="10" t="inlineStr">
         <is>
           <t>Annual calls per programme (check site)</t>
         </is>
       </c>
-      <c r="M269" t="inlineStr">
+      <c r="M269" s="10" t="inlineStr">
         <is>
           <t>EIT Health portal</t>
         </is>
       </c>
-      <c r="N269" t="inlineStr">
+      <c r="N269" s="10" t="inlineStr">
         <is>
           <t>Yes — selection</t>
         </is>
       </c>
-      <c r="O269" t="inlineStr">
+      <c r="O269" s="10" t="inlineStr">
         <is>
           <t>Competitive</t>
         </is>
       </c>
-      <c r="P269" t="inlineStr">
+      <c r="P269" s="10" t="inlineStr">
         <is>
           <t>https://eithealth.eu/</t>
         </is>
       </c>
-      <c r="Q269" t="inlineStr">
+      <c r="Q269" s="10" t="inlineStr">
         <is>
           <t>The most relevant EIT community for biomedical scientists founding companies.</t>
         </is>
       </c>
-      <c r="R269" t="inlineStr">
+      <c r="R269" s="10" t="inlineStr">
         <is>
           <t>Pre-seed;Seed;Growth</t>
         </is>
       </c>
-      <c r="S269" t="inlineStr">
+      <c r="S269" s="10" t="inlineStr">
         <is>
           <t>Founded</t>
         </is>
       </c>
-      <c r="T269" t="inlineStr">
+      <c r="T269" s="10" t="inlineStr">
         <is>
           <t>Grant + acceleration</t>
         </is>
       </c>
     </row>
     <row r="270">
-      <c r="A270" t="inlineStr">
+      <c r="A270" s="10" t="inlineStr">
         <is>
           <t>G266</t>
         </is>
       </c>
-      <c r="B270" t="inlineStr">
+      <c r="B270" s="10" t="inlineStr">
         <is>
           <t>Industry Growth Program (Australia)</t>
         </is>
       </c>
-      <c r="C270" t="inlineStr">
+      <c r="C270" s="10" t="inlineStr">
         <is>
           <t>Australian Government — Department of Industry, Science and Resources</t>
         </is>
       </c>
-      <c r="D270" t="inlineStr">
+      <c r="D270" s="10" t="inlineStr">
         <is>
           <t>Australia (DISR)</t>
         </is>
       </c>
-      <c r="E270" t="inlineStr">
+      <c r="E270" s="10" t="inlineStr">
         <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="F270" t="inlineStr">
+      <c r="F270" s="10" t="inlineStr">
         <is>
           <t>Startup funding (National Reconstruction Fund priorities)</t>
         </is>
       </c>
-      <c r="G270" t="inlineStr">
+      <c r="G270" s="10" t="inlineStr">
         <is>
           <t>Startups &amp; SMEs</t>
         </is>
       </c>
-      <c r="H270" t="inlineStr">
+      <c r="H270" s="10" t="inlineStr">
         <is>
           <t>Australia's flagship commercialisation programme: expert advice plus matched grants for innovative SMEs in national priority areas.</t>
         </is>
       </c>
-      <c r="I270" t="inlineStr">
+      <c r="I270" s="10" t="inlineStr">
         <is>
           <t>Early-stage commercialisation AUD 50k-250k; commercialisation/growth up to AUD 5M (matched)</t>
         </is>
       </c>
-      <c r="J270" t="inlineStr">
+      <c r="J270" s="10" t="inlineStr">
         <is>
           <t>1-2 years</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr">
+      <c r="K270" s="10" t="inlineStr">
         <is>
           <t>Australian company with turnover under AUD 20M, working in a National Reconstruction Fund priority area</t>
         </is>
       </c>
-      <c r="L270" t="inlineStr">
+      <c r="L270" s="10" t="inlineStr">
         <is>
           <t>Rolling (advisor engagement first)</t>
         </is>
       </c>
-      <c r="M270" t="inlineStr">
+      <c r="M270" s="10" t="inlineStr">
         <is>
           <t>business.gov.au portal</t>
         </is>
       </c>
-      <c r="N270" t="inlineStr">
+      <c r="N270" s="10" t="inlineStr">
         <is>
           <t>Yes — advisor assessment</t>
         </is>
       </c>
-      <c r="O270" t="inlineStr">
+      <c r="O270" s="10" t="inlineStr">
         <is>
           <t>Competitive</t>
         </is>
       </c>
-      <c r="P270" t="inlineStr">
+      <c r="P270" s="10" t="inlineStr">
         <is>
           <t>https://business.gov.au/grants-and-programs/industry-growth-program</t>
         </is>
       </c>
-      <c r="Q270" t="inlineStr">
+      <c r="Q270" s="10" t="inlineStr">
         <is>
           <t>Replaced the earlier Accelerating Commercialisation programme; you must engage an Industry Partner adviser first.</t>
         </is>
       </c>
-      <c r="R270" t="inlineStr">
+      <c r="R270" s="10" t="inlineStr">
         <is>
           <t>Pre-seed;Seed;Growth</t>
         </is>
       </c>
-      <c r="S270" t="inlineStr">
+      <c r="S270" s="10" t="inlineStr">
         <is>
           <t>Founded (Australian)</t>
         </is>
       </c>
-      <c r="T270" t="inlineStr">
+      <c r="T270" s="10" t="inlineStr">
         <is>
           <t>Matched grant</t>
         </is>
       </c>
     </row>
     <row r="271">
-      <c r="A271" t="inlineStr">
+      <c r="A271" s="10" t="inlineStr">
         <is>
           <t>G267</t>
         </is>
       </c>
-      <c r="B271" t="inlineStr">
+      <c r="B271" s="10" t="inlineStr">
         <is>
           <t>Australian R&amp;D Tax Incentive</t>
         </is>
       </c>
-      <c r="C271" t="inlineStr">
+      <c r="C271" s="10" t="inlineStr">
         <is>
           <t>Australian Taxation Office &amp; AusIndustry</t>
         </is>
       </c>
-      <c r="D271" t="inlineStr">
+      <c r="D271" s="10" t="inlineStr">
         <is>
           <t>Australia (ATO)</t>
         </is>
       </c>
-      <c r="E271" t="inlineStr">
+      <c r="E271" s="10" t="inlineStr">
         <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="F271" t="inlineStr">
+      <c r="F271" s="10" t="inlineStr">
         <is>
           <t>R&amp;D cost recovery (all sectors)</t>
         </is>
       </c>
-      <c r="G271" t="inlineStr">
+      <c r="G271" s="10" t="inlineStr">
         <is>
           <t>Any company doing R&amp;D</t>
         </is>
       </c>
-      <c r="H271" t="inlineStr">
+      <c r="H271" s="10" t="inlineStr">
         <is>
           <t>Australia's largest innovation programme: a refundable tax offset that returns cash to loss-making startups conducting eligible R&amp;D.</t>
         </is>
       </c>
-      <c r="I271" t="inlineStr">
+      <c r="I271" s="10" t="inlineStr">
         <is>
           <t>43.5% refundable offset for companies under AUD 20M turnover</t>
         </is>
       </c>
-      <c r="J271" t="inlineStr">
+      <c r="J271" s="10" t="inlineStr">
         <is>
           <t>Annual claim</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr">
+      <c r="K271" s="10" t="inlineStr">
         <is>
           <t>Australian company conducting eligible experimental R&amp;D activities</t>
         </is>
       </c>
-      <c r="L271" t="inlineStr">
+      <c r="L271" s="10" t="inlineStr">
         <is>
           <t>Annual registration within 10 months of financial year end</t>
         </is>
       </c>
-      <c r="M271" t="inlineStr">
+      <c r="M271" s="10" t="inlineStr">
         <is>
           <t>AusIndustry portal + tax return</t>
         </is>
       </c>
-      <c r="N271" t="inlineStr">
+      <c r="N271" s="10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="O271" t="inlineStr">
+      <c r="O271" s="10" t="inlineStr">
         <is>
           <t>Very high (if eligible)</t>
         </is>
       </c>
-      <c r="P271" t="inlineStr">
+      <c r="P271" s="10" t="inlineStr">
         <is>
           <t>https://business.gov.au/grants-and-programs/research-and-development-tax-incentive</t>
         </is>
       </c>
-      <c r="Q271" t="inlineStr">
+      <c r="Q271" s="10" t="inlineStr">
         <is>
           <t>For a pre-revenue Australian startup this is often the single biggest source of cash.</t>
         </is>
       </c>
-      <c r="R271" t="inlineStr">
+      <c r="R271" s="10" t="inlineStr">
         <is>
           <t>Pre-seed;Seed;Growth</t>
         </is>
       </c>
-      <c r="S271" t="inlineStr">
+      <c r="S271" s="10" t="inlineStr">
         <is>
           <t>Founded (Australian)</t>
         </is>
       </c>
-      <c r="T271" t="inlineStr">
+      <c r="T271" s="10" t="inlineStr">
         <is>
           <t>Refundable tax offset</t>
         </is>
       </c>
     </row>
     <row r="272">
-      <c r="A272" t="inlineStr">
+      <c r="A272" s="10" t="inlineStr">
         <is>
           <t>G268</t>
         </is>
       </c>
-      <c r="B272" t="inlineStr">
+      <c r="B272" s="10" t="inlineStr">
         <is>
           <t>CSIRO Kick-Start</t>
         </is>
       </c>
-      <c r="C272" t="inlineStr">
+      <c r="C272" s="10" t="inlineStr">
         <is>
           <t>Commonwealth Scientific and Industrial Research Organisation (CSIRO)</t>
         </is>
       </c>
-      <c r="D272" t="inlineStr">
+      <c r="D272" s="10" t="inlineStr">
         <is>
           <t>Australia (CSIRO)</t>
         </is>
       </c>
-      <c r="E272" t="inlineStr">
+      <c r="E272" s="10" t="inlineStr">
         <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="F272" t="inlineStr">
+      <c r="F272" s="10" t="inlineStr">
         <is>
           <t>Research support for startups</t>
         </is>
       </c>
-      <c r="G272" t="inlineStr">
+      <c r="G272" s="10" t="inlineStr">
         <is>
           <t>Early startups &amp; SMEs</t>
         </is>
       </c>
-      <c r="H272" t="inlineStr">
+      <c r="H272" s="10" t="inlineStr">
         <is>
           <t>Provides matched funding for Australian startups to access CSIRO's research expertise and facilities.</t>
         </is>
       </c>
-      <c r="I272" t="inlineStr">
+      <c r="I272" s="10" t="inlineStr">
         <is>
           <t>AUD 10,000-50,000 (dollar-matched)</t>
         </is>
       </c>
-      <c r="J272" t="inlineStr">
+      <c r="J272" s="10" t="inlineStr">
         <is>
           <t>Project-dependent</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr">
+      <c r="K272" s="10" t="inlineStr">
         <is>
           <t>Australian company registered less than 3 years, or turnover under AUD 1.5M</t>
         </is>
       </c>
-      <c r="L272" t="inlineStr">
+      <c r="L272" s="10" t="inlineStr">
         <is>
           <t>Rolling submission</t>
         </is>
       </c>
-      <c r="M272" t="inlineStr">
+      <c r="M272" s="10" t="inlineStr">
         <is>
           <t>CSIRO online application</t>
         </is>
       </c>
-      <c r="N272" t="inlineStr">
+      <c r="N272" s="10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="O272" t="inlineStr">
+      <c r="O272" s="10" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="P272" t="inlineStr">
+      <c r="P272" s="10" t="inlineStr">
         <is>
           <t>https://www.csiro.au/en/work-with-us/funding-programs/programs/kick-start</t>
         </is>
       </c>
-      <c r="Q272" t="inlineStr">
+      <c r="Q272" s="10" t="inlineStr">
         <is>
           <t>Low-friction way to get national-lab-grade research into a young company.</t>
         </is>
       </c>
-      <c r="R272" t="inlineStr">
+      <c r="R272" s="10" t="inlineStr">
         <is>
           <t>Pre-seed;Seed</t>
         </is>
       </c>
-      <c r="S272" t="inlineStr">
+      <c r="S272" s="10" t="inlineStr">
         <is>
           <t>Founded (&lt;3 years)</t>
         </is>
       </c>
-      <c r="T272" t="inlineStr">
+      <c r="T272" s="10" t="inlineStr">
         <is>
           <t>Matched grant</t>
         </is>
       </c>
     </row>
     <row r="273">
-      <c r="A273" t="inlineStr">
+      <c r="A273" s="10" t="inlineStr">
         <is>
           <t>G269</t>
         </is>
       </c>
-      <c r="B273" t="inlineStr">
+      <c r="B273" s="10" t="inlineStr">
         <is>
           <t>Main Sequence Ventures</t>
         </is>
       </c>
-      <c r="C273" t="inlineStr">
+      <c r="C273" s="10" t="inlineStr">
         <is>
           <t>Main Sequence (founded by CSIRO)</t>
         </is>
       </c>
-      <c r="D273" t="inlineStr">
+      <c r="D273" s="10" t="inlineStr">
         <is>
           <t>Australia (Main Sequence)</t>
         </is>
       </c>
-      <c r="E273" t="inlineStr">
+      <c r="E273" s="10" t="inlineStr">
         <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="F273" t="inlineStr">
+      <c r="F273" s="10" t="inlineStr">
         <is>
           <t>Deep tech venture investment</t>
         </is>
       </c>
-      <c r="G273" t="inlineStr">
+      <c r="G273" s="10" t="inlineStr">
         <is>
           <t>Pre-seed to Series B</t>
         </is>
       </c>
-      <c r="H273" t="inlineStr">
+      <c r="H273" s="10" t="inlineStr">
         <is>
           <t>CSIRO-founded deep-tech venture fund investing in Australian science-based companies, often as first institutional money.</t>
         </is>
       </c>
-      <c r="I273" t="inlineStr">
+      <c r="I273" s="10" t="inlineStr">
         <is>
           <t>AUD 500k-20M+ per investment</t>
         </is>
       </c>
-      <c r="J273" t="inlineStr">
+      <c r="J273" s="10" t="inlineStr">
         <is>
           <t>Investment</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr">
+      <c r="K273" s="10" t="inlineStr">
         <is>
           <t>Australian deep-tech companies, frequently research spin-outs</t>
         </is>
       </c>
-      <c r="L273" t="inlineStr">
+      <c r="L273" s="10" t="inlineStr">
         <is>
           <t>Rolling (approach the fund)</t>
         </is>
       </c>
-      <c r="M273" t="inlineStr">
+      <c r="M273" s="10" t="inlineStr">
         <is>
           <t>Direct approach</t>
         </is>
       </c>
-      <c r="N273" t="inlineStr">
+      <c r="N273" s="10" t="inlineStr">
         <is>
           <t>Yes — investment process</t>
         </is>
       </c>
-      <c r="O273" t="inlineStr">
+      <c r="O273" s="10" t="inlineStr">
         <is>
           <t>Selective</t>
         </is>
       </c>
-      <c r="P273" t="inlineStr">
+      <c r="P273" s="10" t="inlineStr">
         <is>
           <t>https://mseq.vc/</t>
         </is>
       </c>
-      <c r="Q273" t="inlineStr">
+      <c r="Q273" s="10" t="inlineStr">
         <is>
           <t>Actively builds companies out of Australian research institutions, not just funds existing ones.</t>
         </is>
       </c>
-      <c r="R273" t="inlineStr">
+      <c r="R273" s="10" t="inlineStr">
         <is>
           <t>Pre-seed;Seed;Growth</t>
         </is>
       </c>
-      <c r="S273" t="inlineStr">
+      <c r="S273" s="10" t="inlineStr">
         <is>
           <t>Founded</t>
         </is>
       </c>
-      <c r="T273" t="inlineStr">
+      <c r="T273" s="10" t="inlineStr">
         <is>
           <t>Equity investment</t>
         </is>
       </c>
     </row>
     <row r="274">
-      <c r="A274" t="inlineStr">
+      <c r="A274" s="10" t="inlineStr">
         <is>
           <t>G270</t>
         </is>
       </c>
-      <c r="B274" t="inlineStr">
+      <c r="B274" s="10" t="inlineStr">
         <is>
           <t>Callaghan Innovation R&amp;D Grants</t>
         </is>
       </c>
-      <c r="C274" t="inlineStr">
+      <c r="C274" s="10" t="inlineStr">
         <is>
           <t>Callaghan Innovation</t>
         </is>
       </c>
-      <c r="D274" t="inlineStr">
+      <c r="D274" s="10" t="inlineStr">
         <is>
           <t>New Zealand (Callaghan)</t>
         </is>
       </c>
-      <c r="E274" t="inlineStr">
+      <c r="E274" s="10" t="inlineStr">
         <is>
           <t>New Zealand</t>
         </is>
       </c>
-      <c r="F274" t="inlineStr">
+      <c r="F274" s="10" t="inlineStr">
         <is>
           <t>Startup and business R&amp;D</t>
         </is>
       </c>
-      <c r="G274" t="inlineStr">
+      <c r="G274" s="10" t="inlineStr">
         <is>
           <t>Startups &amp; established firms</t>
         </is>
       </c>
-      <c r="H274" t="inlineStr">
+      <c r="H274" s="10" t="inlineStr">
         <is>
           <t>New Zealand's innovation agency funds business R&amp;D through Ārohia Trailblazer grants, R&amp;D experience grants and project co-funding.</t>
         </is>
       </c>
-      <c r="I274" t="inlineStr">
+      <c r="I274" s="10" t="inlineStr">
         <is>
           <t>Ārohia up to NZD 4M (matched); student/experience grants smaller</t>
         </is>
       </c>
-      <c r="J274" t="inlineStr">
+      <c r="J274" s="10" t="inlineStr">
         <is>
           <t>1-3 years</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr">
+      <c r="K274" s="10" t="inlineStr">
         <is>
           <t>New Zealand-registered business conducting R&amp;D in New Zealand</t>
         </is>
       </c>
-      <c r="L274" t="inlineStr">
+      <c r="L274" s="10" t="inlineStr">
         <is>
           <t>Periodic rounds (check site)</t>
         </is>
       </c>
-      <c r="M274" t="inlineStr">
+      <c r="M274" s="10" t="inlineStr">
         <is>
           <t>Callaghan Innovation portal</t>
         </is>
       </c>
-      <c r="N274" t="inlineStr">
+      <c r="N274" s="10" t="inlineStr">
         <is>
           <t>Yes — for larger grants</t>
         </is>
       </c>
-      <c r="O274" t="inlineStr">
+      <c r="O274" s="10" t="inlineStr">
         <is>
           <t>Competitive</t>
         </is>
       </c>
-      <c r="P274" t="inlineStr">
+      <c r="P274" s="10" t="inlineStr">
         <is>
           <t>https://www.callaghaninnovation.govt.nz/</t>
         </is>
       </c>
-      <c r="Q274" t="inlineStr">
+      <c r="Q274" s="10" t="inlineStr">
         <is>
           <t>New Zealand also runs a 15% R&amp;D Tax Incentive that most R&amp;D-active startups should claim.</t>
         </is>
       </c>
-      <c r="R274" t="inlineStr">
+      <c r="R274" s="10" t="inlineStr">
         <is>
           <t>Seed;Growth</t>
         </is>
       </c>
-      <c r="S274" t="inlineStr">
+      <c r="S274" s="10" t="inlineStr">
         <is>
           <t>Founded (NZ-registered)</t>
         </is>
       </c>
-      <c r="T274" t="inlineStr">
+      <c r="T274" s="10" t="inlineStr">
         <is>
           <t>Grant (matched)</t>
         </is>
       </c>
     </row>
     <row r="275">
-      <c r="A275" t="inlineStr">
+      <c r="A275" s="10" t="inlineStr">
         <is>
           <t>G271</t>
         </is>
       </c>
-      <c r="B275" t="inlineStr">
+      <c r="B275" s="10" t="inlineStr">
         <is>
           <t>New Zealand R&amp;D Tax Incentive (RDTI)</t>
         </is>
       </c>
-      <c r="C275" t="inlineStr">
+      <c r="C275" s="10" t="inlineStr">
         <is>
           <t>Inland Revenue &amp; Callaghan Innovation</t>
         </is>
       </c>
-      <c r="D275" t="inlineStr">
+      <c r="D275" s="10" t="inlineStr">
         <is>
           <t>New Zealand (RDTI)</t>
         </is>
       </c>
-      <c r="E275" t="inlineStr">
+      <c r="E275" s="10" t="inlineStr">
         <is>
           <t>New Zealand</t>
         </is>
       </c>
-      <c r="F275" t="inlineStr">
+      <c r="F275" s="10" t="inlineStr">
         <is>
           <t>R&amp;D cost recovery (all sectors)</t>
         </is>
       </c>
-      <c r="G275" t="inlineStr">
+      <c r="G275" s="10" t="inlineStr">
         <is>
           <t>Any company doing R&amp;D</t>
         </is>
       </c>
-      <c r="H275" t="inlineStr">
+      <c r="H275" s="10" t="inlineStr">
         <is>
           <t>A 15% tax credit on eligible R&amp;D expenditure, refundable in cash for loss-making companies within limits.</t>
         </is>
       </c>
-      <c r="I275" t="inlineStr">
+      <c r="I275" s="10" t="inlineStr">
         <is>
           <t>15% credit on eligible R&amp;D spend (min NZD 50k/yr)</t>
         </is>
       </c>
-      <c r="J275" t="inlineStr">
+      <c r="J275" s="10" t="inlineStr">
         <is>
           <t>Annual claim</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr">
+      <c r="K275" s="10" t="inlineStr">
         <is>
           <t>New Zealand businesses performing eligible R&amp;D</t>
         </is>
       </c>
-      <c r="L275" t="inlineStr">
+      <c r="L275" s="10" t="inlineStr">
         <is>
           <t>Annual, tied to the tax year (check site)</t>
         </is>
       </c>
-      <c r="M275" t="inlineStr">
+      <c r="M275" s="10" t="inlineStr">
         <is>
           <t>myIR / Callaghan Innovation</t>
         </is>
       </c>
-      <c r="N275" t="inlineStr">
+      <c r="N275" s="10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="O275" t="inlineStr">
+      <c r="O275" s="10" t="inlineStr">
         <is>
           <t>Very high (if eligible)</t>
         </is>
       </c>
-      <c r="P275" t="inlineStr">
+      <c r="P275" s="10" t="inlineStr">
         <is>
           <t>https://www.rdti.govt.nz/</t>
         </is>
       </c>
-      <c r="Q275" t="inlineStr">
+      <c r="Q275" s="10" t="inlineStr">
         <is>
           <t>The baseline support every R&amp;D-active NZ startup should be using.</t>
         </is>
       </c>
-      <c r="R275" t="inlineStr">
+      <c r="R275" s="10" t="inlineStr">
         <is>
           <t>Pre-seed;Seed;Growth</t>
         </is>
       </c>
-      <c r="S275" t="inlineStr">
+      <c r="S275" s="10" t="inlineStr">
         <is>
           <t>Founded (NZ-registered)</t>
         </is>
       </c>
-      <c r="T275" t="inlineStr">
+      <c r="T275" s="10" t="inlineStr">
         <is>
           <t>Tax credit</t>
         </is>
       </c>
     </row>
     <row r="276">
-      <c r="A276" t="inlineStr">
+      <c r="A276" s="10" t="inlineStr">
         <is>
           <t>G272</t>
         </is>
       </c>
-      <c r="B276" t="inlineStr">
+      <c r="B276" s="10" t="inlineStr">
         <is>
           <t>NZ Growth Capital Partners — Aspire Fund</t>
         </is>
       </c>
-      <c r="C276" t="inlineStr">
+      <c r="C276" s="10" t="inlineStr">
         <is>
           <t>New Zealand Growth Capital Partners (NZGCP)</t>
         </is>
       </c>
-      <c r="D276" t="inlineStr">
+      <c r="D276" s="10" t="inlineStr">
         <is>
           <t>New Zealand (NZGCP)</t>
         </is>
       </c>
-      <c r="E276" t="inlineStr">
+      <c r="E276" s="10" t="inlineStr">
         <is>
           <t>New Zealand</t>
         </is>
       </c>
-      <c r="F276" t="inlineStr">
+      <c r="F276" s="10" t="inlineStr">
         <is>
           <t>Early-stage venture investment</t>
         </is>
       </c>
-      <c r="G276" t="inlineStr">
+      <c r="G276" s="10" t="inlineStr">
         <is>
           <t>Pre-seed &amp; seed</t>
         </is>
       </c>
-      <c r="H276" t="inlineStr">
+      <c r="H276" s="10" t="inlineStr">
         <is>
           <t>New Zealand's government-backed early-stage investor, co-investing alongside angels in young New Zealand companies.</t>
         </is>
       </c>
-      <c r="I276" t="inlineStr">
+      <c r="I276" s="10" t="inlineStr">
         <is>
           <t>NZD 250k-2M (co-investment)</t>
         </is>
       </c>
-      <c r="J276" t="inlineStr">
+      <c r="J276" s="10" t="inlineStr">
         <is>
           <t>Investment</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr">
+      <c r="K276" s="10" t="inlineStr">
         <is>
           <t>New Zealand-based startup with a lead private investor</t>
         </is>
       </c>
-      <c r="L276" t="inlineStr">
+      <c r="L276" s="10" t="inlineStr">
         <is>
           <t>Rolling (via investor networks)</t>
         </is>
       </c>
-      <c r="M276" t="inlineStr">
+      <c r="M276" s="10" t="inlineStr">
         <is>
           <t>Direct / via angel network</t>
         </is>
       </c>
-      <c r="N276" t="inlineStr">
+      <c r="N276" s="10" t="inlineStr">
         <is>
           <t>Yes — investment process</t>
         </is>
       </c>
-      <c r="O276" t="inlineStr">
+      <c r="O276" s="10" t="inlineStr">
         <is>
           <t>Selective</t>
         </is>
       </c>
-      <c r="P276" t="inlineStr">
+      <c r="P276" s="10" t="inlineStr">
         <is>
           <t>https://www.nzgcp.co.nz/</t>
         </is>
       </c>
-      <c r="Q276" t="inlineStr">
+      <c r="Q276" s="10" t="inlineStr">
         <is>
           <t>Requires a private lead investor — this is matching capital, not first money.</t>
         </is>
       </c>
-      <c r="R276" t="inlineStr">
+      <c r="R276" s="10" t="inlineStr">
         <is>
           <t>Pre-seed;Seed</t>
         </is>
       </c>
-      <c r="S276" t="inlineStr">
+      <c r="S276" s="10" t="inlineStr">
         <is>
           <t>Founded (NZ-registered)</t>
         </is>
       </c>
-      <c r="T276" t="inlineStr">
+      <c r="T276" s="10" t="inlineStr">
         <is>
           <t>Equity co-investment</t>
         </is>
       </c>
     </row>
     <row r="277">
-      <c r="A277" t="inlineStr">
+      <c r="A277" s="10" t="inlineStr">
         <is>
           <t>G273</t>
         </is>
       </c>
-      <c r="B277" t="inlineStr">
+      <c r="B277" s="10" t="inlineStr">
         <is>
           <t>NEDO Entrepreneurs Programme (NEP) &amp; Deep Tech Startup Support</t>
         </is>
       </c>
-      <c r="C277" t="inlineStr">
+      <c r="C277" s="10" t="inlineStr">
         <is>
           <t>New Energy and Industrial Technology Development Organization (NEDO)</t>
         </is>
       </c>
-      <c r="D277" t="inlineStr">
+      <c r="D277" s="10" t="inlineStr">
         <is>
           <t>Japan (NEDO)</t>
         </is>
       </c>
-      <c r="E277" t="inlineStr">
+      <c r="E277" s="10" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="F277" t="inlineStr">
+      <c r="F277" s="10" t="inlineStr">
         <is>
           <t>Deep tech &amp; energy startup funding</t>
         </is>
       </c>
-      <c r="G277" t="inlineStr">
+      <c r="G277" s="10" t="inlineStr">
         <is>
           <t>Researchers &amp; startups</t>
         </is>
       </c>
-      <c r="H277" t="inlineStr">
+      <c r="H277" s="10" t="inlineStr">
         <is>
           <t>Japan's main technology development agency funds deep-tech entrepreneurs from pre-company research through to large-scale development.</t>
         </is>
       </c>
-      <c r="I277" t="inlineStr">
+      <c r="I277" s="10" t="inlineStr">
         <is>
           <t>NEP up to ¥10M-40M; deep-tech programmes up to ¥2bn for later stages</t>
         </is>
       </c>
-      <c r="J277" t="inlineStr">
+      <c r="J277" s="10" t="inlineStr">
         <is>
           <t>6 months-5 years</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr">
+      <c r="K277" s="10" t="inlineStr">
         <is>
           <t>Individuals or companies developing technology in Japan; programme-specific criteria</t>
         </is>
       </c>
-      <c r="L277" t="inlineStr">
+      <c r="L277" s="10" t="inlineStr">
         <is>
           <t>Annual calls per programme (check site)</t>
         </is>
       </c>
-      <c r="M277" t="inlineStr">
+      <c r="M277" s="10" t="inlineStr">
         <is>
           <t>NEDO online application</t>
         </is>
       </c>
-      <c r="N277" t="inlineStr">
+      <c r="N277" s="10" t="inlineStr">
         <is>
           <t>Yes — selection</t>
         </is>
       </c>
-      <c r="O277" t="inlineStr">
+      <c r="O277" s="10" t="inlineStr">
         <is>
           <t>Competitive</t>
         </is>
       </c>
-      <c r="P277" t="inlineStr">
+      <c r="P277" s="10" t="inlineStr">
         <is>
           <t>https://www.nedo.go.jp/english/</t>
         </is>
       </c>
-      <c r="Q277" t="inlineStr">
+      <c r="Q277" s="10" t="inlineStr">
         <is>
           <t>The Entrepreneurs Programme (NEP) supports individuals before a company exists — the natural first step.</t>
         </is>
       </c>
-      <c r="R277" t="inlineStr">
+      <c r="R277" s="10" t="inlineStr">
         <is>
           <t>Pre-seed;Seed;Growth</t>
         </is>
       </c>
-      <c r="S277" t="inlineStr">
+      <c r="S277" s="10" t="inlineStr">
         <is>
           <t>Not yet founded / founded</t>
         </is>
       </c>
-      <c r="T277" t="inlineStr">
+      <c r="T277" s="10" t="inlineStr">
         <is>
           <t>Grant</t>
         </is>
       </c>
     </row>
     <row r="278">
-      <c r="A278" t="inlineStr">
+      <c r="A278" s="10" t="inlineStr">
         <is>
           <t>G274</t>
         </is>
       </c>
-      <c r="B278" t="inlineStr">
+      <c r="B278" s="10" t="inlineStr">
         <is>
           <t>JST START (University Startup Support)</t>
         </is>
       </c>
-      <c r="C278" t="inlineStr">
+      <c r="C278" s="10" t="inlineStr">
         <is>
           <t>Japan Science and Technology Agency (JST)</t>
         </is>
       </c>
-      <c r="D278" t="inlineStr">
+      <c r="D278" s="10" t="inlineStr">
         <is>
           <t>Japan (JST)</t>
         </is>
       </c>
-      <c r="E278" t="inlineStr">
+      <c r="E278" s="10" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="F278" t="inlineStr">
+      <c r="F278" s="10" t="inlineStr">
         <is>
           <t>University spin-off support</t>
         </is>
       </c>
-      <c r="G278" t="inlineStr">
+      <c r="G278" s="10" t="inlineStr">
         <is>
           <t>Researchers pre-company</t>
         </is>
       </c>
-      <c r="H278" t="inlineStr">
+      <c r="H278" s="10" t="inlineStr">
         <is>
           <t>Funds university researchers, together with a business promotion organisation, to develop research results toward a startup.</t>
         </is>
       </c>
-      <c r="I278" t="inlineStr">
+      <c r="I278" s="10" t="inlineStr">
         <is>
           <t>¥10M-40M per project (project promotion type)</t>
         </is>
       </c>
-      <c r="J278" t="inlineStr">
+      <c r="J278" s="10" t="inlineStr">
         <is>
           <t>1-3 years</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr">
+      <c r="K278" s="10" t="inlineStr">
         <is>
           <t>Researchers at Japanese universities with commercialisable results; business partner required</t>
         </is>
       </c>
-      <c r="L278" t="inlineStr">
+      <c r="L278" s="10" t="inlineStr">
         <is>
           <t>Annual call (typically ~spring; check site)</t>
         </is>
       </c>
-      <c r="M278" t="inlineStr">
+      <c r="M278" s="10" t="inlineStr">
         <is>
           <t>JST e-Rad application</t>
         </is>
       </c>
-      <c r="N278" t="inlineStr">
+      <c r="N278" s="10" t="inlineStr">
         <is>
           <t>Yes — interview</t>
         </is>
       </c>
-      <c r="O278" t="inlineStr">
+      <c r="O278" s="10" t="inlineStr">
         <is>
           <t>Competitive</t>
         </is>
       </c>
-      <c r="P278" t="inlineStr">
+      <c r="P278" s="10" t="inlineStr">
         <is>
           <t>https://www.jst.go.jp/start/en/</t>
         </is>
       </c>
-      <c r="Q278" t="inlineStr">
+      <c r="Q278" s="10" t="inlineStr">
         <is>
           <t>Japan's closest equivalent to EXIST or the Commercialisation Fund.</t>
         </is>
       </c>
-      <c r="R278" t="inlineStr">
+      <c r="R278" s="10" t="inlineStr">
         <is>
           <t>Pre-seed</t>
         </is>
       </c>
-      <c r="S278" t="inlineStr">
+      <c r="S278" s="10" t="inlineStr">
         <is>
           <t>Not yet founded</t>
         </is>
       </c>
-      <c r="T278" t="inlineStr">
+      <c r="T278" s="10" t="inlineStr">
         <is>
           <t>Grant</t>
         </is>
       </c>
     </row>
     <row r="279">
-      <c r="A279" t="inlineStr">
+      <c r="A279" s="10" t="inlineStr">
         <is>
           <t>G275</t>
         </is>
       </c>
-      <c r="B279" t="inlineStr">
+      <c r="B279" s="10" t="inlineStr">
         <is>
           <t>J-Startup</t>
         </is>
       </c>
-      <c r="C279" t="inlineStr">
+      <c r="C279" s="10" t="inlineStr">
         <is>
           <t>Ministry of Economy, Trade and Industry (METI)</t>
         </is>
       </c>
-      <c r="D279" t="inlineStr">
+      <c r="D279" s="10" t="inlineStr">
         <is>
           <t>Japan (METI)</t>
         </is>
       </c>
-      <c r="E279" t="inlineStr">
+      <c r="E279" s="10" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="F279" t="inlineStr">
+      <c r="F279" s="10" t="inlineStr">
         <is>
           <t>Startup endorsement &amp; support</t>
         </is>
       </c>
-      <c r="G279" t="inlineStr">
+      <c r="G279" s="10" t="inlineStr">
         <is>
           <t>High-potential startups</t>
         </is>
       </c>
-      <c r="H279" t="inlineStr">
+      <c r="H279" s="10" t="inlineStr">
         <is>
           <t>Government endorsement programme giving selected Japanese startups access to support, showcases and introductions rather than direct cash.</t>
         </is>
       </c>
-      <c r="I279" t="inlineStr">
+      <c r="I279" s="10" t="inlineStr">
         <is>
           <t>No direct grant — support, exposure and priority access</t>
         </is>
       </c>
-      <c r="J279" t="inlineStr">
+      <c r="J279" s="10" t="inlineStr">
         <is>
           <t>Ongoing status</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr">
+      <c r="K279" s="10" t="inlineStr">
         <is>
           <t>Selected Japanese startups; nomination by recommenders</t>
         </is>
       </c>
-      <c r="L279" t="inlineStr">
+      <c r="L279" s="10" t="inlineStr">
         <is>
           <t>Selection rounds (check site)</t>
         </is>
       </c>
-      <c r="M279" t="inlineStr">
+      <c r="M279" s="10" t="inlineStr">
         <is>
           <t>Nomination-based</t>
         </is>
       </c>
-      <c r="N279" t="inlineStr">
+      <c r="N279" s="10" t="inlineStr">
         <is>
           <t>Yes — selection committee</t>
         </is>
       </c>
-      <c r="O279" t="inlineStr">
+      <c r="O279" s="10" t="inlineStr">
         <is>
           <t>Very selective</t>
         </is>
       </c>
-      <c r="P279" t="inlineStr">
+      <c r="P279" s="10" t="inlineStr">
         <is>
           <t>https://www.j-startup.go.jp/en/</t>
         </is>
       </c>
-      <c r="Q279" t="inlineStr">
+      <c r="Q279" s="10" t="inlineStr">
         <is>
           <t>Status rather than money, but it opens doors to Japanese corporates and other programmes.</t>
         </is>
       </c>
-      <c r="R279" t="inlineStr">
+      <c r="R279" s="10" t="inlineStr">
         <is>
           <t>Seed;Growth</t>
         </is>
       </c>
-      <c r="S279" t="inlineStr">
+      <c r="S279" s="10" t="inlineStr">
         <is>
           <t>Founded</t>
         </is>
       </c>
-      <c r="T279" t="inlineStr">
+      <c r="T279" s="10" t="inlineStr">
         <is>
           <t>Endorsement + support</t>
         </is>
       </c>
     </row>
     <row r="280">
-      <c r="A280" t="inlineStr">
+      <c r="A280" s="10" t="inlineStr">
         <is>
           <t>G276</t>
         </is>
       </c>
-      <c r="B280" t="inlineStr">
+      <c r="B280" s="10" t="inlineStr">
         <is>
           <t>TIPS (Tech Incubator Program for Startups)</t>
         </is>
       </c>
-      <c r="C280" t="inlineStr">
+      <c r="C280" s="10" t="inlineStr">
         <is>
           <t>Korean Ministry of SMEs and Startups (MSS)</t>
         </is>
       </c>
-      <c r="D280" t="inlineStr">
+      <c r="D280" s="10" t="inlineStr">
         <is>
           <t>Korea (TIPS)</t>
         </is>
       </c>
-      <c r="E280" t="inlineStr">
+      <c r="E280" s="10" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="F280" t="inlineStr">
+      <c r="F280" s="10" t="inlineStr">
         <is>
           <t>Deep tech startup funding</t>
         </is>
       </c>
-      <c r="G280" t="inlineStr">
+      <c r="G280" s="10" t="inlineStr">
         <is>
           <t>Seed-stage startups</t>
         </is>
       </c>
-      <c r="H280" t="inlineStr">
+      <c r="H280" s="10" t="inlineStr">
         <is>
           <t>Korea's flagship startup programme: a private accelerator invests, and the government matches with a much larger R&amp;D grant.</t>
         </is>
       </c>
-      <c r="I280" t="inlineStr">
+      <c r="I280" s="10" t="inlineStr">
         <is>
           <t>Up to ₩500M R&amp;D grant (plus ~₩100M+ private investment) — extensions to ₩1.5bn</t>
         </is>
       </c>
-      <c r="J280" t="inlineStr">
+      <c r="J280" s="10" t="inlineStr">
         <is>
           <t>2-3 years</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr">
+      <c r="K280" s="10" t="inlineStr">
         <is>
           <t>Korean startup under 7 years old, selected and invested in by a TIPS operator</t>
         </is>
       </c>
-      <c r="L280" t="inlineStr">
+      <c r="L280" s="10" t="inlineStr">
         <is>
           <t>Rolling via TIPS operators</t>
         </is>
       </c>
-      <c r="M280" t="inlineStr">
+      <c r="M280" s="10" t="inlineStr">
         <is>
           <t>Apply to a TIPS operator (accelerator)</t>
         </is>
       </c>
-      <c r="N280" t="inlineStr">
+      <c r="N280" s="10" t="inlineStr">
         <is>
           <t>Yes — operator and MSS review</t>
         </is>
       </c>
-      <c r="O280" t="inlineStr">
+      <c r="O280" s="10" t="inlineStr">
         <is>
           <t>Competitive</t>
         </is>
       </c>
-      <c r="P280" t="inlineStr">
+      <c r="P280" s="10" t="inlineStr">
         <is>
           <t>https://www.jointips.or.kr/</t>
         </is>
       </c>
-      <c r="Q280" t="inlineStr">
+      <c r="Q280" s="10" t="inlineStr">
         <is>
           <t>You cannot apply directly to the government — you must first be backed by an accredited TIPS operator.</t>
         </is>
       </c>
-      <c r="R280" t="inlineStr">
+      <c r="R280" s="10" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="S280" t="inlineStr">
+      <c r="S280" s="10" t="inlineStr">
         <is>
           <t>Founded (&lt;7 years)</t>
         </is>
       </c>
-      <c r="T280" t="inlineStr">
+      <c r="T280" s="10" t="inlineStr">
         <is>
           <t>Grant (matched to private investment)</t>
         </is>
       </c>
     </row>
     <row r="281">
-      <c r="A281" t="inlineStr">
+      <c r="A281" s="10" t="inlineStr">
         <is>
           <t>G277</t>
         </is>
       </c>
-      <c r="B281" t="inlineStr">
+      <c r="B281" s="10" t="inlineStr">
         <is>
           <t>K-Startup Grand Challenge</t>
         </is>
       </c>
-      <c r="C281" t="inlineStr">
+      <c r="C281" s="10" t="inlineStr">
         <is>
           <t>National IT Industry Promotion Agency (NIPA), Korea</t>
         </is>
       </c>
-      <c r="D281" t="inlineStr">
+      <c r="D281" s="10" t="inlineStr">
         <is>
           <t>Korea (NIPA)</t>
         </is>
       </c>
-      <c r="E281" t="inlineStr">
+      <c r="E281" s="10" t="inlineStr">
         <is>
           <t>South Korea (incoming)</t>
         </is>
       </c>
-      <c r="F281" t="inlineStr">
+      <c r="F281" s="10" t="inlineStr">
         <is>
           <t>Startup acceleration (international founders)</t>
         </is>
       </c>
-      <c r="G281" t="inlineStr">
+      <c r="G281" s="10" t="inlineStr">
         <is>
           <t>Early-stage international startups</t>
         </is>
       </c>
-      <c r="H281" t="inlineStr">
+      <c r="H281" s="10" t="inlineStr">
         <is>
           <t>Korea's flagship programme for foreign startups: a fully funded 3-month acceleration in Korea, with visas, stipend and follow-on funding for top teams.</t>
         </is>
       </c>
-      <c r="I281" t="inlineStr">
+      <c r="I281" s="10" t="inlineStr">
         <is>
           <t>~KRW 20M+ settlement support during the programme; additional grants for winners</t>
         </is>
       </c>
-      <c r="J281" t="inlineStr">
+      <c r="J281" s="10" t="inlineStr">
         <is>
           <t>3-6 months</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr">
+      <c r="K281" s="10" t="inlineStr">
         <is>
           <t>Non-Korean startups with at least one founder able to relocate to Korea</t>
         </is>
       </c>
-      <c r="L281" t="inlineStr">
+      <c r="L281" s="10" t="inlineStr">
         <is>
           <t>Annual call (typically ~Mar-May; check site)</t>
         </is>
       </c>
-      <c r="M281" t="inlineStr">
+      <c r="M281" s="10" t="inlineStr">
         <is>
           <t>K-Startup Grand Challenge portal</t>
         </is>
       </c>
-      <c r="N281" t="inlineStr">
+      <c r="N281" s="10" t="inlineStr">
         <is>
           <t>Yes — pitch selection</t>
         </is>
       </c>
-      <c r="O281" t="inlineStr">
+      <c r="O281" s="10" t="inlineStr">
         <is>
           <t>~2-5%</t>
         </is>
       </c>
-      <c r="P281" t="inlineStr">
+      <c r="P281" s="10" t="inlineStr">
         <is>
           <t>https://www.k-startupgc.org/</t>
         </is>
       </c>
-      <c r="Q281" t="inlineStr">
+      <c r="Q281" s="10" t="inlineStr">
         <is>
           <t>One of the few Asian programmes explicitly designed for foreign founders, including visa support.</t>
         </is>
       </c>
-      <c r="R281" t="inlineStr">
+      <c r="R281" s="10" t="inlineStr">
         <is>
           <t>Pre-seed;Seed</t>
         </is>
       </c>
-      <c r="S281" t="inlineStr">
+      <c r="S281" s="10" t="inlineStr">
         <is>
           <t>Founded</t>
         </is>
       </c>
-      <c r="T281" t="inlineStr">
+      <c r="T281" s="10" t="inlineStr">
         <is>
           <t>Grant + acceleration</t>
         </is>
       </c>
     </row>
     <row r="282">
-      <c r="A282" t="inlineStr">
+      <c r="A282" s="10" t="inlineStr">
         <is>
           <t>G278</t>
         </is>
       </c>
-      <c r="B282" t="inlineStr">
+      <c r="B282" s="10" t="inlineStr">
         <is>
           <t>Korean Government Startup Support (K-Startup / KISED)</t>
         </is>
       </c>
-      <c r="C282" t="inlineStr">
+      <c r="C282" s="10" t="inlineStr">
         <is>
           <t>Korea Institute of Startup and Entrepreneurship Development (KISED)</t>
         </is>
       </c>
-      <c r="D282" t="inlineStr">
+      <c r="D282" s="10" t="inlineStr">
         <is>
           <t>Korea (KISED)</t>
         </is>
       </c>
-      <c r="E282" t="inlineStr">
+      <c r="E282" s="10" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="F282" t="inlineStr">
+      <c r="F282" s="10" t="inlineStr">
         <is>
           <t>Startup funding (all sectors)</t>
         </is>
       </c>
-      <c r="G282" t="inlineStr">
+      <c r="G282" s="10" t="inlineStr">
         <is>
           <t>Pre-founding to growth</t>
         </is>
       </c>
-      <c r="H282" t="inlineStr">
+      <c r="H282" s="10" t="inlineStr">
         <is>
           <t>Umbrella for Korea's national startup programmes, including pre-startup packages, early-stage packages and scale-up support.</t>
         </is>
       </c>
-      <c r="I282" t="inlineStr">
+      <c r="I282" s="10" t="inlineStr">
         <is>
           <t>Pre-startup package up to ₩100M; early-stage packages up to ₩100M+</t>
         </is>
       </c>
-      <c r="J282" t="inlineStr">
+      <c r="J282" s="10" t="inlineStr">
         <is>
           <t>~1 year per programme</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr">
+      <c r="K282" s="10" t="inlineStr">
         <is>
           <t>Korean-registered startups; some tracks open to foreign residents in Korea</t>
         </is>
       </c>
-      <c r="L282" t="inlineStr">
+      <c r="L282" s="10" t="inlineStr">
         <is>
           <t>Annual calls, mostly ~Jan-Mar (check site)</t>
         </is>
       </c>
-      <c r="M282" t="inlineStr">
+      <c r="M282" s="10" t="inlineStr">
         <is>
           <t>K-Startup portal (k-startup.go.kr)</t>
         </is>
       </c>
-      <c r="N282" t="inlineStr">
+      <c r="N282" s="10" t="inlineStr">
         <is>
           <t>Yes — pitch for most tracks</t>
         </is>
       </c>
-      <c r="O282" t="inlineStr">
+      <c r="O282" s="10" t="inlineStr">
         <is>
           <t>Competitive</t>
         </is>
       </c>
-      <c r="P282" t="inlineStr">
+      <c r="P282" s="10" t="inlineStr">
         <is>
           <t>https://www.k-startup.go.kr/</t>
         </is>
       </c>
-      <c r="Q282" t="inlineStr">
+      <c r="Q282" s="10" t="inlineStr">
         <is>
           <t>Most application materials are in Korean; a Korean co-founder or partner makes this far more feasible.</t>
         </is>
       </c>
-      <c r="R282" t="inlineStr">
+      <c r="R282" s="10" t="inlineStr">
         <is>
           <t>Pre-seed;Seed;Growth</t>
         </is>
       </c>
-      <c r="S282" t="inlineStr">
+      <c r="S282" s="10" t="inlineStr">
         <is>
           <t>Not yet founded / founded</t>
         </is>
       </c>
-      <c r="T282" t="inlineStr">
+      <c r="T282" s="10" t="inlineStr">
         <is>
           <t>Grant</t>
         </is>
       </c>
     </row>
     <row r="283">
-      <c r="A283" t="inlineStr">
+      <c r="A283" s="10" t="inlineStr">
         <is>
           <t>G279</t>
         </is>
       </c>
-      <c r="B283" t="inlineStr">
+      <c r="B283" s="10" t="inlineStr">
         <is>
           <t>Startup SG Founder &amp; Startup SG Tech</t>
         </is>
       </c>
-      <c r="C283" t="inlineStr">
+      <c r="C283" s="10" t="inlineStr">
         <is>
           <t>Enterprise Singapore</t>
         </is>
       </c>
-      <c r="D283" t="inlineStr">
+      <c r="D283" s="10" t="inlineStr">
         <is>
           <t>Singapore (EnterpriseSG)</t>
         </is>
       </c>
-      <c r="E283" t="inlineStr">
+      <c r="E283" s="10" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="F283" t="inlineStr">
+      <c r="F283" s="10" t="inlineStr">
         <is>
           <t>Startup funding (all sectors, deep tech track)</t>
         </is>
       </c>
-      <c r="G283" t="inlineStr">
+      <c r="G283" s="10" t="inlineStr">
         <is>
           <t>First-time founders to growth</t>
         </is>
       </c>
-      <c r="H283" t="inlineStr">
+      <c r="H283" s="10" t="inlineStr">
         <is>
           <t>Singapore's national startup programme: mentorship plus capital for first-time founders, and proof-of-concept/value grants for deep tech.</t>
         </is>
       </c>
-      <c r="I283" t="inlineStr">
+      <c r="I283" s="10" t="inlineStr">
         <is>
           <t>Founder: up to SGD 50k (matched 3:1); Tech: POC up to SGD 250k, POV up to SGD 500k</t>
         </is>
       </c>
-      <c r="J283" t="inlineStr">
+      <c r="J283" s="10" t="inlineStr">
         <is>
           <t>1-2 years</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr">
+      <c r="K283" s="10" t="inlineStr">
         <is>
           <t>Singapore-registered company, at least 30% local shareholding for several schemes</t>
         </is>
       </c>
-      <c r="L283" t="inlineStr">
+      <c r="L283" s="10" t="inlineStr">
         <is>
           <t>Rolling via Accredited Mentor Partners / EnterpriseSG</t>
         </is>
       </c>
-      <c r="M283" t="inlineStr">
+      <c r="M283" s="10" t="inlineStr">
         <is>
           <t>Via AMP or EnterpriseSG portal</t>
         </is>
       </c>
-      <c r="N283" t="inlineStr">
+      <c r="N283" s="10" t="inlineStr">
         <is>
           <t>Yes — mentor partner selection</t>
         </is>
       </c>
-      <c r="O283" t="inlineStr">
+      <c r="O283" s="10" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="P283" t="inlineStr">
+      <c r="P283" s="10" t="inlineStr">
         <is>
           <t>https://www.enterprisesg.gov.sg/</t>
         </is>
       </c>
-      <c r="Q283" t="inlineStr">
+      <c r="Q283" s="10" t="inlineStr">
         <is>
           <t>Startup SG Tech is proof-of-concept money for genuinely deep technology — well suited to research spin-offs.</t>
         </is>
       </c>
-      <c r="R283" t="inlineStr">
+      <c r="R283" s="10" t="inlineStr">
         <is>
           <t>Pre-seed;Seed</t>
         </is>
       </c>
-      <c r="S283" t="inlineStr">
+      <c r="S283" s="10" t="inlineStr">
         <is>
           <t>Founded (Singapore-registered)</t>
         </is>
       </c>
-      <c r="T283" t="inlineStr">
+      <c r="T283" s="10" t="inlineStr">
         <is>
           <t>Grant (matched)</t>
         </is>
       </c>
     </row>
     <row r="284">
-      <c r="A284" t="inlineStr">
+      <c r="A284" s="10" t="inlineStr">
         <is>
           <t>G280</t>
         </is>
       </c>
-      <c r="B284" t="inlineStr">
+      <c r="B284" s="10" t="inlineStr">
         <is>
           <t>SGInnovate Deep Tech Programmes</t>
         </is>
       </c>
-      <c r="C284" t="inlineStr">
+      <c r="C284" s="10" t="inlineStr">
         <is>
           <t>SGInnovate</t>
         </is>
       </c>
-      <c r="D284" t="inlineStr">
+      <c r="D284" s="10" t="inlineStr">
         <is>
           <t>Singapore (SGInnovate)</t>
         </is>
       </c>
-      <c r="E284" t="inlineStr">
+      <c r="E284" s="10" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="F284" t="inlineStr">
+      <c r="F284" s="10" t="inlineStr">
         <is>
           <t>Deep tech venture building</t>
         </is>
       </c>
-      <c r="G284" t="inlineStr">
+      <c r="G284" s="10" t="inlineStr">
         <is>
           <t>Researchers &amp; deep tech startups</t>
         </is>
       </c>
-      <c r="H284" t="inlineStr">
+      <c r="H284" s="10" t="inlineStr">
         <is>
           <t>Singapore government-owned deep-tech venture builder that invests in and supports science-based companies, plus talent programmes for researchers.</t>
         </is>
       </c>
-      <c r="I284" t="inlineStr">
+      <c r="I284" s="10" t="inlineStr">
         <is>
           <t>Investment tickets typically SGD 250k-2M; talent programmes vary</t>
         </is>
       </c>
-      <c r="J284" t="inlineStr">
+      <c r="J284" s="10" t="inlineStr">
         <is>
           <t>Investment / programme-dependent</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr">
+      <c r="K284" s="10" t="inlineStr">
         <is>
           <t>Deep-tech companies with a Singapore nexus; researchers for talent programmes</t>
         </is>
       </c>
-      <c r="L284" t="inlineStr">
+      <c r="L284" s="10" t="inlineStr">
         <is>
           <t>Rolling (approach directly)</t>
         </is>
       </c>
-      <c r="M284" t="inlineStr">
+      <c r="M284" s="10" t="inlineStr">
         <is>
           <t>SGInnovate application</t>
         </is>
       </c>
-      <c r="N284" t="inlineStr">
+      <c r="N284" s="10" t="inlineStr">
         <is>
           <t>Yes — investment process</t>
         </is>
       </c>
-      <c r="O284" t="inlineStr">
+      <c r="O284" s="10" t="inlineStr">
         <is>
           <t>Selective</t>
         </is>
       </c>
-      <c r="P284" t="inlineStr">
+      <c r="P284" s="10" t="inlineStr">
         <is>
           <t>https://www.sginnovate.com/</t>
         </is>
       </c>
-      <c r="Q284" t="inlineStr">
+      <c r="Q284" s="10" t="inlineStr">
         <is>
           <t>Also runs Summation and talent programmes that place researchers into deep-tech startups.</t>
         </is>
       </c>
-      <c r="R284" t="inlineStr">
+      <c r="R284" s="10" t="inlineStr">
         <is>
           <t>Pre-seed;Seed</t>
         </is>
       </c>
-      <c r="S284" t="inlineStr">
+      <c r="S284" s="10" t="inlineStr">
         <is>
           <t>Not yet founded / founded</t>
         </is>
       </c>
-      <c r="T284" t="inlineStr">
+      <c r="T284" s="10" t="inlineStr">
         <is>
           <t>Equity + programmes</t>
         </is>
       </c>
     </row>
     <row r="285">
-      <c r="A285" t="inlineStr">
+      <c r="A285" s="10" t="inlineStr">
         <is>
           <t>G281</t>
         </is>
       </c>
-      <c r="B285" t="inlineStr">
+      <c r="B285" s="10" t="inlineStr">
         <is>
           <t>HKSTP Incubation Programmes (Incu-Tech / Incu-Bio)</t>
         </is>
       </c>
-      <c r="C285" t="inlineStr">
+      <c r="C285" s="10" t="inlineStr">
         <is>
           <t>Hong Kong Science and Technology Parks Corporation (HKSTP)</t>
         </is>
       </c>
-      <c r="D285" t="inlineStr">
+      <c r="D285" s="10" t="inlineStr">
         <is>
           <t>Hong Kong (HKSTP)</t>
         </is>
       </c>
-      <c r="E285" t="inlineStr">
+      <c r="E285" s="10" t="inlineStr">
         <is>
           <t>Hong Kong</t>
         </is>
       </c>
-      <c r="F285" t="inlineStr">
+      <c r="F285" s="10" t="inlineStr">
         <is>
           <t>Deep tech &amp; biotech incubation</t>
         </is>
       </c>
-      <c r="G285" t="inlineStr">
+      <c r="G285" s="10" t="inlineStr">
         <is>
           <t>Pre-seed &amp; seed startups</t>
         </is>
       </c>
-      <c r="H285" t="inlineStr">
+      <c r="H285" s="10" t="inlineStr">
         <is>
           <t>Hong Kong's flagship incubation programmes providing funding, subsidised lab and office space, and support for technology and biomedical startups.</t>
         </is>
       </c>
-      <c r="I285" t="inlineStr">
+      <c r="I285" s="10" t="inlineStr">
         <is>
           <t>Up to HKD 1.29M (Incu-Tech) / HKD 6M (Incu-Bio) in financial support</t>
         </is>
       </c>
-      <c r="J285" t="inlineStr">
+      <c r="J285" s="10" t="inlineStr">
         <is>
           <t>3-4 years incubation</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr">
+      <c r="K285" s="10" t="inlineStr">
         <is>
           <t>Startup incorporated in Hong Kong, typically under 5 years old</t>
         </is>
       </c>
-      <c r="L285" t="inlineStr">
+      <c r="L285" s="10" t="inlineStr">
         <is>
           <t>Rolling application rounds (check site)</t>
         </is>
       </c>
-      <c r="M285" t="inlineStr">
+      <c r="M285" s="10" t="inlineStr">
         <is>
           <t>HKSTP online application</t>
         </is>
       </c>
-      <c r="N285" t="inlineStr">
+      <c r="N285" s="10" t="inlineStr">
         <is>
           <t>Yes — assessment panel</t>
         </is>
       </c>
-      <c r="O285" t="inlineStr">
+      <c r="O285" s="10" t="inlineStr">
         <is>
           <t>Competitive</t>
         </is>
       </c>
-      <c r="P285" t="inlineStr">
+      <c r="P285" s="10" t="inlineStr">
         <is>
           <t>https://www.hkstp.org/</t>
         </is>
       </c>
-      <c r="Q285" t="inlineStr">
+      <c r="Q285" s="10" t="inlineStr">
         <is>
           <t>Incu-Bio includes access to shared wet-lab facilities — rare and expensive to replicate.</t>
         </is>
       </c>
-      <c r="R285" t="inlineStr">
+      <c r="R285" s="10" t="inlineStr">
         <is>
           <t>Pre-seed;Seed</t>
         </is>
       </c>
-      <c r="S285" t="inlineStr">
+      <c r="S285" s="10" t="inlineStr">
         <is>
           <t>Founded (HK-incorporated)</t>
         </is>
       </c>
-      <c r="T285" t="inlineStr">
+      <c r="T285" s="10" t="inlineStr">
         <is>
           <t>Grant + incubation</t>
         </is>
       </c>
     </row>
     <row r="286">
-      <c r="A286" t="inlineStr">
+      <c r="A286" s="10" t="inlineStr">
         <is>
           <t>G282</t>
         </is>
       </c>
-      <c r="B286" t="inlineStr">
+      <c r="B286" s="10" t="inlineStr">
         <is>
           <t>Cyberport Incubation Programme</t>
         </is>
       </c>
-      <c r="C286" t="inlineStr">
+      <c r="C286" s="10" t="inlineStr">
         <is>
           <t>Hong Kong Cyberport Management Company</t>
         </is>
       </c>
-      <c r="D286" t="inlineStr">
+      <c r="D286" s="10" t="inlineStr">
         <is>
           <t>Hong Kong (Cyberport)</t>
         </is>
       </c>
-      <c r="E286" t="inlineStr">
+      <c r="E286" s="10" t="inlineStr">
         <is>
           <t>Hong Kong</t>
         </is>
       </c>
-      <c r="F286" t="inlineStr">
+      <c r="F286" s="10" t="inlineStr">
         <is>
           <t>Digital tech startup funding</t>
         </is>
       </c>
-      <c r="G286" t="inlineStr">
+      <c r="G286" s="10" t="inlineStr">
         <is>
           <t>Pre-seed &amp; seed startups</t>
         </is>
       </c>
-      <c r="H286" t="inlineStr">
+      <c r="H286" s="10" t="inlineStr">
         <is>
           <t>Hong Kong's digital technology hub, offering funding, workspace and mentorship to early-stage digital and fintech startups.</t>
         </is>
       </c>
-      <c r="I286" t="inlineStr">
+      <c r="I286" s="10" t="inlineStr">
         <is>
           <t>Up to HKD 500k financial assistance (plus additional schemes)</t>
         </is>
       </c>
-      <c r="J286" t="inlineStr">
+      <c r="J286" s="10" t="inlineStr">
         <is>
           <t>2 years incubation</t>
         </is>
       </c>
-      <c r="K286" t="inlineStr">
+      <c r="K286" s="10" t="inlineStr">
         <is>
           <t>Hong Kong-incorporated digital tech startup, typically under 3-5 years old</t>
         </is>
       </c>
-      <c r="L286" t="inlineStr">
+      <c r="L286" s="10" t="inlineStr">
         <is>
           <t>Periodic intakes (check site)</t>
         </is>
       </c>
-      <c r="M286" t="inlineStr">
+      <c r="M286" s="10" t="inlineStr">
         <is>
           <t>Cyberport online application</t>
         </is>
       </c>
-      <c r="N286" t="inlineStr">
+      <c r="N286" s="10" t="inlineStr">
         <is>
           <t>Yes — assessment</t>
         </is>
       </c>
-      <c r="O286" t="inlineStr">
+      <c r="O286" s="10" t="inlineStr">
         <is>
           <t>Competitive</t>
         </is>
       </c>
-      <c r="P286" t="inlineStr">
+      <c r="P286" s="10" t="inlineStr">
         <is>
           <t>https://www.cyberport.hk/</t>
         </is>
       </c>
-      <c r="Q286" t="inlineStr">
+      <c r="Q286" s="10" t="inlineStr">
         <is>
           <t>Focused on digital, fintech, AI and e-commerce rather than hardware or biotech.</t>
         </is>
       </c>
-      <c r="R286" t="inlineStr">
+      <c r="R286" s="10" t="inlineStr">
         <is>
           <t>Pre-seed;Seed</t>
         </is>
       </c>
-      <c r="S286" t="inlineStr">
+      <c r="S286" s="10" t="inlineStr">
         <is>
           <t>Founded (HK-incorporated)</t>
         </is>
       </c>
-      <c r="T286" t="inlineStr">
+      <c r="T286" s="10" t="inlineStr">
         <is>
           <t>Grant + incubation</t>
         </is>
       </c>
     </row>
     <row r="287">
-      <c r="A287" t="inlineStr">
+      <c r="A287" s="10" t="inlineStr">
         <is>
           <t>G283</t>
         </is>
       </c>
-      <c r="B287" t="inlineStr">
+      <c r="B287" s="10" t="inlineStr">
         <is>
           <t>China Innovation Fund for Small Technology-Based Firms (Torch Programme)</t>
         </is>
       </c>
-      <c r="C287" t="inlineStr">
+      <c r="C287" s="10" t="inlineStr">
         <is>
           <t>Ministry of Science and Technology (MOST), China</t>
         </is>
       </c>
-      <c r="D287" t="inlineStr">
+      <c r="D287" s="10" t="inlineStr">
         <is>
           <t>China (MOST)</t>
         </is>
       </c>
-      <c r="E287" t="inlineStr">
+      <c r="E287" s="10" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
-      <c r="F287" t="inlineStr">
+      <c r="F287" s="10" t="inlineStr">
         <is>
           <t>Technology startup funding</t>
         </is>
       </c>
-      <c r="G287" t="inlineStr">
+      <c r="G287" s="10" t="inlineStr">
         <is>
           <t>Small technology firms</t>
         </is>
       </c>
-      <c r="H287" t="inlineStr">
+      <c r="H287" s="10" t="inlineStr">
         <is>
           <t>China's long-running national programme supporting small technology-based enterprises through grants, subsidies and incubator networks.</t>
         </is>
       </c>
-      <c r="I287" t="inlineStr">
+      <c r="I287" s="10" t="inlineStr">
         <is>
           <t>Typically ¥300,000-2,000,000 per award (varies by province)</t>
         </is>
       </c>
-      <c r="J287" t="inlineStr">
+      <c r="J287" s="10" t="inlineStr">
         <is>
           <t>1-3 years</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr">
+      <c r="K287" s="10" t="inlineStr">
         <is>
           <t>Chinese-registered small technology firms; provincial rules and quotas apply</t>
         </is>
       </c>
-      <c r="L287" t="inlineStr">
+      <c r="L287" s="10" t="inlineStr">
         <is>
           <t>Provincial calls (varies; check local Science &amp; Technology Bureau)</t>
         </is>
       </c>
-      <c r="M287" t="inlineStr">
+      <c r="M287" s="10" t="inlineStr">
         <is>
           <t>Provincial Science and Technology Bureau</t>
         </is>
       </c>
-      <c r="N287" t="inlineStr">
+      <c r="N287" s="10" t="inlineStr">
         <is>
           <t>Varies</t>
         </is>
       </c>
-      <c r="O287" t="inlineStr">
+      <c r="O287" s="10" t="inlineStr">
         <is>
           <t>Varies by province</t>
         </is>
       </c>
-      <c r="P287" t="inlineStr">
+      <c r="P287" s="10" t="inlineStr">
         <is>
           <t>https://en.most.gov.cn/</t>
         </is>
       </c>
-      <c r="Q287" t="inlineStr">
+      <c r="Q287" s="10" t="inlineStr">
         <is>
           <t>Administered provincially with substantial local variation — the local bureau is the real gatekeeper.</t>
         </is>
       </c>
-      <c r="R287" t="inlineStr">
+      <c r="R287" s="10" t="inlineStr">
         <is>
           <t>Seed;Growth</t>
         </is>
       </c>
-      <c r="S287" t="inlineStr">
+      <c r="S287" s="10" t="inlineStr">
         <is>
           <t>Founded (China-registered)</t>
         </is>
       </c>
-      <c r="T287" t="inlineStr">
+      <c r="T287" s="10" t="inlineStr">
         <is>
           <t>Grant</t>
         </is>
       </c>
     </row>
     <row r="288">
-      <c r="A288" t="inlineStr">
+      <c r="A288" s="10" t="inlineStr">
         <is>
           <t>G284</t>
         </is>
       </c>
-      <c r="B288" t="inlineStr">
+      <c r="B288" s="10" t="inlineStr">
         <is>
           <t>DOD SBIR/STTR</t>
         </is>
       </c>
-      <c r="C288" t="inlineStr">
+      <c r="C288" s="10" t="inlineStr">
         <is>
           <t>US Department of Defense (DOD)</t>
         </is>
       </c>
-      <c r="D288" t="inlineStr">
+      <c r="D288" s="10" t="inlineStr">
         <is>
           <t>DOD</t>
         </is>
       </c>
-      <c r="E288" t="inlineStr">
+      <c r="E288" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="F288" t="inlineStr">
+      <c r="F288" s="10" t="inlineStr">
         <is>
           <t>Defence &amp; dual-use technology</t>
         </is>
       </c>
-      <c r="G288" t="inlineStr">
+      <c r="G288" s="10" t="inlineStr">
         <is>
           <t>Startups &amp; small businesses</t>
         </is>
       </c>
-      <c r="H288" t="inlineStr">
+      <c r="H288" s="10" t="inlineStr">
         <is>
           <t>The largest SBIR programme by budget, funding US small businesses developing technologies with defence and dual-use applications.</t>
         </is>
       </c>
-      <c r="I288" t="inlineStr">
+      <c r="I288" s="10" t="inlineStr">
         <is>
           <t>Phase I ~$150-300k; Phase II ~$1-2M (Direct to Phase II available)</t>
         </is>
       </c>
-      <c r="J288" t="inlineStr">
+      <c r="J288" s="10" t="inlineStr">
         <is>
           <t>Phase I 6-12 months; Phase II 2 years</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr">
+      <c r="K288" s="10" t="inlineStr">
         <is>
           <t>US small business, majority US-owned; topic-driven solicitations</t>
         </is>
       </c>
-      <c r="L288" t="inlineStr">
+      <c r="L288" s="10" t="inlineStr">
         <is>
           <t>3+ solicitation cycles per year (check site)</t>
         </is>
       </c>
-      <c r="M288" t="inlineStr">
+      <c r="M288" s="10" t="inlineStr">
         <is>
           <t>DOD SBIR/STTR portal (DSIP)</t>
         </is>
       </c>
-      <c r="N288" t="inlineStr">
+      <c r="N288" s="10" t="inlineStr">
         <is>
           <t>No — technical review</t>
         </is>
       </c>
-      <c r="O288" t="inlineStr">
+      <c r="O288" s="10" t="inlineStr">
         <is>
           <t>~15-20%</t>
         </is>
       </c>
-      <c r="P288" t="inlineStr">
+      <c r="P288" s="10" t="inlineStr">
         <is>
           <t>https://www.dodsbirsttr.mil/submissions/</t>
         </is>
       </c>
-      <c r="Q288" t="inlineStr">
+      <c r="Q288" s="10" t="inlineStr">
         <is>
           <t>Topic-driven: you must match a published need. Direct-to-Phase-II exists if you already have proof of concept.</t>
         </is>
       </c>
-      <c r="R288" t="inlineStr">
+      <c r="R288" s="10" t="inlineStr">
         <is>
           <t>Pre-seed;Seed</t>
         </is>
       </c>
-      <c r="S288" t="inlineStr">
+      <c r="S288" s="10" t="inlineStr">
         <is>
           <t>Founded (US small business)</t>
         </is>
       </c>
-      <c r="T288" t="inlineStr">
+      <c r="T288" s="10" t="inlineStr">
         <is>
           <t>Grant (non-dilutive)</t>
         </is>
       </c>
     </row>
     <row r="289">
-      <c r="A289" t="inlineStr">
+      <c r="A289" s="10" t="inlineStr">
         <is>
           <t>G285</t>
         </is>
       </c>
-      <c r="B289" t="inlineStr">
+      <c r="B289" s="10" t="inlineStr">
         <is>
           <t>NASA SBIR/STTR</t>
         </is>
       </c>
-      <c r="C289" t="inlineStr">
+      <c r="C289" s="10" t="inlineStr">
         <is>
           <t>National Aeronautics and Space Administration (NASA)</t>
         </is>
       </c>
-      <c r="D289" t="inlineStr">
+      <c r="D289" s="10" t="inlineStr">
         <is>
           <t>NASA</t>
         </is>
       </c>
-      <c r="E289" t="inlineStr">
+      <c r="E289" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="F289" t="inlineStr">
+      <c r="F289" s="10" t="inlineStr">
         <is>
           <t>Space &amp; aeronautics technology</t>
         </is>
       </c>
-      <c r="G289" t="inlineStr">
+      <c r="G289" s="10" t="inlineStr">
         <is>
           <t>Startups &amp; small businesses</t>
         </is>
       </c>
-      <c r="H289" t="inlineStr">
+      <c r="H289" s="10" t="inlineStr">
         <is>
           <t>Funds US small businesses developing technologies relevant to NASA's space, aeronautics and science missions.</t>
         </is>
       </c>
-      <c r="I289" t="inlineStr">
+      <c r="I289" s="10" t="inlineStr">
         <is>
           <t>Phase I ~$150k; Phase II ~$850k</t>
         </is>
       </c>
-      <c r="J289" t="inlineStr">
+      <c r="J289" s="10" t="inlineStr">
         <is>
           <t>Phase I 6 months; Phase II 24 months</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr">
+      <c r="K289" s="10" t="inlineStr">
         <is>
           <t>US-based small business (&lt;500 employees); STTR requires a research institution partner</t>
         </is>
       </c>
-      <c r="L289" t="inlineStr">
+      <c r="L289" s="10" t="inlineStr">
         <is>
           <t>Annual solicitation (typically opens ~Jan; check site)</t>
         </is>
       </c>
-      <c r="M289" t="inlineStr">
+      <c r="M289" s="10" t="inlineStr">
         <is>
           <t>NASA SBIR/STTR portal</t>
         </is>
       </c>
-      <c r="N289" t="inlineStr">
+      <c r="N289" s="10" t="inlineStr">
         <is>
           <t>No — technical review</t>
         </is>
       </c>
-      <c r="O289" t="inlineStr">
+      <c r="O289" s="10" t="inlineStr">
         <is>
           <t>~15%</t>
         </is>
       </c>
-      <c r="P289" t="inlineStr">
+      <c r="P289" s="10" t="inlineStr">
         <is>
           <t>https://sbir.nasa.gov/</t>
         </is>
       </c>
-      <c r="Q289" t="inlineStr">
+      <c r="Q289" s="10" t="inlineStr">
         <is>
           <t>Strong pathway if your technology has any space, sensing or materials angle.</t>
         </is>
       </c>
-      <c r="R289" t="inlineStr">
+      <c r="R289" s="10" t="inlineStr">
         <is>
           <t>Pre-seed;Seed</t>
         </is>
       </c>
-      <c r="S289" t="inlineStr">
+      <c r="S289" s="10" t="inlineStr">
         <is>
           <t>Founded (US small business)</t>
         </is>
       </c>
-      <c r="T289" t="inlineStr">
+      <c r="T289" s="10" t="inlineStr">
         <is>
           <t>Grant (non-dilutive)</t>
         </is>
       </c>
     </row>
     <row r="290">
-      <c r="A290" t="inlineStr">
+      <c r="A290" s="10" t="inlineStr">
         <is>
           <t>G286</t>
         </is>
       </c>
-      <c r="B290" t="inlineStr">
+      <c r="B290" s="10" t="inlineStr">
         <is>
           <t>USDA SBIR</t>
         </is>
       </c>
-      <c r="C290" t="inlineStr">
+      <c r="C290" s="10" t="inlineStr">
         <is>
           <t>US Department of Agriculture (USDA NIFA)</t>
         </is>
       </c>
-      <c r="D290" t="inlineStr">
+      <c r="D290" s="10" t="inlineStr">
         <is>
           <t>USDA</t>
         </is>
       </c>
-      <c r="E290" t="inlineStr">
+      <c r="E290" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="F290" t="inlineStr">
+      <c r="F290" s="10" t="inlineStr">
         <is>
           <t>Agriculture, food &amp; rural technology</t>
         </is>
       </c>
-      <c r="G290" t="inlineStr">
+      <c r="G290" s="10" t="inlineStr">
         <is>
           <t>Startups &amp; small businesses</t>
         </is>
       </c>
-      <c r="H290" t="inlineStr">
+      <c r="H290" s="10" t="inlineStr">
         <is>
           <t>Non-dilutive funding for US small businesses innovating in agriculture, food systems, forestry and rural development.</t>
         </is>
       </c>
-      <c r="I290" t="inlineStr">
+      <c r="I290" s="10" t="inlineStr">
         <is>
           <t>Phase I up to $175k; Phase II up to $650k</t>
         </is>
       </c>
-      <c r="J290" t="inlineStr">
+      <c r="J290" s="10" t="inlineStr">
         <is>
           <t>Phase I 8 months; Phase II 24 months</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr">
+      <c r="K290" s="10" t="inlineStr">
         <is>
           <t>US small business; topic areas set annually</t>
         </is>
       </c>
-      <c r="L290" t="inlineStr">
+      <c r="L290" s="10" t="inlineStr">
         <is>
           <t>Annual solicitation (typically ~Oct deadline; check site)</t>
         </is>
       </c>
-      <c r="M290" t="inlineStr">
+      <c r="M290" s="10" t="inlineStr">
         <is>
           <t>Grants.gov</t>
         </is>
       </c>
-      <c r="N290" t="inlineStr">
+      <c r="N290" s="10" t="inlineStr">
         <is>
           <t>No — panel review</t>
         </is>
       </c>
-      <c r="O290" t="inlineStr">
+      <c r="O290" s="10" t="inlineStr">
         <is>
           <t>~15%</t>
         </is>
       </c>
-      <c r="P290" t="inlineStr">
+      <c r="P290" s="10" t="inlineStr">
         <is>
           <t>https://www.nifa.usda.gov/grants/programs/small-business-innovation-research-program-sbir</t>
         </is>
       </c>
-      <c r="Q290" t="inlineStr">
+      <c r="Q290" s="10" t="inlineStr">
         <is>
           <t>Much less crowded than NIH or NSF SBIR if your work touches agriculture or food.</t>
         </is>
       </c>
-      <c r="R290" t="inlineStr">
+      <c r="R290" s="10" t="inlineStr">
         <is>
           <t>Pre-seed;Seed</t>
         </is>
       </c>
-      <c r="S290" t="inlineStr">
+      <c r="S290" s="10" t="inlineStr">
         <is>
           <t>Founded (US small business)</t>
         </is>
       </c>
-      <c r="T290" t="inlineStr">
+      <c r="T290" s="10" t="inlineStr">
         <is>
           <t>Grant (non-dilutive)</t>
         </is>
       </c>
     </row>
     <row r="291">
-      <c r="A291" t="inlineStr">
+      <c r="A291" s="10" t="inlineStr">
         <is>
           <t>G287</t>
         </is>
       </c>
-      <c r="B291" t="inlineStr">
+      <c r="B291" s="10" t="inlineStr">
         <is>
           <t>NSF Partnerships for Innovation (PFI)</t>
         </is>
       </c>
-      <c r="C291" t="inlineStr">
+      <c r="C291" s="10" t="inlineStr">
         <is>
           <t>US National Science Foundation (NSF)</t>
         </is>
       </c>
-      <c r="D291" t="inlineStr">
+      <c r="D291" s="10" t="inlineStr">
         <is>
           <t>NSF</t>
         </is>
       </c>
-      <c r="E291" t="inlineStr">
+      <c r="E291" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="F291" t="inlineStr">
+      <c r="F291" s="10" t="inlineStr">
         <is>
           <t>Research translation &amp; commercialisation</t>
         </is>
       </c>
-      <c r="G291" t="inlineStr">
+      <c r="G291" s="10" t="inlineStr">
         <is>
           <t>Academic researchers → spin-offs</t>
         </is>
       </c>
-      <c r="H291" t="inlineStr">
+      <c r="H291" s="10" t="inlineStr">
         <is>
           <t>Helps academic teams translate NSF-funded research discoveries toward commercial products, including through new ventures.</t>
         </is>
       </c>
-      <c r="I291" t="inlineStr">
+      <c r="I291" s="10" t="inlineStr">
         <is>
           <t>Technology Translation up to $250k; Research Partnerships up to $550k</t>
         </is>
       </c>
-      <c r="J291" t="inlineStr">
+      <c r="J291" s="10" t="inlineStr">
         <is>
           <t>18 months-3 years</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr">
+      <c r="K291" s="10" t="inlineStr">
         <is>
           <t>PI with prior NSF-funded research at a US institution</t>
         </is>
       </c>
-      <c r="L291" t="inlineStr">
+      <c r="L291" s="10" t="inlineStr">
         <is>
           <t>Rolling / annual windows (check solicitation)</t>
         </is>
       </c>
-      <c r="M291" t="inlineStr">
+      <c r="M291" s="10" t="inlineStr">
         <is>
           <t>Research.gov</t>
         </is>
       </c>
-      <c r="N291" t="inlineStr">
+      <c r="N291" s="10" t="inlineStr">
         <is>
           <t>No — merit review</t>
         </is>
       </c>
-      <c r="O291" t="inlineStr">
+      <c r="O291" s="10" t="inlineStr">
         <is>
           <t>Competitive</t>
         </is>
       </c>
-      <c r="P291" t="inlineStr">
+      <c r="P291" s="10" t="inlineStr">
         <is>
           <t>https://new.nsf.gov/funding/opportunities/pfi-partnerships-innovation</t>
         </is>
       </c>
-      <c r="Q291" t="inlineStr">
+      <c r="Q291" s="10" t="inlineStr">
         <is>
           <t>Requires a lineage to prior NSF funding — check the current solicitation for what qualifies.</t>
         </is>
       </c>
-      <c r="R291" t="inlineStr">
+      <c r="R291" s="10" t="inlineStr">
         <is>
           <t>Pre-seed</t>
         </is>
       </c>
-      <c r="S291" t="inlineStr">
+      <c r="S291" s="10" t="inlineStr">
         <is>
           <t>Not yet founded</t>
         </is>
       </c>
-      <c r="T291" t="inlineStr">
+      <c r="T291" s="10" t="inlineStr">
         <is>
           <t>Grant</t>
         </is>
       </c>
     </row>
     <row r="292">
-      <c r="A292" t="inlineStr">
+      <c r="A292" s="10" t="inlineStr">
         <is>
           <t>G288</t>
         </is>
       </c>
-      <c r="B292" t="inlineStr">
+      <c r="B292" s="10" t="inlineStr">
         <is>
           <t>Breakthrough Energy Fellows</t>
         </is>
       </c>
-      <c r="C292" t="inlineStr">
+      <c r="C292" s="10" t="inlineStr">
         <is>
           <t>Breakthrough Energy (Bill Gates-founded)</t>
         </is>
       </c>
-      <c r="D292" t="inlineStr">
+      <c r="D292" s="10" t="inlineStr">
         <is>
           <t>Private (Breakthrough Energy)</t>
         </is>
       </c>
-      <c r="E292" t="inlineStr">
+      <c r="E292" s="10" t="inlineStr">
         <is>
           <t>USA &amp; Europe</t>
         </is>
       </c>
-      <c r="F292" t="inlineStr">
+      <c r="F292" s="10" t="inlineStr">
         <is>
           <t>Climate &amp; clean energy technology</t>
         </is>
       </c>
-      <c r="G292" t="inlineStr">
+      <c r="G292" s="10" t="inlineStr">
         <is>
           <t>Scientist-founders &amp; early teams</t>
         </is>
       </c>
-      <c r="H292" t="inlineStr">
+      <c r="H292" s="10" t="inlineStr">
         <is>
           <t>Supports scientists and engineers turning climate technology research into companies, with funding, mentorship and a two-year programme.</t>
         </is>
       </c>
-      <c r="I292" t="inlineStr">
+      <c r="I292" s="10" t="inlineStr">
         <is>
           <t>Up to ~$500k+ in funding and support per project</t>
         </is>
       </c>
-      <c r="J292" t="inlineStr">
+      <c r="J292" s="10" t="inlineStr">
         <is>
           <t>2 years</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr">
+      <c r="K292" s="10" t="inlineStr">
         <is>
           <t>Teams with a climate-relevant technology at an early stage; US, UK and EU cohorts</t>
         </is>
       </c>
-      <c r="L292" t="inlineStr">
+      <c r="L292" s="10" t="inlineStr">
         <is>
           <t>Annual call (check site)</t>
         </is>
       </c>
-      <c r="M292" t="inlineStr">
+      <c r="M292" s="10" t="inlineStr">
         <is>
           <t>Breakthrough Energy application</t>
         </is>
       </c>
-      <c r="N292" t="inlineStr">
+      <c r="N292" s="10" t="inlineStr">
         <is>
           <t>Yes — multiple rounds</t>
         </is>
       </c>
-      <c r="O292" t="inlineStr">
+      <c r="O292" s="10" t="inlineStr">
         <is>
           <t>Very competitive</t>
         </is>
       </c>
-      <c r="P292" t="inlineStr">
+      <c r="P292" s="10" t="inlineStr">
         <is>
           <t>https://www.breakthroughenergy.org/</t>
         </is>
       </c>
-      <c r="Q292" t="inlineStr">
+      <c r="Q292" s="10" t="inlineStr">
         <is>
           <t>One of the strongest climate-tech routes for researchers who have not yet founded a company.</t>
         </is>
       </c>
-      <c r="R292" t="inlineStr">
+      <c r="R292" s="10" t="inlineStr">
         <is>
           <t>Pre-seed</t>
         </is>
       </c>
-      <c r="S292" t="inlineStr">
+      <c r="S292" s="10" t="inlineStr">
         <is>
           <t>Not yet founded / just founded</t>
         </is>
       </c>
-      <c r="T292" t="inlineStr">
+      <c r="T292" s="10" t="inlineStr">
         <is>
           <t>Fellowship + grant</t>
         </is>
       </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="10" t="inlineStr">
+        <is>
+          <t>G289</t>
+        </is>
+      </c>
+      <c r="B293" s="10" t="inlineStr">
+        <is>
+          <t>Berliner Startup Stipendium</t>
+        </is>
+      </c>
+      <c r="C293" s="10" t="inlineStr">
+        <is>
+          <t>Investitionsbank Berlin (IBB) / Berlin Senate</t>
+        </is>
+      </c>
+      <c r="D293" s="10" t="inlineStr">
+        <is>
+          <t>Germany (Berlin)</t>
+        </is>
+      </c>
+      <c r="E293" s="10" t="inlineStr">
+        <is>
+          <t>Germany (Berlin)</t>
+        </is>
+      </c>
+      <c r="F293" s="10" t="inlineStr">
+        <is>
+          <t>Startup funding (regional)</t>
+        </is>
+      </c>
+      <c r="G293" s="10" t="inlineStr">
+        <is>
+          <t>Founders pre-company</t>
+        </is>
+      </c>
+      <c r="H293" s="10" t="inlineStr">
+        <is>
+          <t>Berlin's founder stipend: pays a salary to early founding teams while they develop their idea inside a partner incubator.</t>
+        </is>
+      </c>
+      <c r="I293" s="10" t="inlineStr">
+        <is>
+          <t>€2,000-2,500/month per founder + coaching</t>
+        </is>
+      </c>
+      <c r="J293" s="10" t="inlineStr">
+        <is>
+          <t>Up to 12 months</t>
+        </is>
+      </c>
+      <c r="K293" s="10" t="inlineStr">
+        <is>
+          <t>Founding teams based in Berlin, hosted by one of the partner incubators; company usually not yet founded</t>
+        </is>
+      </c>
+      <c r="L293" s="10" t="inlineStr">
+        <is>
+          <t>Rolling intakes via partner incubators (check site)</t>
+        </is>
+      </c>
+      <c r="M293" s="10" t="inlineStr">
+        <is>
+          <t>Via a Berlin partner incubator</t>
+        </is>
+      </c>
+      <c r="N293" s="10" t="inlineStr">
+        <is>
+          <t>Yes — jury selection</t>
+        </is>
+      </c>
+      <c r="O293" s="10" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="P293" s="10" t="inlineStr">
+        <is>
+          <t>https://www.ibb.de/</t>
+        </is>
+      </c>
+      <c r="Q293" s="10" t="inlineStr">
+        <is>
+          <t>One of the more accessible German Länder stipends; the incubator partner is your entry point.</t>
+        </is>
+      </c>
+      <c r="R293" s="10" t="inlineStr">
+        <is>
+          <t>Pre-seed</t>
+        </is>
+      </c>
+      <c r="S293" s="10" t="inlineStr">
+        <is>
+          <t>Not yet founded</t>
+        </is>
+      </c>
+      <c r="T293" s="10" t="inlineStr">
+        <is>
+          <t>Grant (salary)</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="10" t="inlineStr">
+        <is>
+          <t>G290</t>
+        </is>
+      </c>
+      <c r="B294" s="10" t="inlineStr">
+        <is>
+          <t>Gründerstipendium NRW</t>
+        </is>
+      </c>
+      <c r="C294" s="10" t="inlineStr">
+        <is>
+          <t>Ministry of Economic Affairs, North Rhine-Westphalia</t>
+        </is>
+      </c>
+      <c r="D294" s="10" t="inlineStr">
+        <is>
+          <t>Germany (NRW)</t>
+        </is>
+      </c>
+      <c r="E294" s="10" t="inlineStr">
+        <is>
+          <t>Germany (North Rhine-Westphalia)</t>
+        </is>
+      </c>
+      <c r="F294" s="10" t="inlineStr">
+        <is>
+          <t>Startup funding (regional)</t>
+        </is>
+      </c>
+      <c r="G294" s="10" t="inlineStr">
+        <is>
+          <t>Founders pre-company</t>
+        </is>
+      </c>
+      <c r="H294" s="10" t="inlineStr">
+        <is>
+          <t>North Rhine-Westphalia's founder stipend, giving early founders a living allowance while validating a business idea.</t>
+        </is>
+      </c>
+      <c r="I294" s="10" t="inlineStr">
+        <is>
+          <t>€1,000/month per founder (up to 3 founders)</t>
+        </is>
+      </c>
+      <c r="J294" s="10" t="inlineStr">
+        <is>
+          <t>12 months</t>
+        </is>
+      </c>
+      <c r="K294" s="10" t="inlineStr">
+        <is>
+          <t>Founders in NRW with an innovative idea; endorsement from an accredited start-up centre required</t>
+        </is>
+      </c>
+      <c r="L294" s="10" t="inlineStr">
+        <is>
+          <t>Rolling via accredited start-up centres</t>
+        </is>
+      </c>
+      <c r="M294" s="10" t="inlineStr">
+        <is>
+          <t>Via an accredited NRW start-up centre</t>
+        </is>
+      </c>
+      <c r="N294" s="10" t="inlineStr">
+        <is>
+          <t>Yes — centre assessment</t>
+        </is>
+      </c>
+      <c r="O294" s="10" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="P294" s="10" t="inlineStr">
+        <is>
+          <t>https://www.wirtschaft.nrw/gruenderstipendium-nrw</t>
+        </is>
+      </c>
+      <c r="Q294" s="10" t="inlineStr">
+        <is>
+          <t>Low-threshold and rolling — a practical first step for founders in Germany's most populous state.</t>
+        </is>
+      </c>
+      <c r="R294" s="10" t="inlineStr">
+        <is>
+          <t>Pre-seed</t>
+        </is>
+      </c>
+      <c r="S294" s="10" t="inlineStr">
+        <is>
+          <t>Not yet founded</t>
+        </is>
+      </c>
+      <c r="T294" s="10" t="inlineStr">
+        <is>
+          <t>Grant (living allowance)</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="10" t="inlineStr">
+        <is>
+          <t>G291</t>
+        </is>
+      </c>
+      <c r="B295" s="10" t="inlineStr">
+        <is>
+          <t>Start-up BW Pre-Seed</t>
+        </is>
+      </c>
+      <c r="C295" s="10" t="inlineStr">
+        <is>
+          <t>Baden-Württemberg Ministry of Economic Affairs / L-Bank</t>
+        </is>
+      </c>
+      <c r="D295" s="10" t="inlineStr">
+        <is>
+          <t>Germany (Baden-Württemberg)</t>
+        </is>
+      </c>
+      <c r="E295" s="10" t="inlineStr">
+        <is>
+          <t>Germany (Baden-Württemberg)</t>
+        </is>
+      </c>
+      <c r="F295" s="10" t="inlineStr">
+        <is>
+          <t>Startup funding (regional)</t>
+        </is>
+      </c>
+      <c r="G295" s="10" t="inlineStr">
+        <is>
+          <t>Pre-seed startups</t>
+        </is>
+      </c>
+      <c r="H295" s="10" t="inlineStr">
+        <is>
+          <t>Baden-Württemberg's pre-seed instrument, providing convertible-style public funding alongside a private co-investor.</t>
+        </is>
+      </c>
+      <c r="I295" s="10" t="inlineStr">
+        <is>
+          <t>Up to €800,000 public share (typically matched 80/20 with a co-investor)</t>
+        </is>
+      </c>
+      <c r="J295" s="10" t="inlineStr">
+        <is>
+          <t>Per investment</t>
+        </is>
+      </c>
+      <c r="K295" s="10" t="inlineStr">
+        <is>
+          <t>Startup based in Baden-Württemberg with an accredited pre-seed partner as co-investor</t>
+        </is>
+      </c>
+      <c r="L295" s="10" t="inlineStr">
+        <is>
+          <t>Rolling via accredited partners</t>
+        </is>
+      </c>
+      <c r="M295" s="10" t="inlineStr">
+        <is>
+          <t>Via a Start-up BW pre-seed partner</t>
+        </is>
+      </c>
+      <c r="N295" s="10" t="inlineStr">
+        <is>
+          <t>Yes — partner assessment</t>
+        </is>
+      </c>
+      <c r="O295" s="10" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="P295" s="10" t="inlineStr">
+        <is>
+          <t>https://www.startupbw.de/</t>
+        </is>
+      </c>
+      <c r="Q295" s="10" t="inlineStr">
+        <is>
+          <t>You approach an accredited partner (incubator or investor), not the state directly.</t>
+        </is>
+      </c>
+      <c r="R295" s="10" t="inlineStr">
+        <is>
+          <t>Pre-seed</t>
+        </is>
+      </c>
+      <c r="S295" s="10" t="inlineStr">
+        <is>
+          <t>Founded or forming</t>
+        </is>
+      </c>
+      <c r="T295" s="10" t="inlineStr">
+        <is>
+          <t>Public co-investment</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="10" t="inlineStr">
+        <is>
+          <t>G292</t>
+        </is>
+      </c>
+      <c r="B296" s="10" t="inlineStr">
+        <is>
+          <t>BayStartUP &amp; Bayerische Forschungsstiftung</t>
+        </is>
+      </c>
+      <c r="C296" s="10" t="inlineStr">
+        <is>
+          <t>Bavarian Ministry of Economic Affairs / BayStartUP</t>
+        </is>
+      </c>
+      <c r="D296" s="10" t="inlineStr">
+        <is>
+          <t>Germany (Bavaria)</t>
+        </is>
+      </c>
+      <c r="E296" s="10" t="inlineStr">
+        <is>
+          <t>Germany (Bavaria)</t>
+        </is>
+      </c>
+      <c r="F296" s="10" t="inlineStr">
+        <is>
+          <t>Startup funding &amp; research (regional)</t>
+        </is>
+      </c>
+      <c r="G296" s="10" t="inlineStr">
+        <is>
+          <t>Founders &amp; researchers</t>
+        </is>
+      </c>
+      <c r="H296" s="10" t="inlineStr">
+        <is>
+          <t>Bavaria's startup network runs business plan competitions and investor matchmaking, while the Bavarian Research Foundation funds applied research projects including university-industry work.</t>
+        </is>
+      </c>
+      <c r="I296" s="10" t="inlineStr">
+        <is>
+          <t>Research foundation projects typically €100k-500k; competitions offer coaching and investor access</t>
+        </is>
+      </c>
+      <c r="J296" s="10" t="inlineStr">
+        <is>
+          <t>Project-dependent</t>
+        </is>
+      </c>
+      <c r="K296" s="10" t="inlineStr">
+        <is>
+          <t>Bavarian companies and research institutions; competition entry open to founders in Bavaria</t>
+        </is>
+      </c>
+      <c r="L296" s="10" t="inlineStr">
+        <is>
+          <t>Rolling (foundation); annual rounds (competitions)</t>
+        </is>
+      </c>
+      <c r="M296" s="10" t="inlineStr">
+        <is>
+          <t>BayStartUP / Bayerische Forschungsstiftung portals</t>
+        </is>
+      </c>
+      <c r="N296" s="10" t="inlineStr">
+        <is>
+          <t>Yes — jury for competitions</t>
+        </is>
+      </c>
+      <c r="O296" s="10" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="P296" s="10" t="inlineStr">
+        <is>
+          <t>https://www.baystartup.de/</t>
+        </is>
+      </c>
+      <c r="Q296" s="10" t="inlineStr">
+        <is>
+          <t>Bavaria also runs the m4 Award specifically for personalised-medicine startups.</t>
+        </is>
+      </c>
+      <c r="R296" s="10" t="inlineStr">
+        <is>
+          <t>Pre-seed;Seed</t>
+        </is>
+      </c>
+      <c r="S296" s="10" t="inlineStr">
+        <is>
+          <t>Not yet founded / founded</t>
+        </is>
+      </c>
+      <c r="T296" s="10" t="inlineStr">
+        <is>
+          <t>Grant + coaching + investor access</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="10" t="inlineStr">
+        <is>
+          <t>G293</t>
+        </is>
+      </c>
+      <c r="B297" s="10" t="inlineStr">
+        <is>
+          <t>LOEWE Programme (Hesse)</t>
+        </is>
+      </c>
+      <c r="C297" s="10" t="inlineStr">
+        <is>
+          <t>State of Hesse — Ministry of Higher Education, Research and the Arts</t>
+        </is>
+      </c>
+      <c r="D297" s="10" t="inlineStr">
+        <is>
+          <t>Germany (Hesse)</t>
+        </is>
+      </c>
+      <c r="E297" s="10" t="inlineStr">
+        <is>
+          <t>Germany (Hesse)</t>
+        </is>
+      </c>
+      <c r="F297" s="10" t="inlineStr">
+        <is>
+          <t>Regional research excellence funding</t>
+        </is>
+      </c>
+      <c r="G297" s="10" t="inlineStr">
+        <is>
+          <t>Researchers &amp; research clusters</t>
+        </is>
+      </c>
+      <c r="H297" s="10" t="inlineStr">
+        <is>
+          <t>Hesse's flagship research programme funding excellence clusters, research groups and early-career projects at institutions in the state.</t>
+        </is>
+      </c>
+      <c r="I297" s="10" t="inlineStr">
+        <is>
+          <t>LOEWE Exploration ~€300k; clusters and centres far larger</t>
+        </is>
+      </c>
+      <c r="J297" s="10" t="inlineStr">
+        <is>
+          <t>2-4 years (Exploration 2 years)</t>
+        </is>
+      </c>
+      <c r="K297" s="10" t="inlineStr">
+        <is>
+          <t>Researchers at higher education and research institutions in Hesse</t>
+        </is>
+      </c>
+      <c r="L297" s="10" t="inlineStr">
+        <is>
+          <t>Annual calls per line (check site)</t>
+        </is>
+      </c>
+      <c r="M297" s="10" t="inlineStr">
+        <is>
+          <t>Via host institution / HMWK</t>
+        </is>
+      </c>
+      <c r="N297" s="10" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="O297" s="10" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="P297" s="10" t="inlineStr">
+        <is>
+          <t>https://wissenschaft.hessen.de/forschen/loewe</t>
+        </is>
+      </c>
+      <c r="Q297" s="10" t="inlineStr">
+        <is>
+          <t>LOEWE Exploration funds unconventional, high-risk ideas with light-touch applications — a rare format.</t>
+        </is>
+      </c>
+      <c r="R297" s="10" t="inlineStr"/>
+      <c r="S297" s="10" t="inlineStr"/>
+      <c r="T297" s="10" t="inlineStr"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="10" t="inlineStr">
+        <is>
+          <t>G294</t>
+        </is>
+      </c>
+      <c r="B298" s="10" t="inlineStr">
+        <is>
+          <t>InnoRampUp &amp; InnoFounder (Hamburg)</t>
+        </is>
+      </c>
+      <c r="C298" s="10" t="inlineStr">
+        <is>
+          <t>Hamburgische Investitions- und Förderbank (IFB Hamburg)</t>
+        </is>
+      </c>
+      <c r="D298" s="10" t="inlineStr">
+        <is>
+          <t>Germany (Hamburg)</t>
+        </is>
+      </c>
+      <c r="E298" s="10" t="inlineStr">
+        <is>
+          <t>Germany (Hamburg)</t>
+        </is>
+      </c>
+      <c r="F298" s="10" t="inlineStr">
+        <is>
+          <t>Startup funding (regional)</t>
+        </is>
+      </c>
+      <c r="G298" s="10" t="inlineStr">
+        <is>
+          <t>Founders &amp; early startups</t>
+        </is>
+      </c>
+      <c r="H298" s="10" t="inlineStr">
+        <is>
+          <t>Hamburg's two-tier startup support: InnoFounder pays a founder stipend with coaching, InnoRampUp grants fund technical development.</t>
+        </is>
+      </c>
+      <c r="I298" s="10" t="inlineStr">
+        <is>
+          <t>InnoFounder ~€2,000/month + coaching; InnoRampUp up to €150,000</t>
+        </is>
+      </c>
+      <c r="J298" s="10" t="inlineStr">
+        <is>
+          <t>InnoFounder 12 months; InnoRampUp project-based</t>
+        </is>
+      </c>
+      <c r="K298" s="10" t="inlineStr">
+        <is>
+          <t>Startup located in (or relocating to) Hamburg</t>
+        </is>
+      </c>
+      <c r="L298" s="10" t="inlineStr">
+        <is>
+          <t>Rolling submission</t>
+        </is>
+      </c>
+      <c r="M298" s="10" t="inlineStr">
+        <is>
+          <t>IFB Hamburg / Innovationsstarter portal</t>
+        </is>
+      </c>
+      <c r="N298" s="10" t="inlineStr">
+        <is>
+          <t>Yes — jury</t>
+        </is>
+      </c>
+      <c r="O298" s="10" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="P298" s="10" t="inlineStr">
+        <is>
+          <t>https://www.ifbhh.de/</t>
+        </is>
+      </c>
+      <c r="Q298" s="10" t="inlineStr">
+        <is>
+          <t>Also runs the Innovationsstarter Fonds Hamburg for equity investment.</t>
+        </is>
+      </c>
+      <c r="R298" s="10" t="inlineStr">
+        <is>
+          <t>Pre-seed;Seed</t>
+        </is>
+      </c>
+      <c r="S298" s="10" t="inlineStr">
+        <is>
+          <t>Not yet founded / founded</t>
+        </is>
+      </c>
+      <c r="T298" s="10" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="10" t="inlineStr">
+        <is>
+          <t>G295</t>
+        </is>
+      </c>
+      <c r="B299" s="10" t="inlineStr">
+        <is>
+          <t>Technologiegründerstipendium &amp; futureSAX (Saxony)</t>
+        </is>
+      </c>
+      <c r="C299" s="10" t="inlineStr">
+        <is>
+          <t>Saxon State Ministry for Economic Affairs / SAB</t>
+        </is>
+      </c>
+      <c r="D299" s="10" t="inlineStr">
+        <is>
+          <t>Germany (Saxony)</t>
+        </is>
+      </c>
+      <c r="E299" s="10" t="inlineStr">
+        <is>
+          <t>Germany (Saxony)</t>
+        </is>
+      </c>
+      <c r="F299" s="10" t="inlineStr">
+        <is>
+          <t>Startup funding (regional)</t>
+        </is>
+      </c>
+      <c r="G299" s="10" t="inlineStr">
+        <is>
+          <t>Founders pre-company</t>
+        </is>
+      </c>
+      <c r="H299" s="10" t="inlineStr">
+        <is>
+          <t>Saxony's technology founder stipend supports researchers and graduates preparing a technology-based spin-off, alongside the futureSAX innovation platform.</t>
+        </is>
+      </c>
+      <c r="I299" s="10" t="inlineStr">
+        <is>
+          <t>Stipend ~€1,000-2,500/month + material costs</t>
+        </is>
+      </c>
+      <c r="J299" s="10" t="inlineStr">
+        <is>
+          <t>Up to 12-18 months</t>
+        </is>
+      </c>
+      <c r="K299" s="10" t="inlineStr">
+        <is>
+          <t>Founders in Saxony with a technology-based idea, typically linked to a university or research institute</t>
+        </is>
+      </c>
+      <c r="L299" s="10" t="inlineStr">
+        <is>
+          <t>Rolling submission (check site)</t>
+        </is>
+      </c>
+      <c r="M299" s="10" t="inlineStr">
+        <is>
+          <t>Sächsische Aufbaubank (SAB)</t>
+        </is>
+      </c>
+      <c r="N299" s="10" t="inlineStr">
+        <is>
+          <t>Yes — assessment</t>
+        </is>
+      </c>
+      <c r="O299" s="10" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="P299" s="10" t="inlineStr">
+        <is>
+          <t>https://www.sab.sachsen.de/</t>
+        </is>
+      </c>
+      <c r="Q299" s="10" t="inlineStr">
+        <is>
+          <t>Dresden and Leipzig have strong microelectronics and biotech ecosystems behind this.</t>
+        </is>
+      </c>
+      <c r="R299" s="10" t="inlineStr">
+        <is>
+          <t>Pre-seed</t>
+        </is>
+      </c>
+      <c r="S299" s="10" t="inlineStr">
+        <is>
+          <t>Not yet founded</t>
+        </is>
+      </c>
+      <c r="T299" s="10" t="inlineStr">
+        <is>
+          <t>Grant (stipend)</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="10" t="inlineStr">
+        <is>
+          <t>G296</t>
+        </is>
+      </c>
+      <c r="B300" s="10" t="inlineStr">
+        <is>
+          <t>Ikerbasque Research Fellowships &amp; Professorships</t>
+        </is>
+      </c>
+      <c r="C300" s="10" t="inlineStr">
+        <is>
+          <t>Ikerbasque — Basque Foundation for Science</t>
+        </is>
+      </c>
+      <c r="D300" s="10" t="inlineStr">
+        <is>
+          <t>Spain (Basque Country)</t>
+        </is>
+      </c>
+      <c r="E300" s="10" t="inlineStr">
+        <is>
+          <t>Spain (Basque Country)</t>
+        </is>
+      </c>
+      <c r="F300" s="10" t="inlineStr">
+        <is>
+          <t>Regional research fellowships</t>
+        </is>
+      </c>
+      <c r="G300" s="10" t="inlineStr">
+        <is>
+          <t>Early postdoc → established</t>
+        </is>
+      </c>
+      <c r="H300" s="10" t="inlineStr">
+        <is>
+          <t>The Basque Country's science foundation recruits international researchers with five-year fellowships and permanent research professorships.</t>
+        </is>
+      </c>
+      <c r="I300" s="10" t="inlineStr">
+        <is>
+          <t>Fellowships: full salary + €25k research budget; Professorships permanent</t>
+        </is>
+      </c>
+      <c r="J300" s="10" t="inlineStr">
+        <is>
+          <t>5 years (fellowships); permanent (professorships)</t>
+        </is>
+      </c>
+      <c r="K300" s="10" t="inlineStr">
+        <is>
+          <t>PhD holders of any nationality; host institution in the Basque Country required</t>
+        </is>
+      </c>
+      <c r="L300" s="10" t="inlineStr">
+        <is>
+          <t>Annual calls (typically ~Mar-Apr; check site)</t>
+        </is>
+      </c>
+      <c r="M300" s="10" t="inlineStr">
+        <is>
+          <t>Ikerbasque online system</t>
+        </is>
+      </c>
+      <c r="N300" s="10" t="inlineStr">
+        <is>
+          <t>Yes — interview for shortlisted</t>
+        </is>
+      </c>
+      <c r="O300" s="10" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="P300" s="10" t="inlineStr">
+        <is>
+          <t>https://www.ikerbasque.net/en</t>
+        </is>
+      </c>
+      <c r="Q300" s="10" t="inlineStr">
+        <is>
+          <t>Fellowships can convert to a permanent position — unusually secure for a regional scheme.</t>
+        </is>
+      </c>
+      <c r="R300" s="10" t="inlineStr"/>
+      <c r="S300" s="10" t="inlineStr"/>
+      <c r="T300" s="10" t="inlineStr"/>
+    </row>
+    <row r="301">
+      <c r="A301" s="10" t="inlineStr">
+        <is>
+          <t>G297</t>
+        </is>
+      </c>
+      <c r="B301" s="10" t="inlineStr">
+        <is>
+          <t>Beatriu de Pinós &amp; FI Fellowships (Catalonia)</t>
+        </is>
+      </c>
+      <c r="C301" s="10" t="inlineStr">
+        <is>
+          <t>AGAUR — Agency for Management of University and Research Grants</t>
+        </is>
+      </c>
+      <c r="D301" s="10" t="inlineStr">
+        <is>
+          <t>Spain (Catalonia)</t>
+        </is>
+      </c>
+      <c r="E301" s="10" t="inlineStr">
+        <is>
+          <t>Spain (Catalonia)</t>
+        </is>
+      </c>
+      <c r="F301" s="10" t="inlineStr">
+        <is>
+          <t>Regional research fellowships</t>
+        </is>
+      </c>
+      <c r="G301" s="10" t="inlineStr">
+        <is>
+          <t>PhD candidates &amp; postdocs</t>
+        </is>
+      </c>
+      <c r="H301" s="10" t="inlineStr">
+        <is>
+          <t>Catalonia's fellowship portfolio: FI grants fund doctoral candidates, Beatriu de Pinós brings experienced postdocs to Catalan institutions.</t>
+        </is>
+      </c>
+      <c r="I301" s="10" t="inlineStr">
+        <is>
+          <t>FI ~€1,200-1,500/month; Beatriu de Pinós ~€48,000/yr</t>
+        </is>
+      </c>
+      <c r="J301" s="10" t="inlineStr">
+        <is>
+          <t>FI 3 years; Beatriu de Pinós 3 years</t>
+        </is>
+      </c>
+      <c r="K301" s="10" t="inlineStr">
+        <is>
+          <t>Beatriu de Pinós requires 2+ years abroad and a Catalan host; FI for doctoral candidates in Catalonia</t>
+        </is>
+      </c>
+      <c r="L301" s="10" t="inlineStr">
+        <is>
+          <t>Annual calls (check site)</t>
+        </is>
+      </c>
+      <c r="M301" s="10" t="inlineStr">
+        <is>
+          <t>AGAUR online system</t>
+        </is>
+      </c>
+      <c r="N301" s="10" t="inlineStr">
+        <is>
+          <t>No — panel review</t>
+        </is>
+      </c>
+      <c r="O301" s="10" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="P301" s="10" t="inlineStr">
+        <is>
+          <t>https://agaur.gencat.cat/en/inici/</t>
+        </is>
+      </c>
+      <c r="Q301" s="10" t="inlineStr">
+        <is>
+          <t>Catalonia also runs ICREA for senior researchers — among the best-paid research positions in Spain.</t>
+        </is>
+      </c>
+      <c r="R301" s="10" t="inlineStr"/>
+      <c r="S301" s="10" t="inlineStr"/>
+      <c r="T301" s="10" t="inlineStr"/>
+    </row>
+    <row r="302">
+      <c r="A302" s="10" t="inlineStr">
+        <is>
+          <t>G298</t>
+        </is>
+      </c>
+      <c r="B302" s="10" t="inlineStr">
+        <is>
+          <t>Atracción de Talento Investigador (Madrid)</t>
+        </is>
+      </c>
+      <c r="C302" s="10" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
+      <c r="D302" s="10" t="inlineStr">
+        <is>
+          <t>Spain (Madrid)</t>
+        </is>
+      </c>
+      <c r="E302" s="10" t="inlineStr">
+        <is>
+          <t>Spain (Madrid)</t>
+        </is>
+      </c>
+      <c r="F302" s="10" t="inlineStr">
+        <is>
+          <t>Regional research fellowships</t>
+        </is>
+      </c>
+      <c r="G302" s="10" t="inlineStr">
+        <is>
+          <t>Early postdoc → senior</t>
+        </is>
+      </c>
+      <c r="H302" s="10" t="inlineStr">
+        <is>
+          <t>Madrid's talent attraction programme funds researchers to join universities and research centres in the region, in junior and senior modalities.</t>
+        </is>
+      </c>
+      <c r="I302" s="10" t="inlineStr">
+        <is>
+          <t>Salary + research budget (typically €40-60k/yr package)</t>
+        </is>
+      </c>
+      <c r="J302" s="10" t="inlineStr">
+        <is>
+          <t>4 years</t>
+        </is>
+      </c>
+      <c r="K302" s="10" t="inlineStr">
+        <is>
+          <t>PhD holders; host institution in the Madrid region; modality-specific experience requirements</t>
+        </is>
+      </c>
+      <c r="L302" s="10" t="inlineStr">
+        <is>
+          <t>Annual call (check site)</t>
+        </is>
+      </c>
+      <c r="M302" s="10" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid portal via host</t>
+        </is>
+      </c>
+      <c r="N302" s="10" t="inlineStr">
+        <is>
+          <t>No — panel review</t>
+        </is>
+      </c>
+      <c r="O302" s="10" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="P302" s="10" t="inlineStr">
+        <is>
+          <t>https://www.comunidad.madrid/</t>
+        </is>
+      </c>
+      <c r="Q302" s="10" t="inlineStr">
+        <is>
+          <t>Applications go through the host institution — line up your host well before the call opens.</t>
+        </is>
+      </c>
+      <c r="R302" s="10" t="inlineStr"/>
+      <c r="S302" s="10" t="inlineStr"/>
+      <c r="T302" s="10" t="inlineStr"/>
+    </row>
+    <row r="303">
+      <c r="A303" s="10" t="inlineStr">
+        <is>
+          <t>G299</t>
+        </is>
+      </c>
+      <c r="B303" s="10" t="inlineStr">
+        <is>
+          <t>ACCIÓ Startup Capital (Catalonia)</t>
+        </is>
+      </c>
+      <c r="C303" s="10" t="inlineStr">
+        <is>
+          <t>ACCIÓ — Catalonia Trade &amp; Investment</t>
+        </is>
+      </c>
+      <c r="D303" s="10" t="inlineStr">
+        <is>
+          <t>Spain (Catalonia)</t>
+        </is>
+      </c>
+      <c r="E303" s="10" t="inlineStr">
+        <is>
+          <t>Spain (Catalonia)</t>
+        </is>
+      </c>
+      <c r="F303" s="10" t="inlineStr">
+        <is>
+          <t>Startup funding (regional)</t>
+        </is>
+      </c>
+      <c r="G303" s="10" t="inlineStr">
+        <is>
+          <t>Pre-seed deep tech</t>
+        </is>
+      </c>
+      <c r="H303" s="10" t="inlineStr">
+        <is>
+          <t>Catalonia's grant for technology-based startups in their first stages, covering product development and market entry.</t>
+        </is>
+      </c>
+      <c r="I303" s="10" t="inlineStr">
+        <is>
+          <t>Up to €99,000 (non-repayable)</t>
+        </is>
+      </c>
+      <c r="J303" s="10" t="inlineStr">
+        <is>
+          <t>Project-dependent</t>
+        </is>
+      </c>
+      <c r="K303" s="10" t="inlineStr">
+        <is>
+          <t>Technology-based company registered in Catalonia, typically under 3 years old</t>
+        </is>
+      </c>
+      <c r="L303" s="10" t="inlineStr">
+        <is>
+          <t>Annual call (check site)</t>
+        </is>
+      </c>
+      <c r="M303" s="10" t="inlineStr">
+        <is>
+          <t>ACCIÓ online portal</t>
+        </is>
+      </c>
+      <c r="N303" s="10" t="inlineStr">
+        <is>
+          <t>No — evaluation</t>
+        </is>
+      </c>
+      <c r="O303" s="10" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="P303" s="10" t="inlineStr">
+        <is>
+          <t>https://www.accio.gencat.cat/en/</t>
+        </is>
+      </c>
+      <c r="Q303" s="10" t="inlineStr">
+        <is>
+          <t>Catalonia is Spain's densest startup ecosystem outside Madrid, with strong deep-tech support.</t>
+        </is>
+      </c>
+      <c r="R303" s="10" t="inlineStr">
+        <is>
+          <t>Pre-seed</t>
+        </is>
+      </c>
+      <c r="S303" s="10" t="inlineStr">
+        <is>
+          <t>Founded (&lt;3 years, Catalonia)</t>
+        </is>
+      </c>
+      <c r="T303" s="10" t="inlineStr">
+        <is>
+          <t>Grant (non-repayable)</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="10" t="inlineStr">
+        <is>
+          <t>G300</t>
+        </is>
+      </c>
+      <c r="B304" s="10" t="inlineStr">
+        <is>
+          <t>Lazio Innova — Pre-seed &amp; Innovation Grants</t>
+        </is>
+      </c>
+      <c r="C304" s="10" t="inlineStr">
+        <is>
+          <t>Lazio Innova (Regione Lazio)</t>
+        </is>
+      </c>
+      <c r="D304" s="10" t="inlineStr">
+        <is>
+          <t>Italy (Lazio)</t>
+        </is>
+      </c>
+      <c r="E304" s="10" t="inlineStr">
+        <is>
+          <t>Italy (Lazio)</t>
+        </is>
+      </c>
+      <c r="F304" s="10" t="inlineStr">
+        <is>
+          <t>Startup funding (regional)</t>
+        </is>
+      </c>
+      <c r="G304" s="10" t="inlineStr">
+        <is>
+          <t>Pre-seed &amp; seed startups</t>
+        </is>
+      </c>
+      <c r="H304" s="10" t="inlineStr">
+        <is>
+          <t>The Rome region's development agency funds innovative startups and research-to-market projects through recurring regional calls.</t>
+        </is>
+      </c>
+      <c r="I304" s="10" t="inlineStr">
+        <is>
+          <t>Typically €30,000-500,000 depending on instrument</t>
+        </is>
+      </c>
+      <c r="J304" s="10" t="inlineStr">
+        <is>
+          <t>1-2 years</t>
+        </is>
+      </c>
+      <c r="K304" s="10" t="inlineStr">
+        <is>
+          <t>Startups and SMEs based in the Lazio region</t>
+        </is>
+      </c>
+      <c r="L304" s="10" t="inlineStr">
+        <is>
+          <t>Periodic calls (check site)</t>
+        </is>
+      </c>
+      <c r="M304" s="10" t="inlineStr">
+        <is>
+          <t>Lazio Innova portal</t>
+        </is>
+      </c>
+      <c r="N304" s="10" t="inlineStr">
+        <is>
+          <t>Yes — for some calls</t>
+        </is>
+      </c>
+      <c r="O304" s="10" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="P304" s="10" t="inlineStr">
+        <is>
+          <t>https://www.lazioinnova.it/</t>
+        </is>
+      </c>
+      <c r="Q304" s="10" t="inlineStr">
+        <is>
+          <t>Italian regions vary enormously — Lombardy, Emilia-Romagna and Piedmont run parallel schemes.</t>
+        </is>
+      </c>
+      <c r="R304" s="10" t="inlineStr">
+        <is>
+          <t>Pre-seed;Seed</t>
+        </is>
+      </c>
+      <c r="S304" s="10" t="inlineStr">
+        <is>
+          <t>Founded (Lazio-based)</t>
+        </is>
+      </c>
+      <c r="T304" s="10" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="10" t="inlineStr">
+        <is>
+          <t>G301</t>
+        </is>
+      </c>
+      <c r="B305" s="10" t="inlineStr">
+        <is>
+          <t>Innov'up &amp; Paris Innovation Amorçage</t>
+        </is>
+      </c>
+      <c r="C305" s="10" t="inlineStr">
+        <is>
+          <t>Région Île-de-France / Bpifrance / Paris&amp;Co</t>
+        </is>
+      </c>
+      <c r="D305" s="10" t="inlineStr">
+        <is>
+          <t>France (Île-de-France)</t>
+        </is>
+      </c>
+      <c r="E305" s="10" t="inlineStr">
+        <is>
+          <t>France (Île-de-France)</t>
+        </is>
+      </c>
+      <c r="F305" s="10" t="inlineStr">
+        <is>
+          <t>Startup funding (regional)</t>
+        </is>
+      </c>
+      <c r="G305" s="10" t="inlineStr">
+        <is>
+          <t>Pre-seed to growth</t>
+        </is>
+      </c>
+      <c r="H305" s="10" t="inlineStr">
+        <is>
+          <t>The Paris region's innovation funding, combining regional grants and repayable advances with incubator-linked seed funding.</t>
+        </is>
+      </c>
+      <c r="I305" s="10" t="inlineStr">
+        <is>
+          <t>Innov'up €30k-3M (grant + repayable advance); PIA up to €150k</t>
+        </is>
+      </c>
+      <c r="J305" s="10" t="inlineStr">
+        <is>
+          <t>1-3 years</t>
+        </is>
+      </c>
+      <c r="K305" s="10" t="inlineStr">
+        <is>
+          <t>Company based in Île-de-France; PIA requires an accredited Paris incubator</t>
+        </is>
+      </c>
+      <c r="L305" s="10" t="inlineStr">
+        <is>
+          <t>Rolling submission</t>
+        </is>
+      </c>
+      <c r="M305" s="10" t="inlineStr">
+        <is>
+          <t>Bpifrance / Paris&amp;Co portals</t>
+        </is>
+      </c>
+      <c r="N305" s="10" t="inlineStr">
+        <is>
+          <t>Yes — committee</t>
+        </is>
+      </c>
+      <c r="O305" s="10" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="P305" s="10" t="inlineStr">
+        <is>
+          <t>https://www.iledefrance.fr/</t>
+        </is>
+      </c>
+      <c r="Q305" s="10" t="inlineStr">
+        <is>
+          <t>Paris Innovation Amorçage runs through incubators — join one first.</t>
+        </is>
+      </c>
+      <c r="R305" s="10" t="inlineStr">
+        <is>
+          <t>Pre-seed;Seed</t>
+        </is>
+      </c>
+      <c r="S305" s="10" t="inlineStr">
+        <is>
+          <t>Founded (Île-de-France)</t>
+        </is>
+      </c>
+      <c r="T305" s="10" t="inlineStr">
+        <is>
+          <t>Grant + repayable advance</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="10" t="inlineStr">
+        <is>
+          <t>G302</t>
+        </is>
+      </c>
+      <c r="B306" s="10" t="inlineStr">
+        <is>
+          <t>Scottish EDGE &amp; Scottish Enterprise High Growth Spin-out Programme</t>
+        </is>
+      </c>
+      <c r="C306" s="10" t="inlineStr">
+        <is>
+          <t>Scottish EDGE / Scottish Enterprise</t>
+        </is>
+      </c>
+      <c r="D306" s="10" t="inlineStr">
+        <is>
+          <t>United Kingdom (Scotland)</t>
+        </is>
+      </c>
+      <c r="E306" s="10" t="inlineStr">
+        <is>
+          <t>United Kingdom (Scotland)</t>
+        </is>
+      </c>
+      <c r="F306" s="10" t="inlineStr">
+        <is>
+          <t>Startup funding (regional)</t>
+        </is>
+      </c>
+      <c r="G306" s="10" t="inlineStr">
+        <is>
+          <t>Founders &amp; academic spin-outs</t>
+        </is>
+      </c>
+      <c r="H306" s="10" t="inlineStr">
+        <is>
+          <t>Scotland's competition-based funding for early startups, alongside Scottish Enterprise's dedicated support for university spin-outs.</t>
+        </is>
+      </c>
+      <c r="I306" s="10" t="inlineStr">
+        <is>
+          <t>Scottish EDGE up to £150,000; HGSP grants for spin-out projects</t>
+        </is>
+      </c>
+      <c r="J306" s="10" t="inlineStr">
+        <is>
+          <t>Project-dependent</t>
+        </is>
+      </c>
+      <c r="K306" s="10" t="inlineStr">
+        <is>
+          <t>Business based in Scotland; HGSP for academic spin-outs from Scottish institutions</t>
+        </is>
+      </c>
+      <c r="L306" s="10" t="inlineStr">
+        <is>
+          <t>Scottish EDGE runs 2 rounds/yr; HGSP rolling</t>
+        </is>
+      </c>
+      <c r="M306" s="10" t="inlineStr">
+        <is>
+          <t>Scottish EDGE / Scottish Enterprise portals</t>
+        </is>
+      </c>
+      <c r="N306" s="10" t="inlineStr">
+        <is>
+          <t>Yes — pitch to judges</t>
+        </is>
+      </c>
+      <c r="O306" s="10" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="P306" s="10" t="inlineStr">
+        <is>
+          <t>https://www.scottish-enterprise.com/</t>
+        </is>
+      </c>
+      <c r="Q306" s="10" t="inlineStr">
+        <is>
+          <t>Scottish EDGE is pitch-competition style; HGSP is the route for university technology.</t>
+        </is>
+      </c>
+      <c r="R306" s="10" t="inlineStr">
+        <is>
+          <t>Pre-seed;Seed</t>
+        </is>
+      </c>
+      <c r="S306" s="10" t="inlineStr">
+        <is>
+          <t>Not yet founded / founded</t>
+        </is>
+      </c>
+      <c r="T306" s="10" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="10" t="inlineStr">
+        <is>
+          <t>G303</t>
+        </is>
+      </c>
+      <c r="B307" s="10" t="inlineStr">
+        <is>
+          <t>Invest Northern Ireland Innovation Support</t>
+        </is>
+      </c>
+      <c r="C307" s="10" t="inlineStr">
+        <is>
+          <t>Invest Northern Ireland</t>
+        </is>
+      </c>
+      <c r="D307" s="10" t="inlineStr">
+        <is>
+          <t>United Kingdom (Northern Ireland)</t>
+        </is>
+      </c>
+      <c r="E307" s="10" t="inlineStr">
+        <is>
+          <t>United Kingdom (Northern Ireland)</t>
+        </is>
+      </c>
+      <c r="F307" s="10" t="inlineStr">
+        <is>
+          <t>Startup funding (regional)</t>
+        </is>
+      </c>
+      <c r="G307" s="10" t="inlineStr">
+        <is>
+          <t>Startups &amp; SMEs</t>
+        </is>
+      </c>
+      <c r="H307" s="10" t="inlineStr">
+        <is>
+          <t>Northern Ireland's economic development agency supports new and growing businesses with innovation grants, R&amp;D funding and proof-of-concept support.</t>
+        </is>
+      </c>
+      <c r="I307" s="10" t="inlineStr">
+        <is>
+          <t>Proof of concept up to ~£50k; R&amp;D grants larger</t>
+        </is>
+      </c>
+      <c r="J307" s="10" t="inlineStr">
+        <is>
+          <t>Project-dependent</t>
+        </is>
+      </c>
+      <c r="K307" s="10" t="inlineStr">
+        <is>
+          <t>Business based in Northern Ireland</t>
+        </is>
+      </c>
+      <c r="L307" s="10" t="inlineStr">
+        <is>
+          <t>Rolling (via client executive)</t>
+        </is>
+      </c>
+      <c r="M307" s="10" t="inlineStr">
+        <is>
+          <t>Invest NI application</t>
+        </is>
+      </c>
+      <c r="N307" s="10" t="inlineStr">
+        <is>
+          <t>Yes — adviser assessment</t>
+        </is>
+      </c>
+      <c r="O307" s="10" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="P307" s="10" t="inlineStr">
+        <is>
+          <t>https://www.investni.com/</t>
+        </is>
+      </c>
+      <c r="Q307" s="10" t="inlineStr">
+        <is>
+          <t>Northern Ireland companies can also access Republic of Ireland cross-border programmes.</t>
+        </is>
+      </c>
+      <c r="R307" s="10" t="inlineStr">
+        <is>
+          <t>Pre-seed;Seed</t>
+        </is>
+      </c>
+      <c r="S307" s="10" t="inlineStr">
+        <is>
+          <t>Founded (NI-based)</t>
+        </is>
+      </c>
+      <c r="T307" s="10" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="10" t="inlineStr">
+        <is>
+          <t>G304</t>
+        </is>
+      </c>
+      <c r="B308" s="10" t="inlineStr">
+        <is>
+          <t>tech2b Incubator (Upper Austria)</t>
+        </is>
+      </c>
+      <c r="C308" s="10" t="inlineStr">
+        <is>
+          <t>tech2b Inkubator GmbH / Land Oberösterreich</t>
+        </is>
+      </c>
+      <c r="D308" s="10" t="inlineStr">
+        <is>
+          <t>Austria (Upper Austria)</t>
+        </is>
+      </c>
+      <c r="E308" s="10" t="inlineStr">
+        <is>
+          <t>Austria (Upper Austria)</t>
+        </is>
+      </c>
+      <c r="F308" s="10" t="inlineStr">
+        <is>
+          <t>Startup incubation (regional)</t>
+        </is>
+      </c>
+      <c r="G308" s="10" t="inlineStr">
+        <is>
+          <t>Academic &amp; tech founders</t>
+        </is>
+      </c>
+      <c r="H308" s="10" t="inlineStr">
+        <is>
+          <t>Upper Austria's academic incubator (part of the AplusB network) supporting technology founders with funding, coaching and infrastructure.</t>
+        </is>
+      </c>
+      <c r="I308" s="10" t="inlineStr">
+        <is>
+          <t>Typically up to ~€50k package + services</t>
+        </is>
+      </c>
+      <c r="J308" s="10" t="inlineStr">
+        <is>
+          <t>12-18 months incubation</t>
+        </is>
+      </c>
+      <c r="K308" s="10" t="inlineStr">
+        <is>
+          <t>Founders based in (or relocating to) Upper Austria; technology or knowledge-based idea</t>
+        </is>
+      </c>
+      <c r="L308" s="10" t="inlineStr">
+        <is>
+          <t>Rolling / batch intakes (check site)</t>
+        </is>
+      </c>
+      <c r="M308" s="10" t="inlineStr">
+        <is>
+          <t>tech2b application + pitch</t>
+        </is>
+      </c>
+      <c r="N308" s="10" t="inlineStr">
+        <is>
+          <t>Yes — jury</t>
+        </is>
+      </c>
+      <c r="O308" s="10" t="inlineStr">
+        <is>
+          <t>Selective</t>
+        </is>
+      </c>
+      <c r="P308" s="10" t="inlineStr">
+        <is>
+          <t>https://www.tech2b.at/</t>
+        </is>
+      </c>
+      <c r="Q308" s="10" t="inlineStr">
+        <is>
+          <t>Linz's strong mechatronics and software ecosystem sits behind this one.</t>
+        </is>
+      </c>
+      <c r="R308" s="10" t="inlineStr">
+        <is>
+          <t>Pre-seed</t>
+        </is>
+      </c>
+      <c r="S308" s="10" t="inlineStr">
+        <is>
+          <t>Not yet founded</t>
+        </is>
+      </c>
+      <c r="T308" s="10" t="inlineStr">
+        <is>
+          <t>Grant + incubation</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="10" t="inlineStr">
+        <is>
+          <t>G305</t>
+        </is>
+      </c>
+      <c r="B309" s="10" t="inlineStr">
+        <is>
+          <t>Standortagentur Tirol &amp; aws Regional Programmes</t>
+        </is>
+      </c>
+      <c r="C309" s="10" t="inlineStr">
+        <is>
+          <t>Standortagentur Tirol / Land Tirol</t>
+        </is>
+      </c>
+      <c r="D309" s="10" t="inlineStr">
+        <is>
+          <t>Austria (Tyrol)</t>
+        </is>
+      </c>
+      <c r="E309" s="10" t="inlineStr">
+        <is>
+          <t>Austria (Tyrol)</t>
+        </is>
+      </c>
+      <c r="F309" s="10" t="inlineStr">
+        <is>
+          <t>Startup &amp; innovation funding (regional)</t>
+        </is>
+      </c>
+      <c r="G309" s="10" t="inlineStr">
+        <is>
+          <t>Founders &amp; SMEs</t>
+        </is>
+      </c>
+      <c r="H309" s="10" t="inlineStr">
+        <is>
+          <t>Tyrol's location agency funds innovation projects, cluster cooperation and startup support for companies in the region.</t>
+        </is>
+      </c>
+      <c r="I309" s="10" t="inlineStr">
+        <is>
+          <t>Typically €10,000-200,000 depending on instrument</t>
+        </is>
+      </c>
+      <c r="J309" s="10" t="inlineStr">
+        <is>
+          <t>Project-dependent</t>
+        </is>
+      </c>
+      <c r="K309" s="10" t="inlineStr">
+        <is>
+          <t>Company or founding team based in Tyrol</t>
+        </is>
+      </c>
+      <c r="L309" s="10" t="inlineStr">
+        <is>
+          <t>Rolling / periodic calls (check site)</t>
+        </is>
+      </c>
+      <c r="M309" s="10" t="inlineStr">
+        <is>
+          <t>Standortagentur Tirol</t>
+        </is>
+      </c>
+      <c r="N309" s="10" t="inlineStr">
+        <is>
+          <t>No — assessment</t>
+        </is>
+      </c>
+      <c r="O309" s="10" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="P309" s="10" t="inlineStr">
+        <is>
+          <t>https://www.standort-tirol.at/</t>
+        </is>
+      </c>
+      <c r="Q309" s="10" t="inlineStr">
+        <is>
+          <t>Innsbruck's life-science and sports-tech clusters are the regional strengths.</t>
+        </is>
+      </c>
+      <c r="R309" s="10" t="inlineStr">
+        <is>
+          <t>Pre-seed;Seed</t>
+        </is>
+      </c>
+      <c r="S309" s="10" t="inlineStr">
+        <is>
+          <t>Founded or forming</t>
+        </is>
+      </c>
+      <c r="T309" s="10" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="10" t="inlineStr">
+        <is>
+          <t>G306</t>
+        </is>
+      </c>
+      <c r="B310" s="10" t="inlineStr">
+        <is>
+          <t>Cancer Research UK Career Development Fellowship</t>
+        </is>
+      </c>
+      <c r="C310" s="10" t="inlineStr">
+        <is>
+          <t>Cancer Research UK (CRUK)</t>
+        </is>
+      </c>
+      <c r="D310" s="10" t="inlineStr">
+        <is>
+          <t>Private (CRUK)</t>
+        </is>
+      </c>
+      <c r="E310" s="10" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="F310" s="10" t="inlineStr">
+        <is>
+          <t>Cancer research</t>
+        </is>
+      </c>
+      <c r="G310" s="10" t="inlineStr">
+        <is>
+          <t>Senior Postdoc → group leader</t>
+        </is>
+      </c>
+      <c r="H310" s="10" t="inlineStr">
+        <is>
+          <t>Europe's largest cancer charity funds researchers establishing their first independent cancer research group in the UK.</t>
+        </is>
+      </c>
+      <c r="I310" s="10" t="inlineStr">
+        <is>
+          <t>Up to ~£1.5M (salary + research costs)</t>
+        </is>
+      </c>
+      <c r="J310" s="10" t="inlineStr">
+        <is>
+          <t>6 years</t>
+        </is>
+      </c>
+      <c r="K310" s="10" t="inlineStr">
+        <is>
+          <t>Postdocs ready for independence; UK host institution; any nationality</t>
+        </is>
+      </c>
+      <c r="L310" s="10" t="inlineStr">
+        <is>
+          <t>Annual rounds (check site)</t>
+        </is>
+      </c>
+      <c r="M310" s="10" t="inlineStr">
+        <is>
+          <t>CRUK eGMS system</t>
+        </is>
+      </c>
+      <c r="N310" s="10" t="inlineStr">
+        <is>
+          <t>Yes — interview</t>
+        </is>
+      </c>
+      <c r="O310" s="10" t="inlineStr">
+        <is>
+          <t>~10%</t>
+        </is>
+      </c>
+      <c r="P310" s="10" t="inlineStr">
+        <is>
+          <t>https://www.cancerresearchuk.org/funding-for-researchers</t>
+        </is>
+      </c>
+      <c r="Q310" s="10" t="inlineStr">
+        <is>
+          <t>CRUK also funds PhD studentships, project awards and clinician scientist fellowships.</t>
+        </is>
+      </c>
+      <c r="R310" s="10" t="inlineStr"/>
+      <c r="S310" s="10" t="inlineStr"/>
+      <c r="T310" s="10" t="inlineStr"/>
+    </row>
+    <row r="311">
+      <c r="A311" s="10" t="inlineStr">
+        <is>
+          <t>G307</t>
+        </is>
+      </c>
+      <c r="B311" s="10" t="inlineStr">
+        <is>
+          <t>British Heart Foundation Fellowships</t>
+        </is>
+      </c>
+      <c r="C311" s="10" t="inlineStr">
+        <is>
+          <t>British Heart Foundation (BHF)</t>
+        </is>
+      </c>
+      <c r="D311" s="10" t="inlineStr">
+        <is>
+          <t>Private (BHF)</t>
+        </is>
+      </c>
+      <c r="E311" s="10" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="F311" s="10" t="inlineStr">
+        <is>
+          <t>Cardiovascular research</t>
+        </is>
+      </c>
+      <c r="G311" s="10" t="inlineStr">
+        <is>
+          <t>PhD candidates → established</t>
+        </is>
+      </c>
+      <c r="H311" s="10" t="inlineStr">
+        <is>
+          <t>The UK's leading heart charity funds the full career ladder, from PhD studentships to intermediate and senior basic science fellowships.</t>
+        </is>
+      </c>
+      <c r="I311" s="10" t="inlineStr">
+        <is>
+          <t>Intermediate fellowships ~£1M+; project grants vary</t>
+        </is>
+      </c>
+      <c r="J311" s="10" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="K311" s="10" t="inlineStr">
+        <is>
+          <t>Cardiovascular researchers at UK institutions</t>
+        </is>
+      </c>
+      <c r="L311" s="10" t="inlineStr">
+        <is>
+          <t>Multiple deadlines per year (check site)</t>
+        </is>
+      </c>
+      <c r="M311" s="10" t="inlineStr">
+        <is>
+          <t>BHF grants portal</t>
+        </is>
+      </c>
+      <c r="N311" s="10" t="inlineStr">
+        <is>
+          <t>Yes — interview for fellowships</t>
+        </is>
+      </c>
+      <c r="O311" s="10" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="P311" s="10" t="inlineStr">
+        <is>
+          <t>https://www.bhf.org.uk/for-professionals/information-for-researchers</t>
+        </is>
+      </c>
+      <c r="Q311" s="10" t="inlineStr">
+        <is>
+          <t>Basic Science and Clinical fellowship tracks run in parallel.</t>
+        </is>
+      </c>
+      <c r="R311" s="10" t="inlineStr"/>
+      <c r="S311" s="10" t="inlineStr"/>
+      <c r="T311" s="10" t="inlineStr"/>
+    </row>
+    <row r="312">
+      <c r="A312" s="10" t="inlineStr">
+        <is>
+          <t>G308</t>
+        </is>
+      </c>
+      <c r="B312" s="10" t="inlineStr">
+        <is>
+          <t>American Cancer Society Research Grants &amp; Fellowships</t>
+        </is>
+      </c>
+      <c r="C312" s="10" t="inlineStr">
+        <is>
+          <t>American Cancer Society (ACS)</t>
+        </is>
+      </c>
+      <c r="D312" s="10" t="inlineStr">
+        <is>
+          <t>Private (ACS)</t>
+        </is>
+      </c>
+      <c r="E312" s="10" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="F312" s="10" t="inlineStr">
+        <is>
+          <t>Cancer research</t>
+        </is>
+      </c>
+      <c r="G312" s="10" t="inlineStr">
+        <is>
+          <t>Early postdoc → early faculty</t>
+        </is>
+      </c>
+      <c r="H312" s="10" t="inlineStr">
+        <is>
+          <t>The largest non-government US cancer funder, supporting postdoctoral fellowships and independent investigator research scholar grants.</t>
+        </is>
+      </c>
+      <c r="I312" s="10" t="inlineStr">
+        <is>
+          <t>Postdoc ~$66k/yr; Research Scholar Grants up to $825k over 4 years</t>
+        </is>
+      </c>
+      <c r="J312" s="10" t="inlineStr">
+        <is>
+          <t>2-4 years</t>
+        </is>
+      </c>
+      <c r="K312" s="10" t="inlineStr">
+        <is>
+          <t>US host institution; postdoc fellowships open to non-US citizens at US institutions</t>
+        </is>
+      </c>
+      <c r="L312" s="10" t="inlineStr">
+        <is>
+          <t>2 rounds/yr (typically ~Apr and ~Oct)</t>
+        </is>
+      </c>
+      <c r="M312" s="10" t="inlineStr">
+        <is>
+          <t>ACS proposalCENTRAL</t>
+        </is>
+      </c>
+      <c r="N312" s="10" t="inlineStr">
+        <is>
+          <t>No — peer review</t>
+        </is>
+      </c>
+      <c r="O312" s="10" t="inlineStr">
+        <is>
+          <t>~10-15%</t>
+        </is>
+      </c>
+      <c r="P312" s="10" t="inlineStr">
+        <is>
+          <t>https://www.cancer.org/research/we-fund-cancer-research.html</t>
+        </is>
+      </c>
+      <c r="Q312" s="10" t="inlineStr">
+        <is>
+          <t>Postdoctoral fellowships are open to international researchers based in the US.</t>
+        </is>
+      </c>
+      <c r="R312" s="10" t="inlineStr"/>
+      <c r="S312" s="10" t="inlineStr"/>
+      <c r="T312" s="10" t="inlineStr"/>
+    </row>
+    <row r="313">
+      <c r="A313" s="10" t="inlineStr">
+        <is>
+          <t>G309</t>
+        </is>
+      </c>
+      <c r="B313" s="10" t="inlineStr">
+        <is>
+          <t>Alzheimer's Association Research Grants</t>
+        </is>
+      </c>
+      <c r="C313" s="10" t="inlineStr">
+        <is>
+          <t>Alzheimer's Association</t>
+        </is>
+      </c>
+      <c r="D313" s="10" t="inlineStr">
+        <is>
+          <t>Private (Alzheimer's Association)</t>
+        </is>
+      </c>
+      <c r="E313" s="10" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F313" s="10" t="inlineStr">
+        <is>
+          <t>Dementia &amp; neurodegeneration</t>
+        </is>
+      </c>
+      <c r="G313" s="10" t="inlineStr">
+        <is>
+          <t>PhD candidates → established</t>
+        </is>
+      </c>
+      <c r="H313" s="10" t="inlineStr">
+        <is>
+          <t>The world's largest non-profit funder of Alzheimer's research, with fellowships, new-investigator grants and clinical trial support.</t>
+        </is>
+      </c>
+      <c r="I313" s="10" t="inlineStr">
+        <is>
+          <t>AARF fellowships ~$175k; AARG grants up to $150k/yr</t>
+        </is>
+      </c>
+      <c r="J313" s="10" t="inlineStr">
+        <is>
+          <t>2-3 years</t>
+        </is>
+      </c>
+      <c r="K313" s="10" t="inlineStr">
+        <is>
+          <t>Researchers worldwide — explicitly international; career-stage-specific tracks</t>
+        </is>
+      </c>
+      <c r="L313" s="10" t="inlineStr">
+        <is>
+          <t>Annual cycle (LOI typically ~autumn; check site)</t>
+        </is>
+      </c>
+      <c r="M313" s="10" t="inlineStr">
+        <is>
+          <t>proposalCENTRAL</t>
+        </is>
+      </c>
+      <c r="N313" s="10" t="inlineStr">
+        <is>
+          <t>No — peer review</t>
+        </is>
+      </c>
+      <c r="O313" s="10" t="inlineStr">
+        <is>
+          <t>~15%</t>
+        </is>
+      </c>
+      <c r="P313" s="10" t="inlineStr">
+        <is>
+          <t>https://www.alz.org/research/for_researchers/grants</t>
+        </is>
+      </c>
+      <c r="Q313" s="10" t="inlineStr">
+        <is>
+          <t>Genuinely global funding — applicants from any country are eligible.</t>
+        </is>
+      </c>
+      <c r="R313" s="10" t="inlineStr"/>
+      <c r="S313" s="10" t="inlineStr"/>
+      <c r="T313" s="10" t="inlineStr"/>
+    </row>
+    <row r="314">
+      <c r="A314" s="10" t="inlineStr">
+        <is>
+          <t>G310</t>
+        </is>
+      </c>
+      <c r="B314" s="10" t="inlineStr">
+        <is>
+          <t>Michael J. Fox Foundation Research Grants</t>
+        </is>
+      </c>
+      <c r="C314" s="10" t="inlineStr">
+        <is>
+          <t>Michael J. Fox Foundation for Parkinson's Research</t>
+        </is>
+      </c>
+      <c r="D314" s="10" t="inlineStr">
+        <is>
+          <t>Private (MJFF)</t>
+        </is>
+      </c>
+      <c r="E314" s="10" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F314" s="10" t="inlineStr">
+        <is>
+          <t>Parkinson's disease research</t>
+        </is>
+      </c>
+      <c r="G314" s="10" t="inlineStr">
+        <is>
+          <t>Postdoc → established</t>
+        </is>
+      </c>
+      <c r="H314" s="10" t="inlineStr">
+        <is>
+          <t>The largest non-profit funder of Parkinson's research, running targeted and open calls worldwide with an emphasis on translation.</t>
+        </is>
+      </c>
+      <c r="I314" s="10" t="inlineStr">
+        <is>
+          <t>Typically $75,000-1,000,000 depending on programme</t>
+        </is>
+      </c>
+      <c r="J314" s="10" t="inlineStr">
+        <is>
+          <t>1-3 years</t>
+        </is>
+      </c>
+      <c r="K314" s="10" t="inlineStr">
+        <is>
+          <t>Researchers at institutions worldwide; programme-specific criteria</t>
+        </is>
+      </c>
+      <c r="L314" s="10" t="inlineStr">
+        <is>
+          <t>Rolling programme of calls (check site)</t>
+        </is>
+      </c>
+      <c r="M314" s="10" t="inlineStr">
+        <is>
+          <t>MJFF grants portal</t>
+        </is>
+      </c>
+      <c r="N314" s="10" t="inlineStr">
+        <is>
+          <t>No — scientific review</t>
+        </is>
+      </c>
+      <c r="O314" s="10" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="P314" s="10" t="inlineStr">
+        <is>
+          <t>https://www.michaeljfox.org/grants</t>
+        </is>
+      </c>
+      <c r="Q314" s="10" t="inlineStr">
+        <is>
+          <t>Very fast, translation-focused review compared with government funders.</t>
+        </is>
+      </c>
+      <c r="R314" s="10" t="inlineStr"/>
+      <c r="S314" s="10" t="inlineStr"/>
+      <c r="T314" s="10" t="inlineStr"/>
+    </row>
+    <row r="315">
+      <c r="A315" s="10" t="inlineStr">
+        <is>
+          <t>G311</t>
+        </is>
+      </c>
+      <c r="B315" s="10" t="inlineStr">
+        <is>
+          <t>Breakthrough T1D (formerly JDRF) Research Grants</t>
+        </is>
+      </c>
+      <c r="C315" s="10" t="inlineStr">
+        <is>
+          <t>Breakthrough T1D</t>
+        </is>
+      </c>
+      <c r="D315" s="10" t="inlineStr">
+        <is>
+          <t>Private (Breakthrough T1D)</t>
+        </is>
+      </c>
+      <c r="E315" s="10" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F315" s="10" t="inlineStr">
+        <is>
+          <t>Type 1 diabetes research</t>
+        </is>
+      </c>
+      <c r="G315" s="10" t="inlineStr">
+        <is>
+          <t>Postdoc → established</t>
+        </is>
+      </c>
+      <c r="H315" s="10" t="inlineStr">
+        <is>
+          <t>The leading global funder of type 1 diabetes research, funding postdoctoral fellowships, career development awards and research projects.</t>
+        </is>
+      </c>
+      <c r="I315" s="10" t="inlineStr">
+        <is>
+          <t>Fellowships ~$60k/yr; career development awards ~$150k/yr</t>
+        </is>
+      </c>
+      <c r="J315" s="10" t="inlineStr">
+        <is>
+          <t>2-5 years</t>
+        </is>
+      </c>
+      <c r="K315" s="10" t="inlineStr">
+        <is>
+          <t>Researchers worldwide at eligible institutions</t>
+        </is>
+      </c>
+      <c r="L315" s="10" t="inlineStr">
+        <is>
+          <t>Annual cycles (check site)</t>
+        </is>
+      </c>
+      <c r="M315" s="10" t="inlineStr">
+        <is>
+          <t>Breakthrough T1D grant portal</t>
+        </is>
+      </c>
+      <c r="N315" s="10" t="inlineStr">
+        <is>
+          <t>No — peer review</t>
+        </is>
+      </c>
+      <c r="O315" s="10" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="P315" s="10" t="inlineStr">
+        <is>
+          <t>https://www.breakthrought1d.org/research/for-researchers/</t>
+        </is>
+      </c>
+      <c r="Q315" s="10" t="inlineStr">
+        <is>
+          <t>Renamed from JDRF in 2024 — older links and papers still use the JDRF name.</t>
+        </is>
+      </c>
+      <c r="R315" s="10" t="inlineStr"/>
+      <c r="S315" s="10" t="inlineStr"/>
+      <c r="T315" s="10" t="inlineStr"/>
+    </row>
+    <row r="316">
+      <c r="A316" s="10" t="inlineStr">
+        <is>
+          <t>G312</t>
+        </is>
+      </c>
+      <c r="B316" s="10" t="inlineStr">
+        <is>
+          <t>Cystic Fibrosis Foundation Research Awards</t>
+        </is>
+      </c>
+      <c r="C316" s="10" t="inlineStr">
+        <is>
+          <t>Cystic Fibrosis Foundation (CFF)</t>
+        </is>
+      </c>
+      <c r="D316" s="10" t="inlineStr">
+        <is>
+          <t>Private (CFF)</t>
+        </is>
+      </c>
+      <c r="E316" s="10" t="inlineStr">
+        <is>
+          <t>USA + international</t>
+        </is>
+      </c>
+      <c r="F316" s="10" t="inlineStr">
+        <is>
+          <t>Cystic fibrosis research</t>
+        </is>
+      </c>
+      <c r="G316" s="10" t="inlineStr">
+        <is>
+          <t>PhD candidates → established</t>
+        </is>
+      </c>
+      <c r="H316" s="10" t="inlineStr">
+        <is>
+          <t>Funds the full pipeline of cystic fibrosis research, from postdoctoral fellowships to clinical trials, and is famous for venture philanthropy successes.</t>
+        </is>
+      </c>
+      <c r="I316" s="10" t="inlineStr">
+        <is>
+          <t>Postdoc fellowships ~$60k/yr; research grants larger</t>
+        </is>
+      </c>
+      <c r="J316" s="10" t="inlineStr">
+        <is>
+          <t>2-4 years</t>
+        </is>
+      </c>
+      <c r="K316" s="10" t="inlineStr">
+        <is>
+          <t>Researchers at eligible institutions; some awards international</t>
+        </is>
+      </c>
+      <c r="L316" s="10" t="inlineStr">
+        <is>
+          <t>Annual cycles (check site)</t>
+        </is>
+      </c>
+      <c r="M316" s="10" t="inlineStr">
+        <is>
+          <t>CFF proposalCENTRAL</t>
+        </is>
+      </c>
+      <c r="N316" s="10" t="inlineStr">
+        <is>
+          <t>No — peer review</t>
+        </is>
+      </c>
+      <c r="O316" s="10" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="P316" s="10" t="inlineStr">
+        <is>
+          <t>https://www.cff.org/researchers</t>
+        </is>
+      </c>
+      <c r="Q316" s="10" t="inlineStr">
+        <is>
+          <t>The CFF's venture-philanthropy model helped produce the CF modulator drugs.</t>
+        </is>
+      </c>
+      <c r="R316" s="10" t="inlineStr"/>
+      <c r="S316" s="10" t="inlineStr"/>
+      <c r="T316" s="10" t="inlineStr"/>
+    </row>
+    <row r="317">
+      <c r="A317" s="10" t="inlineStr">
+        <is>
+          <t>G313</t>
+        </is>
+      </c>
+      <c r="B317" s="10" t="inlineStr">
+        <is>
+          <t>Leukemia &amp; Lymphoma Society Career Development Program</t>
+        </is>
+      </c>
+      <c r="C317" s="10" t="inlineStr">
+        <is>
+          <t>Leukemia &amp; Lymphoma Society (LLS)</t>
+        </is>
+      </c>
+      <c r="D317" s="10" t="inlineStr">
+        <is>
+          <t>Private (LLS)</t>
+        </is>
+      </c>
+      <c r="E317" s="10" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F317" s="10" t="inlineStr">
+        <is>
+          <t>Blood cancer research</t>
+        </is>
+      </c>
+      <c r="G317" s="10" t="inlineStr">
+        <is>
+          <t>Postdoc → early faculty</t>
+        </is>
+      </c>
+      <c r="H317" s="10" t="inlineStr">
+        <is>
+          <t>Career development awards for researchers focused on leukemia, lymphoma and myeloma, from fellow to scholar level.</t>
+        </is>
+      </c>
+      <c r="I317" s="10" t="inlineStr">
+        <is>
+          <t>Fellows ~$65k/yr; Scholars ~$110k/yr</t>
+        </is>
+      </c>
+      <c r="J317" s="10" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="K317" s="10" t="inlineStr">
+        <is>
+          <t>Researchers at institutions worldwide; career-stage tracks</t>
+        </is>
+      </c>
+      <c r="L317" s="10" t="inlineStr">
+        <is>
+          <t>Annual (typically ~Oct; check site)</t>
+        </is>
+      </c>
+      <c r="M317" s="10" t="inlineStr">
+        <is>
+          <t>LLS grants portal</t>
+        </is>
+      </c>
+      <c r="N317" s="10" t="inlineStr">
+        <is>
+          <t>No — peer review</t>
+        </is>
+      </c>
+      <c r="O317" s="10" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="P317" s="10" t="inlineStr">
+        <is>
+          <t>https://www.lls.org/researchers</t>
+        </is>
+      </c>
+      <c r="Q317" s="10" t="inlineStr">
+        <is>
+          <t>International applicants are eligible — unusual for a US disease charity.</t>
+        </is>
+      </c>
+      <c r="R317" s="10" t="inlineStr"/>
+      <c r="S317" s="10" t="inlineStr"/>
+      <c r="T317" s="10" t="inlineStr"/>
+    </row>
+    <row r="318">
+      <c r="A318" s="10" t="inlineStr">
+        <is>
+          <t>G314</t>
+        </is>
+      </c>
+      <c r="B318" s="10" t="inlineStr">
+        <is>
+          <t>MS Society &amp; National MS Society Research Grants</t>
+        </is>
+      </c>
+      <c r="C318" s="10" t="inlineStr">
+        <is>
+          <t>UK MS Society / National Multiple Sclerosis Society (US)</t>
+        </is>
+      </c>
+      <c r="D318" s="10" t="inlineStr">
+        <is>
+          <t>Private (MS charities)</t>
+        </is>
+      </c>
+      <c r="E318" s="10" t="inlineStr">
+        <is>
+          <t>UK &amp; USA</t>
+        </is>
+      </c>
+      <c r="F318" s="10" t="inlineStr">
+        <is>
+          <t>Multiple sclerosis research</t>
+        </is>
+      </c>
+      <c r="G318" s="10" t="inlineStr">
+        <is>
+          <t>PhD candidates → established</t>
+        </is>
+      </c>
+      <c r="H318" s="10" t="inlineStr">
+        <is>
+          <t>The two largest MS charities fund postdoctoral fellowships, project grants and clinical research on multiple sclerosis.</t>
+        </is>
+      </c>
+      <c r="I318" s="10" t="inlineStr">
+        <is>
+          <t>Postdoc fellowships ~$60-70k/yr; project grants larger</t>
+        </is>
+      </c>
+      <c r="J318" s="10" t="inlineStr">
+        <is>
+          <t>2-5 years</t>
+        </is>
+      </c>
+      <c r="K318" s="10" t="inlineStr">
+        <is>
+          <t>Researchers at eligible UK or US institutions respectively</t>
+        </is>
+      </c>
+      <c r="L318" s="10" t="inlineStr">
+        <is>
+          <t>Annual cycles (check each site)</t>
+        </is>
+      </c>
+      <c r="M318" s="10" t="inlineStr">
+        <is>
+          <t>Society grant portals</t>
+        </is>
+      </c>
+      <c r="N318" s="10" t="inlineStr">
+        <is>
+          <t>No — peer review</t>
+        </is>
+      </c>
+      <c r="O318" s="10" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="P318" s="10" t="inlineStr">
+        <is>
+          <t>https://www.nationalmssociety.org/research/for-researchers</t>
+        </is>
+      </c>
+      <c r="Q318" s="10" t="inlineStr">
+        <is>
+          <t>Check both organisations — they fund complementary areas and have separate cycles.</t>
+        </is>
+      </c>
+      <c r="R318" s="10" t="inlineStr"/>
+      <c r="S318" s="10" t="inlineStr"/>
+      <c r="T318" s="10" t="inlineStr"/>
+    </row>
+    <row r="319">
+      <c r="A319" s="10" t="inlineStr">
+        <is>
+          <t>G315</t>
+        </is>
+      </c>
+      <c r="B319" s="10" t="inlineStr">
+        <is>
+          <t>Parkinson's UK Research Grants</t>
+        </is>
+      </c>
+      <c r="C319" s="10" t="inlineStr">
+        <is>
+          <t>Parkinson's UK</t>
+        </is>
+      </c>
+      <c r="D319" s="10" t="inlineStr">
+        <is>
+          <t>Private (Parkinson's UK)</t>
+        </is>
+      </c>
+      <c r="E319" s="10" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="F319" s="10" t="inlineStr">
+        <is>
+          <t>Parkinson's disease research</t>
+        </is>
+      </c>
+      <c r="G319" s="10" t="inlineStr">
+        <is>
+          <t>PhD candidates → established</t>
+        </is>
+      </c>
+      <c r="H319" s="10" t="inlineStr">
+        <is>
+          <t>The UK's leading Parkinson's charity funds studentships, fellowships and project grants, with strong patient involvement in review.</t>
+        </is>
+      </c>
+      <c r="I319" s="10" t="inlineStr">
+        <is>
+          <t>Project grants typically £100k-500k; fellowships larger</t>
+        </is>
+      </c>
+      <c r="J319" s="10" t="inlineStr">
+        <is>
+          <t>1-4 years</t>
+        </is>
+      </c>
+      <c r="K319" s="10" t="inlineStr">
+        <is>
+          <t>Researchers at UK institutions</t>
+        </is>
+      </c>
+      <c r="L319" s="10" t="inlineStr">
+        <is>
+          <t>Annual rounds (check site)</t>
+        </is>
+      </c>
+      <c r="M319" s="10" t="inlineStr">
+        <is>
+          <t>Parkinson's UK grants portal</t>
+        </is>
+      </c>
+      <c r="N319" s="10" t="inlineStr">
+        <is>
+          <t>Yes — for fellowships</t>
+        </is>
+      </c>
+      <c r="O319" s="10" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="P319" s="10" t="inlineStr">
+        <is>
+          <t>https://www.parkinsons.org.uk/research/apply-grant</t>
+        </is>
+      </c>
+      <c r="Q319" s="10" t="inlineStr">
+        <is>
+          <t>People with Parkinson's sit on the review panels — write your lay summary carefully.</t>
+        </is>
+      </c>
+      <c r="R319" s="10" t="inlineStr"/>
+      <c r="S319" s="10" t="inlineStr"/>
+      <c r="T319" s="10" t="inlineStr"/>
+    </row>
+    <row r="320">
+      <c r="A320" s="10" t="inlineStr">
+        <is>
+          <t>G316</t>
+        </is>
+      </c>
+      <c r="B320" s="10" t="inlineStr">
+        <is>
+          <t>Diabetes UK Research Grants</t>
+        </is>
+      </c>
+      <c r="C320" s="10" t="inlineStr">
+        <is>
+          <t>Diabetes UK</t>
+        </is>
+      </c>
+      <c r="D320" s="10" t="inlineStr">
+        <is>
+          <t>Private (Diabetes UK)</t>
+        </is>
+      </c>
+      <c r="E320" s="10" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="F320" s="10" t="inlineStr">
+        <is>
+          <t>Diabetes research</t>
+        </is>
+      </c>
+      <c r="G320" s="10" t="inlineStr">
+        <is>
+          <t>PhD candidates → established</t>
+        </is>
+      </c>
+      <c r="H320" s="10" t="inlineStr">
+        <is>
+          <t>Funds diabetes research across basic science, clinical studies and psychosocial research, including fellowships and studentships.</t>
+        </is>
+      </c>
+      <c r="I320" s="10" t="inlineStr">
+        <is>
+          <t>Project grants up to ~£500k; fellowships salary + costs</t>
+        </is>
+      </c>
+      <c r="J320" s="10" t="inlineStr">
+        <is>
+          <t>1-5 years</t>
+        </is>
+      </c>
+      <c r="K320" s="10" t="inlineStr">
+        <is>
+          <t>Researchers at UK institutions</t>
+        </is>
+      </c>
+      <c r="L320" s="10" t="inlineStr">
+        <is>
+          <t>Annual rounds (check site)</t>
+        </is>
+      </c>
+      <c r="M320" s="10" t="inlineStr">
+        <is>
+          <t>Diabetes UK grants portal</t>
+        </is>
+      </c>
+      <c r="N320" s="10" t="inlineStr">
+        <is>
+          <t>Yes — for fellowships</t>
+        </is>
+      </c>
+      <c r="O320" s="10" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="P320" s="10" t="inlineStr">
+        <is>
+          <t>https://www.diabetes.org.uk/research/for-researchers</t>
+        </is>
+      </c>
+      <c r="Q320" s="10" t="inlineStr">
+        <is>
+          <t>Also funds a dedicated stream on the psychology of living with diabetes.</t>
+        </is>
+      </c>
+      <c r="R320" s="10" t="inlineStr"/>
+      <c r="S320" s="10" t="inlineStr"/>
+      <c r="T320" s="10" t="inlineStr"/>
+    </row>
+    <row r="321">
+      <c r="A321" s="10" t="inlineStr">
+        <is>
+          <t>G317</t>
+        </is>
+      </c>
+      <c r="B321" s="10" t="inlineStr">
+        <is>
+          <t>Fondation pour la Recherche Médicale (FRM)</t>
+        </is>
+      </c>
+      <c r="C321" s="10" t="inlineStr">
+        <is>
+          <t>Fondation pour la Recherche Médicale</t>
+        </is>
+      </c>
+      <c r="D321" s="10" t="inlineStr">
+        <is>
+          <t>Private (FRM)</t>
+        </is>
+      </c>
+      <c r="E321" s="10" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F321" s="10" t="inlineStr">
+        <is>
+          <t>Biomedical &amp; health research</t>
+        </is>
+      </c>
+      <c r="G321" s="10" t="inlineStr">
+        <is>
+          <t>PhD candidates → established</t>
+        </is>
+      </c>
+      <c r="H321" s="10" t="inlineStr">
+        <is>
+          <t>France's largest private biomedical funder, supporting doctoral fourth-year funding, postdoctoral returns and team projects.</t>
+        </is>
+      </c>
+      <c r="I321" s="10" t="inlineStr">
+        <is>
+          <t>PhD 4th-year ~€40k; postdoc ~€60k/yr; team grants €300-500k</t>
+        </is>
+      </c>
+      <c r="J321" s="10" t="inlineStr">
+        <is>
+          <t>1-3 years</t>
+        </is>
+      </c>
+      <c r="K321" s="10" t="inlineStr">
+        <is>
+          <t>Researchers in French laboratories; nationality-open</t>
+        </is>
+      </c>
+      <c r="L321" s="10" t="inlineStr">
+        <is>
+          <t>Annual calls per scheme (check site)</t>
+        </is>
+      </c>
+      <c r="M321" s="10" t="inlineStr">
+        <is>
+          <t>FRM online portal</t>
+        </is>
+      </c>
+      <c r="N321" s="10" t="inlineStr">
+        <is>
+          <t>No — scientific committee</t>
+        </is>
+      </c>
+      <c r="O321" s="10" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="P321" s="10" t="inlineStr">
+        <is>
+          <t>https://www.frm.org/</t>
+        </is>
+      </c>
+      <c r="Q321" s="10" t="inlineStr">
+        <is>
+          <t>The fourth-year doctoral funding is a lifeline where three-year contracts run out.</t>
+        </is>
+      </c>
+      <c r="R321" s="10" t="inlineStr"/>
+      <c r="S321" s="10" t="inlineStr"/>
+      <c r="T321" s="10" t="inlineStr"/>
+    </row>
+    <row r="322">
+      <c r="A322" s="10" t="inlineStr">
+        <is>
+          <t>G318</t>
+        </is>
+      </c>
+      <c r="B322" s="10" t="inlineStr">
+        <is>
+          <t>AIRC Fellowships and Grants (Italy)</t>
+        </is>
+      </c>
+      <c r="C322" s="10" t="inlineStr">
+        <is>
+          <t>Fondazione AIRC per la Ricerca sul Cancro</t>
+        </is>
+      </c>
+      <c r="D322" s="10" t="inlineStr">
+        <is>
+          <t>Private (AIRC)</t>
+        </is>
+      </c>
+      <c r="E322" s="10" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="F322" s="10" t="inlineStr">
+        <is>
+          <t>Cancer research</t>
+        </is>
+      </c>
+      <c r="G322" s="10" t="inlineStr">
+        <is>
+          <t>PhD candidates → established</t>
+        </is>
+      </c>
+      <c r="H322" s="10" t="inlineStr">
+        <is>
+          <t>Italy's dominant cancer research funder, offering fellowships for Italy and abroad plus investigator and start-up grants.</t>
+        </is>
+      </c>
+      <c r="I322" s="10" t="inlineStr">
+        <is>
+          <t>Fellowships ~€30k/yr; Start-Up Grants up to €800k</t>
+        </is>
+      </c>
+      <c r="J322" s="10" t="inlineStr">
+        <is>
+          <t>1-6 years</t>
+        </is>
+      </c>
+      <c r="K322" s="10" t="inlineStr">
+        <is>
+          <t>Researchers in Italy; some fellowships fund Italians going abroad or returning</t>
+        </is>
+      </c>
+      <c r="L322" s="10" t="inlineStr">
+        <is>
+          <t>Annual calls (check site)</t>
+        </is>
+      </c>
+      <c r="M322" s="10" t="inlineStr">
+        <is>
+          <t>AIRC online system</t>
+        </is>
+      </c>
+      <c r="N322" s="10" t="inlineStr">
+        <is>
+          <t>Yes — for larger grants</t>
+        </is>
+      </c>
+      <c r="O322" s="10" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="P322" s="10" t="inlineStr">
+        <is>
+          <t>https://www.airc.it/</t>
+        </is>
+      </c>
+      <c r="Q322" s="10" t="inlineStr">
+        <is>
+          <t>The Start-Up Grant is one of the best routes to independence for cancer researchers in Italy.</t>
+        </is>
+      </c>
+      <c r="R322" s="10" t="inlineStr"/>
+      <c r="S322" s="10" t="inlineStr"/>
+      <c r="T322" s="10" t="inlineStr"/>
+    </row>
+    <row r="323">
+      <c r="A323" s="10" t="inlineStr">
+        <is>
+          <t>G319</t>
+        </is>
+      </c>
+      <c r="B323" s="10" t="inlineStr">
+        <is>
+          <t>Deutsche Krebshilfe (German Cancer Aid) Funding</t>
+        </is>
+      </c>
+      <c r="C323" s="10" t="inlineStr">
+        <is>
+          <t>Deutsche Krebshilfe</t>
+        </is>
+      </c>
+      <c r="D323" s="10" t="inlineStr">
+        <is>
+          <t>Private (Deutsche Krebshilfe)</t>
+        </is>
+      </c>
+      <c r="E323" s="10" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="F323" s="10" t="inlineStr">
+        <is>
+          <t>Cancer research</t>
+        </is>
+      </c>
+      <c r="G323" s="10" t="inlineStr">
+        <is>
+          <t>PhD candidates → established</t>
+        </is>
+      </c>
+      <c r="H323" s="10" t="inlineStr">
+        <is>
+          <t>Germany's leading cancer charity funds research projects, priority programmes and the Mildred Scheel career development fellowships.</t>
+        </is>
+      </c>
+      <c r="I323" s="10" t="inlineStr">
+        <is>
+          <t>Project grants €200k-1M+; Mildred Scheel fellowships salary + costs</t>
+        </is>
+      </c>
+      <c r="J323" s="10" t="inlineStr">
+        <is>
+          <t>2-3 years typical</t>
+        </is>
+      </c>
+      <c r="K323" s="10" t="inlineStr">
+        <is>
+          <t>Researchers at German institutions; Mildred Scheel supports stays abroad</t>
+        </is>
+      </c>
+      <c r="L323" s="10" t="inlineStr">
+        <is>
+          <t>Rolling / periodic (check site)</t>
+        </is>
+      </c>
+      <c r="M323" s="10" t="inlineStr">
+        <is>
+          <t>Deutsche Krebshilfe portal</t>
+        </is>
+      </c>
+      <c r="N323" s="10" t="inlineStr">
+        <is>
+          <t>No — expert review</t>
+        </is>
+      </c>
+      <c r="O323" s="10" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="P323" s="10" t="inlineStr">
+        <is>
+          <t>https://www.krebshilfe.de/</t>
+        </is>
+      </c>
+      <c r="Q323" s="10" t="inlineStr">
+        <is>
+          <t>Mildred Scheel Early Career Centres also fund structured clinician-scientist programmes.</t>
+        </is>
+      </c>
+      <c r="R323" s="10" t="inlineStr"/>
+      <c r="S323" s="10" t="inlineStr"/>
+      <c r="T323" s="10" t="inlineStr"/>
+    </row>
+    <row r="324">
+      <c r="A324" s="10" t="inlineStr">
+        <is>
+          <t>G320</t>
+        </is>
+      </c>
+      <c r="B324" s="10" t="inlineStr">
+        <is>
+          <t>Fondazione Telethon (Italy) — Genetic Disease Research</t>
+        </is>
+      </c>
+      <c r="C324" s="10" t="inlineStr">
+        <is>
+          <t>Fondazione Telethon</t>
+        </is>
+      </c>
+      <c r="D324" s="10" t="inlineStr">
+        <is>
+          <t>Private (Telethon)</t>
+        </is>
+      </c>
+      <c r="E324" s="10" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="F324" s="10" t="inlineStr">
+        <is>
+          <t>Rare genetic diseases</t>
+        </is>
+      </c>
+      <c r="G324" s="10" t="inlineStr">
+        <is>
+          <t>PhD candidates → established</t>
+        </is>
+      </c>
+      <c r="H324" s="10" t="inlineStr">
+        <is>
+          <t>Italy's dedicated funder for rare genetic disease research, from basic mechanisms through to gene therapy trials.</t>
+        </is>
+      </c>
+      <c r="I324" s="10" t="inlineStr">
+        <is>
+          <t>Project grants typically €150k-500k</t>
+        </is>
+      </c>
+      <c r="J324" s="10" t="inlineStr">
+        <is>
+          <t>3 years typical</t>
+        </is>
+      </c>
+      <c r="K324" s="10" t="inlineStr">
+        <is>
+          <t>Researchers at Italian institutions (some international collaborations)</t>
+        </is>
+      </c>
+      <c r="L324" s="10" t="inlineStr">
+        <is>
+          <t>Annual calls (check site)</t>
+        </is>
+      </c>
+      <c r="M324" s="10" t="inlineStr">
+        <is>
+          <t>Telethon online system</t>
+        </is>
+      </c>
+      <c r="N324" s="10" t="inlineStr">
+        <is>
+          <t>No — international peer review</t>
+        </is>
+      </c>
+      <c r="O324" s="10" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="P324" s="10" t="inlineStr">
+        <is>
+          <t>https://www.telethon.it/en/</t>
+        </is>
+      </c>
+      <c r="Q324" s="10" t="inlineStr">
+        <is>
+          <t>Behind several of the world's first approved gene therapies — strong translational track record.</t>
+        </is>
+      </c>
+      <c r="R324" s="10" t="inlineStr"/>
+      <c r="S324" s="10" t="inlineStr"/>
+      <c r="T324" s="10" t="inlineStr"/>
+    </row>
+    <row r="325">
+      <c r="A325" s="10" t="inlineStr">
+        <is>
+          <t>G321</t>
+        </is>
+      </c>
+      <c r="B325" s="10" t="inlineStr">
+        <is>
+          <t>Worldwide Cancer Research Grants</t>
+        </is>
+      </c>
+      <c r="C325" s="10" t="inlineStr">
+        <is>
+          <t>Worldwide Cancer Research</t>
+        </is>
+      </c>
+      <c r="D325" s="10" t="inlineStr">
+        <is>
+          <t>Private (WCR)</t>
+        </is>
+      </c>
+      <c r="E325" s="10" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F325" s="10" t="inlineStr">
+        <is>
+          <t>Cancer research (discovery)</t>
+        </is>
+      </c>
+      <c r="G325" s="10" t="inlineStr">
+        <is>
+          <t>Any / Established</t>
+        </is>
+      </c>
+      <c r="H325" s="10" t="inlineStr">
+        <is>
+          <t>Funds early-stage discovery cancer research anywhere in the world, deliberately backing unconventional ideas.</t>
+        </is>
+      </c>
+      <c r="I325" s="10" t="inlineStr">
+        <is>
+          <t>Up to ~£250,000</t>
+        </is>
+      </c>
+      <c r="J325" s="10" t="inlineStr">
+        <is>
+          <t>3 years</t>
+        </is>
+      </c>
+      <c r="K325" s="10" t="inlineStr">
+        <is>
+          <t>Researchers at institutions in any country</t>
+        </is>
+      </c>
+      <c r="L325" s="10" t="inlineStr">
+        <is>
+          <t>Annual round (typically ~autumn; check site)</t>
+        </is>
+      </c>
+      <c r="M325" s="10" t="inlineStr">
+        <is>
+          <t>WCR grants portal</t>
+        </is>
+      </c>
+      <c r="N325" s="10" t="inlineStr">
+        <is>
+          <t>No — peer review</t>
+        </is>
+      </c>
+      <c r="O325" s="10" t="inlineStr">
+        <is>
+          <t>~10%</t>
+        </is>
+      </c>
+      <c r="P325" s="10" t="inlineStr">
+        <is>
+          <t>https://www.worldwidecancerresearch.org/for-researchers/</t>
+        </is>
+      </c>
+      <c r="Q325" s="10" t="inlineStr">
+        <is>
+          <t>Genuinely international with no host-country restriction — rare among cancer charities.</t>
+        </is>
+      </c>
+      <c r="R325" s="10" t="inlineStr"/>
+      <c r="S325" s="10" t="inlineStr"/>
+      <c r="T325" s="10" t="inlineStr"/>
+    </row>
+    <row r="326">
+      <c r="A326" s="10" t="inlineStr">
+        <is>
+          <t>G322</t>
+        </is>
+      </c>
+      <c r="B326" s="10" t="inlineStr">
+        <is>
+          <t>MQ Mental Health Research Fellowships</t>
+        </is>
+      </c>
+      <c r="C326" s="10" t="inlineStr">
+        <is>
+          <t>MQ Mental Health Research</t>
+        </is>
+      </c>
+      <c r="D326" s="10" t="inlineStr">
+        <is>
+          <t>Private (MQ)</t>
+        </is>
+      </c>
+      <c r="E326" s="10" t="inlineStr">
+        <is>
+          <t>United Kingdom + international</t>
+        </is>
+      </c>
+      <c r="F326" s="10" t="inlineStr">
+        <is>
+          <t>Mental health research</t>
+        </is>
+      </c>
+      <c r="G326" s="10" t="inlineStr">
+        <is>
+          <t>Early postdoc → group leader</t>
+        </is>
+      </c>
+      <c r="H326" s="10" t="inlineStr">
+        <is>
+          <t>The UK's leading mental health research charity funds fellowships and projects across neuroscience, psychology and data science.</t>
+        </is>
+      </c>
+      <c r="I326" s="10" t="inlineStr">
+        <is>
+          <t>Fellowships up to ~£225,000</t>
+        </is>
+      </c>
+      <c r="J326" s="10" t="inlineStr">
+        <is>
+          <t>3 years</t>
+        </is>
+      </c>
+      <c r="K326" s="10" t="inlineStr">
+        <is>
+          <t>Early-career researchers; UK-based and some international eligibility</t>
+        </is>
+      </c>
+      <c r="L326" s="10" t="inlineStr">
+        <is>
+          <t>Annual calls (check site)</t>
+        </is>
+      </c>
+      <c r="M326" s="10" t="inlineStr">
+        <is>
+          <t>MQ grants portal</t>
+        </is>
+      </c>
+      <c r="N326" s="10" t="inlineStr">
+        <is>
+          <t>Yes — interview</t>
+        </is>
+      </c>
+      <c r="O326" s="10" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="P326" s="10" t="inlineStr">
+        <is>
+          <t>https://www.mqmentalhealth.org/research/</t>
+        </is>
+      </c>
+      <c r="Q326" s="10" t="inlineStr">
+        <is>
+          <t>One of very few dedicated funders for mental health science outside government.</t>
+        </is>
+      </c>
+      <c r="R326" s="10" t="inlineStr"/>
+      <c r="S326" s="10" t="inlineStr"/>
+      <c r="T326" s="10" t="inlineStr"/>
+    </row>
+    <row r="327">
+      <c r="A327" s="10" t="inlineStr">
+        <is>
+          <t>G323</t>
+        </is>
+      </c>
+      <c r="B327" s="10" t="inlineStr">
+        <is>
+          <t>Health Research Board (HRB) Ireland</t>
+        </is>
+      </c>
+      <c r="C327" s="10" t="inlineStr">
+        <is>
+          <t>Health Research Board</t>
+        </is>
+      </c>
+      <c r="D327" s="10" t="inlineStr">
+        <is>
+          <t>Ireland (HRB)</t>
+        </is>
+      </c>
+      <c r="E327" s="10" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="F327" s="10" t="inlineStr">
+        <is>
+          <t>Health &amp; biomedical research</t>
+        </is>
+      </c>
+      <c r="G327" s="10" t="inlineStr">
+        <is>
+          <t>PhD candidates → established</t>
+        </is>
+      </c>
+      <c r="H327" s="10" t="inlineStr">
+        <is>
+          <t>Ireland's national health research funder, with emerging investigator awards, applied partnership awards and PhD training programmes.</t>
+        </is>
+      </c>
+      <c r="I327" s="10" t="inlineStr">
+        <is>
+          <t>Emerging Investigator Awards up to ~€500k; other schemes vary</t>
+        </is>
+      </c>
+      <c r="J327" s="10" t="inlineStr">
+        <is>
+          <t>2-5 years</t>
+        </is>
+      </c>
+      <c r="K327" s="10" t="inlineStr">
+        <is>
+          <t>Researchers at Irish host institutions</t>
+        </is>
+      </c>
+      <c r="L327" s="10" t="inlineStr">
+        <is>
+          <t>Annual calls per scheme (check site)</t>
+        </is>
+      </c>
+      <c r="M327" s="10" t="inlineStr">
+        <is>
+          <t>HRB online system</t>
+        </is>
+      </c>
+      <c r="N327" s="10" t="inlineStr">
+        <is>
+          <t>Yes — for larger awards</t>
+        </is>
+      </c>
+      <c r="O327" s="10" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="P327" s="10" t="inlineStr">
+        <is>
+          <t>https://www.hrb.ie/funding/</t>
+        </is>
+      </c>
+      <c r="Q327" s="10" t="inlineStr">
+        <is>
+          <t>Strong emphasis on patient and public involvement in the research design.</t>
+        </is>
+      </c>
+      <c r="R327" s="10" t="inlineStr"/>
+      <c r="S327" s="10" t="inlineStr"/>
+      <c r="T327" s="10" t="inlineStr"/>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>G324</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Google PhD Fellowship Program</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>Corporate (Google)</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>Computer science, AI &amp; related fields</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>PhD candidates</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>Supports outstanding graduate students in computer science and related areas, pairing each fellow with a Google research mentor.</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>Full tuition and fees + stipend (regionally set, typically 2-3 years)</t>
+        </is>
+      </c>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t>2-3 years (region-dependent)</t>
+        </is>
+      </c>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>PhD students nominated by their university; regional programmes for Africa, Asia-Pacific, Europe, India, Latin America, North America</t>
+        </is>
+      </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>Annual — nomination via your university (typically ~spring)</t>
+        </is>
+      </c>
+      <c r="M328" t="inlineStr">
+        <is>
+          <t>University nomination only</t>
+        </is>
+      </c>
+      <c r="N328" t="inlineStr">
+        <is>
+          <t>No — Google review panel</t>
+        </is>
+      </c>
+      <c r="O328" t="inlineStr">
+        <is>
+          <t>Very competitive</t>
+        </is>
+      </c>
+      <c r="P328" t="inlineStr">
+        <is>
+          <t>https://research.google/programs-and-events/phd-fellowship/</t>
+        </is>
+      </c>
+      <c r="Q328" t="inlineStr">
+        <is>
+          <t>Universities may nominate only a limited number, so the internal deadline is the real one.</t>
+        </is>
+      </c>
+      <c r="R328" t="inlineStr"/>
+      <c r="S328" t="inlineStr"/>
+      <c r="T328" t="inlineStr"/>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>G325</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Google Research Scholar Program</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>Corporate (Google)</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>Computer science, AI &amp; related fields</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>Early faculty</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>Unrestricted gifts supporting early-career professors pursuing research in computing and related fields.</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>Up to $60,000 (unrestricted gift)</t>
+        </is>
+      </c>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>1 year</t>
+        </is>
+      </c>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Faculty within ~7 years of their PhD at an eligible institution worldwide</t>
+        </is>
+      </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>Annual call (check site)</t>
+        </is>
+      </c>
+      <c r="M329" t="inlineStr">
+        <is>
+          <t>Google online application</t>
+        </is>
+      </c>
+      <c r="N329" t="inlineStr">
+        <is>
+          <t>No — internal review</t>
+        </is>
+      </c>
+      <c r="O329" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="P329" t="inlineStr">
+        <is>
+          <t>https://research.google/programs-and-events/research-scholar-program/</t>
+        </is>
+      </c>
+      <c r="Q329" t="inlineStr">
+        <is>
+          <t>Unrestricted funds are unusually flexible — no detailed budget justification required.</t>
+        </is>
+      </c>
+      <c r="R329" t="inlineStr"/>
+      <c r="S329" t="inlineStr"/>
+      <c r="T329" t="inlineStr"/>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>G326</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Microsoft Research PhD Fellowship</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>Microsoft Research</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>Corporate (Microsoft)</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>International (regional programmes)</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>Computing, AI &amp; interdisciplinary science</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>PhD candidates</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>Two-year fellowships for exceptional PhD students in computing-related fields, with mentorship and an optional research internship.</t>
+        </is>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>Tuition and fees + stipend + conference allowance</t>
+        </is>
+      </c>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>2 years</t>
+        </is>
+      </c>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>PhD students at eligible universities; separate programmes for the Americas, EMEA and Asia</t>
+        </is>
+      </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>Annual, region-specific (check site)</t>
+        </is>
+      </c>
+      <c r="M330" t="inlineStr">
+        <is>
+          <t>University nomination or direct (varies by region)</t>
+        </is>
+      </c>
+      <c r="N330" t="inlineStr">
+        <is>
+          <t>Yes — for some regions</t>
+        </is>
+      </c>
+      <c r="O330" t="inlineStr">
+        <is>
+          <t>Very competitive</t>
+        </is>
+      </c>
+      <c r="P330" t="inlineStr">
+        <is>
+          <t>https://www.microsoft.com/en-us/research/academic-program/phd-fellowship/</t>
+        </is>
+      </c>
+      <c r="Q330" t="inlineStr">
+        <is>
+          <t>Microsoft also runs Accelerating Foundation Models Research with compute grants.</t>
+        </is>
+      </c>
+      <c r="R330" t="inlineStr"/>
+      <c r="S330" t="inlineStr"/>
+      <c r="T330" t="inlineStr"/>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>G327</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Meta Research PhD Fellowship</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>Corporate (Meta)</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>Computer science, AI &amp; related fields</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>PhD candidates</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>Supports promising doctoral students working in areas relevant to Meta's research, with two years of funding and community events.</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>Tuition and fees + ~$42,000/yr stipend + travel</t>
+        </is>
+      </c>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>2 years</t>
+        </is>
+      </c>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>PhD students worldwide in relevant fields; apply directly</t>
+        </is>
+      </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>Annual (typically ~Sep-Oct; check site)</t>
+        </is>
+      </c>
+      <c r="M331" t="inlineStr">
+        <is>
+          <t>Meta online application</t>
+        </is>
+      </c>
+      <c r="N331" t="inlineStr">
+        <is>
+          <t>No — research review</t>
+        </is>
+      </c>
+      <c r="O331" t="inlineStr">
+        <is>
+          <t>Very competitive</t>
+        </is>
+      </c>
+      <c r="P331" t="inlineStr">
+        <is>
+          <t>https://research.facebook.com/fellowship/</t>
+        </is>
+      </c>
+      <c r="Q331" t="inlineStr">
+        <is>
+          <t>Direct application, no university nomination needed — unlike Google's programme.</t>
+        </is>
+      </c>
+      <c r="R331" t="inlineStr"/>
+      <c r="S331" t="inlineStr"/>
+      <c r="T331" t="inlineStr"/>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>G328</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>NVIDIA Graduate Fellowship &amp; Academic Grant Program</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>Corporate (NVIDIA)</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>AI, graphics, HPC &amp; computational science</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>PhD candidates &amp; academic researchers</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>Two tracks: fellowships for PhD students doing GPU-accelerated research, and hardware/compute grants for academic labs.</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>Fellowship up to $60,000; Academic grants provide GPUs or cloud compute</t>
+        </is>
+      </c>
+      <c r="J332" t="inlineStr">
+        <is>
+          <t>1 year (fellowship, renewable)</t>
+        </is>
+      </c>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>PhD students with completed research using GPU computing; academics for hardware grants</t>
+        </is>
+      </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>Fellowship annual (~Sep); grants rolling</t>
+        </is>
+      </c>
+      <c r="M332" t="inlineStr">
+        <is>
+          <t>NVIDIA online application</t>
+        </is>
+      </c>
+      <c r="N332" t="inlineStr">
+        <is>
+          <t>No — technical review</t>
+        </is>
+      </c>
+      <c r="O332" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="P332" t="inlineStr">
+        <is>
+          <t>https://www.nvidia.com/en-us/industries/higher-education-research/graduate-fellowships/</t>
+        </is>
+      </c>
+      <c r="Q332" t="inlineStr">
+        <is>
+          <t>The hardware grant programme is much less competitive than the fellowship — worth knowing.</t>
+        </is>
+      </c>
+      <c r="R332" t="inlineStr"/>
+      <c r="S332" t="inlineStr"/>
+      <c r="T332" t="inlineStr"/>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>G329</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>IBM PhD Fellowship Program</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>IBM Research</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>Corporate (IBM)</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>AI, quantum, computing &amp; hybrid cloud</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>PhD candidates</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>Supports doctoral students working in areas of mutual interest with IBM Research, including quantum computing and AI.</t>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>Stipend + education allowance (typically 2 years)</t>
+        </is>
+      </c>
+      <c r="J333" t="inlineStr">
+        <is>
+          <t>2 years</t>
+        </is>
+      </c>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>PhD students nominated by a faculty adviser at an eligible university worldwide</t>
+        </is>
+      </c>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>Annual (nomination typically ~autumn; check site)</t>
+        </is>
+      </c>
+      <c r="M333" t="inlineStr">
+        <is>
+          <t>Faculty nomination</t>
+        </is>
+      </c>
+      <c r="N333" t="inlineStr">
+        <is>
+          <t>No — IBM review</t>
+        </is>
+      </c>
+      <c r="O333" t="inlineStr">
+        <is>
+          <t>Very competitive</t>
+        </is>
+      </c>
+      <c r="P333" t="inlineStr">
+        <is>
+          <t>https://research.ibm.com/university/awards/fellowships.html</t>
+        </is>
+      </c>
+      <c r="Q333" t="inlineStr">
+        <is>
+          <t>Requires faculty nomination and usually a research connection to IBM's areas.</t>
+        </is>
+      </c>
+      <c r="R333" t="inlineStr"/>
+      <c r="S333" t="inlineStr"/>
+      <c r="T333" t="inlineStr"/>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>G330</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Amazon Research Awards</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>Corporate (Amazon)</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>AI, machine learning, robotics &amp; cloud</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>Early faculty → established</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>Unrestricted awards plus AWS credits for academic researchers working in Amazon's areas of scientific interest.</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>Up to $80,000 cash + up to $40,000 AWS credits</t>
+        </is>
+      </c>
+      <c r="J334" t="inlineStr">
+        <is>
+          <t>1 year</t>
+        </is>
+      </c>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Faculty at accredited universities worldwide; call-topic specific</t>
+        </is>
+      </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>Periodic calls (check site)</t>
+        </is>
+      </c>
+      <c r="M334" t="inlineStr">
+        <is>
+          <t>Amazon Research Awards portal</t>
+        </is>
+      </c>
+      <c r="N334" t="inlineStr">
+        <is>
+          <t>No — internal review</t>
+        </is>
+      </c>
+      <c r="O334" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="P334" t="inlineStr">
+        <is>
+          <t>https://www.amazon.science/research-awards</t>
+        </is>
+      </c>
+      <c r="Q334" t="inlineStr">
+        <is>
+          <t>The AWS credit component alone can be transformative for compute-heavy projects.</t>
+        </is>
+      </c>
+      <c r="R334" t="inlineStr"/>
+      <c r="S334" t="inlineStr"/>
+      <c r="T334" t="inlineStr"/>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>G331</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Roche Postdoctoral Fellowship (RPF) Programme</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>F. Hoffmann-La Roche</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>Corporate (Roche)</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>Switzerland, USA, Germany &amp; other Roche sites</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>Biomedical &amp; pharmaceutical research</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>Early postdoc</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>Three-year postdoctoral positions run jointly between a Roche research site and an academic laboratory, on pre-competitive science.</t>
+        </is>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>Full Roche salary and benefits + research budget</t>
+        </is>
+      </c>
+      <c r="J335" t="inlineStr">
+        <is>
+          <t>3 years</t>
+        </is>
+      </c>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>PhD holders; project jointly proposed by a Roche scientist and an academic supervisor</t>
+        </is>
+      </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t>Two calls per year (check site)</t>
+        </is>
+      </c>
+      <c r="M335" t="inlineStr">
+        <is>
+          <t>Joint proposal via a Roche scientist</t>
+        </is>
+      </c>
+      <c r="N335" t="inlineStr">
+        <is>
+          <t>Yes — interview</t>
+        </is>
+      </c>
+      <c r="O335" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="P335" t="inlineStr">
+        <is>
+          <t>https://www.roche.com/careers/our-locations/switzerland/rpf</t>
+        </is>
+      </c>
+      <c r="Q335" t="inlineStr">
+        <is>
+          <t>Publication is expected — this is genuinely academic-style research inside industry.</t>
+        </is>
+      </c>
+      <c r="R335" t="inlineStr"/>
+      <c r="S335" t="inlineStr"/>
+      <c r="T335" t="inlineStr"/>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>G332</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Novartis FreeNovation &amp; Novartis Foundation Grants</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>Novartis</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>Corporate (Novartis)</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>Biomedical &amp; life sciences</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>Any / Established</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>FreeNovation funds unconventional, high-risk biomedical ideas from external researchers, with a deliberately light application process.</t>
+        </is>
+      </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>Typically CHF 100,000-200,000</t>
+        </is>
+      </c>
+      <c r="J336" t="inlineStr">
+        <is>
+          <t>1-2 years</t>
+        </is>
+      </c>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>Academic researchers worldwide; open, unconstrained topics within life sciences</t>
+        </is>
+      </c>
+      <c r="L336" t="inlineStr">
+        <is>
+          <t>Periodic calls (check site)</t>
+        </is>
+      </c>
+      <c r="M336" t="inlineStr">
+        <is>
+          <t>Novartis online submission</t>
+        </is>
+      </c>
+      <c r="N336" t="inlineStr">
+        <is>
+          <t>No — internal panel</t>
+        </is>
+      </c>
+      <c r="O336" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="P336" t="inlineStr">
+        <is>
+          <t>https://www.novartis.com/research-development/research-collaborations</t>
+        </is>
+      </c>
+      <c r="Q336" t="inlineStr">
+        <is>
+          <t>Deliberately short applications — designed to fund ideas that would fail conventional review.</t>
+        </is>
+      </c>
+      <c r="R336" t="inlineStr"/>
+      <c r="S336" t="inlineStr"/>
+      <c r="T336" t="inlineStr"/>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>G333</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Bayer Foundation Fellowships (Jeff Schell &amp; Otto Bayer)</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>Bayer Foundation</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>Corporate (Bayer Foundation)</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>Life sciences, agriculture &amp; medicine</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>Master's, PhD &amp; postdocs</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>Fellowships supporting talented students and early researchers in life sciences, medicine, agriculture and sustainability, including research stays abroad.</t>
+        </is>
+      </c>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>Typically €5,000-15,000 per fellowship (project-dependent)</t>
+        </is>
+      </c>
+      <c r="J337" t="inlineStr">
+        <is>
+          <t>Months to 1 year</t>
+        </is>
+      </c>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Students and early-career researchers; specific fellowship tracks by field and career stage</t>
+        </is>
+      </c>
+      <c r="L337" t="inlineStr">
+        <is>
+          <t>Annual call (typically ~summer; check site)</t>
+        </is>
+      </c>
+      <c r="M337" t="inlineStr">
+        <is>
+          <t>Bayer Foundation online portal</t>
+        </is>
+      </c>
+      <c r="N337" t="inlineStr">
+        <is>
+          <t>No — selection committee</t>
+        </is>
+      </c>
+      <c r="O337" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="P337" t="inlineStr">
+        <is>
+          <t>https://www.bayer-foundation.com/</t>
+        </is>
+      </c>
+      <c r="Q337" t="inlineStr">
+        <is>
+          <t>Smaller amounts, but flexible funding for research stays that other schemes will not cover.</t>
+        </is>
+      </c>
+      <c r="R337" t="inlineStr"/>
+      <c r="S337" t="inlineStr"/>
+      <c r="T337" t="inlineStr"/>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>G334</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Merck (Merck KGaA) Research Grants &amp; Future Insight Prize</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>Merck KGaA, Darmstadt</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>Corporate (Merck KGaA)</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>Life sciences, healthcare &amp; materials</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>PhD candidates → established</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>Merck funds external research through open grant calls in areas such as drug discovery, sustainability and advanced materials.</t>
+        </is>
+      </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>Typically €100,000-450,000 per grant</t>
+        </is>
+      </c>
+      <c r="J338" t="inlineStr">
+        <is>
+          <t>1-3 years</t>
+        </is>
+      </c>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Academic researchers worldwide; topics defined per call</t>
+        </is>
+      </c>
+      <c r="L338" t="inlineStr">
+        <is>
+          <t>Annual calls (check site)</t>
+        </is>
+      </c>
+      <c r="M338" t="inlineStr">
+        <is>
+          <t>Merck research grants portal</t>
+        </is>
+      </c>
+      <c r="N338" t="inlineStr">
+        <is>
+          <t>No — scientific review</t>
+        </is>
+      </c>
+      <c r="O338" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="P338" t="inlineStr">
+        <is>
+          <t>https://www.merckgroup.com/en/research/open-innovation/grants-and-awards.html</t>
+        </is>
+      </c>
+      <c r="Q338" t="inlineStr">
+        <is>
+          <t>Note this is Merck KGaA (Germany), distinct from Merck &amp; Co (US, known as MSD outside North America).</t>
+        </is>
+      </c>
+      <c r="R338" t="inlineStr"/>
+      <c r="S338" t="inlineStr"/>
+      <c r="T338" t="inlineStr"/>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>G335</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>AstraZeneca Postdoctoral Research Programme</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>AstraZeneca</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>Corporate (AstraZeneca)</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>UK, Sweden, USA &amp; other AZ sites</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>Biomedical &amp; pharmaceutical research</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>Early postdoc</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>Industry postdoc positions with academic-style freedom, encouraging publication and often run jointly with a university partner.</t>
+        </is>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>Competitive industry salary + research budget</t>
+        </is>
+      </c>
+      <c r="J339" t="inlineStr">
+        <is>
+          <t>2-3 years</t>
+        </is>
+      </c>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>PhD holders; positions advertised by research area and site</t>
+        </is>
+      </c>
+      <c r="L339" t="inlineStr">
+        <is>
+          <t>Rolling advertised positions (check site)</t>
+        </is>
+      </c>
+      <c r="M339" t="inlineStr">
+        <is>
+          <t>AstraZeneca careers portal</t>
+        </is>
+      </c>
+      <c r="N339" t="inlineStr">
+        <is>
+          <t>Yes — interview</t>
+        </is>
+      </c>
+      <c r="O339" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="P339" t="inlineStr">
+        <is>
+          <t>https://careers.astrazeneca.com/postdoc</t>
+        </is>
+      </c>
+      <c r="Q339" t="inlineStr">
+        <is>
+          <t>A genuine research career track — postdocs publish and present like academic peers.</t>
+        </is>
+      </c>
+      <c r="R339" t="inlineStr"/>
+      <c r="S339" t="inlineStr"/>
+      <c r="T339" t="inlineStr"/>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>G336</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Pfizer Global Medical &amp; Independent Grants (ASPIRE)</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>Pfizer</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>Corporate (Pfizer)</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>Clinical &amp; health outcomes research</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>Clinical researchers &amp; established</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>Competitive grants for investigator-initiated clinical, health-outcomes and quality-improvement research in Pfizer's therapeutic areas.</t>
+        </is>
+      </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>Typically $50,000-500,000 depending on call</t>
+        </is>
+      </c>
+      <c r="J340" t="inlineStr">
+        <is>
+          <t>1-3 years</t>
+        </is>
+      </c>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Researchers and institutions worldwide; therapeutic-area specific calls</t>
+        </is>
+      </c>
+      <c r="L340" t="inlineStr">
+        <is>
+          <t>Rolling programme of calls (check site)</t>
+        </is>
+      </c>
+      <c r="M340" t="inlineStr">
+        <is>
+          <t>Pfizer Grants portal</t>
+        </is>
+      </c>
+      <c r="N340" t="inlineStr">
+        <is>
+          <t>No — independent review committee</t>
+        </is>
+      </c>
+      <c r="O340" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="P340" t="inlineStr">
+        <is>
+          <t>https://www.pfizer.com/purpose/independent-grants</t>
+        </is>
+      </c>
+      <c r="Q340" t="inlineStr">
+        <is>
+          <t>Review is deliberately independent of Pfizer's commercial teams; mainly relevant to clinical researchers.</t>
+        </is>
+      </c>
+      <c r="R340" t="inlineStr"/>
+      <c r="S340" t="inlineStr"/>
+      <c r="T340" t="inlineStr"/>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>G337</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Johnson &amp; Johnson WiSTEM2D Scholars Award</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>Johnson &amp; Johnson</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>Corporate (J&amp;J)</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>Science, technology, engineering, maths, manufacturing &amp; design</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>Early faculty (women)</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>Awards for women assistant professors advancing research across the STEM2D disciplines, with funding and mentorship.</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>$150,000 over 3 years + mentorship</t>
+        </is>
+      </c>
+      <c r="J341" t="inlineStr">
+        <is>
+          <t>3 years</t>
+        </is>
+      </c>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>Women in the first years of a tenure-track (or equivalent) position; global eligibility</t>
+        </is>
+      </c>
+      <c r="L341" t="inlineStr">
+        <is>
+          <t>Annual call (typically ~summer; check site)</t>
+        </is>
+      </c>
+      <c r="M341" t="inlineStr">
+        <is>
+          <t>J&amp;J online application</t>
+        </is>
+      </c>
+      <c r="N341" t="inlineStr">
+        <is>
+          <t>Yes — final review</t>
+        </is>
+      </c>
+      <c r="O341" t="inlineStr">
+        <is>
+          <t>Very competitive</t>
+        </is>
+      </c>
+      <c r="P341" t="inlineStr">
+        <is>
+          <t>https://wistem2d.jnj.com/</t>
+        </is>
+      </c>
+      <c r="Q341" t="inlineStr">
+        <is>
+          <t>Six disciplines, one award each per year — small numbers but genuinely global.</t>
+        </is>
+      </c>
+      <c r="R341" t="inlineStr"/>
+      <c r="S341" t="inlineStr"/>
+      <c r="T341" t="inlineStr"/>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>G338</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Cloud &amp; Compute Credits for Research (AWS, Google Cloud, Azure)</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>Amazon Web Services / Google Cloud / Microsoft Azure</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>Corporate (cloud providers)</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>Computational research (all fields)</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>PhD candidates → established</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>The major cloud providers all run research credit programmes giving academics free compute and storage for scientific projects.</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>Typically $1,000-100,000 in credits (occasionally more)</t>
+        </is>
+      </c>
+      <c r="J342" t="inlineStr">
+        <is>
+          <t>6 months-2 years</t>
+        </is>
+      </c>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>Academic researchers and students; institution and project criteria vary by provider</t>
+        </is>
+      </c>
+      <c r="L342" t="inlineStr">
+        <is>
+          <t>Rolling applications (check each provider)</t>
+        </is>
+      </c>
+      <c r="M342" t="inlineStr">
+        <is>
+          <t>Provider research-credit portals</t>
+        </is>
+      </c>
+      <c r="N342" t="inlineStr">
+        <is>
+          <t>No — internal review</t>
+        </is>
+      </c>
+      <c r="O342" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="P342" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/grants/</t>
+        </is>
+      </c>
+      <c r="Q342" t="inlineStr">
+        <is>
+          <t>Often overlooked but easy to obtain — credits can replace a large equipment budget line for computational work.</t>
+        </is>
+      </c>
+      <c r="R342" t="inlineStr"/>
+      <c r="S342" t="inlineStr"/>
+      <c r="T342" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:Q52"/>

--- a/data/grants.xlsx
+++ b/data/grants.xlsx
@@ -508,7 +508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:U402"/>
+  <dimension ref="A1:U444"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="6" customWidth="1" style="10" min="1" max="1"/>
@@ -36056,3325 +36056,7435 @@
       </c>
     </row>
     <row r="368">
-      <c r="A368" t="inlineStr">
+      <c r="A368" s="10" t="inlineStr">
         <is>
           <t>A26</t>
         </is>
       </c>
-      <c r="B368" t="inlineStr">
+      <c r="B368" s="10" t="inlineStr">
         <is>
           <t>National Medal of Science</t>
         </is>
       </c>
-      <c r="C368" t="inlineStr">
+      <c r="C368" s="10" t="inlineStr">
         <is>
           <t>US National Science Foundation / White House</t>
         </is>
       </c>
-      <c r="D368" t="inlineStr">
+      <c r="D368" s="10" t="inlineStr">
         <is>
           <t>NSF</t>
         </is>
       </c>
-      <c r="E368" t="inlineStr">
+      <c r="E368" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="F368" t="inlineStr">
+      <c r="F368" s="10" t="inlineStr">
         <is>
           <t>All sciences &amp; engineering</t>
         </is>
       </c>
-      <c r="G368" t="inlineStr">
+      <c r="G368" s="10" t="inlineStr">
         <is>
           <t>Any / Established</t>
         </is>
       </c>
-      <c r="H368" t="inlineStr">
+      <c r="H368" s="10" t="inlineStr">
         <is>
           <t>The highest US honour for scientists and engineers, awarded by the President for outstanding lifetime contributions.</t>
         </is>
       </c>
-      <c r="I368" t="inlineStr">
+      <c r="I368" s="10" t="inlineStr">
         <is>
           <t>Presidential medal (honorary)</t>
         </is>
       </c>
-      <c r="J368" t="inlineStr">
+      <c r="J368" s="10" t="inlineStr">
         <is>
           <t>Periodic</t>
         </is>
       </c>
-      <c r="K368" t="inlineStr">
+      <c r="K368" s="10" t="inlineStr">
         <is>
           <t>US citizens; by nomination through the NSF process</t>
         </is>
       </c>
-      <c r="L368" t="inlineStr">
+      <c r="L368" s="10" t="inlineStr">
         <is>
           <t>Nomination cycles announced by NSF</t>
         </is>
       </c>
-      <c r="M368" t="inlineStr">
+      <c r="M368" s="10" t="inlineStr">
         <is>
           <t>Nomination only</t>
         </is>
       </c>
-      <c r="N368" t="inlineStr">
+      <c r="N368" s="10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="O368" t="inlineStr">
+      <c r="O368" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P368" t="inlineStr">
+      <c r="P368" s="10" t="inlineStr">
         <is>
           <t>https://www.nsf.gov/od/nms/</t>
         </is>
       </c>
-      <c r="Q368" t="inlineStr">
+      <c r="Q368" s="10" t="inlineStr">
         <is>
           <t>The most prestigious science honour conferred by the US government.</t>
         </is>
       </c>
-      <c r="R368" t="inlineStr"/>
-      <c r="S368" t="inlineStr"/>
-      <c r="T368" t="inlineStr"/>
-      <c r="U368" t="inlineStr">
+      <c r="R368" s="10" t="inlineStr"/>
+      <c r="S368" s="10" t="inlineStr"/>
+      <c r="T368" s="10" t="inlineStr"/>
+      <c r="U368" s="10" t="inlineStr">
         <is>
           <t>award</t>
         </is>
       </c>
     </row>
     <row r="369">
-      <c r="A369" t="inlineStr">
+      <c r="A369" s="10" t="inlineStr">
         <is>
           <t>A27</t>
         </is>
       </c>
-      <c r="B369" t="inlineStr">
+      <c r="B369" s="10" t="inlineStr">
         <is>
           <t>NAS Awards (National Academy of Sciences)</t>
         </is>
       </c>
-      <c r="C369" t="inlineStr">
+      <c r="C369" s="10" t="inlineStr">
         <is>
           <t>National Academy of Sciences</t>
         </is>
       </c>
-      <c r="D369" t="inlineStr">
+      <c r="D369" s="10" t="inlineStr">
         <is>
           <t>NAS</t>
         </is>
       </c>
-      <c r="E369" t="inlineStr">
+      <c r="E369" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="F369" t="inlineStr">
+      <c r="F369" s="10" t="inlineStr">
         <is>
           <t>All sciences</t>
         </is>
       </c>
-      <c r="G369" t="inlineStr">
+      <c r="G369" s="10" t="inlineStr">
         <is>
           <t>Any / Established</t>
         </is>
       </c>
-      <c r="H369" t="inlineStr">
+      <c r="H369" s="10" t="inlineStr">
         <is>
           <t>A portfolio of prestigious disciplinary awards spanning chemistry, physics, biology, mathematics and the social sciences.</t>
         </is>
       </c>
-      <c r="I369" t="inlineStr">
+      <c r="I369" s="10" t="inlineStr">
         <is>
           <t>$25,000-$100,000 depending on award</t>
         </is>
       </c>
-      <c r="J369" t="inlineStr">
+      <c r="J369" s="10" t="inlineStr">
         <is>
           <t>Annual</t>
         </is>
       </c>
-      <c r="K369" t="inlineStr">
+      <c r="K369" s="10" t="inlineStr">
         <is>
           <t>By nomination; open to researchers internationally for several awards</t>
         </is>
       </c>
-      <c r="L369" t="inlineStr">
+      <c r="L369" s="10" t="inlineStr">
         <is>
           <t>Annual nomination ~Oct (check site)</t>
         </is>
       </c>
-      <c r="M369" t="inlineStr">
+      <c r="M369" s="10" t="inlineStr">
         <is>
           <t>Nomination only</t>
         </is>
       </c>
-      <c r="N369" t="inlineStr">
+      <c r="N369" s="10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="O369" t="inlineStr">
+      <c r="O369" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P369" t="inlineStr">
+      <c r="P369" s="10" t="inlineStr">
         <is>
           <t>https://www.nasonline.org/programs/awards/</t>
         </is>
       </c>
-      <c r="Q369" t="inlineStr">
+      <c r="Q369" s="10" t="inlineStr">
         <is>
           <t>Includes the NAS Award in Molecular Biology, often an early-Nobel signal.</t>
         </is>
       </c>
-      <c r="R369" t="inlineStr"/>
-      <c r="S369" t="inlineStr"/>
-      <c r="T369" t="inlineStr"/>
-      <c r="U369" t="inlineStr">
+      <c r="R369" s="10" t="inlineStr"/>
+      <c r="S369" s="10" t="inlineStr"/>
+      <c r="T369" s="10" t="inlineStr"/>
+      <c r="U369" s="10" t="inlineStr">
         <is>
           <t>award</t>
         </is>
       </c>
     </row>
     <row r="370">
-      <c r="A370" t="inlineStr">
+      <c r="A370" s="10" t="inlineStr">
         <is>
           <t>A28</t>
         </is>
       </c>
-      <c r="B370" t="inlineStr">
+      <c r="B370" s="10" t="inlineStr">
         <is>
           <t>Alan T. Waterman Award</t>
         </is>
       </c>
-      <c r="C370" t="inlineStr">
+      <c r="C370" s="10" t="inlineStr">
         <is>
           <t>US National Science Foundation (NSF)</t>
         </is>
       </c>
-      <c r="D370" t="inlineStr">
+      <c r="D370" s="10" t="inlineStr">
         <is>
           <t>NSF</t>
         </is>
       </c>
-      <c r="E370" t="inlineStr">
+      <c r="E370" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="F370" t="inlineStr">
+      <c r="F370" s="10" t="inlineStr">
         <is>
           <t>All sciences &amp; engineering</t>
         </is>
       </c>
-      <c r="G370" t="inlineStr">
+      <c r="G370" s="10" t="inlineStr">
         <is>
           <t>Early-career (under 40 / within 10 yrs of PhD)</t>
         </is>
       </c>
-      <c r="H370" t="inlineStr">
+      <c r="H370" s="10" t="inlineStr">
         <is>
           <t>The US government's highest honour for early-career scientists and engineers.</t>
         </is>
       </c>
-      <c r="I370" t="inlineStr">
+      <c r="I370" s="10" t="inlineStr">
         <is>
           <t>$1,000,000 over 5 years</t>
         </is>
       </c>
-      <c r="J370" t="inlineStr">
+      <c r="J370" s="10" t="inlineStr">
         <is>
           <t>Annual</t>
         </is>
       </c>
-      <c r="K370" t="inlineStr">
+      <c r="K370" s="10" t="inlineStr">
         <is>
           <t>US citizens/permanent residents under 40 or within 10 years of PhD; by nomination</t>
         </is>
       </c>
-      <c r="L370" t="inlineStr">
+      <c r="L370" s="10" t="inlineStr">
         <is>
           <t>Annual: ~Oct nomination (check site)</t>
         </is>
       </c>
-      <c r="M370" t="inlineStr">
+      <c r="M370" s="10" t="inlineStr">
         <is>
           <t>Nomination only</t>
         </is>
       </c>
-      <c r="N370" t="inlineStr">
+      <c r="N370" s="10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="O370" t="inlineStr">
+      <c r="O370" s="10" t="inlineStr">
         <is>
           <t>Very competitive</t>
         </is>
       </c>
-      <c r="P370" t="inlineStr">
+      <c r="P370" s="10" t="inlineStr">
         <is>
           <t>https://www.nsf.gov/awards/waterman/</t>
         </is>
       </c>
-      <c r="Q370" t="inlineStr">
+      <c r="Q370" s="10" t="inlineStr">
         <is>
           <t>One of the few top honours reserved specifically for young researchers.</t>
         </is>
       </c>
-      <c r="R370" t="inlineStr"/>
-      <c r="S370" t="inlineStr"/>
-      <c r="T370" t="inlineStr"/>
-      <c r="U370" t="inlineStr">
+      <c r="R370" s="10" t="inlineStr"/>
+      <c r="S370" s="10" t="inlineStr"/>
+      <c r="T370" s="10" t="inlineStr"/>
+      <c r="U370" s="10" t="inlineStr">
         <is>
           <t>award</t>
         </is>
       </c>
     </row>
     <row r="371">
-      <c r="A371" t="inlineStr">
+      <c r="A371" s="10" t="inlineStr">
         <is>
           <t>A29</t>
         </is>
       </c>
-      <c r="B371" t="inlineStr">
+      <c r="B371" s="10" t="inlineStr">
         <is>
           <t>MacArthur Fellowship ('Genius Grant')</t>
         </is>
       </c>
-      <c r="C371" t="inlineStr">
+      <c r="C371" s="10" t="inlineStr">
         <is>
           <t>John D. and Catherine T. MacArthur Foundation</t>
         </is>
       </c>
-      <c r="D371" t="inlineStr">
+      <c r="D371" s="10" t="inlineStr">
         <is>
           <t>MacArthur</t>
         </is>
       </c>
-      <c r="E371" t="inlineStr">
+      <c r="E371" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="F371" t="inlineStr">
+      <c r="F371" s="10" t="inlineStr">
         <is>
           <t>All fields (incl. sciences)</t>
         </is>
       </c>
-      <c r="G371" t="inlineStr">
+      <c r="G371" s="10" t="inlineStr">
         <is>
           <t>Any (exceptional creativity)</t>
         </is>
       </c>
-      <c r="H371" t="inlineStr">
+      <c r="H371" s="10" t="inlineStr">
         <is>
           <t>The famous 'no-strings' fellowship for extraordinarily creative individuals, awarded across sciences, arts and humanities.</t>
         </is>
       </c>
-      <c r="I371" t="inlineStr">
+      <c r="I371" s="10" t="inlineStr">
         <is>
           <t>$800,000 over 5 years (no conditions)</t>
         </is>
       </c>
-      <c r="J371" t="inlineStr">
+      <c r="J371" s="10" t="inlineStr">
         <is>
           <t>Every year (rolling classes)</t>
         </is>
       </c>
-      <c r="K371" t="inlineStr">
+      <c r="K371" s="10" t="inlineStr">
         <is>
           <t>US residents/citizens; by confidential nomination only — no applications</t>
         </is>
       </c>
-      <c r="L371" t="inlineStr">
+      <c r="L371" s="10" t="inlineStr">
         <is>
           <t>Confidential; announced annually</t>
         </is>
       </c>
-      <c r="M371" t="inlineStr">
+      <c r="M371" s="10" t="inlineStr">
         <is>
           <t>Nomination only (secret)</t>
         </is>
       </c>
-      <c r="N371" t="inlineStr">
+      <c r="N371" s="10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="O371" t="inlineStr">
+      <c r="O371" s="10" t="inlineStr">
         <is>
           <t>Extremely selective</t>
         </is>
       </c>
-      <c r="P371" t="inlineStr">
+      <c r="P371" s="10" t="inlineStr">
         <is>
           <t>https://www.macfound.org/programs/awards/fellows/</t>
         </is>
       </c>
-      <c r="Q371" t="inlineStr">
+      <c r="Q371" s="10" t="inlineStr">
         <is>
           <t>You cannot apply or know you were nominated; recipients are surprised by a phone call.</t>
         </is>
       </c>
-      <c r="R371" t="inlineStr"/>
-      <c r="S371" t="inlineStr"/>
-      <c r="T371" t="inlineStr"/>
-      <c r="U371" t="inlineStr">
+      <c r="R371" s="10" t="inlineStr"/>
+      <c r="S371" s="10" t="inlineStr"/>
+      <c r="T371" s="10" t="inlineStr"/>
+      <c r="U371" s="10" t="inlineStr">
         <is>
           <t>award</t>
         </is>
       </c>
     </row>
     <row r="372">
-      <c r="A372" t="inlineStr">
+      <c r="A372" s="10" t="inlineStr">
         <is>
           <t>A30</t>
         </is>
       </c>
-      <c r="B372" t="inlineStr">
+      <c r="B372" s="10" t="inlineStr">
         <is>
           <t>Shaw Prize</t>
         </is>
       </c>
-      <c r="C372" t="inlineStr">
+      <c r="C372" s="10" t="inlineStr">
         <is>
           <t>The Shaw Prize Foundation</t>
         </is>
       </c>
-      <c r="D372" t="inlineStr">
+      <c r="D372" s="10" t="inlineStr">
         <is>
           <t>Shaw Prize</t>
         </is>
       </c>
-      <c r="E372" t="inlineStr">
+      <c r="E372" s="10" t="inlineStr">
         <is>
           <t>International</t>
         </is>
       </c>
-      <c r="F372" t="inlineStr">
+      <c r="F372" s="10" t="inlineStr">
         <is>
           <t>Astronomy, life science &amp; medicine, mathematical sciences</t>
         </is>
       </c>
-      <c r="G372" t="inlineStr">
+      <c r="G372" s="10" t="inlineStr">
         <is>
           <t>Any / Established</t>
         </is>
       </c>
-      <c r="H372" t="inlineStr">
+      <c r="H372" s="10" t="inlineStr">
         <is>
           <t>A major international award, sometimes called the 'Nobel of the East', for recent breakthroughs in three fields.</t>
         </is>
       </c>
-      <c r="I372" t="inlineStr">
+      <c r="I372" s="10" t="inlineStr">
         <is>
           <t>$1,200,000 per prize</t>
         </is>
       </c>
-      <c r="J372" t="inlineStr">
+      <c r="J372" s="10" t="inlineStr">
         <is>
           <t>Annual</t>
         </is>
       </c>
-      <c r="K372" t="inlineStr">
+      <c r="K372" s="10" t="inlineStr">
         <is>
           <t>By nomination from the international community</t>
         </is>
       </c>
-      <c r="L372" t="inlineStr">
+      <c r="L372" s="10" t="inlineStr">
         <is>
           <t>Annual nomination ~Sep-Nov (check site)</t>
         </is>
       </c>
-      <c r="M372" t="inlineStr">
+      <c r="M372" s="10" t="inlineStr">
         <is>
           <t>Nomination only</t>
         </is>
       </c>
-      <c r="N372" t="inlineStr">
+      <c r="N372" s="10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="O372" t="inlineStr">
+      <c r="O372" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P372" t="inlineStr">
+      <c r="P372" s="10" t="inlineStr">
         <is>
           <t>https://www.shawprize.org/</t>
         </is>
       </c>
-      <c r="Q372" t="inlineStr">
+      <c r="Q372" s="10" t="inlineStr">
         <is>
           <t>Based in Hong Kong; among the most lucrative science prizes globally.</t>
         </is>
       </c>
-      <c r="R372" t="inlineStr"/>
-      <c r="S372" t="inlineStr"/>
-      <c r="T372" t="inlineStr"/>
-      <c r="U372" t="inlineStr">
+      <c r="R372" s="10" t="inlineStr"/>
+      <c r="S372" s="10" t="inlineStr"/>
+      <c r="T372" s="10" t="inlineStr"/>
+      <c r="U372" s="10" t="inlineStr">
         <is>
           <t>award</t>
         </is>
       </c>
     </row>
     <row r="373">
-      <c r="A373" t="inlineStr">
+      <c r="A373" s="10" t="inlineStr">
         <is>
           <t>A31</t>
         </is>
       </c>
-      <c r="B373" t="inlineStr">
+      <c r="B373" s="10" t="inlineStr">
         <is>
           <t>Gairdner Awards</t>
         </is>
       </c>
-      <c r="C373" t="inlineStr">
+      <c r="C373" s="10" t="inlineStr">
         <is>
           <t>Gairdner Foundation</t>
         </is>
       </c>
-      <c r="D373" t="inlineStr">
+      <c r="D373" s="10" t="inlineStr">
         <is>
           <t>Gairdner</t>
         </is>
       </c>
-      <c r="E373" t="inlineStr">
+      <c r="E373" s="10" t="inlineStr">
         <is>
           <t>Canada / International</t>
         </is>
       </c>
-      <c r="F373" t="inlineStr">
+      <c r="F373" s="10" t="inlineStr">
         <is>
           <t>Biomedical &amp; global health research</t>
         </is>
       </c>
-      <c r="G373" t="inlineStr">
+      <c r="G373" s="10" t="inlineStr">
         <is>
           <t>Any / Established</t>
         </is>
       </c>
-      <c r="H373" t="inlineStr">
+      <c r="H373" s="10" t="inlineStr">
         <is>
           <t>Canada's premier biomedical research prize, with a strong record of preceding the Nobel.</t>
         </is>
       </c>
-      <c r="I373" t="inlineStr">
+      <c r="I373" s="10" t="inlineStr">
         <is>
           <t>CAD 250,000 per award</t>
         </is>
       </c>
-      <c r="J373" t="inlineStr">
+      <c r="J373" s="10" t="inlineStr">
         <is>
           <t>Annual</t>
         </is>
       </c>
-      <c r="K373" t="inlineStr">
+      <c r="K373" s="10" t="inlineStr">
         <is>
           <t>By nomination; international candidates eligible</t>
         </is>
       </c>
-      <c r="L373" t="inlineStr">
+      <c r="L373" s="10" t="inlineStr">
         <is>
           <t>Annual nomination (check site)</t>
         </is>
       </c>
-      <c r="M373" t="inlineStr">
+      <c r="M373" s="10" t="inlineStr">
         <is>
           <t>Nomination only</t>
         </is>
       </c>
-      <c r="N373" t="inlineStr">
+      <c r="N373" s="10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="O373" t="inlineStr">
+      <c r="O373" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P373" t="inlineStr">
+      <c r="P373" s="10" t="inlineStr">
         <is>
           <t>https://gairdner.org/</t>
         </is>
       </c>
-      <c r="Q373" t="inlineStr">
+      <c r="Q373" s="10" t="inlineStr">
         <is>
           <t>Roughly a quarter of Gairdner laureates go on to win a Nobel.</t>
         </is>
       </c>
-      <c r="R373" t="inlineStr"/>
-      <c r="S373" t="inlineStr"/>
-      <c r="T373" t="inlineStr"/>
-      <c r="U373" t="inlineStr">
+      <c r="R373" s="10" t="inlineStr"/>
+      <c r="S373" s="10" t="inlineStr"/>
+      <c r="T373" s="10" t="inlineStr"/>
+      <c r="U373" s="10" t="inlineStr">
         <is>
           <t>award</t>
         </is>
       </c>
     </row>
     <row r="374">
-      <c r="A374" t="inlineStr">
+      <c r="A374" s="10" t="inlineStr">
         <is>
           <t>A32</t>
         </is>
       </c>
-      <c r="B374" t="inlineStr">
+      <c r="B374" s="10" t="inlineStr">
         <is>
           <t>Killam Prizes &amp; Killam Fellowships</t>
         </is>
       </c>
-      <c r="C374" t="inlineStr">
+      <c r="C374" s="10" t="inlineStr">
         <is>
           <t>National Research Council of Canada (Killam Program)</t>
         </is>
       </c>
-      <c r="D374" t="inlineStr">
+      <c r="D374" s="10" t="inlineStr">
         <is>
           <t>Killam</t>
         </is>
       </c>
-      <c r="E374" t="inlineStr">
+      <c r="E374" s="10" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="F374" t="inlineStr">
+      <c r="F374" s="10" t="inlineStr">
         <is>
           <t>Natural sciences, health sciences, engineering, social sciences &amp; humanities</t>
         </is>
       </c>
-      <c r="G374" t="inlineStr">
+      <c r="G374" s="10" t="inlineStr">
         <is>
           <t>Established (Prizes); mid-career (Fellowships)</t>
         </is>
       </c>
-      <c r="H374" t="inlineStr">
+      <c r="H374" s="10" t="inlineStr">
         <is>
           <t>Among Canada's most distinguished awards for scholars, recognising career achievement and funding two years of research freedom.</t>
         </is>
       </c>
-      <c r="I374" t="inlineStr">
+      <c r="I374" s="10" t="inlineStr">
         <is>
           <t>Prizes CAD 100,000; Fellowships up to CAD 160,000</t>
         </is>
       </c>
-      <c r="J374" t="inlineStr">
+      <c r="J374" s="10" t="inlineStr">
         <is>
           <t>Annual</t>
         </is>
       </c>
-      <c r="K374" t="inlineStr">
+      <c r="K374" s="10" t="inlineStr">
         <is>
           <t>Canadian scholars; by nomination</t>
         </is>
       </c>
-      <c r="L374" t="inlineStr">
+      <c r="L374" s="10" t="inlineStr">
         <is>
           <t>Annual nomination (check site)</t>
         </is>
       </c>
-      <c r="M374" t="inlineStr">
+      <c r="M374" s="10" t="inlineStr">
         <is>
           <t>Nomination only</t>
         </is>
       </c>
-      <c r="N374" t="inlineStr">
+      <c r="N374" s="10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="O374" t="inlineStr">
+      <c r="O374" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P374" t="inlineStr">
+      <c r="P374" s="10" t="inlineStr">
         <is>
           <t>https://killamlaureates.ca/</t>
         </is>
       </c>
-      <c r="Q374" t="inlineStr">
+      <c r="Q374" s="10" t="inlineStr">
         <is>
           <t>The Killam Fellowships buy out two years of teaching for full-time research.</t>
         </is>
       </c>
-      <c r="R374" t="inlineStr"/>
-      <c r="S374" t="inlineStr"/>
-      <c r="T374" t="inlineStr"/>
-      <c r="U374" t="inlineStr">
+      <c r="R374" s="10" t="inlineStr"/>
+      <c r="S374" s="10" t="inlineStr"/>
+      <c r="T374" s="10" t="inlineStr"/>
+      <c r="U374" s="10" t="inlineStr">
         <is>
           <t>award</t>
         </is>
       </c>
     </row>
     <row r="375">
-      <c r="A375" t="inlineStr">
+      <c r="A375" s="10" t="inlineStr">
         <is>
           <t>A33</t>
         </is>
       </c>
-      <c r="B375" t="inlineStr">
+      <c r="B375" s="10" t="inlineStr">
         <is>
           <t>NSERC Prizes (Herzberg, Steacie, Polanyi)</t>
         </is>
       </c>
-      <c r="C375" t="inlineStr">
+      <c r="C375" s="10" t="inlineStr">
         <is>
           <t>Natural Sciences and Engineering Research Council (NSERC)</t>
         </is>
       </c>
-      <c r="D375" t="inlineStr">
+      <c r="D375" s="10" t="inlineStr">
         <is>
           <t>Canada (NSERC)</t>
         </is>
       </c>
-      <c r="E375" t="inlineStr">
+      <c r="E375" s="10" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="F375" t="inlineStr">
+      <c r="F375" s="10" t="inlineStr">
         <is>
           <t>Natural sciences &amp; engineering</t>
         </is>
       </c>
-      <c r="G375" t="inlineStr">
+      <c r="G375" s="10" t="inlineStr">
         <is>
           <t>Early-career to lifetime (by prize)</t>
         </is>
       </c>
-      <c r="H375" t="inlineStr">
+      <c r="H375" s="10" t="inlineStr">
         <is>
           <t>NSERC's suite of national honours, including the Herzberg Gold Medal (top prize) and the Steacie Memorial Fellowships for young researchers.</t>
         </is>
       </c>
-      <c r="I375" t="inlineStr">
+      <c r="I375" s="10" t="inlineStr">
         <is>
           <t>Herzberg CAD 1,000,000 research grant; Steacie ~CAD 250,000</t>
         </is>
       </c>
-      <c r="J375" t="inlineStr">
+      <c r="J375" s="10" t="inlineStr">
         <is>
           <t>Annual</t>
         </is>
       </c>
-      <c r="K375" t="inlineStr">
+      <c r="K375" s="10" t="inlineStr">
         <is>
           <t>Researchers at Canadian institutions; by nomination</t>
         </is>
       </c>
-      <c r="L375" t="inlineStr">
+      <c r="L375" s="10" t="inlineStr">
         <is>
           <t>Annual nomination (check site)</t>
         </is>
       </c>
-      <c r="M375" t="inlineStr">
+      <c r="M375" s="10" t="inlineStr">
         <is>
           <t>Nomination only</t>
         </is>
       </c>
-      <c r="N375" t="inlineStr">
+      <c r="N375" s="10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="O375" t="inlineStr">
+      <c r="O375" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P375" t="inlineStr">
+      <c r="P375" s="10" t="inlineStr">
         <is>
           <t>https://www.nserc-crsng.gc.ca/prizes-prix/</t>
         </is>
       </c>
-      <c r="Q375" t="inlineStr">
+      <c r="Q375" s="10" t="inlineStr">
         <is>
           <t>The Steacie Fellowships are the key early-to-mid-career honour.</t>
         </is>
       </c>
-      <c r="R375" t="inlineStr"/>
-      <c r="S375" t="inlineStr"/>
-      <c r="T375" t="inlineStr"/>
-      <c r="U375" t="inlineStr">
+      <c r="R375" s="10" t="inlineStr"/>
+      <c r="S375" s="10" t="inlineStr"/>
+      <c r="T375" s="10" t="inlineStr"/>
+      <c r="U375" s="10" t="inlineStr">
         <is>
           <t>award</t>
         </is>
       </c>
     </row>
     <row r="376">
-      <c r="A376" t="inlineStr">
+      <c r="A376" s="10" t="inlineStr">
         <is>
           <t>A34</t>
         </is>
       </c>
-      <c r="B376" t="inlineStr">
+      <c r="B376" s="10" t="inlineStr">
         <is>
           <t>Banting Award / CIHR Prizes</t>
         </is>
       </c>
-      <c r="C376" t="inlineStr">
+      <c r="C376" s="10" t="inlineStr">
         <is>
           <t>Canadian Institutes of Health Research (CIHR)</t>
         </is>
       </c>
-      <c r="D376" t="inlineStr">
+      <c r="D376" s="10" t="inlineStr">
         <is>
           <t>Canada (CIHR)</t>
         </is>
       </c>
-      <c r="E376" t="inlineStr">
+      <c r="E376" s="10" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="F376" t="inlineStr">
+      <c r="F376" s="10" t="inlineStr">
         <is>
           <t>Health &amp; medical research</t>
         </is>
       </c>
-      <c r="G376" t="inlineStr">
+      <c r="G376" s="10" t="inlineStr">
         <is>
           <t>Any / Established</t>
         </is>
       </c>
-      <c r="H376" t="inlineStr">
+      <c r="H376" s="10" t="inlineStr">
         <is>
           <t>CIHR's recognition awards celebrating outstanding health research achievements across Canada.</t>
         </is>
       </c>
-      <c r="I376" t="inlineStr">
+      <c r="I376" s="10" t="inlineStr">
         <is>
           <t>Varies by prize (recognition + some cash)</t>
         </is>
       </c>
-      <c r="J376" t="inlineStr">
+      <c r="J376" s="10" t="inlineStr">
         <is>
           <t>Annual</t>
         </is>
       </c>
-      <c r="K376" t="inlineStr">
+      <c r="K376" s="10" t="inlineStr">
         <is>
           <t>Health researchers in Canada; by nomination</t>
         </is>
       </c>
-      <c r="L376" t="inlineStr">
+      <c r="L376" s="10" t="inlineStr">
         <is>
           <t>Annual nomination (check site)</t>
         </is>
       </c>
-      <c r="M376" t="inlineStr">
+      <c r="M376" s="10" t="inlineStr">
         <is>
           <t>Nomination only</t>
         </is>
       </c>
-      <c r="N376" t="inlineStr">
+      <c r="N376" s="10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="O376" t="inlineStr">
+      <c r="O376" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P376" t="inlineStr">
+      <c r="P376" s="10" t="inlineStr">
         <is>
           <t>https://cihr-irsc.gc.ca/</t>
         </is>
       </c>
-      <c r="Q376" t="inlineStr">
+      <c r="Q376" s="10" t="inlineStr">
         <is>
           <t>Named partly for Frederick Banting, co-discoverer of insulin.</t>
         </is>
       </c>
-      <c r="R376" t="inlineStr"/>
-      <c r="S376" t="inlineStr"/>
-      <c r="T376" t="inlineStr"/>
-      <c r="U376" t="inlineStr">
+      <c r="R376" s="10" t="inlineStr"/>
+      <c r="S376" s="10" t="inlineStr"/>
+      <c r="T376" s="10" t="inlineStr"/>
+      <c r="U376" s="10" t="inlineStr">
         <is>
           <t>award</t>
         </is>
       </c>
     </row>
     <row r="377">
-      <c r="A377" t="inlineStr">
+      <c r="A377" s="10" t="inlineStr">
         <is>
           <t>A35</t>
         </is>
       </c>
-      <c r="B377" t="inlineStr">
+      <c r="B377" s="10" t="inlineStr">
         <is>
           <t>Royal Society Medals &amp; Awards (Copley, Davy, Darwin)</t>
         </is>
       </c>
-      <c r="C377" t="inlineStr">
+      <c r="C377" s="10" t="inlineStr">
         <is>
           <t>The Royal Society</t>
         </is>
       </c>
-      <c r="D377" t="inlineStr">
+      <c r="D377" s="10" t="inlineStr">
         <is>
           <t>Royal Society</t>
         </is>
       </c>
-      <c r="E377" t="inlineStr">
+      <c r="E377" s="10" t="inlineStr">
         <is>
           <t>United Kingdom / International</t>
         </is>
       </c>
-      <c r="F377" t="inlineStr">
+      <c r="F377" s="10" t="inlineStr">
         <is>
           <t>All sciences</t>
         </is>
       </c>
-      <c r="G377" t="inlineStr">
+      <c r="G377" s="10" t="inlineStr">
         <is>
           <t>Any / Established</t>
         </is>
       </c>
-      <c r="H377" t="inlineStr">
+      <c r="H377" s="10" t="inlineStr">
         <is>
           <t>The Royal Society's medals include the Copley Medal, the world's oldest scientific prize, plus premier awards across the sciences.</t>
         </is>
       </c>
-      <c r="I377" t="inlineStr">
+      <c r="I377" s="10" t="inlineStr">
         <is>
           <t>£1,000-£25,000 depending on medal</t>
         </is>
       </c>
-      <c r="J377" t="inlineStr">
+      <c r="J377" s="10" t="inlineStr">
         <is>
           <t>Annual</t>
         </is>
       </c>
-      <c r="K377" t="inlineStr">
+      <c r="K377" s="10" t="inlineStr">
         <is>
           <t>By nomination; several medals open to international candidates</t>
         </is>
       </c>
-      <c r="L377" t="inlineStr">
+      <c r="L377" s="10" t="inlineStr">
         <is>
           <t>Annual nomination (check site)</t>
         </is>
       </c>
-      <c r="M377" t="inlineStr">
+      <c r="M377" s="10" t="inlineStr">
         <is>
           <t>Nomination only</t>
         </is>
       </c>
-      <c r="N377" t="inlineStr">
+      <c r="N377" s="10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="O377" t="inlineStr">
+      <c r="O377" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P377" t="inlineStr">
+      <c r="P377" s="10" t="inlineStr">
         <is>
           <t>https://royalsociety.org/medals-and-prizes/</t>
         </is>
       </c>
-      <c r="Q377" t="inlineStr">
+      <c r="Q377" s="10" t="inlineStr">
         <is>
           <t>The Copley Medal dates to 1731 and predates the Nobel by 170 years.</t>
         </is>
       </c>
-      <c r="R377" t="inlineStr"/>
-      <c r="S377" t="inlineStr"/>
-      <c r="T377" t="inlineStr"/>
-      <c r="U377" t="inlineStr">
+      <c r="R377" s="10" t="inlineStr"/>
+      <c r="S377" s="10" t="inlineStr"/>
+      <c r="T377" s="10" t="inlineStr"/>
+      <c r="U377" s="10" t="inlineStr">
         <is>
           <t>award</t>
         </is>
       </c>
     </row>
     <row r="378">
-      <c r="A378" t="inlineStr">
+      <c r="A378" s="10" t="inlineStr">
         <is>
           <t>A36</t>
         </is>
       </c>
-      <c r="B378" t="inlineStr">
+      <c r="B378" s="10" t="inlineStr">
         <is>
           <t>Royal Society Research Merit / early-career medals</t>
         </is>
       </c>
-      <c r="C378" t="inlineStr">
+      <c r="C378" s="10" t="inlineStr">
         <is>
           <t>The Royal Society</t>
         </is>
       </c>
-      <c r="D378" t="inlineStr">
+      <c r="D378" s="10" t="inlineStr">
         <is>
           <t>Royal Society</t>
         </is>
       </c>
-      <c r="E378" t="inlineStr">
+      <c r="E378" s="10" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="F378" t="inlineStr">
+      <c r="F378" s="10" t="inlineStr">
         <is>
           <t>All sciences</t>
         </is>
       </c>
-      <c r="G378" t="inlineStr">
+      <c r="G378" s="10" t="inlineStr">
         <is>
           <t>Early-career → established</t>
         </is>
       </c>
-      <c r="H378" t="inlineStr">
+      <c r="H378" s="10" t="inlineStr">
         <is>
           <t>Includes early-career medals such as the Francis Crick Medal for a scientist in the early stage of their career.</t>
         </is>
       </c>
-      <c r="I378" t="inlineStr">
+      <c r="I378" s="10" t="inlineStr">
         <is>
           <t>Medal + lecture (some with cash)</t>
         </is>
       </c>
-      <c r="J378" t="inlineStr">
+      <c r="J378" s="10" t="inlineStr">
         <is>
           <t>Annual</t>
         </is>
       </c>
-      <c r="K378" t="inlineStr">
+      <c r="K378" s="10" t="inlineStr">
         <is>
           <t>UK-based researchers for several; by nomination</t>
         </is>
       </c>
-      <c r="L378" t="inlineStr">
+      <c r="L378" s="10" t="inlineStr">
         <is>
           <t>Annual nomination (check site)</t>
         </is>
       </c>
-      <c r="M378" t="inlineStr">
+      <c r="M378" s="10" t="inlineStr">
         <is>
           <t>Nomination only</t>
         </is>
       </c>
-      <c r="N378" t="inlineStr">
+      <c r="N378" s="10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="O378" t="inlineStr">
+      <c r="O378" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P378" t="inlineStr">
+      <c r="P378" s="10" t="inlineStr">
         <is>
           <t>https://royalsociety.org/medals-and-prizes/</t>
         </is>
       </c>
-      <c r="Q378" t="inlineStr">
+      <c r="Q378" s="10" t="inlineStr">
         <is>
           <t>The Francis Crick Medal specifically targets early-career biologists.</t>
         </is>
       </c>
-      <c r="R378" t="inlineStr"/>
-      <c r="S378" t="inlineStr"/>
-      <c r="T378" t="inlineStr"/>
-      <c r="U378" t="inlineStr">
+      <c r="R378" s="10" t="inlineStr"/>
+      <c r="S378" s="10" t="inlineStr"/>
+      <c r="T378" s="10" t="inlineStr"/>
+      <c r="U378" s="10" t="inlineStr">
         <is>
           <t>award</t>
         </is>
       </c>
     </row>
     <row r="379">
-      <c r="A379" t="inlineStr">
+      <c r="A379" s="10" t="inlineStr">
         <is>
           <t>A37</t>
         </is>
       </c>
-      <c r="B379" t="inlineStr">
+      <c r="B379" s="10" t="inlineStr">
         <is>
           <t>Royal Academy of Engineering — MacRobert Award</t>
         </is>
       </c>
-      <c r="C379" t="inlineStr">
+      <c r="C379" s="10" t="inlineStr">
         <is>
           <t>Royal Academy of Engineering</t>
         </is>
       </c>
-      <c r="D379" t="inlineStr">
+      <c r="D379" s="10" t="inlineStr">
         <is>
           <t>RAEng</t>
         </is>
       </c>
-      <c r="E379" t="inlineStr">
+      <c r="E379" s="10" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="F379" t="inlineStr">
+      <c r="F379" s="10" t="inlineStr">
         <is>
           <t>Engineering &amp; innovation</t>
         </is>
       </c>
-      <c r="G379" t="inlineStr">
+      <c r="G379" s="10" t="inlineStr">
         <is>
           <t>Teams / companies</t>
         </is>
       </c>
-      <c r="H379" t="inlineStr">
+      <c r="H379" s="10" t="inlineStr">
         <is>
           <t>The UK's premier prize for engineering innovation, awarded for a demonstrable commercial or social benefit.</t>
         </is>
       </c>
-      <c r="I379" t="inlineStr">
+      <c r="I379" s="10" t="inlineStr">
         <is>
           <t>£50,000</t>
         </is>
       </c>
-      <c r="J379" t="inlineStr">
+      <c r="J379" s="10" t="inlineStr">
         <is>
           <t>Annual</t>
         </is>
       </c>
-      <c r="K379" t="inlineStr">
+      <c r="K379" s="10" t="inlineStr">
         <is>
           <t>UK-based engineering teams and companies; by entry/nomination</t>
         </is>
       </c>
-      <c r="L379" t="inlineStr">
+      <c r="L379" s="10" t="inlineStr">
         <is>
           <t>Annual (check site)</t>
         </is>
       </c>
-      <c r="M379" t="inlineStr">
+      <c r="M379" s="10" t="inlineStr">
         <is>
           <t>Entry / nomination</t>
         </is>
       </c>
-      <c r="N379" t="inlineStr">
+      <c r="N379" s="10" t="inlineStr">
         <is>
           <t>Yes — judging</t>
         </is>
       </c>
-      <c r="O379" t="inlineStr">
+      <c r="O379" s="10" t="inlineStr">
         <is>
           <t>Competitive</t>
         </is>
       </c>
-      <c r="P379" t="inlineStr">
+      <c r="P379" s="10" t="inlineStr">
         <is>
           <t>https://raeng.org.uk/macrobert-award</t>
         </is>
       </c>
-      <c r="Q379" t="inlineStr">
+      <c r="Q379" s="10" t="inlineStr">
         <is>
           <t>Focused on engineering that has reached real-world impact.</t>
         </is>
       </c>
-      <c r="R379" t="inlineStr"/>
-      <c r="S379" t="inlineStr"/>
-      <c r="T379" t="inlineStr"/>
-      <c r="U379" t="inlineStr">
+      <c r="R379" s="10" t="inlineStr"/>
+      <c r="S379" s="10" t="inlineStr"/>
+      <c r="T379" s="10" t="inlineStr"/>
+      <c r="U379" s="10" t="inlineStr">
         <is>
           <t>award</t>
         </is>
       </c>
     </row>
     <row r="380">
-      <c r="A380" t="inlineStr">
+      <c r="A380" s="10" t="inlineStr">
         <is>
           <t>A38</t>
         </is>
       </c>
-      <c r="B380" t="inlineStr">
+      <c r="B380" s="10" t="inlineStr">
         <is>
           <t>Academy of Medical Sciences — Awards &amp; Medals</t>
         </is>
       </c>
-      <c r="C380" t="inlineStr">
+      <c r="C380" s="10" t="inlineStr">
         <is>
           <t>Academy of Medical Sciences</t>
         </is>
       </c>
-      <c r="D380" t="inlineStr">
+      <c r="D380" s="10" t="inlineStr">
         <is>
           <t>AMS</t>
         </is>
       </c>
-      <c r="E380" t="inlineStr">
+      <c r="E380" s="10" t="inlineStr">
         <is>
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="F380" t="inlineStr">
+      <c r="F380" s="10" t="inlineStr">
         <is>
           <t>Biomedical &amp; health sciences</t>
         </is>
       </c>
-      <c r="G380" t="inlineStr">
+      <c r="G380" s="10" t="inlineStr">
         <is>
           <t>Early-career → established</t>
         </is>
       </c>
-      <c r="H380" t="inlineStr">
+      <c r="H380" s="10" t="inlineStr">
         <is>
           <t>Recognises excellence in medical research, including career awards and the prestigious medals of the Academy.</t>
         </is>
       </c>
-      <c r="I380" t="inlineStr">
+      <c r="I380" s="10" t="inlineStr">
         <is>
           <t>Varies (medals + some cash)</t>
         </is>
       </c>
-      <c r="J380" t="inlineStr">
+      <c r="J380" s="10" t="inlineStr">
         <is>
           <t>Annual</t>
         </is>
       </c>
-      <c r="K380" t="inlineStr">
+      <c r="K380" s="10" t="inlineStr">
         <is>
           <t>UK-based biomedical researchers; by nomination</t>
         </is>
       </c>
-      <c r="L380" t="inlineStr">
+      <c r="L380" s="10" t="inlineStr">
         <is>
           <t>Annual nomination (check site)</t>
         </is>
       </c>
-      <c r="M380" t="inlineStr">
+      <c r="M380" s="10" t="inlineStr">
         <is>
           <t>Nomination only</t>
         </is>
       </c>
-      <c r="N380" t="inlineStr">
+      <c r="N380" s="10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="O380" t="inlineStr">
+      <c r="O380" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P380" t="inlineStr">
+      <c r="P380" s="10" t="inlineStr">
         <is>
           <t>https://acmedsci.ac.uk/</t>
         </is>
       </c>
-      <c r="Q380" t="inlineStr">
+      <c r="Q380" s="10" t="inlineStr">
         <is>
           <t>Also runs career development grants alongside its honours.</t>
         </is>
       </c>
-      <c r="R380" t="inlineStr"/>
-      <c r="S380" t="inlineStr"/>
-      <c r="T380" t="inlineStr"/>
-      <c r="U380" t="inlineStr">
+      <c r="R380" s="10" t="inlineStr"/>
+      <c r="S380" s="10" t="inlineStr"/>
+      <c r="T380" s="10" t="inlineStr"/>
+      <c r="U380" s="10" t="inlineStr">
         <is>
           <t>award</t>
         </is>
       </c>
     </row>
     <row r="381">
-      <c r="A381" t="inlineStr">
+      <c r="A381" s="10" t="inlineStr">
         <is>
           <t>A39</t>
         </is>
       </c>
-      <c r="B381" t="inlineStr">
+      <c r="B381" s="10" t="inlineStr">
         <is>
           <t>Royal Irish Academy Gold Medals</t>
         </is>
       </c>
-      <c r="C381" t="inlineStr">
+      <c r="C381" s="10" t="inlineStr">
         <is>
           <t>Royal Irish Academy</t>
         </is>
       </c>
-      <c r="D381" t="inlineStr">
+      <c r="D381" s="10" t="inlineStr">
         <is>
           <t>RIA</t>
         </is>
       </c>
-      <c r="E381" t="inlineStr">
+      <c r="E381" s="10" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="F381" t="inlineStr">
+      <c r="F381" s="10" t="inlineStr">
         <is>
           <t>Sciences &amp; humanities</t>
         </is>
       </c>
-      <c r="G381" t="inlineStr">
+      <c r="G381" s="10" t="inlineStr">
         <is>
           <t>Established</t>
         </is>
       </c>
-      <c r="H381" t="inlineStr">
+      <c r="H381" s="10" t="inlineStr">
         <is>
           <t>Ireland's highest academic accolade, recognising outstanding scholarly contributions across the sciences and humanities.</t>
         </is>
       </c>
-      <c r="I381" t="inlineStr">
+      <c r="I381" s="10" t="inlineStr">
         <is>
           <t>Gold medal (honorary)</t>
         </is>
       </c>
-      <c r="J381" t="inlineStr">
+      <c r="J381" s="10" t="inlineStr">
         <is>
           <t>Annual</t>
         </is>
       </c>
-      <c r="K381" t="inlineStr">
+      <c r="K381" s="10" t="inlineStr">
         <is>
           <t>Scholars connected to Ireland; by nomination</t>
         </is>
       </c>
-      <c r="L381" t="inlineStr">
+      <c r="L381" s="10" t="inlineStr">
         <is>
           <t>Annual nomination (check site)</t>
         </is>
       </c>
-      <c r="M381" t="inlineStr">
+      <c r="M381" s="10" t="inlineStr">
         <is>
           <t>Nomination only</t>
         </is>
       </c>
-      <c r="N381" t="inlineStr">
+      <c r="N381" s="10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="O381" t="inlineStr">
+      <c r="O381" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P381" t="inlineStr">
+      <c r="P381" s="10" t="inlineStr">
         <is>
           <t>https://www.ria.ie/</t>
         </is>
       </c>
-      <c r="Q381" t="inlineStr">
+      <c r="Q381" s="10" t="inlineStr">
         <is>
           <t>Ireland's premier learned-society honour.</t>
         </is>
       </c>
-      <c r="R381" t="inlineStr"/>
-      <c r="S381" t="inlineStr"/>
-      <c r="T381" t="inlineStr"/>
-      <c r="U381" t="inlineStr">
+      <c r="R381" s="10" t="inlineStr"/>
+      <c r="S381" s="10" t="inlineStr"/>
+      <c r="T381" s="10" t="inlineStr"/>
+      <c r="U381" s="10" t="inlineStr">
         <is>
           <t>award</t>
         </is>
       </c>
     </row>
     <row r="382">
-      <c r="A382" t="inlineStr">
+      <c r="A382" s="10" t="inlineStr">
         <is>
           <t>A40</t>
         </is>
       </c>
-      <c r="B382" t="inlineStr">
+      <c r="B382" s="10" t="inlineStr">
         <is>
           <t>Descartes Prize / EU research recognition</t>
         </is>
       </c>
-      <c r="C382" t="inlineStr">
+      <c r="C382" s="10" t="inlineStr">
         <is>
           <t>European Commission</t>
         </is>
       </c>
-      <c r="D382" t="inlineStr">
+      <c r="D382" s="10" t="inlineStr">
         <is>
           <t>EU</t>
         </is>
       </c>
-      <c r="E382" t="inlineStr">
+      <c r="E382" s="10" t="inlineStr">
         <is>
           <t>EU + Associated Countries</t>
         </is>
       </c>
-      <c r="F382" t="inlineStr">
+      <c r="F382" s="10" t="inlineStr">
         <is>
           <t>All sciences (collaborative research)</t>
         </is>
       </c>
-      <c r="G382" t="inlineStr">
+      <c r="G382" s="10" t="inlineStr">
         <is>
           <t>Teams</t>
         </is>
       </c>
-      <c r="H382" t="inlineStr">
+      <c r="H382" s="10" t="inlineStr">
         <is>
           <t>EU-level recognition for outstanding collaborative research achievements by transnational teams (successor recognitions continue under Horizon Europe).</t>
         </is>
       </c>
-      <c r="I382" t="inlineStr">
+      <c r="I382" s="10" t="inlineStr">
         <is>
           <t>Historically up to €1,000,000 shared</t>
         </is>
       </c>
-      <c r="J382" t="inlineStr">
+      <c r="J382" s="10" t="inlineStr">
         <is>
           <t>Periodic</t>
         </is>
       </c>
-      <c r="K382" t="inlineStr">
+      <c r="K382" s="10" t="inlineStr">
         <is>
           <t>Transnational research collaborations in EU/associated countries</t>
         </is>
       </c>
-      <c r="L382" t="inlineStr">
+      <c r="L382" s="10" t="inlineStr">
         <is>
           <t>Per call (check site)</t>
         </is>
       </c>
-      <c r="M382" t="inlineStr">
+      <c r="M382" s="10" t="inlineStr">
         <is>
           <t>Nomination / call</t>
         </is>
       </c>
-      <c r="N382" t="inlineStr">
+      <c r="N382" s="10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="O382" t="inlineStr">
+      <c r="O382" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P382" t="inlineStr">
+      <c r="P382" s="10" t="inlineStr">
         <is>
           <t>https://research-and-innovation.ec.europa.eu/</t>
         </is>
       </c>
-      <c r="Q382" t="inlineStr">
+      <c r="Q382" s="10" t="inlineStr">
         <is>
           <t>Celebrates the collaborative, cross-border nature of European research.</t>
         </is>
       </c>
-      <c r="R382" t="inlineStr"/>
-      <c r="S382" t="inlineStr"/>
-      <c r="T382" t="inlineStr"/>
-      <c r="U382" t="inlineStr">
+      <c r="R382" s="10" t="inlineStr"/>
+      <c r="S382" s="10" t="inlineStr"/>
+      <c r="T382" s="10" t="inlineStr"/>
+      <c r="U382" s="10" t="inlineStr">
         <is>
           <t>award</t>
         </is>
       </c>
     </row>
     <row r="383">
-      <c r="A383" t="inlineStr">
+      <c r="A383" s="10" t="inlineStr">
         <is>
           <t>A41</t>
         </is>
       </c>
-      <c r="B383" t="inlineStr">
+      <c r="B383" s="10" t="inlineStr">
         <is>
           <t>Körber European Science Prize</t>
         </is>
       </c>
-      <c r="C383" t="inlineStr">
+      <c r="C383" s="10" t="inlineStr">
         <is>
           <t>Körber Foundation</t>
         </is>
       </c>
-      <c r="D383" t="inlineStr">
+      <c r="D383" s="10" t="inlineStr">
         <is>
           <t>Körber</t>
         </is>
       </c>
-      <c r="E383" t="inlineStr">
+      <c r="E383" s="10" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="F383" t="inlineStr">
+      <c r="F383" s="10" t="inlineStr">
         <is>
           <t>Life &amp; physical sciences</t>
         </is>
       </c>
-      <c r="G383" t="inlineStr">
+      <c r="G383" s="10" t="inlineStr">
         <is>
           <t>Established</t>
         </is>
       </c>
-      <c r="H383" t="inlineStr">
+      <c r="H383" s="10" t="inlineStr">
         <is>
           <t>One of Europe's most valuable science prizes, funding a specific forward-looking research project by a leading European scientist.</t>
         </is>
       </c>
-      <c r="I383" t="inlineStr">
+      <c r="I383" s="10" t="inlineStr">
         <is>
           <t>€1,000,000</t>
         </is>
       </c>
-      <c r="J383" t="inlineStr">
+      <c r="J383" s="10" t="inlineStr">
         <is>
           <t>Annual</t>
         </is>
       </c>
-      <c r="K383" t="inlineStr">
+      <c r="K383" s="10" t="inlineStr">
         <is>
           <t>Researchers working in Europe; by nomination</t>
         </is>
       </c>
-      <c r="L383" t="inlineStr">
+      <c r="L383" s="10" t="inlineStr">
         <is>
           <t>Annual nomination (check site)</t>
         </is>
       </c>
-      <c r="M383" t="inlineStr">
+      <c r="M383" s="10" t="inlineStr">
         <is>
           <t>Nomination only</t>
         </is>
       </c>
-      <c r="N383" t="inlineStr">
+      <c r="N383" s="10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="O383" t="inlineStr">
+      <c r="O383" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P383" t="inlineStr">
+      <c r="P383" s="10" t="inlineStr">
         <is>
           <t>https://www.koerber-stiftung.de/en/koerber-prize</t>
         </is>
       </c>
-      <c r="Q383" t="inlineStr">
+      <c r="Q383" s="10" t="inlineStr">
         <is>
           <t>The money funds future research rather than rewarding past work alone.</t>
         </is>
       </c>
-      <c r="R383" t="inlineStr"/>
-      <c r="S383" t="inlineStr"/>
-      <c r="T383" t="inlineStr"/>
-      <c r="U383" t="inlineStr">
+      <c r="R383" s="10" t="inlineStr"/>
+      <c r="S383" s="10" t="inlineStr"/>
+      <c r="T383" s="10" t="inlineStr"/>
+      <c r="U383" s="10" t="inlineStr">
         <is>
           <t>award</t>
         </is>
       </c>
     </row>
     <row r="384">
-      <c r="A384" t="inlineStr">
+      <c r="A384" s="10" t="inlineStr">
         <is>
           <t>A42</t>
         </is>
       </c>
-      <c r="B384" t="inlineStr">
+      <c r="B384" s="10" t="inlineStr">
         <is>
           <t>Balzan Prize</t>
         </is>
       </c>
-      <c r="C384" t="inlineStr">
+      <c r="C384" s="10" t="inlineStr">
         <is>
           <t>International Balzan Prize Foundation</t>
         </is>
       </c>
-      <c r="D384" t="inlineStr">
+      <c r="D384" s="10" t="inlineStr">
         <is>
           <t>Balzan</t>
         </is>
       </c>
-      <c r="E384" t="inlineStr">
+      <c r="E384" s="10" t="inlineStr">
         <is>
           <t>International (Europe-based)</t>
         </is>
       </c>
-      <c r="F384" t="inlineStr">
+      <c r="F384" s="10" t="inlineStr">
         <is>
           <t>Sciences, humanities &amp; culture (rotating fields)</t>
         </is>
       </c>
-      <c r="G384" t="inlineStr">
+      <c r="G384" s="10" t="inlineStr">
         <is>
           <t>Established</t>
         </is>
       </c>
-      <c r="H384" t="inlineStr">
+      <c r="H384" s="10" t="inlineStr">
         <is>
           <t>A major prize across rotating fields in the sciences and humanities, requiring half the award to fund young researchers.</t>
         </is>
       </c>
-      <c r="I384" t="inlineStr">
+      <c r="I384" s="10" t="inlineStr">
         <is>
           <t>CHF 750,000 per prize</t>
         </is>
       </c>
-      <c r="J384" t="inlineStr">
+      <c r="J384" s="10" t="inlineStr">
         <is>
           <t>Annual</t>
         </is>
       </c>
-      <c r="K384" t="inlineStr">
+      <c r="K384" s="10" t="inlineStr">
         <is>
           <t>By nomination; fields rotate each year</t>
         </is>
       </c>
-      <c r="L384" t="inlineStr">
+      <c r="L384" s="10" t="inlineStr">
         <is>
           <t>Annual nomination (check site)</t>
         </is>
       </c>
-      <c r="M384" t="inlineStr">
+      <c r="M384" s="10" t="inlineStr">
         <is>
           <t>Nomination only</t>
         </is>
       </c>
-      <c r="N384" t="inlineStr">
+      <c r="N384" s="10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="O384" t="inlineStr">
+      <c r="O384" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P384" t="inlineStr">
+      <c r="P384" s="10" t="inlineStr">
         <is>
           <t>https://www.balzan.org/en</t>
         </is>
       </c>
-      <c r="Q384" t="inlineStr">
+      <c r="Q384" s="10" t="inlineStr">
         <is>
           <t>Uniquely, laureates must devote half the prize to funding young scholars.</t>
         </is>
       </c>
-      <c r="R384" t="inlineStr"/>
-      <c r="S384" t="inlineStr"/>
-      <c r="T384" t="inlineStr"/>
-      <c r="U384" t="inlineStr">
+      <c r="R384" s="10" t="inlineStr"/>
+      <c r="S384" s="10" t="inlineStr"/>
+      <c r="T384" s="10" t="inlineStr"/>
+      <c r="U384" s="10" t="inlineStr">
         <is>
           <t>award</t>
         </is>
       </c>
     </row>
     <row r="385">
-      <c r="A385" t="inlineStr">
+      <c r="A385" s="10" t="inlineStr">
         <is>
           <t>A43</t>
         </is>
       </c>
-      <c r="B385" t="inlineStr">
+      <c r="B385" s="10" t="inlineStr">
         <is>
           <t>Louis-Jeantet Prize for Medicine</t>
         </is>
       </c>
-      <c r="C385" t="inlineStr">
+      <c r="C385" s="10" t="inlineStr">
         <is>
           <t>Louis-Jeantet Foundation</t>
         </is>
       </c>
-      <c r="D385" t="inlineStr">
+      <c r="D385" s="10" t="inlineStr">
         <is>
           <t>Jeantet</t>
         </is>
       </c>
-      <c r="E385" t="inlineStr">
+      <c r="E385" s="10" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="F385" t="inlineStr">
+      <c r="F385" s="10" t="inlineStr">
         <is>
           <t>Biomedical research</t>
         </is>
       </c>
-      <c r="G385" t="inlineStr">
+      <c r="G385" s="10" t="inlineStr">
         <is>
           <t>Established</t>
         </is>
       </c>
-      <c r="H385" t="inlineStr">
+      <c r="H385" s="10" t="inlineStr">
         <is>
           <t>A leading European biomedical prize, funding ongoing research by scientists working in Council of Europe member states.</t>
         </is>
       </c>
-      <c r="I385" t="inlineStr">
+      <c r="I385" s="10" t="inlineStr">
         <is>
           <t>CHF 500,000 (mostly for continued research)</t>
         </is>
       </c>
-      <c r="J385" t="inlineStr">
+      <c r="J385" s="10" t="inlineStr">
         <is>
           <t>Annual</t>
         </is>
       </c>
-      <c r="K385" t="inlineStr">
+      <c r="K385" s="10" t="inlineStr">
         <is>
           <t>Researchers in Council of Europe states; by nomination</t>
         </is>
       </c>
-      <c r="L385" t="inlineStr">
+      <c r="L385" s="10" t="inlineStr">
         <is>
           <t>Annual nomination (check site)</t>
         </is>
       </c>
-      <c r="M385" t="inlineStr">
+      <c r="M385" s="10" t="inlineStr">
         <is>
           <t>Nomination only</t>
         </is>
       </c>
-      <c r="N385" t="inlineStr">
+      <c r="N385" s="10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="O385" t="inlineStr">
+      <c r="O385" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P385" t="inlineStr">
+      <c r="P385" s="10" t="inlineStr">
         <is>
           <t>https://www.jeantet.ch/en/</t>
         </is>
       </c>
-      <c r="Q385" t="inlineStr">
+      <c r="Q385" s="10" t="inlineStr">
         <is>
           <t>Most of the prize is earmarked to continue the laureate's research.</t>
         </is>
       </c>
-      <c r="R385" t="inlineStr"/>
-      <c r="S385" t="inlineStr"/>
-      <c r="T385" t="inlineStr"/>
-      <c r="U385" t="inlineStr">
+      <c r="R385" s="10" t="inlineStr"/>
+      <c r="S385" s="10" t="inlineStr"/>
+      <c r="T385" s="10" t="inlineStr"/>
+      <c r="U385" s="10" t="inlineStr">
         <is>
           <t>award</t>
         </is>
       </c>
     </row>
     <row r="386">
-      <c r="A386" t="inlineStr">
+      <c r="A386" s="10" t="inlineStr">
         <is>
           <t>A44</t>
         </is>
       </c>
-      <c r="B386" t="inlineStr">
+      <c r="B386" s="10" t="inlineStr">
         <is>
           <t>Brain Prize (Lundbeck Foundation)</t>
         </is>
       </c>
-      <c r="C386" t="inlineStr">
+      <c r="C386" s="10" t="inlineStr">
         <is>
           <t>Lundbeck Foundation</t>
         </is>
       </c>
-      <c r="D386" t="inlineStr">
+      <c r="D386" s="10" t="inlineStr">
         <is>
           <t>Lundbeck</t>
         </is>
       </c>
-      <c r="E386" t="inlineStr">
+      <c r="E386" s="10" t="inlineStr">
         <is>
           <t>International</t>
         </is>
       </c>
-      <c r="F386" t="inlineStr">
+      <c r="F386" s="10" t="inlineStr">
         <is>
           <t>Neuroscience</t>
         </is>
       </c>
-      <c r="G386" t="inlineStr">
+      <c r="G386" s="10" t="inlineStr">
         <is>
           <t>Established</t>
         </is>
       </c>
-      <c r="H386" t="inlineStr">
+      <c r="H386" s="10" t="inlineStr">
         <is>
           <t>The world's largest neuroscience prize, recognising outstanding contributions to brain research.</t>
         </is>
       </c>
-      <c r="I386" t="inlineStr">
+      <c r="I386" s="10" t="inlineStr">
         <is>
           <t>DKK 10,000,000 (~€1.3M)</t>
         </is>
       </c>
-      <c r="J386" t="inlineStr">
+      <c r="J386" s="10" t="inlineStr">
         <is>
           <t>Annual</t>
         </is>
       </c>
-      <c r="K386" t="inlineStr">
+      <c r="K386" s="10" t="inlineStr">
         <is>
           <t>By nomination; open internationally</t>
         </is>
       </c>
-      <c r="L386" t="inlineStr">
+      <c r="L386" s="10" t="inlineStr">
         <is>
           <t>Annual nomination (check site)</t>
         </is>
       </c>
-      <c r="M386" t="inlineStr">
+      <c r="M386" s="10" t="inlineStr">
         <is>
           <t>Nomination only</t>
         </is>
       </c>
-      <c r="N386" t="inlineStr">
+      <c r="N386" s="10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="O386" t="inlineStr">
+      <c r="O386" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P386" t="inlineStr">
+      <c r="P386" s="10" t="inlineStr">
         <is>
           <t>https://lundbeckfonden.com/en/the-brain-prize</t>
         </is>
       </c>
-      <c r="Q386" t="inlineStr">
+      <c r="Q386" s="10" t="inlineStr">
         <is>
           <t>The single most prestigious award in neuroscience.</t>
         </is>
       </c>
-      <c r="R386" t="inlineStr"/>
-      <c r="S386" t="inlineStr"/>
-      <c r="T386" t="inlineStr"/>
-      <c r="U386" t="inlineStr">
+      <c r="R386" s="10" t="inlineStr"/>
+      <c r="S386" s="10" t="inlineStr"/>
+      <c r="T386" s="10" t="inlineStr"/>
+      <c r="U386" s="10" t="inlineStr">
         <is>
           <t>award</t>
         </is>
       </c>
     </row>
     <row r="387">
-      <c r="A387" t="inlineStr">
+      <c r="A387" s="10" t="inlineStr">
         <is>
           <t>A45</t>
         </is>
       </c>
-      <c r="B387" t="inlineStr">
+      <c r="B387" s="10" t="inlineStr">
         <is>
           <t>Gottfried Wilhelm Leibniz Prize</t>
         </is>
       </c>
-      <c r="C387" t="inlineStr">
+      <c r="C387" s="10" t="inlineStr">
         <is>
           <t>German Research Foundation (DFG)</t>
         </is>
       </c>
-      <c r="D387" t="inlineStr">
+      <c r="D387" s="10" t="inlineStr">
         <is>
           <t>DFG</t>
         </is>
       </c>
-      <c r="E387" t="inlineStr">
+      <c r="E387" s="10" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="F387" t="inlineStr">
+      <c r="F387" s="10" t="inlineStr">
         <is>
           <t>All disciplines</t>
         </is>
       </c>
-      <c r="G387" t="inlineStr">
+      <c r="G387" s="10" t="inlineStr">
         <is>
           <t>Established (active researchers)</t>
         </is>
       </c>
-      <c r="H387" t="inlineStr">
+      <c r="H387" s="10" t="inlineStr">
         <is>
           <t>Germany's most important research prize, giving laureates exceptional funding freedom for their ongoing work.</t>
         </is>
       </c>
-      <c r="I387" t="inlineStr">
+      <c r="I387" s="10" t="inlineStr">
         <is>
           <t>€2,500,000</t>
         </is>
       </c>
-      <c r="J387" t="inlineStr">
+      <c r="J387" s="10" t="inlineStr">
         <is>
           <t>Annual</t>
         </is>
       </c>
-      <c r="K387" t="inlineStr">
+      <c r="K387" s="10" t="inlineStr">
         <is>
           <t>Researchers at German institutions; by nomination</t>
         </is>
       </c>
-      <c r="L387" t="inlineStr">
+      <c r="L387" s="10" t="inlineStr">
         <is>
           <t>Annual nomination (check site)</t>
         </is>
       </c>
-      <c r="M387" t="inlineStr">
+      <c r="M387" s="10" t="inlineStr">
         <is>
           <t>Nomination only</t>
         </is>
       </c>
-      <c r="N387" t="inlineStr">
+      <c r="N387" s="10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="O387" t="inlineStr">
+      <c r="O387" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P387" t="inlineStr">
+      <c r="P387" s="10" t="inlineStr">
         <is>
           <t>https://www.dfg.de/en/</t>
         </is>
       </c>
-      <c r="Q387" t="inlineStr">
+      <c r="Q387" s="10" t="inlineStr">
         <is>
           <t>The best-funded research prize in the world by award amount.</t>
         </is>
       </c>
-      <c r="R387" t="inlineStr"/>
-      <c r="S387" t="inlineStr"/>
-      <c r="T387" t="inlineStr"/>
-      <c r="U387" t="inlineStr">
+      <c r="R387" s="10" t="inlineStr"/>
+      <c r="S387" s="10" t="inlineStr"/>
+      <c r="T387" s="10" t="inlineStr"/>
+      <c r="U387" s="10" t="inlineStr">
         <is>
           <t>award</t>
         </is>
       </c>
     </row>
     <row r="388">
-      <c r="A388" t="inlineStr">
+      <c r="A388" s="10" t="inlineStr">
         <is>
           <t>A46</t>
         </is>
       </c>
-      <c r="B388" t="inlineStr">
+      <c r="B388" s="10" t="inlineStr">
         <is>
           <t>Leopoldina &amp; Max Planck Research Awards</t>
         </is>
       </c>
-      <c r="C388" t="inlineStr">
+      <c r="C388" s="10" t="inlineStr">
         <is>
           <t>Leopoldina / Alexander von Humboldt Foundation</t>
         </is>
       </c>
-      <c r="D388" t="inlineStr">
+      <c r="D388" s="10" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="E388" t="inlineStr">
+      <c r="E388" s="10" t="inlineStr">
         <is>
           <t>Germany / International</t>
         </is>
       </c>
-      <c r="F388" t="inlineStr">
+      <c r="F388" s="10" t="inlineStr">
         <is>
           <t>All sciences</t>
         </is>
       </c>
-      <c r="G388" t="inlineStr">
+      <c r="G388" s="10" t="inlineStr">
         <is>
           <t>Established</t>
         </is>
       </c>
-      <c r="H388" t="inlineStr">
+      <c r="H388" s="10" t="inlineStr">
         <is>
           <t>German national-academy and Max Planck honours recognising internationally outstanding researchers, several open to non-German scientists.</t>
         </is>
       </c>
-      <c r="I388" t="inlineStr">
+      <c r="I388" s="10" t="inlineStr">
         <is>
           <t>Up to €750,000 (Max Planck Research Award)</t>
         </is>
       </c>
-      <c r="J388" t="inlineStr">
+      <c r="J388" s="10" t="inlineStr">
         <is>
           <t>Annual / periodic</t>
         </is>
       </c>
-      <c r="K388" t="inlineStr">
+      <c r="K388" s="10" t="inlineStr">
         <is>
           <t>By nomination; several open internationally</t>
         </is>
       </c>
-      <c r="L388" t="inlineStr">
+      <c r="L388" s="10" t="inlineStr">
         <is>
           <t>Annual nomination (check site)</t>
         </is>
       </c>
-      <c r="M388" t="inlineStr">
+      <c r="M388" s="10" t="inlineStr">
         <is>
           <t>Nomination only</t>
         </is>
       </c>
-      <c r="N388" t="inlineStr">
+      <c r="N388" s="10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="O388" t="inlineStr">
+      <c r="O388" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P388" t="inlineStr">
+      <c r="P388" s="10" t="inlineStr">
         <is>
           <t>https://www.leopoldina.org/en/</t>
         </is>
       </c>
-      <c r="Q388" t="inlineStr">
+      <c r="Q388" s="10" t="inlineStr">
         <is>
           <t>The Max Planck Research Award explicitly funds international collaboration.</t>
         </is>
       </c>
-      <c r="R388" t="inlineStr"/>
-      <c r="S388" t="inlineStr"/>
-      <c r="T388" t="inlineStr"/>
-      <c r="U388" t="inlineStr">
+      <c r="R388" s="10" t="inlineStr"/>
+      <c r="S388" s="10" t="inlineStr"/>
+      <c r="T388" s="10" t="inlineStr"/>
+      <c r="U388" s="10" t="inlineStr">
         <is>
           <t>award</t>
         </is>
       </c>
     </row>
     <row r="389">
-      <c r="A389" t="inlineStr">
+      <c r="A389" s="10" t="inlineStr">
         <is>
           <t>A47</t>
         </is>
       </c>
-      <c r="B389" t="inlineStr">
+      <c r="B389" s="10" t="inlineStr">
         <is>
           <t>CNRS Gold, Silver &amp; Bronze Medals</t>
         </is>
       </c>
-      <c r="C389" t="inlineStr">
+      <c r="C389" s="10" t="inlineStr">
         <is>
           <t>Centre National de la Recherche Scientifique (CNRS)</t>
         </is>
       </c>
-      <c r="D389" t="inlineStr">
+      <c r="D389" s="10" t="inlineStr">
         <is>
           <t>CNRS</t>
         </is>
       </c>
-      <c r="E389" t="inlineStr">
+      <c r="E389" s="10" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="F389" t="inlineStr">
+      <c r="F389" s="10" t="inlineStr">
         <is>
           <t>All sciences</t>
         </is>
       </c>
-      <c r="G389" t="inlineStr">
+      <c r="G389" s="10" t="inlineStr">
         <is>
           <t>Early-career → lifetime (by medal)</t>
         </is>
       </c>
-      <c r="H389" t="inlineStr">
+      <c r="H389" s="10" t="inlineStr">
         <is>
           <t>France's national research honours: the Gold Medal for lifetime achievement, Silver for established and Bronze for early-career researchers.</t>
         </is>
       </c>
-      <c r="I389" t="inlineStr">
+      <c r="I389" s="10" t="inlineStr">
         <is>
           <t>Medal + recognition</t>
         </is>
       </c>
-      <c r="J389" t="inlineStr">
+      <c r="J389" s="10" t="inlineStr">
         <is>
           <t>Annual</t>
         </is>
       </c>
-      <c r="K389" t="inlineStr">
+      <c r="K389" s="10" t="inlineStr">
         <is>
           <t>Researchers connected to French science; by nomination</t>
         </is>
       </c>
-      <c r="L389" t="inlineStr">
+      <c r="L389" s="10" t="inlineStr">
         <is>
           <t>Annual (check site)</t>
         </is>
       </c>
-      <c r="M389" t="inlineStr">
+      <c r="M389" s="10" t="inlineStr">
         <is>
           <t>Nomination only</t>
         </is>
       </c>
-      <c r="N389" t="inlineStr">
+      <c r="N389" s="10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="O389" t="inlineStr">
+      <c r="O389" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P389" t="inlineStr">
+      <c r="P389" s="10" t="inlineStr">
         <is>
           <t>https://www.cnrs.fr/en</t>
         </is>
       </c>
-      <c r="Q389" t="inlineStr">
+      <c r="Q389" s="10" t="inlineStr">
         <is>
           <t>The Bronze Medal is a notable early-career marker in France.</t>
         </is>
       </c>
-      <c r="R389" t="inlineStr"/>
-      <c r="S389" t="inlineStr"/>
-      <c r="T389" t="inlineStr"/>
-      <c r="U389" t="inlineStr">
+      <c r="R389" s="10" t="inlineStr"/>
+      <c r="S389" s="10" t="inlineStr"/>
+      <c r="T389" s="10" t="inlineStr"/>
+      <c r="U389" s="10" t="inlineStr">
         <is>
           <t>award</t>
         </is>
       </c>
     </row>
     <row r="390">
-      <c r="A390" t="inlineStr">
+      <c r="A390" s="10" t="inlineStr">
         <is>
           <t>A48</t>
         </is>
       </c>
-      <c r="B390" t="inlineStr">
+      <c r="B390" s="10" t="inlineStr">
         <is>
           <t>Spinoza &amp; Stevin Prizes (NWO)</t>
         </is>
       </c>
-      <c r="C390" t="inlineStr">
+      <c r="C390" s="10" t="inlineStr">
         <is>
           <t>Dutch Research Council (NWO)</t>
         </is>
       </c>
-      <c r="D390" t="inlineStr">
+      <c r="D390" s="10" t="inlineStr">
         <is>
           <t>Netherlands (NWO)</t>
         </is>
       </c>
-      <c r="E390" t="inlineStr">
+      <c r="E390" s="10" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
-      <c r="F390" t="inlineStr">
+      <c r="F390" s="10" t="inlineStr">
         <is>
           <t>All disciplines</t>
         </is>
       </c>
-      <c r="G390" t="inlineStr">
+      <c r="G390" s="10" t="inlineStr">
         <is>
           <t>Established</t>
         </is>
       </c>
-      <c r="H390" t="inlineStr">
+      <c r="H390" s="10" t="inlineStr">
         <is>
           <t>The Netherlands' highest scientific awards — the Spinoza Prize for scientific excellence and the Stevin Prize for societal impact.</t>
         </is>
       </c>
-      <c r="I390" t="inlineStr">
+      <c r="I390" s="10" t="inlineStr">
         <is>
           <t>€1,500,000 each (for research)</t>
         </is>
       </c>
-      <c r="J390" t="inlineStr">
+      <c r="J390" s="10" t="inlineStr">
         <is>
           <t>Annual</t>
         </is>
       </c>
-      <c r="K390" t="inlineStr">
+      <c r="K390" s="10" t="inlineStr">
         <is>
           <t>Researchers at Dutch institutions; by nomination</t>
         </is>
       </c>
-      <c r="L390" t="inlineStr">
+      <c r="L390" s="10" t="inlineStr">
         <is>
           <t>Annual nomination (check site)</t>
         </is>
       </c>
-      <c r="M390" t="inlineStr">
+      <c r="M390" s="10" t="inlineStr">
         <is>
           <t>Nomination only</t>
         </is>
       </c>
-      <c r="N390" t="inlineStr">
+      <c r="N390" s="10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="O390" t="inlineStr">
+      <c r="O390" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P390" t="inlineStr">
+      <c r="P390" s="10" t="inlineStr">
         <is>
           <t>https://www.nwo.nl/en/spinoza-and-stevin-prizes</t>
         </is>
       </c>
-      <c r="Q390" t="inlineStr">
+      <c r="Q390" s="10" t="inlineStr">
         <is>
           <t>Often called the 'Dutch Nobel'; the money funds future research.</t>
         </is>
       </c>
-      <c r="R390" t="inlineStr"/>
-      <c r="S390" t="inlineStr"/>
-      <c r="T390" t="inlineStr"/>
-      <c r="U390" t="inlineStr">
+      <c r="R390" s="10" t="inlineStr"/>
+      <c r="S390" s="10" t="inlineStr"/>
+      <c r="T390" s="10" t="inlineStr"/>
+      <c r="U390" s="10" t="inlineStr">
         <is>
           <t>award</t>
         </is>
       </c>
     </row>
     <row r="391">
-      <c r="A391" t="inlineStr">
+      <c r="A391" s="10" t="inlineStr">
         <is>
           <t>A49</t>
         </is>
       </c>
-      <c r="B391" t="inlineStr">
+      <c r="B391" s="10" t="inlineStr">
         <is>
           <t>Marcus Wallenberg &amp; Crafoord Prizes</t>
         </is>
       </c>
-      <c r="C391" t="inlineStr">
+      <c r="C391" s="10" t="inlineStr">
         <is>
           <t>Royal Swedish Academy of Sciences / Wallenberg</t>
         </is>
       </c>
-      <c r="D391" t="inlineStr">
+      <c r="D391" s="10" t="inlineStr">
         <is>
           <t>Sweden</t>
         </is>
       </c>
-      <c r="E391" t="inlineStr">
+      <c r="E391" s="10" t="inlineStr">
         <is>
           <t>Sweden / International</t>
         </is>
       </c>
-      <c r="F391" t="inlineStr">
+      <c r="F391" s="10" t="inlineStr">
         <is>
           <t>Fields not covered by the Nobel (Crafoord); forestry (Wallenberg)</t>
         </is>
       </c>
-      <c r="G391" t="inlineStr">
+      <c r="G391" s="10" t="inlineStr">
         <is>
           <t>Established</t>
         </is>
       </c>
-      <c r="H391" t="inlineStr">
+      <c r="H391" s="10" t="inlineStr">
         <is>
           <t>Swedish international prizes filling gaps left by the Nobel — the Crafoord Prize covers mathematics, geosciences, biosciences and astronomy.</t>
         </is>
       </c>
-      <c r="I391" t="inlineStr">
+      <c r="I391" s="10" t="inlineStr">
         <is>
           <t>Crafoord ~6M SEK; Marcus Wallenberg ~SEK 5M</t>
         </is>
       </c>
-      <c r="J391" t="inlineStr">
+      <c r="J391" s="10" t="inlineStr">
         <is>
           <t>Annual (Crafoord fields rotate)</t>
         </is>
       </c>
-      <c r="K391" t="inlineStr">
+      <c r="K391" s="10" t="inlineStr">
         <is>
           <t>By nomination; international candidates</t>
         </is>
       </c>
-      <c r="L391" t="inlineStr">
+      <c r="L391" s="10" t="inlineStr">
         <is>
           <t>Annual nomination (check site)</t>
         </is>
       </c>
-      <c r="M391" t="inlineStr">
+      <c r="M391" s="10" t="inlineStr">
         <is>
           <t>Nomination only</t>
         </is>
       </c>
-      <c r="N391" t="inlineStr">
+      <c r="N391" s="10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="O391" t="inlineStr">
+      <c r="O391" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P391" t="inlineStr">
+      <c r="P391" s="10" t="inlineStr">
         <is>
           <t>https://www.crafoordprize.se/</t>
         </is>
       </c>
-      <c r="Q391" t="inlineStr">
+      <c r="Q391" s="10" t="inlineStr">
         <is>
           <t>The Crafoord deliberately covers sciences the Nobel omits.</t>
         </is>
       </c>
-      <c r="R391" t="inlineStr"/>
-      <c r="S391" t="inlineStr"/>
-      <c r="T391" t="inlineStr"/>
-      <c r="U391" t="inlineStr">
+      <c r="R391" s="10" t="inlineStr"/>
+      <c r="S391" s="10" t="inlineStr"/>
+      <c r="T391" s="10" t="inlineStr"/>
+      <c r="U391" s="10" t="inlineStr">
         <is>
           <t>award</t>
         </is>
       </c>
     </row>
     <row r="392">
-      <c r="A392" t="inlineStr">
+      <c r="A392" s="10" t="inlineStr">
         <is>
           <t>A50</t>
         </is>
       </c>
-      <c r="B392" t="inlineStr">
+      <c r="B392" s="10" t="inlineStr">
         <is>
           <t>Novozymes Prize &amp; Novo Nordisk Prize</t>
         </is>
       </c>
-      <c r="C392" t="inlineStr">
+      <c r="C392" s="10" t="inlineStr">
         <is>
           <t>Novo Nordisk Foundation</t>
         </is>
       </c>
-      <c r="D392" t="inlineStr">
+      <c r="D392" s="10" t="inlineStr">
         <is>
           <t>Denmark</t>
         </is>
       </c>
-      <c r="E392" t="inlineStr">
+      <c r="E392" s="10" t="inlineStr">
         <is>
           <t>Denmark / International</t>
         </is>
       </c>
-      <c r="F392" t="inlineStr">
+      <c r="F392" s="10" t="inlineStr">
         <is>
           <t>Biotechnology &amp; biomedical research</t>
         </is>
       </c>
-      <c r="G392" t="inlineStr">
+      <c r="G392" s="10" t="inlineStr">
         <is>
           <t>Established</t>
         </is>
       </c>
-      <c r="H392" t="inlineStr">
+      <c r="H392" s="10" t="inlineStr">
         <is>
           <t>Major Danish international prizes recognising outstanding biomedical and biotechnology research.</t>
         </is>
       </c>
-      <c r="I392" t="inlineStr">
+      <c r="I392" s="10" t="inlineStr">
         <is>
           <t>DKK 3,000,000-5,000,000</t>
         </is>
       </c>
-      <c r="J392" t="inlineStr">
+      <c r="J392" s="10" t="inlineStr">
         <is>
           <t>Annual</t>
         </is>
       </c>
-      <c r="K392" t="inlineStr">
+      <c r="K392" s="10" t="inlineStr">
         <is>
           <t>By nomination; open internationally</t>
         </is>
       </c>
-      <c r="L392" t="inlineStr">
+      <c r="L392" s="10" t="inlineStr">
         <is>
           <t>Annual nomination (check site)</t>
         </is>
       </c>
-      <c r="M392" t="inlineStr">
+      <c r="M392" s="10" t="inlineStr">
         <is>
           <t>Nomination only</t>
         </is>
       </c>
-      <c r="N392" t="inlineStr">
+      <c r="N392" s="10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="O392" t="inlineStr">
+      <c r="O392" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P392" t="inlineStr">
+      <c r="P392" s="10" t="inlineStr">
         <is>
           <t>https://novonordiskfonden.dk/en/prizes/</t>
         </is>
       </c>
-      <c r="Q392" t="inlineStr">
+      <c r="Q392" s="10" t="inlineStr">
         <is>
           <t>Among the largest life-science prizes in the Nordic region.</t>
         </is>
       </c>
-      <c r="R392" t="inlineStr"/>
-      <c r="S392" t="inlineStr"/>
-      <c r="T392" t="inlineStr"/>
-      <c r="U392" t="inlineStr">
+      <c r="R392" s="10" t="inlineStr"/>
+      <c r="S392" s="10" t="inlineStr"/>
+      <c r="T392" s="10" t="inlineStr"/>
+      <c r="U392" s="10" t="inlineStr">
         <is>
           <t>award</t>
         </is>
       </c>
     </row>
     <row r="393">
-      <c r="A393" t="inlineStr">
+      <c r="A393" s="10" t="inlineStr">
         <is>
           <t>A51</t>
         </is>
       </c>
-      <c r="B393" t="inlineStr">
+      <c r="B393" s="10" t="inlineStr">
         <is>
           <t>ERC-style national young academy memberships / Die Junge Akademie</t>
         </is>
       </c>
-      <c r="C393" t="inlineStr">
+      <c r="C393" s="10" t="inlineStr">
         <is>
           <t>Die Junge Akademie (Germany)</t>
         </is>
       </c>
-      <c r="D393" t="inlineStr">
+      <c r="D393" s="10" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="E393" t="inlineStr">
+      <c r="E393" s="10" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="F393" t="inlineStr">
+      <c r="F393" s="10" t="inlineStr">
         <is>
           <t>All disciplines</t>
         </is>
       </c>
-      <c r="G393" t="inlineStr">
+      <c r="G393" s="10" t="inlineStr">
         <is>
           <t>Early-career</t>
         </is>
       </c>
-      <c r="H393" t="inlineStr">
+      <c r="H393" s="10" t="inlineStr">
         <is>
           <t>Membership-based recognition for outstanding early-career researchers, offering funding, networks and a national platform.</t>
         </is>
       </c>
-      <c r="I393" t="inlineStr">
+      <c r="I393" s="10" t="inlineStr">
         <is>
           <t>Annual research budget + membership</t>
         </is>
       </c>
-      <c r="J393" t="inlineStr">
+      <c r="J393" s="10" t="inlineStr">
         <is>
           <t>5-year membership</t>
         </is>
       </c>
-      <c r="K393" t="inlineStr">
+      <c r="K393" s="10" t="inlineStr">
         <is>
           <t>Outstanding researchers 3-7 years post-PhD; by application/nomination</t>
         </is>
       </c>
-      <c r="L393" t="inlineStr">
+      <c r="L393" s="10" t="inlineStr">
         <is>
           <t>Annual call (check site)</t>
         </is>
       </c>
-      <c r="M393" t="inlineStr">
+      <c r="M393" s="10" t="inlineStr">
         <is>
           <t>Application / nomination</t>
         </is>
       </c>
-      <c r="N393" t="inlineStr">
+      <c r="N393" s="10" t="inlineStr">
         <is>
           <t>Yes — selection</t>
         </is>
       </c>
-      <c r="O393" t="inlineStr">
+      <c r="O393" s="10" t="inlineStr">
         <is>
           <t>Competitive</t>
         </is>
       </c>
-      <c r="P393" t="inlineStr">
+      <c r="P393" s="10" t="inlineStr">
         <is>
           <t>https://www.diejungeakademie.de/en/</t>
         </is>
       </c>
-      <c r="Q393" t="inlineStr">
+      <c r="Q393" s="10" t="inlineStr">
         <is>
           <t>Most European countries now have an equivalent 'young academy'.</t>
         </is>
       </c>
-      <c r="R393" t="inlineStr"/>
-      <c r="S393" t="inlineStr"/>
-      <c r="T393" t="inlineStr"/>
-      <c r="U393" t="inlineStr">
+      <c r="R393" s="10" t="inlineStr"/>
+      <c r="S393" s="10" t="inlineStr"/>
+      <c r="T393" s="10" t="inlineStr"/>
+      <c r="U393" s="10" t="inlineStr">
         <is>
           <t>award</t>
         </is>
       </c>
     </row>
     <row r="394">
-      <c r="A394" t="inlineStr">
+      <c r="A394" s="10" t="inlineStr">
         <is>
           <t>A52</t>
         </is>
       </c>
-      <c r="B394" t="inlineStr">
+      <c r="B394" s="10" t="inlineStr">
         <is>
           <t>For Women in Science National Rising Talent Awards</t>
         </is>
       </c>
-      <c r="C394" t="inlineStr">
+      <c r="C394" s="10" t="inlineStr">
         <is>
           <t>L'Oréal &amp; national partners</t>
         </is>
       </c>
-      <c r="D394" t="inlineStr">
+      <c r="D394" s="10" t="inlineStr">
         <is>
           <t>L'Oréal</t>
         </is>
       </c>
-      <c r="E394" t="inlineStr">
+      <c r="E394" s="10" t="inlineStr">
         <is>
           <t>International (national programmes)</t>
         </is>
       </c>
-      <c r="F394" t="inlineStr">
+      <c r="F394" s="10" t="inlineStr">
         <is>
           <t>Life &amp; physical sciences (women)</t>
         </is>
       </c>
-      <c r="G394" t="inlineStr">
+      <c r="G394" s="10" t="inlineStr">
         <is>
           <t>PhD &amp; early postdoc (women)</t>
         </is>
       </c>
-      <c r="H394" t="inlineStr">
+      <c r="H394" s="10" t="inlineStr">
         <is>
           <t>National rising-talent fellowships (distinct from the international awards) supporting early-career women scientists in dozens of countries.</t>
         </is>
       </c>
-      <c r="I394" t="inlineStr">
+      <c r="I394" s="10" t="inlineStr">
         <is>
           <t>€10,000-30,000 depending on country</t>
         </is>
       </c>
-      <c r="J394" t="inlineStr">
+      <c r="J394" s="10" t="inlineStr">
         <is>
           <t>Annual</t>
         </is>
       </c>
-      <c r="K394" t="inlineStr">
+      <c r="K394" s="10" t="inlineStr">
         <is>
           <t>Women PhD students and postdocs; nationality/residency per country programme</t>
         </is>
       </c>
-      <c r="L394" t="inlineStr">
+      <c r="L394" s="10" t="inlineStr">
         <is>
           <t>Annual national deadlines (check site)</t>
         </is>
       </c>
-      <c r="M394" t="inlineStr">
+      <c r="M394" s="10" t="inlineStr">
         <is>
           <t>National application</t>
         </is>
       </c>
-      <c r="N394" t="inlineStr">
+      <c r="N394" s="10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="O394" t="inlineStr">
+      <c r="O394" s="10" t="inlineStr">
         <is>
           <t>Competitive</t>
         </is>
       </c>
-      <c r="P394" t="inlineStr">
+      <c r="P394" s="10" t="inlineStr">
         <is>
           <t>https://www.forwomeninscience.com/</t>
         </is>
       </c>
-      <c r="Q394" t="inlineStr">
+      <c r="Q394" s="10" t="inlineStr">
         <is>
           <t>Runs in over 100 countries — check your national programme's specifics.</t>
         </is>
       </c>
-      <c r="R394" t="inlineStr"/>
-      <c r="S394" t="inlineStr"/>
-      <c r="T394" t="inlineStr"/>
-      <c r="U394" t="inlineStr">
+      <c r="R394" s="10" t="inlineStr"/>
+      <c r="S394" s="10" t="inlineStr"/>
+      <c r="T394" s="10" t="inlineStr"/>
+      <c r="U394" s="10" t="inlineStr">
         <is>
           <t>award</t>
         </is>
       </c>
     </row>
     <row r="395">
-      <c r="A395" t="inlineStr">
+      <c r="A395" s="10" t="inlineStr">
         <is>
           <t>A53</t>
         </is>
       </c>
-      <c r="B395" t="inlineStr">
+      <c r="B395" s="10" t="inlineStr">
         <is>
           <t>ASPIRE / national academies' early-career medals</t>
         </is>
       </c>
-      <c r="C395" t="inlineStr">
+      <c r="C395" s="10" t="inlineStr">
         <is>
           <t>Various national academies</t>
         </is>
       </c>
-      <c r="D395" t="inlineStr">
+      <c r="D395" s="10" t="inlineStr">
         <is>
           <t>National academies</t>
         </is>
       </c>
-      <c r="E395" t="inlineStr">
+      <c r="E395" s="10" t="inlineStr">
         <is>
           <t>International</t>
         </is>
       </c>
-      <c r="F395" t="inlineStr">
+      <c r="F395" s="10" t="inlineStr">
         <is>
           <t>All sciences</t>
         </is>
       </c>
-      <c r="G395" t="inlineStr">
+      <c r="G395" s="10" t="inlineStr">
         <is>
           <t>Early-career</t>
         </is>
       </c>
-      <c r="H395" t="inlineStr">
+      <c r="H395" s="10" t="inlineStr">
         <is>
           <t>Most national science academies award early-career medals (e.g. the Australian Academy's Fenner and Gottschalk awards, the Royal Society of Canada's medals).</t>
         </is>
       </c>
-      <c r="I395" t="inlineStr">
+      <c r="I395" s="10" t="inlineStr">
         <is>
           <t>Medal + some cash (varies)</t>
         </is>
       </c>
-      <c r="J395" t="inlineStr">
+      <c r="J395" s="10" t="inlineStr">
         <is>
           <t>Annual</t>
         </is>
       </c>
-      <c r="K395" t="inlineStr">
+      <c r="K395" s="10" t="inlineStr">
         <is>
           <t>Early-career researchers in the relevant country; by nomination</t>
         </is>
       </c>
-      <c r="L395" t="inlineStr">
+      <c r="L395" s="10" t="inlineStr">
         <is>
           <t>Annual nomination (check each academy)</t>
         </is>
       </c>
-      <c r="M395" t="inlineStr">
+      <c r="M395" s="10" t="inlineStr">
         <is>
           <t>Nomination only</t>
         </is>
       </c>
-      <c r="N395" t="inlineStr">
+      <c r="N395" s="10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="O395" t="inlineStr">
+      <c r="O395" s="10" t="inlineStr">
         <is>
           <t>Competitive</t>
         </is>
       </c>
-      <c r="P395" t="inlineStr">
+      <c r="P395" s="10" t="inlineStr">
         <is>
           <t>https://www.science.org.au/opportunities/recognition</t>
         </is>
       </c>
-      <c r="Q395" t="inlineStr">
+      <c r="Q395" s="10" t="inlineStr">
         <is>
           <t>Check your national academy — nearly all run early- and mid-career honorific awards.</t>
         </is>
       </c>
-      <c r="R395" t="inlineStr"/>
-      <c r="S395" t="inlineStr"/>
-      <c r="T395" t="inlineStr"/>
-      <c r="U395" t="inlineStr">
+      <c r="R395" s="10" t="inlineStr"/>
+      <c r="S395" s="10" t="inlineStr"/>
+      <c r="T395" s="10" t="inlineStr"/>
+      <c r="U395" s="10" t="inlineStr">
         <is>
           <t>award</t>
         </is>
       </c>
     </row>
     <row r="396">
-      <c r="A396" t="inlineStr">
+      <c r="A396" s="10" t="inlineStr">
         <is>
           <t>A54</t>
         </is>
       </c>
-      <c r="B396" t="inlineStr">
+      <c r="B396" s="10" t="inlineStr">
         <is>
           <t>Wihuri, Sofja Kovalevskaja &amp; other 'bring-a-star' awards</t>
         </is>
       </c>
-      <c r="C396" t="inlineStr">
+      <c r="C396" s="10" t="inlineStr">
         <is>
           <t>Various (Humboldt Sofja Kovalevskaja, Wihuri Foundation, etc.)</t>
         </is>
       </c>
-      <c r="D396" t="inlineStr">
+      <c r="D396" s="10" t="inlineStr">
         <is>
           <t>Various</t>
         </is>
       </c>
-      <c r="E396" t="inlineStr">
+      <c r="E396" s="10" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="F396" t="inlineStr">
+      <c r="F396" s="10" t="inlineStr">
         <is>
           <t>All sciences</t>
         </is>
       </c>
-      <c r="G396" t="inlineStr">
+      <c r="G396" s="10" t="inlineStr">
         <is>
           <t>Early postdoc → group leader</t>
         </is>
       </c>
-      <c r="H396" t="inlineStr">
+      <c r="H396" s="10" t="inlineStr">
         <is>
           <t>Prize-style awards that fund a talented young researcher to build a group in a new country — half prize, half start-up grant.</t>
         </is>
       </c>
-      <c r="I396" t="inlineStr">
+      <c r="I396" s="10" t="inlineStr">
         <is>
           <t>Sofja Kovalevskaja up to €1.65M</t>
         </is>
       </c>
-      <c r="J396" t="inlineStr">
+      <c r="J396" s="10" t="inlineStr">
         <is>
           <t>Up to 5 years</t>
         </is>
       </c>
-      <c r="K396" t="inlineStr">
+      <c r="K396" s="10" t="inlineStr">
         <is>
           <t>Outstanding researchers (usually &lt;6 yrs post-PhD) relocating; scheme-specific</t>
         </is>
       </c>
-      <c r="L396" t="inlineStr">
+      <c r="L396" s="10" t="inlineStr">
         <is>
           <t>Annual calls (check site)</t>
         </is>
       </c>
-      <c r="M396" t="inlineStr">
+      <c r="M396" s="10" t="inlineStr">
         <is>
           <t>Application / nomination</t>
         </is>
       </c>
-      <c r="N396" t="inlineStr">
+      <c r="N396" s="10" t="inlineStr">
         <is>
           <t>Yes — for some</t>
         </is>
       </c>
-      <c r="O396" t="inlineStr">
+      <c r="O396" s="10" t="inlineStr">
         <is>
           <t>Very competitive</t>
         </is>
       </c>
-      <c r="P396" t="inlineStr">
+      <c r="P396" s="10" t="inlineStr">
         <is>
           <t>https://www.humboldt-foundation.de/en/apply/sponsorship-programmes/sofja-kovalevskaja-award</t>
         </is>
       </c>
-      <c r="Q396" t="inlineStr">
+      <c r="Q396" s="10" t="inlineStr">
         <is>
           <t>The Sofja Kovalevskaja Award is one of the most generous young-researcher prizes in the world.</t>
         </is>
       </c>
-      <c r="R396" t="inlineStr"/>
-      <c r="S396" t="inlineStr"/>
-      <c r="T396" t="inlineStr"/>
-      <c r="U396" t="inlineStr">
+      <c r="R396" s="10" t="inlineStr"/>
+      <c r="S396" s="10" t="inlineStr"/>
+      <c r="T396" s="10" t="inlineStr"/>
+      <c r="U396" s="10" t="inlineStr">
         <is>
           <t>award</t>
         </is>
       </c>
     </row>
     <row r="397">
-      <c r="A397" t="inlineStr">
+      <c r="A397" s="10" t="inlineStr">
         <is>
           <t>A55</t>
         </is>
       </c>
-      <c r="B397" t="inlineStr">
+      <c r="B397" s="10" t="inlineStr">
         <is>
           <t>National Inventors / Innovation Awards (EPO European Inventor Award)</t>
         </is>
       </c>
-      <c r="C397" t="inlineStr">
+      <c r="C397" s="10" t="inlineStr">
         <is>
           <t>European Patent Office (EPO)</t>
         </is>
       </c>
-      <c r="D397" t="inlineStr">
+      <c r="D397" s="10" t="inlineStr">
         <is>
           <t>EPO</t>
         </is>
       </c>
-      <c r="E397" t="inlineStr">
+      <c r="E397" s="10" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="F397" t="inlineStr">
+      <c r="F397" s="10" t="inlineStr">
         <is>
           <t>Invention &amp; innovation</t>
         </is>
       </c>
-      <c r="G397" t="inlineStr">
+      <c r="G397" s="10" t="inlineStr">
         <is>
           <t>Any / Established</t>
         </is>
       </c>
-      <c r="H397" t="inlineStr">
+      <c r="H397" s="10" t="inlineStr">
         <is>
           <t>The EPO's flagship award celebrating inventors whose patented work has delivered major technical and societal impact.</t>
         </is>
       </c>
-      <c r="I397" t="inlineStr">
+      <c r="I397" s="10" t="inlineStr">
         <is>
           <t>Trophy + recognition (no cash)</t>
         </is>
       </c>
-      <c r="J397" t="inlineStr">
+      <c r="J397" s="10" t="inlineStr">
         <is>
           <t>Annual</t>
         </is>
       </c>
-      <c r="K397" t="inlineStr">
+      <c r="K397" s="10" t="inlineStr">
         <is>
           <t>Inventors with granted European patents; by nomination</t>
         </is>
       </c>
-      <c r="L397" t="inlineStr">
+      <c r="L397" s="10" t="inlineStr">
         <is>
           <t>Annual nomination (check site)</t>
         </is>
       </c>
-      <c r="M397" t="inlineStr">
+      <c r="M397" s="10" t="inlineStr">
         <is>
           <t>Nomination only</t>
         </is>
       </c>
-      <c r="N397" t="inlineStr">
+      <c r="N397" s="10" t="inlineStr">
         <is>
           <t>Yes — public vote + jury</t>
         </is>
       </c>
-      <c r="O397" t="inlineStr">
+      <c r="O397" s="10" t="inlineStr">
         <is>
           <t>Competitive</t>
         </is>
       </c>
-      <c r="P397" t="inlineStr">
+      <c r="P397" s="10" t="inlineStr">
         <is>
           <t>https://www.epo.org/en/news-events/european-inventor-award</t>
         </is>
       </c>
-      <c r="Q397" t="inlineStr">
+      <c r="Q397" s="10" t="inlineStr">
         <is>
           <t>Categories include Industry, Research, SMEs and a Popular Prize public vote.</t>
         </is>
       </c>
-      <c r="R397" t="inlineStr"/>
-      <c r="S397" t="inlineStr"/>
-      <c r="T397" t="inlineStr"/>
-      <c r="U397" t="inlineStr">
+      <c r="R397" s="10" t="inlineStr"/>
+      <c r="S397" s="10" t="inlineStr"/>
+      <c r="T397" s="10" t="inlineStr"/>
+      <c r="U397" s="10" t="inlineStr">
         <is>
           <t>award</t>
         </is>
       </c>
     </row>
     <row r="398">
-      <c r="A398" t="inlineStr">
+      <c r="A398" s="10" t="inlineStr">
         <is>
           <t>A56</t>
         </is>
       </c>
-      <c r="B398" t="inlineStr">
+      <c r="B398" s="10" t="inlineStr">
         <is>
           <t>US Presidential / national startup &amp; SBIR Tibbetts Awards</t>
         </is>
       </c>
-      <c r="C398" t="inlineStr">
+      <c r="C398" s="10" t="inlineStr">
         <is>
           <t>US Small Business Administration (SBA)</t>
         </is>
       </c>
-      <c r="D398" t="inlineStr">
+      <c r="D398" s="10" t="inlineStr">
         <is>
           <t>SBA</t>
         </is>
       </c>
-      <c r="E398" t="inlineStr">
+      <c r="E398" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="F398" t="inlineStr">
+      <c r="F398" s="10" t="inlineStr">
         <is>
           <t>Deep tech &amp; small business innovation</t>
         </is>
       </c>
-      <c r="G398" t="inlineStr">
+      <c r="G398" s="10" t="inlineStr">
         <is>
           <t>Startups &amp; small businesses</t>
         </is>
       </c>
-      <c r="H398" t="inlineStr">
+      <c r="H398" s="10" t="inlineStr">
         <is>
           <t>The Tibbetts Award recognises SBIR/STTR-funded small businesses that exemplify excellence in high-tech innovation.</t>
         </is>
       </c>
-      <c r="I398" t="inlineStr">
+      <c r="I398" s="10" t="inlineStr">
         <is>
           <t>Recognition (no direct cash)</t>
         </is>
       </c>
-      <c r="J398" t="inlineStr">
+      <c r="J398" s="10" t="inlineStr">
         <is>
           <t>Annual</t>
         </is>
       </c>
-      <c r="K398" t="inlineStr">
+      <c r="K398" s="10" t="inlineStr">
         <is>
           <t>US small businesses with a strong SBIR/STTR record; by nomination</t>
         </is>
       </c>
-      <c r="L398" t="inlineStr">
+      <c r="L398" s="10" t="inlineStr">
         <is>
           <t>Annual nomination (check site)</t>
         </is>
       </c>
-      <c r="M398" t="inlineStr">
+      <c r="M398" s="10" t="inlineStr">
         <is>
           <t>Nomination</t>
         </is>
       </c>
-      <c r="N398" t="inlineStr">
+      <c r="N398" s="10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="O398" t="inlineStr">
+      <c r="O398" s="10" t="inlineStr">
         <is>
           <t>Selective</t>
         </is>
       </c>
-      <c r="P398" t="inlineStr">
+      <c r="P398" s="10" t="inlineStr">
         <is>
           <t>https://www.sbir.gov/tibbetts-hall-of-fame</t>
         </is>
       </c>
-      <c r="Q398" t="inlineStr">
+      <c r="Q398" s="10" t="inlineStr">
         <is>
           <t>National recognition that strengthens future funding and investor credibility.</t>
         </is>
       </c>
-      <c r="R398" t="inlineStr"/>
-      <c r="S398" t="inlineStr"/>
-      <c r="T398" t="inlineStr"/>
-      <c r="U398" t="inlineStr">
+      <c r="R398" s="10" t="inlineStr"/>
+      <c r="S398" s="10" t="inlineStr"/>
+      <c r="T398" s="10" t="inlineStr"/>
+      <c r="U398" s="10" t="inlineStr">
         <is>
           <t>award</t>
         </is>
       </c>
     </row>
     <row r="399">
-      <c r="A399" t="inlineStr">
+      <c r="A399" s="10" t="inlineStr">
         <is>
           <t>A57</t>
         </is>
       </c>
-      <c r="B399" t="inlineStr">
+      <c r="B399" s="10" t="inlineStr">
         <is>
           <t>Canada — Manning Innovation Awards</t>
         </is>
       </c>
-      <c r="C399" t="inlineStr">
+      <c r="C399" s="10" t="inlineStr">
         <is>
           <t>Ernest C. Manning Awards Foundation</t>
         </is>
       </c>
-      <c r="D399" t="inlineStr">
+      <c r="D399" s="10" t="inlineStr">
         <is>
           <t>Manning</t>
         </is>
       </c>
-      <c r="E399" t="inlineStr">
+      <c r="E399" s="10" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="F399" t="inlineStr">
+      <c r="F399" s="10" t="inlineStr">
         <is>
           <t>Innovation &amp; entrepreneurship</t>
         </is>
       </c>
-      <c r="G399" t="inlineStr">
+      <c r="G399" s="10" t="inlineStr">
         <is>
           <t>Innovators &amp; founders</t>
         </is>
       </c>
-      <c r="H399" t="inlineStr">
+      <c r="H399" s="10" t="inlineStr">
         <is>
           <t>Canada's principal awards celebrating Canadian innovators who have commercialised new products and technologies.</t>
         </is>
       </c>
-      <c r="I399" t="inlineStr">
+      <c r="I399" s="10" t="inlineStr">
         <is>
           <t>Up to CAD 100,000 (Principal Award)</t>
         </is>
       </c>
-      <c r="J399" t="inlineStr">
+      <c r="J399" s="10" t="inlineStr">
         <is>
           <t>Annual</t>
         </is>
       </c>
-      <c r="K399" t="inlineStr">
+      <c r="K399" s="10" t="inlineStr">
         <is>
           <t>Canadian innovators with a marketed innovation; by nomination</t>
         </is>
       </c>
-      <c r="L399" t="inlineStr">
+      <c r="L399" s="10" t="inlineStr">
         <is>
           <t>Annual nomination (check site)</t>
         </is>
       </c>
-      <c r="M399" t="inlineStr">
+      <c r="M399" s="10" t="inlineStr">
         <is>
           <t>Nomination</t>
         </is>
       </c>
-      <c r="N399" t="inlineStr">
+      <c r="N399" s="10" t="inlineStr">
         <is>
           <t>Yes — judging</t>
         </is>
       </c>
-      <c r="O399" t="inlineStr">
+      <c r="O399" s="10" t="inlineStr">
         <is>
           <t>Competitive</t>
         </is>
       </c>
-      <c r="P399" t="inlineStr">
+      <c r="P399" s="10" t="inlineStr">
         <is>
           <t>https://www.manninginnovation.ca/</t>
         </is>
       </c>
-      <c r="Q399" t="inlineStr">
+      <c r="Q399" s="10" t="inlineStr">
         <is>
           <t>Recognises commercialised innovation specifically, not just invention.</t>
         </is>
       </c>
-      <c r="R399" t="inlineStr"/>
-      <c r="S399" t="inlineStr"/>
-      <c r="T399" t="inlineStr"/>
-      <c r="U399" t="inlineStr">
+      <c r="R399" s="10" t="inlineStr"/>
+      <c r="S399" s="10" t="inlineStr"/>
+      <c r="T399" s="10" t="inlineStr"/>
+      <c r="U399" s="10" t="inlineStr">
         <is>
           <t>award</t>
         </is>
       </c>
     </row>
     <row r="400">
-      <c r="A400" t="inlineStr">
+      <c r="A400" s="10" t="inlineStr">
         <is>
           <t>A58</t>
         </is>
       </c>
-      <c r="B400" t="inlineStr">
+      <c r="B400" s="10" t="inlineStr">
         <is>
           <t>EU Social Innovation Competition</t>
         </is>
       </c>
-      <c r="C400" t="inlineStr">
+      <c r="C400" s="10" t="inlineStr">
         <is>
           <t>European Commission / European Innovation Council</t>
         </is>
       </c>
-      <c r="D400" t="inlineStr">
+      <c r="D400" s="10" t="inlineStr">
         <is>
           <t>EIC</t>
         </is>
       </c>
-      <c r="E400" t="inlineStr">
+      <c r="E400" s="10" t="inlineStr">
         <is>
           <t>EU + Associated Countries</t>
         </is>
       </c>
-      <c r="F400" t="inlineStr">
+      <c r="F400" s="10" t="inlineStr">
         <is>
           <t>Social innovation &amp; impact ventures</t>
         </is>
       </c>
-      <c r="G400" t="inlineStr">
+      <c r="G400" s="10" t="inlineStr">
         <is>
           <t>Founders &amp; teams</t>
         </is>
       </c>
-      <c r="H400" t="inlineStr">
+      <c r="H400" s="10" t="inlineStr">
         <is>
           <t>An annual challenge-based competition rewarding the best early-stage social innovations addressing a defined yearly theme.</t>
         </is>
       </c>
-      <c r="I400" t="inlineStr">
+      <c r="I400" s="10" t="inlineStr">
         <is>
           <t>€50,000 per winner (3 winners)</t>
         </is>
       </c>
-      <c r="J400" t="inlineStr">
+      <c r="J400" s="10" t="inlineStr">
         <is>
           <t>Annual</t>
         </is>
       </c>
-      <c r="K400" t="inlineStr">
+      <c r="K400" s="10" t="inlineStr">
         <is>
           <t>Individuals and organisations in EU/associated countries; by application</t>
         </is>
       </c>
-      <c r="L400" t="inlineStr">
+      <c r="L400" s="10" t="inlineStr">
         <is>
           <t>Annual call (typically ~spring; check site)</t>
         </is>
       </c>
-      <c r="M400" t="inlineStr">
+      <c r="M400" s="10" t="inlineStr">
         <is>
           <t>Online application</t>
         </is>
       </c>
-      <c r="N400" t="inlineStr">
+      <c r="N400" s="10" t="inlineStr">
         <is>
           <t>Yes — academy + final</t>
         </is>
       </c>
-      <c r="O400" t="inlineStr">
+      <c r="O400" s="10" t="inlineStr">
         <is>
           <t>Competitive</t>
         </is>
       </c>
-      <c r="P400" t="inlineStr">
+      <c r="P400" s="10" t="inlineStr">
         <is>
           <t>https://eusic.challenges.org/</t>
         </is>
       </c>
-      <c r="Q400" t="inlineStr">
+      <c r="Q400" s="10" t="inlineStr">
         <is>
           <t>Theme changes each year; strong route for impact-driven founders.</t>
         </is>
       </c>
-      <c r="R400" t="inlineStr"/>
-      <c r="S400" t="inlineStr"/>
-      <c r="T400" t="inlineStr"/>
-      <c r="U400" t="inlineStr">
+      <c r="R400" s="10" t="inlineStr"/>
+      <c r="S400" s="10" t="inlineStr"/>
+      <c r="T400" s="10" t="inlineStr"/>
+      <c r="U400" s="10" t="inlineStr">
         <is>
           <t>award</t>
         </is>
       </c>
     </row>
     <row r="401">
-      <c r="A401" t="inlineStr">
+      <c r="A401" s="10" t="inlineStr">
         <is>
           <t>A59</t>
         </is>
       </c>
-      <c r="B401" t="inlineStr">
+      <c r="B401" s="10" t="inlineStr">
         <is>
           <t>James Dyson Award — national stages</t>
         </is>
       </c>
-      <c r="C401" t="inlineStr">
+      <c r="C401" s="10" t="inlineStr">
         <is>
           <t>James Dyson Foundation</t>
         </is>
       </c>
-      <c r="D401" t="inlineStr">
+      <c r="D401" s="10" t="inlineStr">
         <is>
           <t>Dyson</t>
         </is>
       </c>
-      <c r="E401" t="inlineStr">
+      <c r="E401" s="10" t="inlineStr">
         <is>
           <t>International (national + international)</t>
         </is>
       </c>
-      <c r="F401" t="inlineStr">
+      <c r="F401" s="10" t="inlineStr">
         <is>
           <t>Design engineering &amp; invention</t>
         </is>
       </c>
-      <c r="G401" t="inlineStr">
+      <c r="G401" s="10" t="inlineStr">
         <is>
           <t>Students &amp; recent graduates</t>
         </is>
       </c>
-      <c r="H401" t="inlineStr">
+      <c r="H401" s="10" t="inlineStr">
         <is>
           <t>National rounds of the Dyson Award across ~30 countries, feeding the international final — a realistic entry point for student inventors.</t>
         </is>
       </c>
-      <c r="I401" t="inlineStr">
+      <c r="I401" s="10" t="inlineStr">
         <is>
           <t>National winners £5,000; international £30,000</t>
         </is>
       </c>
-      <c r="J401" t="inlineStr">
+      <c r="J401" s="10" t="inlineStr">
         <is>
           <t>Annual</t>
         </is>
       </c>
-      <c r="K401" t="inlineStr">
+      <c r="K401" s="10" t="inlineStr">
         <is>
           <t>Students/recent graduates in participating countries</t>
         </is>
       </c>
-      <c r="L401" t="inlineStr">
+      <c r="L401" s="10" t="inlineStr">
         <is>
           <t>Annual (~spring-summer; check site)</t>
         </is>
       </c>
-      <c r="M401" t="inlineStr">
+      <c r="M401" s="10" t="inlineStr">
         <is>
           <t>Online application</t>
         </is>
       </c>
-      <c r="N401" t="inlineStr">
+      <c r="N401" s="10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="O401" t="inlineStr">
+      <c r="O401" s="10" t="inlineStr">
         <is>
           <t>Competitive</t>
         </is>
       </c>
-      <c r="P401" t="inlineStr">
+      <c r="P401" s="10" t="inlineStr">
         <is>
           <t>https://www.jamesdysonaward.org/</t>
         </is>
       </c>
-      <c r="Q401" t="inlineStr">
+      <c r="Q401" s="10" t="inlineStr">
         <is>
           <t>Winning even the national stage is a strong signal for early hardware founders.</t>
         </is>
       </c>
-      <c r="R401" t="inlineStr"/>
-      <c r="S401" t="inlineStr"/>
-      <c r="T401" t="inlineStr"/>
-      <c r="U401" t="inlineStr">
+      <c r="R401" s="10" t="inlineStr"/>
+      <c r="S401" s="10" t="inlineStr"/>
+      <c r="T401" s="10" t="inlineStr"/>
+      <c r="U401" s="10" t="inlineStr">
         <is>
           <t>award</t>
         </is>
       </c>
     </row>
     <row r="402">
-      <c r="A402" t="inlineStr">
+      <c r="A402" s="10" t="inlineStr">
         <is>
           <t>A60</t>
         </is>
       </c>
-      <c r="B402" t="inlineStr">
+      <c r="B402" s="10" t="inlineStr">
         <is>
           <t>Regional deep-tech prizes (Hello Tomorrow Global Challenge)</t>
         </is>
       </c>
-      <c r="C402" t="inlineStr">
+      <c r="C402" s="10" t="inlineStr">
         <is>
           <t>Hello Tomorrow</t>
         </is>
       </c>
-      <c r="D402" t="inlineStr">
+      <c r="D402" s="10" t="inlineStr">
         <is>
           <t>Hello Tomorrow</t>
         </is>
       </c>
-      <c r="E402" t="inlineStr">
+      <c r="E402" s="10" t="inlineStr">
         <is>
           <t>International</t>
         </is>
       </c>
-      <c r="F402" t="inlineStr">
+      <c r="F402" s="10" t="inlineStr">
         <is>
           <t>Deep tech across sectors</t>
         </is>
       </c>
-      <c r="G402" t="inlineStr">
+      <c r="G402" s="10" t="inlineStr">
         <is>
           <t>Early-stage deep-tech startups</t>
         </is>
       </c>
-      <c r="H402" t="inlineStr">
+      <c r="H402" s="10" t="inlineStr">
         <is>
           <t>A global deep-tech competition connecting early science-based startups with investors and industry, with sizeable cash prizes.</t>
         </is>
       </c>
-      <c r="I402" t="inlineStr">
+      <c r="I402" s="10" t="inlineStr">
         <is>
           <t>€100,000 grand prize + track prizes</t>
         </is>
       </c>
-      <c r="J402" t="inlineStr">
+      <c r="J402" s="10" t="inlineStr">
         <is>
           <t>Annual</t>
         </is>
       </c>
-      <c r="K402" t="inlineStr">
+      <c r="K402" s="10" t="inlineStr">
         <is>
           <t>Early-stage deep-tech startups worldwide; by application</t>
         </is>
       </c>
-      <c r="L402" t="inlineStr">
+      <c r="L402" s="10" t="inlineStr">
         <is>
           <t>Annual call (check site)</t>
         </is>
       </c>
-      <c r="M402" t="inlineStr">
+      <c r="M402" s="10" t="inlineStr">
         <is>
           <t>Online application</t>
         </is>
       </c>
-      <c r="N402" t="inlineStr">
+      <c r="N402" s="10" t="inlineStr">
         <is>
           <t>Yes — pitch finals</t>
         </is>
       </c>
-      <c r="O402" t="inlineStr">
+      <c r="O402" s="10" t="inlineStr">
         <is>
           <t>Competitive</t>
         </is>
       </c>
-      <c r="P402" t="inlineStr">
+      <c r="P402" s="10" t="inlineStr">
         <is>
           <t>https://hello-tomorrow.org/</t>
         </is>
       </c>
-      <c r="Q402" t="inlineStr">
+      <c r="Q402" s="10" t="inlineStr">
         <is>
           <t>Specifically built for science-based ventures — a strong fit for research spin-offs.</t>
         </is>
       </c>
-      <c r="R402" t="inlineStr"/>
-      <c r="S402" t="inlineStr"/>
-      <c r="T402" t="inlineStr"/>
-      <c r="U402" t="inlineStr">
+      <c r="R402" s="10" t="inlineStr"/>
+      <c r="S402" s="10" t="inlineStr"/>
+      <c r="T402" s="10" t="inlineStr"/>
+      <c r="U402" s="10" t="inlineStr">
+        <is>
+          <t>award</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="10" t="inlineStr">
+        <is>
+          <t>G339</t>
+        </is>
+      </c>
+      <c r="B403" s="10" t="inlineStr">
+        <is>
+          <t>Human Frontier Science Program (HFSP) Research Grants</t>
+        </is>
+      </c>
+      <c r="C403" s="10" t="inlineStr">
+        <is>
+          <t>HFSP Organization</t>
+        </is>
+      </c>
+      <c r="D403" s="10" t="inlineStr">
+        <is>
+          <t>HFSP</t>
+        </is>
+      </c>
+      <c r="E403" s="10" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F403" s="10" t="inlineStr">
+        <is>
+          <t>Life sciences (interdisciplinary)</t>
+        </is>
+      </c>
+      <c r="G403" s="10" t="inlineStr">
+        <is>
+          <t>Any / Established</t>
+        </is>
+      </c>
+      <c r="H403" s="10" t="inlineStr">
+        <is>
+          <t>Funds bold international teams tackling fundamental problems in the life sciences, with a strong emphasis on cross-border, interdisciplinary collaboration.</t>
+        </is>
+      </c>
+      <c r="I403" s="10" t="inlineStr">
+        <is>
+          <t>$400,000-450,000/yr per team</t>
+        </is>
+      </c>
+      <c r="J403" s="10" t="inlineStr">
+        <is>
+          <t>3 years</t>
+        </is>
+      </c>
+      <c r="K403" s="10" t="inlineStr">
+        <is>
+          <t>Teams of 2-4 PIs from different countries; intercontinental collaboration favoured</t>
+        </is>
+      </c>
+      <c r="L403" s="10" t="inlineStr">
+        <is>
+          <t>Annual: letter of intent ~Mar (check site)</t>
+        </is>
+      </c>
+      <c r="M403" s="10" t="inlineStr">
+        <is>
+          <t>HFSP proposal system</t>
+        </is>
+      </c>
+      <c r="N403" s="10" t="inlineStr">
+        <is>
+          <t>No — international review</t>
+        </is>
+      </c>
+      <c r="O403" s="10" t="inlineStr">
+        <is>
+          <t>~3-4%</t>
+        </is>
+      </c>
+      <c r="P403" s="10" t="inlineStr">
+        <is>
+          <t>https://www.hfsp.org/</t>
+        </is>
+      </c>
+      <c r="Q403" s="10" t="inlineStr">
+        <is>
+          <t>One of the few funders requiring genuinely international teams; open to all nationalities.</t>
+        </is>
+      </c>
+      <c r="R403" s="10" t="inlineStr"/>
+      <c r="S403" s="10" t="inlineStr"/>
+      <c r="T403" s="10" t="inlineStr"/>
+      <c r="U403" s="10" t="inlineStr">
+        <is>
+          <t>grant</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="10" t="inlineStr">
+        <is>
+          <t>G340</t>
+        </is>
+      </c>
+      <c r="B404" s="10" t="inlineStr">
+        <is>
+          <t>Chan Zuckerberg Initiative Science Grants</t>
+        </is>
+      </c>
+      <c r="C404" s="10" t="inlineStr">
+        <is>
+          <t>Chan Zuckerberg Initiative (CZI)</t>
+        </is>
+      </c>
+      <c r="D404" s="10" t="inlineStr">
+        <is>
+          <t>Private (CZI)</t>
+        </is>
+      </c>
+      <c r="E404" s="10" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F404" s="10" t="inlineStr">
+        <is>
+          <t>Biomedical &amp; life sciences</t>
+        </is>
+      </c>
+      <c r="G404" s="10" t="inlineStr">
+        <is>
+          <t>Any / Established</t>
+        </is>
+      </c>
+      <c r="H404" s="10" t="inlineStr">
+        <is>
+          <t>Funds tools, technologies and collaborative science toward curing, preventing or managing disease, including open-science infrastructure.</t>
+        </is>
+      </c>
+      <c r="I404" s="10" t="inlineStr">
+        <is>
+          <t>Varies widely ($100k-several million)</t>
+        </is>
+      </c>
+      <c r="J404" s="10" t="inlineStr">
+        <is>
+          <t>1-5 years</t>
+        </is>
+      </c>
+      <c r="K404" s="10" t="inlineStr">
+        <is>
+          <t>Researchers worldwide; programme-specific eligibility</t>
+        </is>
+      </c>
+      <c r="L404" s="10" t="inlineStr">
+        <is>
+          <t>Rolling RFAs (check site)</t>
+        </is>
+      </c>
+      <c r="M404" s="10" t="inlineStr">
+        <is>
+          <t>CZI application portal</t>
+        </is>
+      </c>
+      <c r="N404" s="10" t="inlineStr">
+        <is>
+          <t>No — review varies</t>
+        </is>
+      </c>
+      <c r="O404" s="10" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="P404" s="10" t="inlineStr">
+        <is>
+          <t>https://chanzuckerberg.com/science/</t>
+        </is>
+      </c>
+      <c r="Q404" s="10" t="inlineStr">
+        <is>
+          <t>Strong on imaging, single-cell biology and open-source science software.</t>
+        </is>
+      </c>
+      <c r="R404" s="10" t="inlineStr"/>
+      <c r="S404" s="10" t="inlineStr"/>
+      <c r="T404" s="10" t="inlineStr"/>
+      <c r="U404" s="10" t="inlineStr">
+        <is>
+          <t>grant</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="10" t="inlineStr">
+        <is>
+          <t>G341</t>
+        </is>
+      </c>
+      <c r="B405" s="10" t="inlineStr">
+        <is>
+          <t>Allen Distinguished Investigator Awards</t>
+        </is>
+      </c>
+      <c r="C405" s="10" t="inlineStr">
+        <is>
+          <t>Paul G. Allen Frontiers Group</t>
+        </is>
+      </c>
+      <c r="D405" s="10" t="inlineStr">
+        <is>
+          <t>Private (Allen)</t>
+        </is>
+      </c>
+      <c r="E405" s="10" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F405" s="10" t="inlineStr">
+        <is>
+          <t>Bioscience (frontier questions)</t>
+        </is>
+      </c>
+      <c r="G405" s="10" t="inlineStr">
+        <is>
+          <t>Any / Established</t>
+        </is>
+      </c>
+      <c r="H405" s="10" t="inlineStr">
+        <is>
+          <t>Backs early-stage, unconventional bioscience projects considered too risky for traditional funders.</t>
+        </is>
+      </c>
+      <c r="I405" s="10" t="inlineStr">
+        <is>
+          <t>~$1,500,000 over 3 years</t>
+        </is>
+      </c>
+      <c r="J405" s="10" t="inlineStr">
+        <is>
+          <t>3 years</t>
+        </is>
+      </c>
+      <c r="K405" s="10" t="inlineStr">
+        <is>
+          <t>Researchers worldwide; by nomination/invitation and open calls</t>
+        </is>
+      </c>
+      <c r="L405" s="10" t="inlineStr">
+        <is>
+          <t>Periodic calls (check site)</t>
+        </is>
+      </c>
+      <c r="M405" s="10" t="inlineStr">
+        <is>
+          <t>Allen Frontiers portal</t>
+        </is>
+      </c>
+      <c r="N405" s="10" t="inlineStr">
+        <is>
+          <t>No — review</t>
+        </is>
+      </c>
+      <c r="O405" s="10" t="inlineStr">
+        <is>
+          <t>Very competitive</t>
+        </is>
+      </c>
+      <c r="P405" s="10" t="inlineStr">
+        <is>
+          <t>https://alleninstitute.org/division/frontiers-group/</t>
+        </is>
+      </c>
+      <c r="Q405" s="10" t="inlineStr">
+        <is>
+          <t>Explicitly funds pioneering, high-risk ideas.</t>
+        </is>
+      </c>
+      <c r="R405" s="10" t="inlineStr"/>
+      <c r="S405" s="10" t="inlineStr"/>
+      <c r="T405" s="10" t="inlineStr"/>
+      <c r="U405" s="10" t="inlineStr">
+        <is>
+          <t>grant</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="10" t="inlineStr">
+        <is>
+          <t>G342</t>
+        </is>
+      </c>
+      <c r="B406" s="10" t="inlineStr">
+        <is>
+          <t>Templeton World Charity Foundation Grants</t>
+        </is>
+      </c>
+      <c r="C406" s="10" t="inlineStr">
+        <is>
+          <t>Templeton World Charity Foundation</t>
+        </is>
+      </c>
+      <c r="D406" s="10" t="inlineStr">
+        <is>
+          <t>Private (TWCF)</t>
+        </is>
+      </c>
+      <c r="E406" s="10" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F406" s="10" t="inlineStr">
+        <is>
+          <t>Interdisciplinary (consciousness, human flourishing)</t>
+        </is>
+      </c>
+      <c r="G406" s="10" t="inlineStr">
+        <is>
+          <t>Any / Established</t>
+        </is>
+      </c>
+      <c r="H406" s="10" t="inlineStr">
+        <is>
+          <t>Funds research on big questions in human flourishing, consciousness and the boundaries of science.</t>
+        </is>
+      </c>
+      <c r="I406" s="10" t="inlineStr">
+        <is>
+          <t>$50,000-$2,000,000</t>
+        </is>
+      </c>
+      <c r="J406" s="10" t="inlineStr">
+        <is>
+          <t>1-3 years</t>
+        </is>
+      </c>
+      <c r="K406" s="10" t="inlineStr">
+        <is>
+          <t>Researchers worldwide; theme-specific calls</t>
+        </is>
+      </c>
+      <c r="L406" s="10" t="inlineStr">
+        <is>
+          <t>Rolling / periodic (check site)</t>
+        </is>
+      </c>
+      <c r="M406" s="10" t="inlineStr">
+        <is>
+          <t>TWCF portal (LOI first)</t>
+        </is>
+      </c>
+      <c r="N406" s="10" t="inlineStr">
+        <is>
+          <t>No — staged review</t>
+        </is>
+      </c>
+      <c r="O406" s="10" t="inlineStr">
+        <is>
+          <t>Selective</t>
+        </is>
+      </c>
+      <c r="P406" s="10" t="inlineStr">
+        <is>
+          <t>https://www.templetonworldcharity.org/</t>
+        </is>
+      </c>
+      <c r="Q406" s="10" t="inlineStr">
+        <is>
+          <t>Distinct from the John Templeton Foundation, with its own priorities.</t>
+        </is>
+      </c>
+      <c r="R406" s="10" t="inlineStr"/>
+      <c r="S406" s="10" t="inlineStr"/>
+      <c r="T406" s="10" t="inlineStr"/>
+      <c r="U406" s="10" t="inlineStr">
+        <is>
+          <t>grant</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="10" t="inlineStr">
+        <is>
+          <t>G343</t>
+        </is>
+      </c>
+      <c r="B407" s="10" t="inlineStr">
+        <is>
+          <t>Moore Foundation Investigator &amp; Science Grants</t>
+        </is>
+      </c>
+      <c r="C407" s="10" t="inlineStr">
+        <is>
+          <t>Gordon and Betty Moore Foundation</t>
+        </is>
+      </c>
+      <c r="D407" s="10" t="inlineStr">
+        <is>
+          <t>Private (Moore)</t>
+        </is>
+      </c>
+      <c r="E407" s="10" t="inlineStr">
+        <is>
+          <t>USA / International</t>
+        </is>
+      </c>
+      <c r="F407" s="10" t="inlineStr">
+        <is>
+          <t>Physics, biology, environmental science</t>
+        </is>
+      </c>
+      <c r="G407" s="10" t="inlineStr">
+        <is>
+          <t>Any / Established</t>
+        </is>
+      </c>
+      <c r="H407" s="10" t="inlineStr">
+        <is>
+          <t>Funds ambitious, discovery-driven science, from marine microbiology to fundamental physics and scientific instrumentation.</t>
+        </is>
+      </c>
+      <c r="I407" s="10" t="inlineStr">
+        <is>
+          <t>Varies ($250k-several million)</t>
+        </is>
+      </c>
+      <c r="J407" s="10" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="K407" s="10" t="inlineStr">
+        <is>
+          <t>Often by invitation; some open calls; international eligibility for several</t>
+        </is>
+      </c>
+      <c r="L407" s="10" t="inlineStr">
+        <is>
+          <t>Periodic (check site)</t>
+        </is>
+      </c>
+      <c r="M407" s="10" t="inlineStr">
+        <is>
+          <t>Moore Foundation portal</t>
+        </is>
+      </c>
+      <c r="N407" s="10" t="inlineStr">
+        <is>
+          <t>No — review</t>
+        </is>
+      </c>
+      <c r="O407" s="10" t="inlineStr">
+        <is>
+          <t>Selective</t>
+        </is>
+      </c>
+      <c r="P407" s="10" t="inlineStr">
+        <is>
+          <t>https://www.moore.org/</t>
+        </is>
+      </c>
+      <c r="Q407" s="10" t="inlineStr">
+        <is>
+          <t>Known for patient, long-horizon funding of basic science.</t>
+        </is>
+      </c>
+      <c r="R407" s="10" t="inlineStr"/>
+      <c r="S407" s="10" t="inlineStr"/>
+      <c r="T407" s="10" t="inlineStr"/>
+      <c r="U407" s="10" t="inlineStr">
+        <is>
+          <t>grant</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="10" t="inlineStr">
+        <is>
+          <t>G344</t>
+        </is>
+      </c>
+      <c r="B408" s="10" t="inlineStr">
+        <is>
+          <t>ARIA (Advanced Research and Invention Agency) Programmes</t>
+        </is>
+      </c>
+      <c r="C408" s="10" t="inlineStr">
+        <is>
+          <t>Advanced Research and Invention Agency</t>
+        </is>
+      </c>
+      <c r="D408" s="10" t="inlineStr">
+        <is>
+          <t>United Kingdom (ARIA)</t>
+        </is>
+      </c>
+      <c r="E408" s="10" t="inlineStr">
+        <is>
+          <t>United Kingdom / International</t>
+        </is>
+      </c>
+      <c r="F408" s="10" t="inlineStr">
+        <is>
+          <t>High-risk, high-reward science &amp; technology</t>
+        </is>
+      </c>
+      <c r="G408" s="10" t="inlineStr">
+        <is>
+          <t>Any / teams</t>
+        </is>
+      </c>
+      <c r="H408" s="10" t="inlineStr">
+        <is>
+          <t>The UK's ARPA-style agency funding edge-of-the-possible research programmes with high risk tolerance and light bureaucracy.</t>
+        </is>
+      </c>
+      <c r="I408" s="10" t="inlineStr">
+        <is>
+          <t>Programme-dependent (often £0.5-5M)</t>
+        </is>
+      </c>
+      <c r="J408" s="10" t="inlineStr">
+        <is>
+          <t>Programme-dependent</t>
+        </is>
+      </c>
+      <c r="K408" s="10" t="inlineStr">
+        <is>
+          <t>Individuals, universities and companies; some programmes accept international teams</t>
+        </is>
+      </c>
+      <c r="L408" s="10" t="inlineStr">
+        <is>
+          <t>Per programme solicitation (check site)</t>
+        </is>
+      </c>
+      <c r="M408" s="10" t="inlineStr">
+        <is>
+          <t>ARIA programme applications</t>
+        </is>
+      </c>
+      <c r="N408" s="10" t="inlineStr">
+        <is>
+          <t>No — programme director led</t>
+        </is>
+      </c>
+      <c r="O408" s="10" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="P408" s="10" t="inlineStr">
+        <is>
+          <t>https://www.aria.org.uk/</t>
+        </is>
+      </c>
+      <c r="Q408" s="10" t="inlineStr">
+        <is>
+          <t>Programmes are shaped by individual programme directors; watch for opportunity announcements.</t>
+        </is>
+      </c>
+      <c r="R408" s="10" t="inlineStr"/>
+      <c r="S408" s="10" t="inlineStr"/>
+      <c r="T408" s="10" t="inlineStr"/>
+      <c r="U408" s="10" t="inlineStr">
+        <is>
+          <t>grant</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="10" t="inlineStr">
+        <is>
+          <t>G345</t>
+        </is>
+      </c>
+      <c r="B409" s="10" t="inlineStr">
+        <is>
+          <t>Wellcome Career Development Awards</t>
+        </is>
+      </c>
+      <c r="C409" s="10" t="inlineStr">
+        <is>
+          <t>Wellcome Trust</t>
+        </is>
+      </c>
+      <c r="D409" s="10" t="inlineStr">
+        <is>
+          <t>Private (Wellcome)</t>
+        </is>
+      </c>
+      <c r="E409" s="10" t="inlineStr">
+        <is>
+          <t>UK, Ireland &amp; LMICs</t>
+        </is>
+      </c>
+      <c r="F409" s="10" t="inlineStr">
+        <is>
+          <t>Health-related research (broadly)</t>
+        </is>
+      </c>
+      <c r="G409" s="10" t="inlineStr">
+        <is>
+          <t>Senior Postdoc → independent</t>
+        </is>
+      </c>
+      <c r="H409" s="10" t="inlineStr">
+        <is>
+          <t>Funds researchers to develop into independent leaders, working on human-health-relevant questions across disciplines.</t>
+        </is>
+      </c>
+      <c r="I409" s="10" t="inlineStr">
+        <is>
+          <t>Salary + up to ~£1M+ research costs</t>
+        </is>
+      </c>
+      <c r="J409" s="10" t="inlineStr">
+        <is>
+          <t>8 years</t>
+        </is>
+      </c>
+      <c r="K409" s="10" t="inlineStr">
+        <is>
+          <t>Ready-for-independence researchers; eligible host organisation</t>
+        </is>
+      </c>
+      <c r="L409" s="10" t="inlineStr">
+        <is>
+          <t>Annual rounds (check site)</t>
+        </is>
+      </c>
+      <c r="M409" s="10" t="inlineStr">
+        <is>
+          <t>Wellcome Funding portal</t>
+        </is>
+      </c>
+      <c r="N409" s="10" t="inlineStr">
+        <is>
+          <t>Yes — interview</t>
+        </is>
+      </c>
+      <c r="O409" s="10" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="P409" s="10" t="inlineStr">
+        <is>
+          <t>https://wellcome.org/grant-funding/schemes/career-development-awards</t>
+        </is>
+      </c>
+      <c r="Q409" s="10" t="inlineStr">
+        <is>
+          <t>From October 2026 Wellcome tightened eligibility — check the current criteria.</t>
+        </is>
+      </c>
+      <c r="R409" s="10" t="inlineStr"/>
+      <c r="S409" s="10" t="inlineStr"/>
+      <c r="T409" s="10" t="inlineStr"/>
+      <c r="U409" s="10" t="inlineStr">
+        <is>
+          <t>grant</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="10" t="inlineStr">
+        <is>
+          <t>G346</t>
+        </is>
+      </c>
+      <c r="B410" s="10" t="inlineStr">
+        <is>
+          <t>Human Capital / Marie Skłodowska-Curie COFUND</t>
+        </is>
+      </c>
+      <c r="C410" s="10" t="inlineStr">
+        <is>
+          <t>European Commission (MSCA)</t>
+        </is>
+      </c>
+      <c r="D410" s="10" t="inlineStr">
+        <is>
+          <t>Horizon Europe</t>
+        </is>
+      </c>
+      <c r="E410" s="10" t="inlineStr">
+        <is>
+          <t>EU + Associated Countries</t>
+        </is>
+      </c>
+      <c r="F410" s="10" t="inlineStr">
+        <is>
+          <t>All disciplines</t>
+        </is>
+      </c>
+      <c r="G410" s="10" t="inlineStr">
+        <is>
+          <t>PhD candidates &amp; postdocs</t>
+        </is>
+      </c>
+      <c r="H410" s="10" t="inlineStr">
+        <is>
+          <t>Co-funds regional, national and international doctoral and postdoctoral programmes, creating many locally-run fellowships under one umbrella.</t>
+        </is>
+      </c>
+      <c r="I410" s="10" t="inlineStr">
+        <is>
+          <t>Salary-level fellowships (co-funded)</t>
+        </is>
+      </c>
+      <c r="J410" s="10" t="inlineStr">
+        <is>
+          <t>PhD 3-4 yrs; postdoc 1-3 yrs</t>
+        </is>
+      </c>
+      <c r="K410" s="10" t="inlineStr">
+        <is>
+          <t>Via the individual COFUND-supported programme; check each programme's rules</t>
+        </is>
+      </c>
+      <c r="L410" s="10" t="inlineStr">
+        <is>
+          <t>Programme-specific (many annual; check site)</t>
+        </is>
+      </c>
+      <c r="M410" s="10" t="inlineStr">
+        <is>
+          <t>Via the host COFUND programme</t>
+        </is>
+      </c>
+      <c r="N410" s="10" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="O410" s="10" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="P410" s="10" t="inlineStr">
+        <is>
+          <t>https://marie-sklodowska-curie-actions.ec.europa.eu/</t>
+        </is>
+      </c>
+      <c r="Q410" s="10" t="inlineStr">
+        <is>
+          <t>COFUND creates hundreds of fellowships — search for programmes in your field and country.</t>
+        </is>
+      </c>
+      <c r="R410" s="10" t="inlineStr"/>
+      <c r="S410" s="10" t="inlineStr"/>
+      <c r="T410" s="10" t="inlineStr"/>
+      <c r="U410" s="10" t="inlineStr">
+        <is>
+          <t>grant</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="10" t="inlineStr">
+        <is>
+          <t>G347</t>
+        </is>
+      </c>
+      <c r="B411" s="10" t="inlineStr">
+        <is>
+          <t>Simons Foundation International / SFARI</t>
+        </is>
+      </c>
+      <c r="C411" s="10" t="inlineStr">
+        <is>
+          <t>Simons Foundation</t>
+        </is>
+      </c>
+      <c r="D411" s="10" t="inlineStr">
+        <is>
+          <t>Private (Simons)</t>
+        </is>
+      </c>
+      <c r="E411" s="10" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F411" s="10" t="inlineStr">
+        <is>
+          <t>Mathematics, physics, autism research (SFARI)</t>
+        </is>
+      </c>
+      <c r="G411" s="10" t="inlineStr">
+        <is>
+          <t>Any / Established</t>
+        </is>
+      </c>
+      <c r="H411" s="10" t="inlineStr">
+        <is>
+          <t>Beyond its US programmes, the Simons Foundation funds international collaborations and autism research (SFARI) worldwide.</t>
+        </is>
+      </c>
+      <c r="I411" s="10" t="inlineStr">
+        <is>
+          <t>Program-dependent</t>
+        </is>
+      </c>
+      <c r="J411" s="10" t="inlineStr">
+        <is>
+          <t>Program-dependent</t>
+        </is>
+      </c>
+      <c r="K411" s="10" t="inlineStr">
+        <is>
+          <t>Researchers worldwide; program-specific</t>
+        </is>
+      </c>
+      <c r="L411" s="10" t="inlineStr">
+        <is>
+          <t>Program-specific deadlines (check site)</t>
+        </is>
+      </c>
+      <c r="M411" s="10" t="inlineStr">
+        <is>
+          <t>Simons proposal system</t>
+        </is>
+      </c>
+      <c r="N411" s="10" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="O411" s="10" t="inlineStr">
+        <is>
+          <t>Selective</t>
+        </is>
+      </c>
+      <c r="P411" s="10" t="inlineStr">
+        <is>
+          <t>https://www.simonsfoundation.org/funding-opportunities/</t>
+        </is>
+      </c>
+      <c r="Q411" s="10" t="inlineStr">
+        <is>
+          <t>SFARI is the world's largest private funder of autism science.</t>
+        </is>
+      </c>
+      <c r="R411" s="10" t="inlineStr"/>
+      <c r="S411" s="10" t="inlineStr"/>
+      <c r="T411" s="10" t="inlineStr"/>
+      <c r="U411" s="10" t="inlineStr">
+        <is>
+          <t>grant</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="10" t="inlineStr">
+        <is>
+          <t>G348</t>
+        </is>
+      </c>
+      <c r="B412" s="10" t="inlineStr">
+        <is>
+          <t>Fondation ARC &amp; French disease-charity research grants</t>
+        </is>
+      </c>
+      <c r="C412" s="10" t="inlineStr">
+        <is>
+          <t>Fondation ARC pour la recherche sur le cancer</t>
+        </is>
+      </c>
+      <c r="D412" s="10" t="inlineStr">
+        <is>
+          <t>France (Fondation ARC)</t>
+        </is>
+      </c>
+      <c r="E412" s="10" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F412" s="10" t="inlineStr">
+        <is>
+          <t>Cancer research</t>
+        </is>
+      </c>
+      <c r="G412" s="10" t="inlineStr">
+        <is>
+          <t>PhD candidates → established</t>
+        </is>
+      </c>
+      <c r="H412" s="10" t="inlineStr">
+        <is>
+          <t>A leading French cancer-research charity funding fellowships, project grants and equipment across oncology.</t>
+        </is>
+      </c>
+      <c r="I412" s="10" t="inlineStr">
+        <is>
+          <t>PhD/postdoc fellowships + project grants (€30k-500k)</t>
+        </is>
+      </c>
+      <c r="J412" s="10" t="inlineStr">
+        <is>
+          <t>1-3 years</t>
+        </is>
+      </c>
+      <c r="K412" s="10" t="inlineStr">
+        <is>
+          <t>Researchers in French laboratories</t>
+        </is>
+      </c>
+      <c r="L412" s="10" t="inlineStr">
+        <is>
+          <t>Annual calls (check site)</t>
+        </is>
+      </c>
+      <c r="M412" s="10" t="inlineStr">
+        <is>
+          <t>Fondation ARC portal</t>
+        </is>
+      </c>
+      <c r="N412" s="10" t="inlineStr">
+        <is>
+          <t>No — scientific council</t>
+        </is>
+      </c>
+      <c r="O412" s="10" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="P412" s="10" t="inlineStr">
+        <is>
+          <t>https://www.fondation-arc.org/</t>
+        </is>
+      </c>
+      <c r="Q412" s="10" t="inlineStr">
+        <is>
+          <t>France's dedicated cancer charity, complementing INCa public funding.</t>
+        </is>
+      </c>
+      <c r="R412" s="10" t="inlineStr"/>
+      <c r="S412" s="10" t="inlineStr"/>
+      <c r="T412" s="10" t="inlineStr"/>
+      <c r="U412" s="10" t="inlineStr">
+        <is>
+          <t>grant</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="10" t="inlineStr">
+        <is>
+          <t>G349</t>
+        </is>
+      </c>
+      <c r="B413" s="10" t="inlineStr">
+        <is>
+          <t>DBT/Wellcome India Alliance Fellowships</t>
+        </is>
+      </c>
+      <c r="C413" s="10" t="inlineStr">
+        <is>
+          <t>India Alliance (DBT/Wellcome)</t>
+        </is>
+      </c>
+      <c r="D413" s="10" t="inlineStr">
+        <is>
+          <t>India Alliance</t>
+        </is>
+      </c>
+      <c r="E413" s="10" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F413" s="10" t="inlineStr">
+        <is>
+          <t>Biomedical &amp; health research</t>
+        </is>
+      </c>
+      <c r="G413" s="10" t="inlineStr">
+        <is>
+          <t>PhD → established</t>
+        </is>
+      </c>
+      <c r="H413" s="10" t="inlineStr">
+        <is>
+          <t>India's premier biomedical fellowship programme, funding researchers from early to senior career at Indian institutions.</t>
+        </is>
+      </c>
+      <c r="I413" s="10" t="inlineStr">
+        <is>
+          <t>Salary + generous research support</t>
+        </is>
+      </c>
+      <c r="J413" s="10" t="inlineStr">
+        <is>
+          <t>5 years</t>
+        </is>
+      </c>
+      <c r="K413" s="10" t="inlineStr">
+        <is>
+          <t>Researchers committing to work in India; Indian nationals and others eligible</t>
+        </is>
+      </c>
+      <c r="L413" s="10" t="inlineStr">
+        <is>
+          <t>Annual rounds (check site)</t>
+        </is>
+      </c>
+      <c r="M413" s="10" t="inlineStr">
+        <is>
+          <t>India Alliance portal</t>
+        </is>
+      </c>
+      <c r="N413" s="10" t="inlineStr">
+        <is>
+          <t>Yes — interview</t>
+        </is>
+      </c>
+      <c r="O413" s="10" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="P413" s="10" t="inlineStr">
+        <is>
+          <t>https://www.indiaalliance.org/</t>
+        </is>
+      </c>
+      <c r="Q413" s="10" t="inlineStr">
+        <is>
+          <t>The leading route to independent biomedical research funding in India.</t>
+        </is>
+      </c>
+      <c r="R413" s="10" t="inlineStr"/>
+      <c r="S413" s="10" t="inlineStr"/>
+      <c r="T413" s="10" t="inlineStr"/>
+      <c r="U413" s="10" t="inlineStr">
+        <is>
+          <t>grant</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="10" t="inlineStr">
+        <is>
+          <t>G350</t>
+        </is>
+      </c>
+      <c r="B414" s="10" t="inlineStr">
+        <is>
+          <t>FAPESP Research Grants &amp; Fellowships (Brazil)</t>
+        </is>
+      </c>
+      <c r="C414" s="10" t="inlineStr">
+        <is>
+          <t>São Paulo Research Foundation (FAPESP)</t>
+        </is>
+      </c>
+      <c r="D414" s="10" t="inlineStr">
+        <is>
+          <t>Brazil (FAPESP)</t>
+        </is>
+      </c>
+      <c r="E414" s="10" t="inlineStr">
+        <is>
+          <t>Brazil (São Paulo)</t>
+        </is>
+      </c>
+      <c r="F414" s="10" t="inlineStr">
+        <is>
+          <t>All disciplines</t>
+        </is>
+      </c>
+      <c r="G414" s="10" t="inlineStr">
+        <is>
+          <t>PhD → established</t>
+        </is>
+      </c>
+      <c r="H414" s="10" t="inlineStr">
+        <is>
+          <t>One of Latin America's strongest funders, supporting fellowships, thematic projects and international collaborations in São Paulo state.</t>
+        </is>
+      </c>
+      <c r="I414" s="10" t="inlineStr">
+        <is>
+          <t>Scholarships + project funding (varies)</t>
+        </is>
+      </c>
+      <c r="J414" s="10" t="inlineStr">
+        <is>
+          <t>1-5 years</t>
+        </is>
+      </c>
+      <c r="K414" s="10" t="inlineStr">
+        <is>
+          <t>Researchers at institutions in São Paulo state; some international collaboration schemes</t>
+        </is>
+      </c>
+      <c r="L414" s="10" t="inlineStr">
+        <is>
+          <t>Rolling / periodic (check site)</t>
+        </is>
+      </c>
+      <c r="M414" s="10" t="inlineStr">
+        <is>
+          <t>FAPESP SAGe system</t>
+        </is>
+      </c>
+      <c r="N414" s="10" t="inlineStr">
+        <is>
+          <t>No — peer review</t>
+        </is>
+      </c>
+      <c r="O414" s="10" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="P414" s="10" t="inlineStr">
+        <is>
+          <t>https://fapesp.br/en</t>
+        </is>
+      </c>
+      <c r="Q414" s="10" t="inlineStr">
+        <is>
+          <t>Also funds visiting researchers and international mobility to São Paulo.</t>
+        </is>
+      </c>
+      <c r="R414" s="10" t="inlineStr"/>
+      <c r="S414" s="10" t="inlineStr"/>
+      <c r="T414" s="10" t="inlineStr"/>
+      <c r="U414" s="10" t="inlineStr">
+        <is>
+          <t>grant</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="10" t="inlineStr">
+        <is>
+          <t>G351</t>
+        </is>
+      </c>
+      <c r="B415" s="10" t="inlineStr">
+        <is>
+          <t>Horizon Europe EIC Pathfinder Open</t>
+        </is>
+      </c>
+      <c r="C415" s="10" t="inlineStr">
+        <is>
+          <t>European Innovation Council (EIC)</t>
+        </is>
+      </c>
+      <c r="D415" s="10" t="inlineStr">
+        <is>
+          <t>Horizon Europe</t>
+        </is>
+      </c>
+      <c r="E415" s="10" t="inlineStr">
+        <is>
+          <t>EU + Associated Countries</t>
+        </is>
+      </c>
+      <c r="F415" s="10" t="inlineStr">
+        <is>
+          <t>Deep science-to-tech research</t>
+        </is>
+      </c>
+      <c r="G415" s="10" t="inlineStr">
+        <is>
+          <t>Research teams → ventures</t>
+        </is>
+      </c>
+      <c r="H415" s="10" t="inlineStr">
+        <is>
+          <t>Funds early-stage, high-risk research toward radically new technologies — the science base from which deep-tech startups later grow.</t>
+        </is>
+      </c>
+      <c r="I415" s="10" t="inlineStr">
+        <is>
+          <t>Up to €3-4M per project</t>
+        </is>
+      </c>
+      <c r="J415" s="10" t="inlineStr">
+        <is>
+          <t>3-4 years</t>
+        </is>
+      </c>
+      <c r="K415" s="10" t="inlineStr">
+        <is>
+          <t>Consortia (Open) or single entities (Challenges) in eligible countries</t>
+        </is>
+      </c>
+      <c r="L415" s="10" t="inlineStr">
+        <is>
+          <t>Annual cut-offs (check work programme)</t>
+        </is>
+      </c>
+      <c r="M415" s="10" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders Portal</t>
+        </is>
+      </c>
+      <c r="N415" s="10" t="inlineStr">
+        <is>
+          <t>No — panel</t>
+        </is>
+      </c>
+      <c r="O415" s="10" t="inlineStr">
+        <is>
+          <t>~7-10%</t>
+        </is>
+      </c>
+      <c r="P415" s="10" t="inlineStr">
+        <is>
+          <t>https://eic.ec.europa.eu/eic-funding-opportunities/eic-pathfinder_en</t>
+        </is>
+      </c>
+      <c r="Q415" s="10" t="inlineStr">
+        <is>
+          <t>Where many future deep-tech ventures begin as collaborative research.</t>
+        </is>
+      </c>
+      <c r="R415" s="10" t="inlineStr">
+        <is>
+          <t>Pre-seed</t>
+        </is>
+      </c>
+      <c r="S415" s="10" t="inlineStr">
+        <is>
+          <t>Not yet founded</t>
+        </is>
+      </c>
+      <c r="T415" s="10" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="U415" s="10" t="inlineStr">
+        <is>
+          <t>grant</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="10" t="inlineStr">
+        <is>
+          <t>G352</t>
+        </is>
+      </c>
+      <c r="B416" s="10" t="inlineStr">
+        <is>
+          <t>Yozma-style &amp; Israel Innovation Authority Grants</t>
+        </is>
+      </c>
+      <c r="C416" s="10" t="inlineStr">
+        <is>
+          <t>Israel Innovation Authority</t>
+        </is>
+      </c>
+      <c r="D416" s="10" t="inlineStr">
+        <is>
+          <t>Israel (IIA)</t>
+        </is>
+      </c>
+      <c r="E416" s="10" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="F416" s="10" t="inlineStr">
+        <is>
+          <t>Deep tech &amp; startup R&amp;D</t>
+        </is>
+      </c>
+      <c r="G416" s="10" t="inlineStr">
+        <is>
+          <t>Pre-seed to growth</t>
+        </is>
+      </c>
+      <c r="H416" s="10" t="inlineStr">
+        <is>
+          <t>Israel's national innovation agency runs an extensive suite: incubator incentives, early-stage R&amp;D grants and the Tnufa pre-seed programme.</t>
+        </is>
+      </c>
+      <c r="I416" s="10" t="inlineStr">
+        <is>
+          <t>Tnufa up to ~$50k (85% of costs); R&amp;D grants much larger</t>
+        </is>
+      </c>
+      <c r="J416" s="10" t="inlineStr">
+        <is>
+          <t>1-2 years</t>
+        </is>
+      </c>
+      <c r="K416" s="10" t="inlineStr">
+        <is>
+          <t>Israeli companies and entrepreneurs; Tnufa open to individual inventors pre-company</t>
+        </is>
+      </c>
+      <c r="L416" s="10" t="inlineStr">
+        <is>
+          <t>Rolling / periodic (check site)</t>
+        </is>
+      </c>
+      <c r="M416" s="10" t="inlineStr">
+        <is>
+          <t>Israel Innovation Authority portal</t>
+        </is>
+      </c>
+      <c r="N416" s="10" t="inlineStr">
+        <is>
+          <t>No — review</t>
+        </is>
+      </c>
+      <c r="O416" s="10" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="P416" s="10" t="inlineStr">
+        <is>
+          <t>https://innovationisrael.org.il/en/</t>
+        </is>
+      </c>
+      <c r="Q416" s="10" t="inlineStr">
+        <is>
+          <t>Tnufa is one of the few programmes funding individual inventors before a company exists.</t>
+        </is>
+      </c>
+      <c r="R416" s="10" t="inlineStr">
+        <is>
+          <t>Pre-seed;Seed</t>
+        </is>
+      </c>
+      <c r="S416" s="10" t="inlineStr">
+        <is>
+          <t>Not yet founded</t>
+        </is>
+      </c>
+      <c r="T416" s="10" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="U416" s="10" t="inlineStr">
+        <is>
+          <t>grant</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="10" t="inlineStr">
+        <is>
+          <t>G353</t>
+        </is>
+      </c>
+      <c r="B417" s="10" t="inlineStr">
+        <is>
+          <t>MassChallenge (Zero-Equity Accelerator)</t>
+        </is>
+      </c>
+      <c r="C417" s="10" t="inlineStr">
+        <is>
+          <t>MassChallenge</t>
+        </is>
+      </c>
+      <c r="D417" s="10" t="inlineStr">
+        <is>
+          <t>Private non-profit</t>
+        </is>
+      </c>
+      <c r="E417" s="10" t="inlineStr">
+        <is>
+          <t>International (US, Europe, Israel hubs)</t>
+        </is>
+      </c>
+      <c r="F417" s="10" t="inlineStr">
+        <is>
+          <t>Startup acceleration (all sectors)</t>
+        </is>
+      </c>
+      <c r="G417" s="10" t="inlineStr">
+        <is>
+          <t>Early-stage startups</t>
+        </is>
+      </c>
+      <c r="H417" s="10" t="inlineStr">
+        <is>
+          <t>A global accelerator that takes no equity, offering mentorship, resources and cash prizes to cohorts of early startups.</t>
+        </is>
+      </c>
+      <c r="I417" s="10" t="inlineStr">
+        <is>
+          <t>Cash prizes (no equity taken)</t>
+        </is>
+      </c>
+      <c r="J417" s="10" t="inlineStr">
+        <is>
+          <t>4-6 month programmes</t>
+        </is>
+      </c>
+      <c r="K417" s="10" t="inlineStr">
+        <is>
+          <t>Early-stage startups; sector-agnostic; hub-specific intakes</t>
+        </is>
+      </c>
+      <c r="L417" s="10" t="inlineStr">
+        <is>
+          <t>Annual applications per hub (check site)</t>
+        </is>
+      </c>
+      <c r="M417" s="10" t="inlineStr">
+        <is>
+          <t>MassChallenge application</t>
+        </is>
+      </c>
+      <c r="N417" s="10" t="inlineStr">
+        <is>
+          <t>Yes — selection</t>
+        </is>
+      </c>
+      <c r="O417" s="10" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="P417" s="10" t="inlineStr">
+        <is>
+          <t>https://masschallenge.org/</t>
+        </is>
+      </c>
+      <c r="Q417" s="10" t="inlineStr">
+        <is>
+          <t>Zero-equity model is rare and valuable — you keep 100% of your company.</t>
+        </is>
+      </c>
+      <c r="R417" s="10" t="inlineStr">
+        <is>
+          <t>Pre-seed;Seed</t>
+        </is>
+      </c>
+      <c r="S417" s="10" t="inlineStr">
+        <is>
+          <t>Founded &lt; 3 years</t>
+        </is>
+      </c>
+      <c r="T417" s="10" t="inlineStr">
+        <is>
+          <t>Support / services only</t>
+        </is>
+      </c>
+      <c r="U417" s="10" t="inlineStr">
+        <is>
+          <t>grant</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="10" t="inlineStr">
+        <is>
+          <t>G354</t>
+        </is>
+      </c>
+      <c r="B418" s="10" t="inlineStr">
+        <is>
+          <t>Y Combinator</t>
+        </is>
+      </c>
+      <c r="C418" s="10" t="inlineStr">
+        <is>
+          <t>Y Combinator</t>
+        </is>
+      </c>
+      <c r="D418" s="10" t="inlineStr">
+        <is>
+          <t>Private (YC)</t>
+        </is>
+      </c>
+      <c r="E418" s="10" t="inlineStr">
+        <is>
+          <t>International (relocate to US)</t>
+        </is>
+      </c>
+      <c r="F418" s="10" t="inlineStr">
+        <is>
+          <t>Startup acceleration (all sectors)</t>
+        </is>
+      </c>
+      <c r="G418" s="10" t="inlineStr">
+        <is>
+          <t>Pre-seed &amp; seed</t>
+        </is>
+      </c>
+      <c r="H418" s="10" t="inlineStr">
+        <is>
+          <t>The world's most influential startup accelerator, investing a standard amount for equity and providing an intensive 3-month programme.</t>
+        </is>
+      </c>
+      <c r="I418" s="10" t="inlineStr">
+        <is>
+          <t>$500,000 standard deal (for ~7% equity)</t>
+        </is>
+      </c>
+      <c r="J418" s="10" t="inlineStr">
+        <is>
+          <t>3-month batches (2x/yr)</t>
+        </is>
+      </c>
+      <c r="K418" s="10" t="inlineStr">
+        <is>
+          <t>Any startup willing to participate in the US programme; any nationality</t>
+        </is>
+      </c>
+      <c r="L418" s="10" t="inlineStr">
+        <is>
+          <t>2 batches/yr (rolling application; check site)</t>
+        </is>
+      </c>
+      <c r="M418" s="10" t="inlineStr">
+        <is>
+          <t>YC online application</t>
+        </is>
+      </c>
+      <c r="N418" s="10" t="inlineStr">
+        <is>
+          <t>Yes — interview</t>
+        </is>
+      </c>
+      <c r="O418" s="10" t="inlineStr">
+        <is>
+          <t>~1-2%</t>
+        </is>
+      </c>
+      <c r="P418" s="10" t="inlineStr">
+        <is>
+          <t>https://www.ycombinator.com/</t>
+        </is>
+      </c>
+      <c r="Q418" s="10" t="inlineStr">
+        <is>
+          <t>Equity-based and highly selective, but transformative for those accepted.</t>
+        </is>
+      </c>
+      <c r="R418" s="10" t="inlineStr">
+        <is>
+          <t>Pre-seed;Seed</t>
+        </is>
+      </c>
+      <c r="S418" s="10" t="inlineStr">
+        <is>
+          <t>Not yet founded</t>
+        </is>
+      </c>
+      <c r="T418" s="10" t="inlineStr">
+        <is>
+          <t>Equity / investment</t>
+        </is>
+      </c>
+      <c r="U418" s="10" t="inlineStr">
+        <is>
+          <t>grant</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="10" t="inlineStr">
+        <is>
+          <t>G355</t>
+        </is>
+      </c>
+      <c r="B419" s="10" t="inlineStr">
+        <is>
+          <t>Techstars Accelerators</t>
+        </is>
+      </c>
+      <c r="C419" s="10" t="inlineStr">
+        <is>
+          <t>Techstars</t>
+        </is>
+      </c>
+      <c r="D419" s="10" t="inlineStr">
+        <is>
+          <t>Private (Techstars)</t>
+        </is>
+      </c>
+      <c r="E419" s="10" t="inlineStr">
+        <is>
+          <t>International (many city/theme hubs)</t>
+        </is>
+      </c>
+      <c r="F419" s="10" t="inlineStr">
+        <is>
+          <t>Startup acceleration (all sectors)</t>
+        </is>
+      </c>
+      <c r="G419" s="10" t="inlineStr">
+        <is>
+          <t>Pre-seed &amp; seed</t>
+        </is>
+      </c>
+      <c r="H419" s="10" t="inlineStr">
+        <is>
+          <t>A global network of mentorship-driven accelerators investing for equity across dozens of cities and themes.</t>
+        </is>
+      </c>
+      <c r="I419" s="10" t="inlineStr">
+        <is>
+          <t>~$120,000 (for equity) + mentorship</t>
+        </is>
+      </c>
+      <c r="J419" s="10" t="inlineStr">
+        <is>
+          <t>3-month programmes</t>
+        </is>
+      </c>
+      <c r="K419" s="10" t="inlineStr">
+        <is>
+          <t>Early-stage startups; apply to a specific programme</t>
+        </is>
+      </c>
+      <c r="L419" s="10" t="inlineStr">
+        <is>
+          <t>Rolling per programme (check site)</t>
+        </is>
+      </c>
+      <c r="M419" s="10" t="inlineStr">
+        <is>
+          <t>Techstars application</t>
+        </is>
+      </c>
+      <c r="N419" s="10" t="inlineStr">
+        <is>
+          <t>Yes — interview</t>
+        </is>
+      </c>
+      <c r="O419" s="10" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="P419" s="10" t="inlineStr">
+        <is>
+          <t>https://www.techstars.com/</t>
+        </is>
+      </c>
+      <c r="Q419" s="10" t="inlineStr">
+        <is>
+          <t>Choose the programme by city or vertical that fits your startup.</t>
+        </is>
+      </c>
+      <c r="R419" s="10" t="inlineStr">
+        <is>
+          <t>Pre-seed;Seed</t>
+        </is>
+      </c>
+      <c r="S419" s="10" t="inlineStr">
+        <is>
+          <t>Founded &lt; 3 years</t>
+        </is>
+      </c>
+      <c r="T419" s="10" t="inlineStr">
+        <is>
+          <t>Equity / investment</t>
+        </is>
+      </c>
+      <c r="U419" s="10" t="inlineStr">
+        <is>
+          <t>grant</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="10" t="inlineStr">
+        <is>
+          <t>G356</t>
+        </is>
+      </c>
+      <c r="B420" s="10" t="inlineStr">
+        <is>
+          <t>Antler Global</t>
+        </is>
+      </c>
+      <c r="C420" s="10" t="inlineStr">
+        <is>
+          <t>Antler</t>
+        </is>
+      </c>
+      <c r="D420" s="10" t="inlineStr">
+        <is>
+          <t>Private (Antler)</t>
+        </is>
+      </c>
+      <c r="E420" s="10" t="inlineStr">
+        <is>
+          <t>International (many countries)</t>
+        </is>
+      </c>
+      <c r="F420" s="10" t="inlineStr">
+        <is>
+          <t>Day-zero venture building</t>
+        </is>
+      </c>
+      <c r="G420" s="10" t="inlineStr">
+        <is>
+          <t>Aspiring founders (pre-company)</t>
+        </is>
+      </c>
+      <c r="H420" s="10" t="inlineStr">
+        <is>
+          <t>An early-stage investor that backs individuals before they even have a co-founder or idea, running residencies worldwide.</t>
+        </is>
+      </c>
+      <c r="I420" s="10" t="inlineStr">
+        <is>
+          <t>~$100-250k investment (for equity) after residency</t>
+        </is>
+      </c>
+      <c r="J420" s="10" t="inlineStr">
+        <is>
+          <t>~6-month residency + investment</t>
+        </is>
+      </c>
+      <c r="K420" s="10" t="inlineStr">
+        <is>
+          <t>Aspiring founders willing to join a local Antler residency</t>
+        </is>
+      </c>
+      <c r="L420" s="10" t="inlineStr">
+        <is>
+          <t>Rolling cohorts per location (check site)</t>
+        </is>
+      </c>
+      <c r="M420" s="10" t="inlineStr">
+        <is>
+          <t>Antler application</t>
+        </is>
+      </c>
+      <c r="N420" s="10" t="inlineStr">
+        <is>
+          <t>Yes — selection</t>
+        </is>
+      </c>
+      <c r="O420" s="10" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="P420" s="10" t="inlineStr">
+        <is>
+          <t>https://www.antler.co/</t>
+        </is>
+      </c>
+      <c r="Q420" s="10" t="inlineStr">
+        <is>
+          <t>Uniquely backs people pre-idea — good for researchers wanting to become founders.</t>
+        </is>
+      </c>
+      <c r="R420" s="10" t="inlineStr">
+        <is>
+          <t>Pre-seed</t>
+        </is>
+      </c>
+      <c r="S420" s="10" t="inlineStr">
+        <is>
+          <t>Not yet founded</t>
+        </is>
+      </c>
+      <c r="T420" s="10" t="inlineStr">
+        <is>
+          <t>Equity / investment</t>
+        </is>
+      </c>
+      <c r="U420" s="10" t="inlineStr">
+        <is>
+          <t>grant</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="10" t="inlineStr">
+        <is>
+          <t>G357</t>
+        </is>
+      </c>
+      <c r="B421" s="10" t="inlineStr">
+        <is>
+          <t>Nordic Innovation Grants</t>
+        </is>
+      </c>
+      <c r="C421" s="10" t="inlineStr">
+        <is>
+          <t>Nordic Innovation (Nordic Council of Ministers)</t>
+        </is>
+      </c>
+      <c r="D421" s="10" t="inlineStr">
+        <is>
+          <t>Nordic Innovation</t>
+        </is>
+      </c>
+      <c r="E421" s="10" t="inlineStr">
+        <is>
+          <t>Nordics (cross-border)</t>
+        </is>
+      </c>
+      <c r="F421" s="10" t="inlineStr">
+        <is>
+          <t>Cross-border innovation (all sectors)</t>
+        </is>
+      </c>
+      <c r="G421" s="10" t="inlineStr">
+        <is>
+          <t>SMEs &amp; startups</t>
+        </is>
+      </c>
+      <c r="H421" s="10" t="inlineStr">
+        <is>
+          <t>Funds cross-border Nordic collaboration projects helping startups and SMEs scale across the Nordic region.</t>
+        </is>
+      </c>
+      <c r="I421" s="10" t="inlineStr">
+        <is>
+          <t>Project-dependent (often €100k-500k)</t>
+        </is>
+      </c>
+      <c r="J421" s="10" t="inlineStr">
+        <is>
+          <t>1-3 years</t>
+        </is>
+      </c>
+      <c r="K421" s="10" t="inlineStr">
+        <is>
+          <t>Companies/organisations from at least 2-3 Nordic countries</t>
+        </is>
+      </c>
+      <c r="L421" s="10" t="inlineStr">
+        <is>
+          <t>Periodic calls (check site)</t>
+        </is>
+      </c>
+      <c r="M421" s="10" t="inlineStr">
+        <is>
+          <t>Nordic Innovation portal</t>
+        </is>
+      </c>
+      <c r="N421" s="10" t="inlineStr">
+        <is>
+          <t>No — review</t>
+        </is>
+      </c>
+      <c r="O421" s="10" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="P421" s="10" t="inlineStr">
+        <is>
+          <t>https://www.nordicinnovation.org/</t>
+        </is>
+      </c>
+      <c r="Q421" s="10" t="inlineStr">
+        <is>
+          <t>Requires partners across Nordic borders — designed for regional scaling.</t>
+        </is>
+      </c>
+      <c r="R421" s="10" t="inlineStr">
+        <is>
+          <t>Seed;Growth</t>
+        </is>
+      </c>
+      <c r="S421" s="10" t="inlineStr">
+        <is>
+          <t>Founded &lt; 5 years</t>
+        </is>
+      </c>
+      <c r="T421" s="10" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="U421" s="10" t="inlineStr">
+        <is>
+          <t>grant</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="10" t="inlineStr">
+        <is>
+          <t>G358</t>
+        </is>
+      </c>
+      <c r="B422" s="10" t="inlineStr">
+        <is>
+          <t>Swiss National Science Foundation BRIDGE (with Innosuisse)</t>
+        </is>
+      </c>
+      <c r="C422" s="10" t="inlineStr">
+        <is>
+          <t>SNSF &amp; Innosuisse</t>
+        </is>
+      </c>
+      <c r="D422" s="10" t="inlineStr">
+        <is>
+          <t>Switzerland (BRIDGE)</t>
+        </is>
+      </c>
+      <c r="E422" s="10" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="F422" s="10" t="inlineStr">
+        <is>
+          <t>Research-to-market (Proof of Concept &amp; Discovery)</t>
+        </is>
+      </c>
+      <c r="G422" s="10" t="inlineStr">
+        <is>
+          <t>PhD → early group leader</t>
+        </is>
+      </c>
+      <c r="H422" s="10" t="inlineStr">
+        <is>
+          <t>A joint SNSF-Innosuisse programme bridging basic research and application, with Proof of Concept grants for young researchers.</t>
+        </is>
+      </c>
+      <c r="I422" s="10" t="inlineStr">
+        <is>
+          <t>Proof of Concept up to CHF 130k; Discovery larger</t>
+        </is>
+      </c>
+      <c r="J422" s="10" t="inlineStr">
+        <is>
+          <t>1-2 years (PoC)</t>
+        </is>
+      </c>
+      <c r="K422" s="10" t="inlineStr">
+        <is>
+          <t>Researchers at Swiss institutions with results to translate</t>
+        </is>
+      </c>
+      <c r="L422" s="10" t="inlineStr">
+        <is>
+          <t>Annual cut-offs (check site)</t>
+        </is>
+      </c>
+      <c r="M422" s="10" t="inlineStr">
+        <is>
+          <t>BRIDGE portal</t>
+        </is>
+      </c>
+      <c r="N422" s="10" t="inlineStr">
+        <is>
+          <t>No — review</t>
+        </is>
+      </c>
+      <c r="O422" s="10" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="P422" s="10" t="inlineStr">
+        <is>
+          <t>https://www.bridge.ch/en/</t>
+        </is>
+      </c>
+      <c r="Q422" s="10" t="inlineStr">
+        <is>
+          <t>The natural pre-company step for Swiss researchers before Innosuisse or Venture Kick.</t>
+        </is>
+      </c>
+      <c r="R422" s="10" t="inlineStr">
+        <is>
+          <t>Pre-seed</t>
+        </is>
+      </c>
+      <c r="S422" s="10" t="inlineStr">
+        <is>
+          <t>Not yet founded</t>
+        </is>
+      </c>
+      <c r="T422" s="10" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="U422" s="10" t="inlineStr">
+        <is>
+          <t>grant</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="10" t="inlineStr">
+        <is>
+          <t>G359</t>
+        </is>
+      </c>
+      <c r="B423" s="10" t="inlineStr">
+        <is>
+          <t>Startup Chile / regional 'soft landing' programmes</t>
+        </is>
+      </c>
+      <c r="C423" s="10" t="inlineStr">
+        <is>
+          <t>Startup Chile (CORFO)</t>
+        </is>
+      </c>
+      <c r="D423" s="10" t="inlineStr">
+        <is>
+          <t>Chile (CORFO)</t>
+        </is>
+      </c>
+      <c r="E423" s="10" t="inlineStr">
+        <is>
+          <t>Chile (incoming, international)</t>
+        </is>
+      </c>
+      <c r="F423" s="10" t="inlineStr">
+        <is>
+          <t>Startup acceleration (equity-free)</t>
+        </is>
+      </c>
+      <c r="G423" s="10" t="inlineStr">
+        <is>
+          <t>Early-stage startups</t>
+        </is>
+      </c>
+      <c r="H423" s="10" t="inlineStr">
+        <is>
+          <t>A pioneering government accelerator offering equity-free grants and a soft landing for international founders in Latin America.</t>
+        </is>
+      </c>
+      <c r="I423" s="10" t="inlineStr">
+        <is>
+          <t>Up to ~$80,000 equity-free + visa support</t>
+        </is>
+      </c>
+      <c r="J423" s="10" t="inlineStr">
+        <is>
+          <t>6-month programmes</t>
+        </is>
+      </c>
+      <c r="K423" s="10" t="inlineStr">
+        <is>
+          <t>International and Chilean startups; programme-specific stage rules</t>
+        </is>
+      </c>
+      <c r="L423" s="10" t="inlineStr">
+        <is>
+          <t>Periodic calls (check site)</t>
+        </is>
+      </c>
+      <c r="M423" s="10" t="inlineStr">
+        <is>
+          <t>Startup Chile application</t>
+        </is>
+      </c>
+      <c r="N423" s="10" t="inlineStr">
+        <is>
+          <t>Yes — selection</t>
+        </is>
+      </c>
+      <c r="O423" s="10" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="P423" s="10" t="inlineStr">
+        <is>
+          <t>https://startupchile.org/en/</t>
+        </is>
+      </c>
+      <c r="Q423" s="10" t="inlineStr">
+        <is>
+          <t>Equity-free public funding plus a base for the Latin American market.</t>
+        </is>
+      </c>
+      <c r="R423" s="10" t="inlineStr">
+        <is>
+          <t>Pre-seed;Seed</t>
+        </is>
+      </c>
+      <c r="S423" s="10" t="inlineStr">
+        <is>
+          <t>Founded &lt; 3 years</t>
+        </is>
+      </c>
+      <c r="T423" s="10" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="U423" s="10" t="inlineStr">
+        <is>
+          <t>grant</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="10" t="inlineStr">
+        <is>
+          <t>G360</t>
+        </is>
+      </c>
+      <c r="B424" s="10" t="inlineStr">
+        <is>
+          <t>Tech Nation-style visa-linked &amp; Innovator Founder routes</t>
+        </is>
+      </c>
+      <c r="C424" s="10" t="inlineStr">
+        <is>
+          <t>UK Government (Innovator Founder visa endorsement)</t>
+        </is>
+      </c>
+      <c r="D424" s="10" t="inlineStr">
+        <is>
+          <t>UK (Innovator Founder)</t>
+        </is>
+      </c>
+      <c r="E424" s="10" t="inlineStr">
+        <is>
+          <t>United Kingdom (incoming)</t>
+        </is>
+      </c>
+      <c r="F424" s="10" t="inlineStr">
+        <is>
+          <t>Startup visa endorsement</t>
+        </is>
+      </c>
+      <c r="G424" s="10" t="inlineStr">
+        <is>
+          <t>International founders</t>
+        </is>
+      </c>
+      <c r="H424" s="10" t="inlineStr">
+        <is>
+          <t>Not funding itself, but the endorsement route lets international founders base an innovative startup in the UK — often paired with grants.</t>
+        </is>
+      </c>
+      <c r="I424" s="10" t="inlineStr">
+        <is>
+          <t>No direct grant (enables UK access)</t>
+        </is>
+      </c>
+      <c r="J424" s="10" t="inlineStr">
+        <is>
+          <t>Visa-linked</t>
+        </is>
+      </c>
+      <c r="K424" s="10" t="inlineStr">
+        <is>
+          <t>Non-UK founders with an innovative, viable, scalable business idea; endorsing body approval</t>
+        </is>
+      </c>
+      <c r="L424" s="10" t="inlineStr">
+        <is>
+          <t>Rolling (via endorsing bodies)</t>
+        </is>
+      </c>
+      <c r="M424" s="10" t="inlineStr">
+        <is>
+          <t>Endorsing body application</t>
+        </is>
+      </c>
+      <c r="N424" s="10" t="inlineStr">
+        <is>
+          <t>Yes — endorsement assessment</t>
+        </is>
+      </c>
+      <c r="O424" s="10" t="inlineStr">
+        <is>
+          <t>Selective</t>
+        </is>
+      </c>
+      <c r="P424" s="10" t="inlineStr">
+        <is>
+          <t>https://www.gov.uk/innovator-founder-visa</t>
+        </is>
+      </c>
+      <c r="Q424" s="10" t="inlineStr">
+        <is>
+          <t>Pair with Innovate UK grants once established in the UK.</t>
+        </is>
+      </c>
+      <c r="R424" s="10" t="inlineStr">
+        <is>
+          <t>Pre-seed;Seed</t>
+        </is>
+      </c>
+      <c r="S424" s="10" t="inlineStr">
+        <is>
+          <t>Not yet founded</t>
+        </is>
+      </c>
+      <c r="T424" s="10" t="inlineStr">
+        <is>
+          <t>Support / services only</t>
+        </is>
+      </c>
+      <c r="U424" s="10" t="inlineStr">
+        <is>
+          <t>grant</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>A61</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Dirac Medal</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>International Centre for Theoretical Physics (ICTP)</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>ICTP</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>Theoretical physics</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>Any / Established</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>One of the most prestigious awards in theoretical physics, awarded on Dirac's birthday each year.</t>
+        </is>
+      </c>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>Honorarium + medal</t>
+        </is>
+      </c>
+      <c r="J425" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>By nomination; open internationally</t>
+        </is>
+      </c>
+      <c r="L425" t="inlineStr">
+        <is>
+          <t>Annual nomination (check site)</t>
+        </is>
+      </c>
+      <c r="M425" t="inlineStr">
+        <is>
+          <t>Nomination only</t>
+        </is>
+      </c>
+      <c r="N425" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O425" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P425" t="inlineStr">
+        <is>
+          <t>https://www.ictp.it/about-ictp/prizes-awards/the-dirac-medal</t>
+        </is>
+      </c>
+      <c r="Q425" t="inlineStr">
+        <is>
+          <t>Named for Paul Dirac; many laureates later win the Nobel.</t>
+        </is>
+      </c>
+      <c r="R425" t="inlineStr"/>
+      <c r="S425" t="inlineStr"/>
+      <c r="T425" t="inlineStr"/>
+      <c r="U425" t="inlineStr">
+        <is>
+          <t>award</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>A62</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>Wollaston Medal / Geological Society Awards</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>Geological Society of London</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>Geological Society</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>United Kingdom / International</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>Earth sciences</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>Any / Established</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>The Geological Society's highest award, plus a suite of medals across the earth sciences.</t>
+        </is>
+      </c>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>Medal + recognition</t>
+        </is>
+      </c>
+      <c r="J426" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>By nomination; open internationally</t>
+        </is>
+      </c>
+      <c r="L426" t="inlineStr">
+        <is>
+          <t>Annual nomination (check site)</t>
+        </is>
+      </c>
+      <c r="M426" t="inlineStr">
+        <is>
+          <t>Nomination only</t>
+        </is>
+      </c>
+      <c r="N426" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O426" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P426" t="inlineStr">
+        <is>
+          <t>https://www.geolsoc.org.uk/awards</t>
+        </is>
+      </c>
+      <c r="Q426" t="inlineStr">
+        <is>
+          <t>The Wollaston Medal has been awarded since 1831.</t>
+        </is>
+      </c>
+      <c r="R426" t="inlineStr"/>
+      <c r="S426" t="inlineStr"/>
+      <c r="T426" t="inlineStr"/>
+      <c r="U426" t="inlineStr">
+        <is>
+          <t>award</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>A63</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>IEEE Medals &amp; Technical Field Awards</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>Institute of Electrical and Electronics Engineers (IEEE)</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>IEEE</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>Electrical engineering, computing &amp; electronics</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>Any / Established</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>The world's largest technical professional body awards medals across computing, communications, power and electronics.</t>
+        </is>
+      </c>
+      <c r="I427" t="inlineStr">
+        <is>
+          <t>$10,000-$50,000 depending on medal</t>
+        </is>
+      </c>
+      <c r="J427" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>By nomination through IEEE; open internationally</t>
+        </is>
+      </c>
+      <c r="L427" t="inlineStr">
+        <is>
+          <t>Annual nomination (check site)</t>
+        </is>
+      </c>
+      <c r="M427" t="inlineStr">
+        <is>
+          <t>Nomination only</t>
+        </is>
+      </c>
+      <c r="N427" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O427" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P427" t="inlineStr">
+        <is>
+          <t>https://www.ieee.org/about/awards/</t>
+        </is>
+      </c>
+      <c r="Q427" t="inlineStr">
+        <is>
+          <t>Includes the IEEE Medal of Honor, the field's highest distinction.</t>
+        </is>
+      </c>
+      <c r="R427" t="inlineStr"/>
+      <c r="S427" t="inlineStr"/>
+      <c r="T427" t="inlineStr"/>
+      <c r="U427" t="inlineStr">
+        <is>
+          <t>award</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>A64</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>ACS National Awards (American Chemical Society)</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>American Chemical Society (ACS)</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>ACS</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>Early-career → lifetime</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>Dozens of national awards spanning every subfield of chemistry, from early-career to lifetime achievement.</t>
+        </is>
+      </c>
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>$5,000-$25,000 depending on award</t>
+        </is>
+      </c>
+      <c r="J428" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>By nomination; many open internationally</t>
+        </is>
+      </c>
+      <c r="L428" t="inlineStr">
+        <is>
+          <t>Annual nomination ~summer (check site)</t>
+        </is>
+      </c>
+      <c r="M428" t="inlineStr">
+        <is>
+          <t>Nomination only</t>
+        </is>
+      </c>
+      <c r="N428" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O428" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P428" t="inlineStr">
+        <is>
+          <t>https://www.acs.org/funding/awards.html</t>
+        </is>
+      </c>
+      <c r="Q428" t="inlineStr">
+        <is>
+          <t>The Priestley Medal is the ACS's highest honour.</t>
+        </is>
+      </c>
+      <c r="R428" t="inlineStr"/>
+      <c r="S428" t="inlineStr"/>
+      <c r="T428" t="inlineStr"/>
+      <c r="U428" t="inlineStr">
+        <is>
+          <t>award</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>A65</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>Fewster / Royal Society of Chemistry Prizes</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>Royal Society of Chemistry (RSC)</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>RSC</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>United Kingdom / International</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>Early-career → lifetime</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>The RSC's prizes recognise excellence across chemistry, including early-career and research-team awards.</t>
+        </is>
+      </c>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>Up to £50,000 (Faraday/Longstaff)</t>
+        </is>
+      </c>
+      <c r="J429" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>By nomination; many open internationally</t>
+        </is>
+      </c>
+      <c r="L429" t="inlineStr">
+        <is>
+          <t>Annual nomination (check site)</t>
+        </is>
+      </c>
+      <c r="M429" t="inlineStr">
+        <is>
+          <t>Nomination only</t>
+        </is>
+      </c>
+      <c r="N429" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O429" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P429" t="inlineStr">
+        <is>
+          <t>https://www.rsc.org/prizes-funding/prizes/</t>
+        </is>
+      </c>
+      <c r="Q429" t="inlineStr">
+        <is>
+          <t>Recently restructured into research, innovation, and education categories.</t>
+        </is>
+      </c>
+      <c r="R429" t="inlineStr"/>
+      <c r="S429" t="inlineStr"/>
+      <c r="T429" t="inlineStr"/>
+      <c r="U429" t="inlineStr">
+        <is>
+          <t>award</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>A66</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>Fields-adjacent: Abel Prize</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>Norwegian Academy of Science and Letters</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>Abel Prize</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>Any / Established</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>One of the highest honours in mathematics, awarded annually for outstanding lifetime work — a true counterpart to the Nobel.</t>
+        </is>
+      </c>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>NOK 7,500,000 (~€650k)</t>
+        </is>
+      </c>
+      <c r="J430" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>By nomination; open internationally</t>
+        </is>
+      </c>
+      <c r="L430" t="inlineStr">
+        <is>
+          <t>Annual nomination ~Sep (check site)</t>
+        </is>
+      </c>
+      <c r="M430" t="inlineStr">
+        <is>
+          <t>Nomination only</t>
+        </is>
+      </c>
+      <c r="N430" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O430" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P430" t="inlineStr">
+        <is>
+          <t>https://abelprize.no/</t>
+        </is>
+      </c>
+      <c r="Q430" t="inlineStr">
+        <is>
+          <t>Unlike the Fields Medal, the Abel has no age limit.</t>
+        </is>
+      </c>
+      <c r="R430" t="inlineStr"/>
+      <c r="S430" t="inlineStr"/>
+      <c r="T430" t="inlineStr"/>
+      <c r="U430" t="inlineStr">
+        <is>
+          <t>award</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>A67</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>Breakthrough New Horizons &amp; Maryam Mirzakhani Prizes</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>Breakthrough Prize Foundation</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>Breakthrough Prize</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>Physics &amp; mathematics</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>Early-career</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>Early-career offshoots of the Breakthrough Prize: New Horizons for junior physicists/mathematicians and Mirzakhani for women mathematicians.</t>
+        </is>
+      </c>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>$100,000 (New Horizons); $50,000 (Mirzakhani)</t>
+        </is>
+      </c>
+      <c r="J431" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>By nomination; early-career researchers</t>
+        </is>
+      </c>
+      <c r="L431" t="inlineStr">
+        <is>
+          <t>Annual nomination (check site)</t>
+        </is>
+      </c>
+      <c r="M431" t="inlineStr">
+        <is>
+          <t>Nomination only</t>
+        </is>
+      </c>
+      <c r="N431" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O431" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P431" t="inlineStr">
+        <is>
+          <t>https://breakthroughprize.org/</t>
+        </is>
+      </c>
+      <c r="Q431" t="inlineStr">
+        <is>
+          <t>A realistic aspiration for outstanding early-career theorists.</t>
+        </is>
+      </c>
+      <c r="R431" t="inlineStr"/>
+      <c r="S431" t="inlineStr"/>
+      <c r="T431" t="inlineStr"/>
+      <c r="U431" t="inlineStr">
+        <is>
+          <t>award</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>A68</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>ASM &amp; FEMS microbiology awards</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>American Society for Microbiology / FEMS</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>ASM / FEMS</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>Microbiology</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>Early-career → lifetime</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>The major microbiology societies award prizes across the field, from early-career to distinguished achievement.</t>
+        </is>
+      </c>
+      <c r="I432" t="inlineStr">
+        <is>
+          <t>Varies (medal + cash)</t>
+        </is>
+      </c>
+      <c r="J432" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>By nomination; society membership often required</t>
+        </is>
+      </c>
+      <c r="L432" t="inlineStr">
+        <is>
+          <t>Annual nomination (check site)</t>
+        </is>
+      </c>
+      <c r="M432" t="inlineStr">
+        <is>
+          <t>Nomination only</t>
+        </is>
+      </c>
+      <c r="N432" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O432" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P432" t="inlineStr">
+        <is>
+          <t>https://asm.org/Awards</t>
+        </is>
+      </c>
+      <c r="Q432" t="inlineStr">
+        <is>
+          <t>Strong recognition within the microbiology community.</t>
+        </is>
+      </c>
+      <c r="R432" t="inlineStr"/>
+      <c r="S432" t="inlineStr"/>
+      <c r="T432" t="inlineStr"/>
+      <c r="U432" t="inlineStr">
+        <is>
+          <t>award</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>A69</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>Society for Neuroscience Awards</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>Society for Neuroscience (SfN)</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>SfN</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>Neuroscience</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>Early-career → lifetime</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>The world's largest neuroscience society grants awards spanning young investigators to lifetime achievement.</t>
+        </is>
+      </c>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>Varies (up to ~$25,000)</t>
+        </is>
+      </c>
+      <c r="J433" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>By nomination; many open internationally</t>
+        </is>
+      </c>
+      <c r="L433" t="inlineStr">
+        <is>
+          <t>Annual nomination (check site)</t>
+        </is>
+      </c>
+      <c r="M433" t="inlineStr">
+        <is>
+          <t>Nomination only</t>
+        </is>
+      </c>
+      <c r="N433" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O433" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P433" t="inlineStr">
+        <is>
+          <t>https://www.sfn.org/careers/awards</t>
+        </is>
+      </c>
+      <c r="Q433" t="inlineStr">
+        <is>
+          <t>The Young Investigator Award is a notable early-career marker.</t>
+        </is>
+      </c>
+      <c r="R433" t="inlineStr"/>
+      <c r="S433" t="inlineStr"/>
+      <c r="T433" t="inlineStr"/>
+      <c r="U433" t="inlineStr">
+        <is>
+          <t>award</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>A70</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>EMBO Young Investigator Programme</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>European Molecular Biology Organization (EMBO)</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>EMBO</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>Europe + eligible countries</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>Life sciences</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>Early group leader</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>Not a prize but a prestigious recognition-plus-support scheme for young group leaders in the life sciences, with funding and networking.</t>
+        </is>
+      </c>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>€15,000 award + benefits + networks</t>
+        </is>
+      </c>
+      <c r="J434" t="inlineStr">
+        <is>
+          <t>4-year membership</t>
+        </is>
+      </c>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>Group leaders in their first years; in EMBC member states</t>
+        </is>
+      </c>
+      <c r="L434" t="inlineStr">
+        <is>
+          <t>Annual: ~1 Apr (check site)</t>
+        </is>
+      </c>
+      <c r="M434" t="inlineStr">
+        <is>
+          <t>EMBO application</t>
+        </is>
+      </c>
+      <c r="N434" t="inlineStr">
+        <is>
+          <t>No — selection</t>
+        </is>
+      </c>
+      <c r="O434" t="inlineStr">
+        <is>
+          <t>~15%</t>
+        </is>
+      </c>
+      <c r="P434" t="inlineStr">
+        <is>
+          <t>https://www.embo.org/funding/fellowships-grants-and-career-support/young-investigator-programme/</t>
+        </is>
+      </c>
+      <c r="Q434" t="inlineStr">
+        <is>
+          <t>A major career marker for European life scientists starting a lab.</t>
+        </is>
+      </c>
+      <c r="R434" t="inlineStr"/>
+      <c r="S434" t="inlineStr"/>
+      <c r="T434" t="inlineStr"/>
+      <c r="U434" t="inlineStr">
+        <is>
+          <t>award</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>A71</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>Vallee, Wiley &amp; Gruber Prizes</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>Vallee Foundation / Wiley Foundation / Gruber Foundation</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>Various foundations</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>Biomedical &amp; fundamental sciences</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>Established</t>
+        </is>
+      </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>A cluster of prestigious foundation prizes in biomedical science, neuroscience, genetics, cosmology and justice.</t>
+        </is>
+      </c>
+      <c r="I435" t="inlineStr">
+        <is>
+          <t>$50,000-$500,000 depending on prize</t>
+        </is>
+      </c>
+      <c r="J435" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>By nomination; open internationally</t>
+        </is>
+      </c>
+      <c r="L435" t="inlineStr">
+        <is>
+          <t>Annual nomination (check each)</t>
+        </is>
+      </c>
+      <c r="M435" t="inlineStr">
+        <is>
+          <t>Nomination only</t>
+        </is>
+      </c>
+      <c r="N435" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O435" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P435" t="inlineStr">
+        <is>
+          <t>https://gruber.yale.edu/</t>
+        </is>
+      </c>
+      <c r="Q435" t="inlineStr">
+        <is>
+          <t>The Gruber prizes cover cosmology, genetics and neuroscience specifically.</t>
+        </is>
+      </c>
+      <c r="R435" t="inlineStr"/>
+      <c r="S435" t="inlineStr"/>
+      <c r="T435" t="inlineStr"/>
+      <c r="U435" t="inlineStr">
+        <is>
+          <t>award</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>A72</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>National Academy of Engineering — Draper &amp; Russ Prizes</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>National Academy of Engineering (NAE)</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>NAE</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>USA / International</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>Any / Established</t>
+        </is>
+      </c>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>The NAE's Draper Prize (engineering's top honour) and Russ Prize (bioengineering) recognise engineering achievements benefiting society.</t>
+        </is>
+      </c>
+      <c r="I436" t="inlineStr">
+        <is>
+          <t>$500,000 each</t>
+        </is>
+      </c>
+      <c r="J436" t="inlineStr">
+        <is>
+          <t>Draper annual; Russ biennial</t>
+        </is>
+      </c>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>By nomination; open internationally</t>
+        </is>
+      </c>
+      <c r="L436" t="inlineStr">
+        <is>
+          <t>Annual/biennial nomination (check site)</t>
+        </is>
+      </c>
+      <c r="M436" t="inlineStr">
+        <is>
+          <t>Nomination only</t>
+        </is>
+      </c>
+      <c r="N436" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O436" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P436" t="inlineStr">
+        <is>
+          <t>https://www.nae.edu/Projects/Awards.aspx</t>
+        </is>
+      </c>
+      <c r="Q436" t="inlineStr">
+        <is>
+          <t>The Draper Prize is often called the 'Nobel of engineering'.</t>
+        </is>
+      </c>
+      <c r="R436" t="inlineStr"/>
+      <c r="S436" t="inlineStr"/>
+      <c r="T436" t="inlineStr"/>
+      <c r="U436" t="inlineStr">
+        <is>
+          <t>award</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>A73</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>Japan Prize &amp; Kyoto Prize</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>Japan Prize Foundation / Inamori Foundation</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>Japan / International</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>Science, technology &amp; the arts</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>Any / Established</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>Two of Asia's most prestigious international awards, recognising lifetime contributions to science, technology and civilisation.</t>
+        </is>
+      </c>
+      <c r="I437" t="inlineStr">
+        <is>
+          <t>Japan Prize ¥50M; Kyoto Prize ¥100M</t>
+        </is>
+      </c>
+      <c r="J437" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>By nomination; open internationally</t>
+        </is>
+      </c>
+      <c r="L437" t="inlineStr">
+        <is>
+          <t>Annual nomination (check site)</t>
+        </is>
+      </c>
+      <c r="M437" t="inlineStr">
+        <is>
+          <t>Nomination only</t>
+        </is>
+      </c>
+      <c r="N437" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O437" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P437" t="inlineStr">
+        <is>
+          <t>https://www.japanprize.jp/en/</t>
+        </is>
+      </c>
+      <c r="Q437" t="inlineStr">
+        <is>
+          <t>The Kyoto Prize also honours arts and philosophy alongside science.</t>
+        </is>
+      </c>
+      <c r="R437" t="inlineStr"/>
+      <c r="S437" t="inlineStr"/>
+      <c r="T437" t="inlineStr"/>
+      <c r="U437" t="inlineStr">
+        <is>
+          <t>award</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>A74</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>Tang Prize</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>Tang Prize Foundation</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>Tang Prize</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>International (Taiwan-based)</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>Sustainable development, biopharma, sinology, rule of law</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>Any / Established</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>A major international award recognising achievements in four fields relevant to 21st-century challenges.</t>
+        </is>
+      </c>
+      <c r="I438" t="inlineStr">
+        <is>
+          <t>NT$50,000,000 (~€1.4M) per category</t>
+        </is>
+      </c>
+      <c r="J438" t="inlineStr">
+        <is>
+          <t>Every 2 years</t>
+        </is>
+      </c>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>By nomination; open internationally</t>
+        </is>
+      </c>
+      <c r="L438" t="inlineStr">
+        <is>
+          <t>Biennial nomination (check site)</t>
+        </is>
+      </c>
+      <c r="M438" t="inlineStr">
+        <is>
+          <t>Nomination only</t>
+        </is>
+      </c>
+      <c r="N438" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O438" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P438" t="inlineStr">
+        <is>
+          <t>https://www.tang-prize.org/en/</t>
+        </is>
+      </c>
+      <c r="Q438" t="inlineStr">
+        <is>
+          <t>One of the most valuable prizes in its fields, based in Taiwan.</t>
+        </is>
+      </c>
+      <c r="R438" t="inlineStr"/>
+      <c r="S438" t="inlineStr"/>
+      <c r="T438" t="inlineStr"/>
+      <c r="U438" t="inlineStr">
+        <is>
+          <t>award</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>A75</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>VinFuture Prize</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>VinFuture Foundation</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>VinFuture</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>International (Vietnam-based)</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>Science &amp; technology for humanity</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>Any / Established</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>A global prize recognising transformative science and technology with impact for millions of people, with dedicated categories for innovators from developing countries and women.</t>
+        </is>
+      </c>
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>$3,000,000 grand prize + $500k special prizes</t>
+        </is>
+      </c>
+      <c r="J439" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>By nomination; strong focus on global-impact and underrepresented innovators</t>
+        </is>
+      </c>
+      <c r="L439" t="inlineStr">
+        <is>
+          <t>Annual nomination (check site)</t>
+        </is>
+      </c>
+      <c r="M439" t="inlineStr">
+        <is>
+          <t>Nomination only</t>
+        </is>
+      </c>
+      <c r="N439" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O439" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P439" t="inlineStr">
+        <is>
+          <t>https://vinfutureprize.org/</t>
+        </is>
+      </c>
+      <c r="Q439" t="inlineStr">
+        <is>
+          <t>One of the largest global science prizes, with an explicit developing-world focus.</t>
+        </is>
+      </c>
+      <c r="R439" t="inlineStr"/>
+      <c r="S439" t="inlineStr"/>
+      <c r="T439" t="inlineStr"/>
+      <c r="U439" t="inlineStr">
+        <is>
+          <t>award</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>A76</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>ASEAN &amp; national young-scientist awards (TWAS Prizes)</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>The World Academy of Sciences (TWAS)</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>TWAS</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>International (developing countries)</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>All sciences</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>Early-career → established</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>TWAS awards prizes and young-affiliate positions specifically recognising scientists in and from the developing world.</t>
+        </is>
+      </c>
+      <c r="I440" t="inlineStr">
+        <is>
+          <t>Up to $15,000 + recognition</t>
+        </is>
+      </c>
+      <c r="J440" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>Researchers in developing countries; by nomination</t>
+        </is>
+      </c>
+      <c r="L440" t="inlineStr">
+        <is>
+          <t>Annual nomination (check site)</t>
+        </is>
+      </c>
+      <c r="M440" t="inlineStr">
+        <is>
+          <t>Nomination only</t>
+        </is>
+      </c>
+      <c r="N440" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O440" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P440" t="inlineStr">
+        <is>
+          <t>https://twas.org/opportunities/prizes-awards</t>
+        </is>
+      </c>
+      <c r="Q440" t="inlineStr">
+        <is>
+          <t>The leading recognition route for scientists in the Global South.</t>
+        </is>
+      </c>
+      <c r="R440" t="inlineStr"/>
+      <c r="S440" t="inlineStr"/>
+      <c r="T440" t="inlineStr"/>
+      <c r="U440" t="inlineStr">
+        <is>
+          <t>award</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>A77</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>Australian Prime Minister's Prizes for Science</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>Australian Government</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>All sciences</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>Early-career → lifetime</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>Australia's most prestigious science awards, spanning lifetime achievement, physical and life sciences, and early-career researchers.</t>
+        </is>
+      </c>
+      <c r="I441" t="inlineStr">
+        <is>
+          <t>Up to AUD 250,000 (top prize)</t>
+        </is>
+      </c>
+      <c r="J441" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>Researchers in Australia; by nomination</t>
+        </is>
+      </c>
+      <c r="L441" t="inlineStr">
+        <is>
+          <t>Annual nomination (check site)</t>
+        </is>
+      </c>
+      <c r="M441" t="inlineStr">
+        <is>
+          <t>Nomination only</t>
+        </is>
+      </c>
+      <c r="N441" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O441" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P441" t="inlineStr">
+        <is>
+          <t>https://www.industry.gov.au/science-technology-and-innovation/science-prizes</t>
+        </is>
+      </c>
+      <c r="Q441" t="inlineStr">
+        <is>
+          <t>Includes dedicated Frank Fenner and Malcolm McIntosh early-career prizes.</t>
+        </is>
+      </c>
+      <c r="R441" t="inlineStr"/>
+      <c r="S441" t="inlineStr"/>
+      <c r="T441" t="inlineStr"/>
+      <c r="U441" t="inlineStr">
+        <is>
+          <t>award</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>A78</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>Prime Minister's Science Prizes (New Zealand)</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>New Zealand Government</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>All sciences</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>Early-career → lifetime</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>New Zealand's flagship science prizes, including a MacDiarmid Emerging Scientist Prize and a Future Scientist prize for students.</t>
+        </is>
+      </c>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>Up to NZD 500,000 (top prize)</t>
+        </is>
+      </c>
+      <c r="J442" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>Researchers and students in New Zealand; by nomination</t>
+        </is>
+      </c>
+      <c r="L442" t="inlineStr">
+        <is>
+          <t>Annual nomination (check site)</t>
+        </is>
+      </c>
+      <c r="M442" t="inlineStr">
+        <is>
+          <t>Nomination only</t>
+        </is>
+      </c>
+      <c r="N442" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O442" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P442" t="inlineStr">
+        <is>
+          <t>https://www.pmscienceprizes.org.nz/</t>
+        </is>
+      </c>
+      <c r="Q442" t="inlineStr">
+        <is>
+          <t>The MacDiarmid prize specifically recognises outstanding early-career scientists.</t>
+        </is>
+      </c>
+      <c r="R442" t="inlineStr"/>
+      <c r="S442" t="inlineStr"/>
+      <c r="T442" t="inlineStr"/>
+      <c r="U442" t="inlineStr">
+        <is>
+          <t>award</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>A79</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>Canada Gairdner Momentum &amp; national early-career awards</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>Gairdner Foundation / Canadian societies</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>Biomedical &amp; health sciences</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>Early-career</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>The Gairdner Momentum Awards specifically recognise mid-career biomedical scientists in Canada poised for major impact.</t>
+        </is>
+      </c>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>CAD 100,000</t>
+        </is>
+      </c>
+      <c r="J443" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>Canada-based biomedical researchers ~5-10 yrs post first appointment; by nomination</t>
+        </is>
+      </c>
+      <c r="L443" t="inlineStr">
+        <is>
+          <t>Annual nomination (check site)</t>
+        </is>
+      </c>
+      <c r="M443" t="inlineStr">
+        <is>
+          <t>Nomination only</t>
+        </is>
+      </c>
+      <c r="N443" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O443" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P443" t="inlineStr">
+        <is>
+          <t>https://gairdner.org/</t>
+        </is>
+      </c>
+      <c r="Q443" t="inlineStr">
+        <is>
+          <t>A newer complement to the main Gairdner International Awards.</t>
+        </is>
+      </c>
+      <c r="R443" t="inlineStr"/>
+      <c r="S443" t="inlineStr"/>
+      <c r="T443" t="inlineStr"/>
+      <c r="U443" t="inlineStr">
+        <is>
+          <t>award</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>A80</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>Falling Walls Female Science Talents &amp; national heats</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>Falling Walls Foundation</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>Falling Walls</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>All sciences &amp; innovation</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>Early-career</t>
+        </is>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>Beyond the Lab pitch contest, Falling Walls runs Female Science Talents and Science Breakthrough categories with international reach.</t>
+        </is>
+      </c>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>Programme participation + recognition</t>
+        </is>
+      </c>
+      <c r="J444" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>Early-career researchers and innovators worldwide</t>
+        </is>
+      </c>
+      <c r="L444" t="inlineStr">
+        <is>
+          <t>Annual (check site)</t>
+        </is>
+      </c>
+      <c r="M444" t="inlineStr">
+        <is>
+          <t>Application / nomination</t>
+        </is>
+      </c>
+      <c r="N444" t="inlineStr">
+        <is>
+          <t>Yes — for some</t>
+        </is>
+      </c>
+      <c r="O444" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="P444" t="inlineStr">
+        <is>
+          <t>https://falling-walls.com/</t>
+        </is>
+      </c>
+      <c r="Q444" t="inlineStr">
+        <is>
+          <t>A structured intensive for outstanding early-career women in science.</t>
+        </is>
+      </c>
+      <c r="R444" t="inlineStr"/>
+      <c r="S444" t="inlineStr"/>
+      <c r="T444" t="inlineStr"/>
+      <c r="U444" t="inlineStr">
         <is>
           <t>award</t>
         </is>
